--- a/dg_list.xlsx
+++ b/dg_list.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DG_System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{82D496DE-EDB5-498D-94BC-FE6CD2F97FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263E37EF-211C-4FFC-9ABC-7A0C873983CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8505" yWindow="780" windowWidth="20550" windowHeight="11835" xr2:uid="{F1D97EF0-83B0-40F3-98B7-80945C13C10D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="27630" windowHeight="16440" xr2:uid="{F1D97EF0-83B0-40F3-98B7-80945C13C10D}"/>
   </bookViews>
   <sheets>
     <sheet name="IAL" sheetId="1" r:id="rId1"/>
+    <sheet name="EMC" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="68">
   <si>
     <t>UN號碼</t>
   </si>
@@ -153,6 +154,96 @@
   </si>
   <si>
     <t>這些雜項危險品禁收 。</t>
+  </si>
+  <si>
+    <t>Partner</t>
+  </si>
+  <si>
+    <t>UN</t>
+  </si>
+  <si>
+    <t>Is_Absolute_Prohibited</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>EMC</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>爆炸品全類別絕對禁收</t>
+  </si>
+  <si>
+    <t>1011, 1035, 1075, 1954, 1961, 1964, 1965, 1966, 1969, 1971, 1972, 1978, 2034, 2200, 2203, 2601, 3161, 3167, 3553</t>
+  </si>
+  <si>
+    <t>易燃氣體特定 UN 號碼禁收</t>
+  </si>
+  <si>
+    <t>非易燃非毒性氣體特定 UN 號碼禁收</t>
+  </si>
+  <si>
+    <t>毒性氣體全類別絕對禁收</t>
+  </si>
+  <si>
+    <t>1088, 1089, 1090, 1093, 1099, 1100, 1108, 1113, 1127, 1131, 1144, 1146, 1154, 1155, 1159, 1160, 1164, 1167, 1190, 1194, 1203, 1208, 1218, 1221, 1234, 1243, 1265, 1275, 1277, 1280, 1298, 1302, 1303, 1921, 1991, 2045, 2246, 2251, 2256, 2270, 2287, 2288, 2301, 2336, 2347, 2350, 2356, 2363, 2370, 2371, 2373, 2377, 2384, 2389, 2398, 2482, 2456, 2457, 2458, 2459, 2460, 2461, 2561, 2612, 2615, 2749, 2983, 3165, 3274, 3343, 3357, 3379</t>
+  </si>
+  <si>
+    <t>注意：未列出但閃點&lt;-18℃或沸點&lt;=35℃之Class 3亦禁收(UN3528除外)</t>
+  </si>
+  <si>
+    <t>1347, 2956, 3097, 3221, 3222, 3223, 3224, 3225, 3226, 3227, 3228, 3229, 3230, 3231, 3232, 3233, 3234, 3235, 3236, 3237, 3238, 3239, 3240, 3344, 3345, 3251, 3319, 3380, 3533, 3534</t>
+  </si>
+  <si>
+    <t>易燃固體特定 UN 號碼禁收</t>
+  </si>
+  <si>
+    <t>1361, 1362, 1363, 1364, 1376, 1380, 1381, 1387, 1857, 2447, 2545, 2846, 2870, 3126, 3127, 3128, 3194, 3200, 3255, 3341, 3342, 3391, 3392, 3393, 3394</t>
+  </si>
+  <si>
+    <t>自燃性物質特定 UN 號碼禁收</t>
+  </si>
+  <si>
+    <t>1241, 1295, 1391, 1408, 1411, 1415, 1418, 1928, 2813, 2988, 3129, 3130, 3131, 3132, 3133, 3134, 3135, 3148, 3170, 3208, 3395, 3396, 3397, 3482</t>
+  </si>
+  <si>
+    <t>注意：具Class 3副危且閃點&lt;-18℃或沸點&lt;=35℃之Class 4.3亦禁收</t>
+  </si>
+  <si>
+    <t>1450, 1458, 1459, 1461, 1462, 1471, 1477, 1479, 1481, 1482, 1483, 1501, 1512, 1746, 1748, 1873, 1941, 2015, 2067, 2208, 2426, 2465, 2468, 2626, 2627, 2741, 2880, 3085, 3087, 3098, 3099, 3100, 3121, 3137, 3139, 3210, 3211, 3212, 3213, 3214, 3218, 3219, 3375, 3485, 3486, 3487</t>
+  </si>
+  <si>
+    <t>漂白粉/次氯酸鈣類(見附錄1)限長榮船租長榮櫃，需文件審查</t>
+  </si>
+  <si>
+    <t>有機過氧化物全類別絕對禁收</t>
+  </si>
+  <si>
+    <t>1051, 1092, 1098, 1259, 1510, 1613, 1642, 1700, 2023, 2186, 2334, 2480, 2481, 3294, 3383, 3489, 3490, 3491, 3507, 3558</t>
+  </si>
+  <si>
+    <t>注意：具Class 3副危且閃點&lt;-18℃或沸點&lt;=35℃之Class 6.1亦禁收</t>
+  </si>
+  <si>
+    <t>感染性物質全類別絕對禁收</t>
+  </si>
+  <si>
+    <t>放射性物質全類別絕對禁收</t>
+  </si>
+  <si>
+    <t>1791, 1818, 1826, 1832, 1906</t>
+  </si>
+  <si>
+    <t>注意：具Class 3副危且閃點&lt;-18℃或沸點&lt;=35℃之Class 8亦禁收</t>
+  </si>
+  <si>
+    <t>2211, 2212, 2315, 2590, 3151, 3152, 3245, 3257, 3258, 3314, 3432, 3509, 3536</t>
+  </si>
+  <si>
+    <t>需文件審查；需控溫之物質禁收</t>
   </si>
 </sst>
 </file>
@@ -226,7 +317,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -235,6 +326,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -899,4 +996,287 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E1EC5FE-200C-42A0-BD8E-F678946A520D}">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="285.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="4">
+        <v>2.1</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C4" s="4">
+        <v>2455</v>
+      </c>
+      <c r="D4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="4">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="4">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="375.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="360.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="4">
+        <v>5.2</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="300.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="4">
+        <v>6.1</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="4">
+        <v>6.2</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="4">
+        <v>7</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="4">
+        <v>8</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="195.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="4">
+        <v>9</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/dg_list.xlsx
+++ b/dg_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DG_System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263E37EF-211C-4FFC-9ABC-7A0C873983CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB769D33-EFA4-4393-A379-CD54525D9340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="27630" windowHeight="16440" xr2:uid="{F1D97EF0-83B0-40F3-98B7-80945C13C10D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="27630" windowHeight="16440" activeTab="1" xr2:uid="{F1D97EF0-83B0-40F3-98B7-80945C13C10D}"/>
   </bookViews>
   <sheets>
     <sheet name="IAL" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="64">
   <si>
     <t>UN號碼</t>
   </si>
@@ -156,94 +156,82 @@
     <t>這些雜項危險品禁收 。</t>
   </si>
   <si>
-    <t>Partner</t>
-  </si>
-  <si>
-    <t>UN</t>
-  </si>
-  <si>
-    <t>Is_Absolute_Prohibited</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>EMC</t>
-  </si>
-  <si>
     <t>ALL</t>
   </si>
   <si>
-    <t>爆炸品全類別絕對禁收</t>
-  </si>
-  <si>
     <t>1011, 1035, 1075, 1954, 1961, 1964, 1965, 1966, 1969, 1971, 1972, 1978, 2034, 2200, 2203, 2601, 3161, 3167, 3553</t>
   </si>
   <si>
-    <t>易燃氣體特定 UN 號碼禁收</t>
-  </si>
-  <si>
-    <t>非易燃非毒性氣體特定 UN 號碼禁收</t>
-  </si>
-  <si>
-    <t>毒性氣體全類別絕對禁收</t>
-  </si>
-  <si>
     <t>1088, 1089, 1090, 1093, 1099, 1100, 1108, 1113, 1127, 1131, 1144, 1146, 1154, 1155, 1159, 1160, 1164, 1167, 1190, 1194, 1203, 1208, 1218, 1221, 1234, 1243, 1265, 1275, 1277, 1280, 1298, 1302, 1303, 1921, 1991, 2045, 2246, 2251, 2256, 2270, 2287, 2288, 2301, 2336, 2347, 2350, 2356, 2363, 2370, 2371, 2373, 2377, 2384, 2389, 2398, 2482, 2456, 2457, 2458, 2459, 2460, 2461, 2561, 2612, 2615, 2749, 2983, 3165, 3274, 3343, 3357, 3379</t>
   </si>
   <si>
-    <t>注意：未列出但閃點&lt;-18℃或沸點&lt;=35℃之Class 3亦禁收(UN3528除外)</t>
-  </si>
-  <si>
-    <t>1347, 2956, 3097, 3221, 3222, 3223, 3224, 3225, 3226, 3227, 3228, 3229, 3230, 3231, 3232, 3233, 3234, 3235, 3236, 3237, 3238, 3239, 3240, 3344, 3345, 3251, 3319, 3380, 3533, 3534</t>
-  </si>
-  <si>
-    <t>易燃固體特定 UN 號碼禁收</t>
-  </si>
-  <si>
     <t>1361, 1362, 1363, 1364, 1376, 1380, 1381, 1387, 1857, 2447, 2545, 2846, 2870, 3126, 3127, 3128, 3194, 3200, 3255, 3341, 3342, 3391, 3392, 3393, 3394</t>
   </si>
   <si>
-    <t>自燃性物質特定 UN 號碼禁收</t>
-  </si>
-  <si>
     <t>1241, 1295, 1391, 1408, 1411, 1415, 1418, 1928, 2813, 2988, 3129, 3130, 3131, 3132, 3133, 3134, 3135, 3148, 3170, 3208, 3395, 3396, 3397, 3482</t>
   </si>
   <si>
-    <t>注意：具Class 3副危且閃點&lt;-18℃或沸點&lt;=35℃之Class 4.3亦禁收</t>
-  </si>
-  <si>
     <t>1450, 1458, 1459, 1461, 1462, 1471, 1477, 1479, 1481, 1482, 1483, 1501, 1512, 1746, 1748, 1873, 1941, 2015, 2067, 2208, 2426, 2465, 2468, 2626, 2627, 2741, 2880, 3085, 3087, 3098, 3099, 3100, 3121, 3137, 3139, 3210, 3211, 3212, 3213, 3214, 3218, 3219, 3375, 3485, 3486, 3487</t>
   </si>
   <si>
-    <t>漂白粉/次氯酸鈣類(見附錄1)限長榮船租長榮櫃，需文件審查</t>
-  </si>
-  <si>
-    <t>有機過氧化物全類別絕對禁收</t>
-  </si>
-  <si>
-    <t>1051, 1092, 1098, 1259, 1510, 1613, 1642, 1700, 2023, 2186, 2334, 2480, 2481, 3294, 3383, 3489, 3490, 3491, 3507, 3558</t>
-  </si>
-  <si>
-    <t>注意：具Class 3副危且閃點&lt;-18℃或沸點&lt;=35℃之Class 6.1亦禁收</t>
-  </si>
-  <si>
-    <t>感染性物質全類別絕對禁收</t>
-  </si>
-  <si>
-    <t>放射性物質全類別絕對禁收</t>
-  </si>
-  <si>
     <t>1791, 1818, 1826, 1832, 1906</t>
   </si>
   <si>
-    <t>注意：具Class 3副危且閃點&lt;-18℃或沸點&lt;=35℃之Class 8亦禁收</t>
-  </si>
-  <si>
     <t>2211, 2212, 2315, 2590, 3151, 3152, 3245, 3257, 3258, 3314, 3432, 3509, 3536</t>
   </si>
   <si>
-    <t>需文件審查；需控溫之物質禁收</t>
+    <t xml:space="preserve">爆炸品全類別絕對禁收 </t>
+  </si>
+  <si>
+    <t>🔴 特定UN禁收</t>
+  </si>
+  <si>
+    <t xml:space="preserve">易燃氣體特定 UN 號碼禁收 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">非易燃非毒性氣體特定 UN 號碼禁收 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">毒性氣體全類別絕對禁收 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">注意：未列出但閃點&lt;-18℃或沸點&lt;=35℃之Class 3亦禁收(UN3528除外) </t>
+  </si>
+  <si>
+    <t>1347, 2956, 3097, 3221, 3222, 3223, 3224, 3225, 3226, 3227, 3228, 3229, 3230, 3231, 3234, 3235, 3236, 3237, 3238, 3239, 3240, 3344, 3345, 3251, 3319, 3380, 3533, 3534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">易燃固體特定 UN 號碼禁收 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">自燃性物質特定 UN 號碼禁收 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">注意：具Class 3副危且閃點&lt;-18℃或沸點&lt;=35℃之Class 4.3亦禁收 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">漂白粉/次氯酸鈣類限長榮船櫃，需文件審查 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">有機過氧化物全類別絕對禁收 </t>
+  </si>
+  <si>
+    <t>1051, 1092, 1098, 1259, 1510, 1613, 1642, 1700, 2023, 2334, 2480, 2481, 3294, 3383, 3489, 3490, 3491, 3507, 3558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">注意：具Class 3副危且閃點&lt;-18℃或沸點&lt;=35℃之Class 6.1亦禁收 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">感染性物質全類別絕對禁收 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">放射性物質全類別絕對禁收 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">注意：具Class 3副危且閃點&lt;-18℃或沸點&lt;=35℃之Class 8亦禁收 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">審查文件；控溫物質禁收 </t>
   </si>
 </sst>
 </file>
@@ -1000,146 +988,122 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E1EC5FE-200C-42A0-BD8E-F678946A520D}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B2" s="4">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="285.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="300" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4">
         <v>2.1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>2455</v>
       </c>
       <c r="B4" s="4">
         <v>2.2000000000000002</v>
       </c>
-      <c r="C4" s="4">
-        <v>2455</v>
-      </c>
-      <c r="D4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B5" s="4">
         <v>2.2999999999999998</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B6" s="4">
         <v>3</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B7" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="375.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="394.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" s="4">
         <v>4.2</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="360.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="378.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>42</v>
       </c>
@@ -1147,132 +1111,108 @@
         <v>4.3</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B11" s="4">
         <v>5.2</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="300.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="300" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="B12" s="4">
         <v>6.1</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B13" s="4">
         <v>6.2</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B14" s="4">
         <v>7</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B15" s="4">
         <v>8</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="195.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="205.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B16" s="4">
         <v>9</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/dg_list.xlsx
+++ b/dg_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DG_System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB769D33-EFA4-4393-A379-CD54525D9340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B63FF3-130E-42D5-9556-ADB20D8CC83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="27630" windowHeight="16440" activeTab="1" xr2:uid="{F1D97EF0-83B0-40F3-98B7-80945C13C10D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="27630" windowHeight="16440" xr2:uid="{F1D97EF0-83B0-40F3-98B7-80945C13C10D}"/>
   </bookViews>
   <sheets>
     <sheet name="IAL" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="65">
   <si>
     <t>UN號碼</t>
   </si>
@@ -232,6 +232,10 @@
   </si>
   <si>
     <t xml:space="preserve">審查文件；控溫物質禁收 </t>
+  </si>
+  <si>
+    <t>ALL</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -674,7 +678,7 @@
     </row>
     <row r="2" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -688,7 +692,7 @@
     </row>
     <row r="3" spans="1:4" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="B3" s="2">
         <v>2.2999999999999998</v>
@@ -702,7 +706,7 @@
     </row>
     <row r="4" spans="1:4" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="B4" s="2">
         <v>4.3</v>
@@ -716,7 +720,7 @@
     </row>
     <row r="5" spans="1:4" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="B5" s="2">
         <v>5.2</v>
@@ -730,7 +734,7 @@
     </row>
     <row r="6" spans="1:4" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="B6" s="2">
         <v>6.2</v>
@@ -744,7 +748,7 @@
     </row>
     <row r="7" spans="1:4" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="B7" s="2">
         <v>7</v>

--- a/dg_list.xlsx
+++ b/dg_list.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIM\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C24AA1C-8111-4445-A9F6-D6AB9E732289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2EC6AF-6339-4F6E-98B0-C3A1C049B806}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="IAL" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,10 +25,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">

--- a/dg_list.xlsx
+++ b/dg_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ialasia.sharepoint.com/sites/IALDGDESK/Shared Documents/General/Query System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="175" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF251495-5ED2-4FAA-B7DB-DE7C1BC937DA}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{216E9655-074F-4887-B3C6-896D0E5744DA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="27630" windowHeight="16440" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="27630" windowHeight="16440" activeTab="3" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
   </bookViews>
   <sheets>
     <sheet name="IAL" sheetId="1" r:id="rId1"/>
@@ -1309,10 +1309,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13056,7 +13052,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -23439,17 +23435,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c3e85fef-df06-4e67-8632-489752715f52" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6fd297-1f65-4950-8fc9-157e29c7b648">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文件" ma:contentTypeID="0x0101000EE87651FA4E794C9F9EBAB47B2914A1" ma:contentTypeVersion="17" ma:contentTypeDescription="建立新的文件。" ma:contentTypeScope="" ma:versionID="9c09e6d34a2a63fd0a91c0d4c1bf4f8b">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ea6fd297-1f65-4950-8fc9-157e29c7b648" xmlns:ns3="c3e85fef-df06-4e67-8632-489752715f52" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="425bb3ba415c7c22851a56042b3a2c83" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000EE87651FA4E794C9F9EBAB47B2914A1" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e3b55ab03191701fac28f92542a127ea">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ea6fd297-1f65-4950-8fc9-157e29c7b648" xmlns:ns3="c3e85fef-df06-4e67-8632-489752715f52" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fefe44c3222484af0f545068bb015341" ns2:_="" ns3:_="">
     <xsd:import namespace="ea6fd297-1f65-4950-8fc9-157e29c7b648"/>
     <xsd:import namespace="c3e85fef-df06-4e67-8632-489752715f52"/>
     <xsd:element name="properties">
@@ -23548,7 +23546,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="影像標籤" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="7f7e4587-cf63-4ff3-92d6-48abe44d80a4" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="7f7e4587-cf63-4ff3-92d6-48abe44d80a4" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -23559,7 +23557,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c3e85fef-df06-4e67-8632-489752715f52" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="共用對象:" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -23578,7 +23576,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="共用詳細資料" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -23606,8 +23604,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="內容類型"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="標題"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -23697,26 +23695,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c3e85fef-df06-4e67-8632-489752715f52" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6fd297-1f65-4950-8fc9-157e29c7b648">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171B3C16-7124-4B98-87E3-5FC6A9D45406}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98411DB4-5541-4967-8DBE-AF3E324DD5F5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c3e85fef-df06-4e67-8632-489752715f52"/>
+    <ds:schemaRef ds:uri="ea6fd297-1f65-4950-8fc9-157e29c7b648"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D53AE126-6F09-4BBB-AD0C-4EFC39D23541}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F8715B0-3E5B-4FC2-BF2D-C75A193CD594}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -23735,12 +23734,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98411DB4-5541-4967-8DBE-AF3E324DD5F5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171B3C16-7124-4B98-87E3-5FC6A9D45406}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c3e85fef-df06-4e67-8632-489752715f52"/>
-    <ds:schemaRef ds:uri="ea6fd297-1f65-4950-8fc9-157e29c7b648"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/dg_list.xlsx
+++ b/dg_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ialasia.sharepoint.com/sites/IALDGDESK/Shared Documents/General/Query System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="232" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1091DACC-193E-44B8-B57E-C3BF0A20BB91}"/>
+  <xr:revisionPtr revIDLastSave="250" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8199D398-1B17-4CC0-A177-61361D755230}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="27630" windowHeight="16440" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
   </bookViews>
   <sheets>
     <sheet name="IAL" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3464" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3455" uniqueCount="263">
   <si>
     <t>UN Number</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1238,10 +1238,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1561,7 +1557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A3E2D92-EC0D-473D-A229-F530C42B6D6E}">
-  <dimension ref="A1:I231"/>
+  <dimension ref="A1:I222"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.625" style="1" customWidth="1"/>
@@ -1694,6 +1690,9 @@
       <c r="F9" s="1" t="s">
         <v>262</v>
       </c>
+      <c r="G9" s="1" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -1702,9 +1701,11 @@
       <c r="B10" s="1">
         <v>2.1</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="F10" s="1" t="s">
-        <v>261</v>
+      <c r="C10" s="4">
+        <v>1057</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1715,7 +1716,7 @@
         <v>2.1</v>
       </c>
       <c r="C11" s="4">
-        <v>1057</v>
+        <v>1961</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>4</v>
@@ -1729,7 +1730,7 @@
         <v>2.1</v>
       </c>
       <c r="C12" s="4">
-        <v>1961</v>
+        <v>1966</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>4</v>
@@ -1743,7 +1744,7 @@
         <v>2.1</v>
       </c>
       <c r="C13" s="4">
-        <v>1966</v>
+        <v>1972</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>4</v>
@@ -1754,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B14" s="1">
-        <v>2.1</v>
-      </c>
-      <c r="C14" s="4">
-        <v>1972</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>4</v>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1770,8 +1771,11 @@
       <c r="B15" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>262</v>
+      <c r="C15" s="4">
+        <v>2455</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1779,76 +1783,89 @@
         <v>3</v>
       </c>
       <c r="B16" s="1">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="F16" s="1" t="s">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="1">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="1">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="C17" s="4">
-        <v>2455</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B18" s="1">
-        <v>2.2999999999999998</v>
+        <v>3</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1088</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B19" s="1">
         <v>3</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C19" s="4">
+        <v>1089</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B20" s="1">
         <v>3</v>
       </c>
-      <c r="C20" s="1"/>
-      <c r="F20" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C20" s="4">
+        <v>1090</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B21" s="1">
         <v>3</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C21" s="4">
+        <v>1100</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
@@ -1856,13 +1873,13 @@
         <v>3</v>
       </c>
       <c r="C22" s="4">
-        <v>1088</v>
+        <v>1108</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>3</v>
       </c>
@@ -1870,13 +1887,13 @@
         <v>3</v>
       </c>
       <c r="C23" s="4">
-        <v>1089</v>
+        <v>1131</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>3</v>
       </c>
@@ -1884,13 +1901,13 @@
         <v>3</v>
       </c>
       <c r="C24" s="4">
-        <v>1090</v>
+        <v>1144</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>3</v>
       </c>
@@ -1898,13 +1915,13 @@
         <v>3</v>
       </c>
       <c r="C25" s="4">
-        <v>1100</v>
+        <v>1146</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>3</v>
       </c>
@@ -1912,13 +1929,13 @@
         <v>3</v>
       </c>
       <c r="C26" s="4">
-        <v>1108</v>
+        <v>1154</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>3</v>
       </c>
@@ -1926,13 +1943,13 @@
         <v>3</v>
       </c>
       <c r="C27" s="4">
-        <v>1131</v>
+        <v>1155</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>3</v>
       </c>
@@ -1940,13 +1957,13 @@
         <v>3</v>
       </c>
       <c r="C28" s="4">
-        <v>1144</v>
+        <v>1159</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>3</v>
       </c>
@@ -1954,13 +1971,13 @@
         <v>3</v>
       </c>
       <c r="C29" s="4">
-        <v>1146</v>
+        <v>1164</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>3</v>
       </c>
@@ -1968,13 +1985,13 @@
         <v>3</v>
       </c>
       <c r="C30" s="4">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>3</v>
       </c>
@@ -1982,13 +1999,13 @@
         <v>3</v>
       </c>
       <c r="C31" s="4">
-        <v>1155</v>
+        <v>1190</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>3</v>
       </c>
@@ -1996,7 +2013,7 @@
         <v>3</v>
       </c>
       <c r="C32" s="4">
-        <v>1159</v>
+        <v>1218</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>4</v>
@@ -2010,7 +2027,7 @@
         <v>3</v>
       </c>
       <c r="C33" s="4">
-        <v>1164</v>
+        <v>1221</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>4</v>
@@ -2024,7 +2041,7 @@
         <v>3</v>
       </c>
       <c r="C34" s="4">
-        <v>1167</v>
+        <v>1234</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>4</v>
@@ -2038,7 +2055,7 @@
         <v>3</v>
       </c>
       <c r="C35" s="4">
-        <v>1190</v>
+        <v>1243</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>4</v>
@@ -2052,7 +2069,7 @@
         <v>3</v>
       </c>
       <c r="C36" s="4">
-        <v>1218</v>
+        <v>1275</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>4</v>
@@ -2066,7 +2083,7 @@
         <v>3</v>
       </c>
       <c r="C37" s="4">
-        <v>1221</v>
+        <v>1277</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>4</v>
@@ -2080,7 +2097,7 @@
         <v>3</v>
       </c>
       <c r="C38" s="4">
-        <v>1234</v>
+        <v>1280</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>4</v>
@@ -2094,7 +2111,7 @@
         <v>3</v>
       </c>
       <c r="C39" s="4">
-        <v>1243</v>
+        <v>1298</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>4</v>
@@ -2108,7 +2125,7 @@
         <v>3</v>
       </c>
       <c r="C40" s="4">
-        <v>1275</v>
+        <v>1302</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>4</v>
@@ -2122,7 +2139,7 @@
         <v>3</v>
       </c>
       <c r="C41" s="4">
-        <v>1277</v>
+        <v>1303</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>4</v>
@@ -2136,7 +2153,7 @@
         <v>3</v>
       </c>
       <c r="C42" s="4">
-        <v>1280</v>
+        <v>1891</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>4</v>
@@ -2150,7 +2167,7 @@
         <v>3</v>
       </c>
       <c r="C43" s="4">
-        <v>1298</v>
+        <v>1991</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>4</v>
@@ -2164,7 +2181,7 @@
         <v>3</v>
       </c>
       <c r="C44" s="4">
-        <v>1302</v>
+        <v>1999</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>4</v>
@@ -2178,7 +2195,7 @@
         <v>3</v>
       </c>
       <c r="C45" s="4">
-        <v>1303</v>
+        <v>2045</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>4</v>
@@ -2192,7 +2209,7 @@
         <v>3</v>
       </c>
       <c r="C46" s="4">
-        <v>1891</v>
+        <v>2056</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>4</v>
@@ -2206,7 +2223,7 @@
         <v>3</v>
       </c>
       <c r="C47" s="4">
-        <v>1991</v>
+        <v>2246</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>4</v>
@@ -2220,7 +2237,7 @@
         <v>3</v>
       </c>
       <c r="C48" s="4">
-        <v>1999</v>
+        <v>2251</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>4</v>
@@ -2234,7 +2251,7 @@
         <v>3</v>
       </c>
       <c r="C49" s="4">
-        <v>2045</v>
+        <v>2301</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>4</v>
@@ -2248,7 +2265,7 @@
         <v>3</v>
       </c>
       <c r="C50" s="4">
-        <v>2056</v>
+        <v>2356</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>4</v>
@@ -2262,7 +2279,7 @@
         <v>3</v>
       </c>
       <c r="C51" s="4">
-        <v>2246</v>
+        <v>2363</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>4</v>
@@ -2276,7 +2293,7 @@
         <v>3</v>
       </c>
       <c r="C52" s="4">
-        <v>2251</v>
+        <v>2371</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>4</v>
@@ -2290,7 +2307,7 @@
         <v>3</v>
       </c>
       <c r="C53" s="4">
-        <v>2301</v>
+        <v>2384</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>4</v>
@@ -2304,7 +2321,7 @@
         <v>3</v>
       </c>
       <c r="C54" s="4">
-        <v>2356</v>
+        <v>2389</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>4</v>
@@ -2318,7 +2335,7 @@
         <v>3</v>
       </c>
       <c r="C55" s="4">
-        <v>2363</v>
+        <v>2398</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>4</v>
@@ -2332,7 +2349,7 @@
         <v>3</v>
       </c>
       <c r="C56" s="4">
-        <v>2371</v>
+        <v>2402</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>4</v>
@@ -2346,7 +2363,7 @@
         <v>3</v>
       </c>
       <c r="C57" s="4">
-        <v>2384</v>
+        <v>2456</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>4</v>
@@ -2360,7 +2377,7 @@
         <v>3</v>
       </c>
       <c r="C58" s="4">
-        <v>2389</v>
+        <v>2457</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>4</v>
@@ -2374,7 +2391,7 @@
         <v>3</v>
       </c>
       <c r="C59" s="4">
-        <v>2398</v>
+        <v>2459</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>4</v>
@@ -2388,7 +2405,7 @@
         <v>3</v>
       </c>
       <c r="C60" s="4">
-        <v>2402</v>
+        <v>2460</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>4</v>
@@ -2402,7 +2419,7 @@
         <v>3</v>
       </c>
       <c r="C61" s="4">
-        <v>2456</v>
+        <v>2461</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>4</v>
@@ -2416,7 +2433,7 @@
         <v>3</v>
       </c>
       <c r="C62" s="4">
-        <v>2457</v>
+        <v>2561</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>4</v>
@@ -2430,7 +2447,7 @@
         <v>3</v>
       </c>
       <c r="C63" s="4">
-        <v>2459</v>
+        <v>2612</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>4</v>
@@ -2444,13 +2461,13 @@
         <v>3</v>
       </c>
       <c r="C64" s="4">
-        <v>2460</v>
+        <v>2615</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>3</v>
       </c>
@@ -2458,13 +2475,13 @@
         <v>3</v>
       </c>
       <c r="C65" s="4">
-        <v>2461</v>
+        <v>2749</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>3</v>
       </c>
@@ -2472,92 +2489,100 @@
         <v>3</v>
       </c>
       <c r="C66" s="4">
-        <v>2561</v>
+        <v>2983</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B67" s="1">
-        <v>3</v>
-      </c>
-      <c r="C67" s="4">
-        <v>2612</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B68" s="1">
-        <v>3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C68" s="4">
-        <v>2615</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1334</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B69" s="1">
-        <v>3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C69" s="4">
-        <v>2749</v>
+        <v>1309</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B70" s="1">
-        <v>3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C70" s="4">
-        <v>2983</v>
+        <v>1323</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B71" s="1">
         <v>4.0999999999999996</v>
       </c>
-      <c r="F71" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C71" s="4">
+        <v>1333</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B72" s="1">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C72" s="1"/>
-      <c r="F72" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C72" s="4">
+        <v>1339</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>3</v>
       </c>
@@ -2565,16 +2590,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C73" s="4">
-        <v>1334</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1343</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>3</v>
       </c>
@@ -2582,13 +2604,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C74" s="4">
-        <v>1309</v>
+        <v>1358</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>3</v>
       </c>
@@ -2596,13 +2618,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C75" s="4">
-        <v>1323</v>
+        <v>1869</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>3</v>
       </c>
@@ -2610,13 +2632,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C76" s="4">
-        <v>1333</v>
+        <v>2858</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>3</v>
       </c>
@@ -2624,13 +2646,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C77" s="4">
-        <v>1339</v>
+        <v>2878</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>3</v>
       </c>
@@ -2638,13 +2660,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C78" s="4">
-        <v>1343</v>
+        <v>3089</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>3</v>
       </c>
@@ -2652,13 +2674,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C79" s="4">
-        <v>1358</v>
+        <v>3221</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>3</v>
       </c>
@@ -2666,7 +2688,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C80" s="4">
-        <v>1869</v>
+        <v>3222</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>4</v>
@@ -2680,7 +2702,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C81" s="4">
-        <v>2858</v>
+        <v>3223</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>4</v>
@@ -2694,7 +2716,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C82" s="4">
-        <v>2878</v>
+        <v>3224</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>4</v>
@@ -2708,7 +2730,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C83" s="4">
-        <v>3089</v>
+        <v>3225</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>4</v>
@@ -2722,7 +2744,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C84" s="4">
-        <v>3221</v>
+        <v>3226</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>4</v>
@@ -2736,7 +2758,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C85" s="4">
-        <v>3222</v>
+        <v>3227</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>4</v>
@@ -2750,7 +2772,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C86" s="4">
-        <v>3223</v>
+        <v>3228</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>4</v>
@@ -2764,7 +2786,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C87" s="4">
-        <v>3224</v>
+        <v>3229</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>4</v>
@@ -2778,7 +2800,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C88" s="4">
-        <v>3225</v>
+        <v>3230</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>4</v>
@@ -2792,7 +2814,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C89" s="4">
-        <v>3226</v>
+        <v>3231</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>4</v>
@@ -2806,7 +2828,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C90" s="4">
-        <v>3227</v>
+        <v>3232</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>4</v>
@@ -2820,7 +2842,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C91" s="4">
-        <v>3228</v>
+        <v>3233</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>4</v>
@@ -2834,7 +2856,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C92" s="4">
-        <v>3229</v>
+        <v>3234</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>4</v>
@@ -2848,7 +2870,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C93" s="4">
-        <v>3230</v>
+        <v>3235</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>4</v>
@@ -2862,7 +2884,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C94" s="4">
-        <v>3231</v>
+        <v>3236</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>4</v>
@@ -2876,7 +2898,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C95" s="4">
-        <v>3232</v>
+        <v>3237</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>4</v>
@@ -2890,13 +2912,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C96" s="4">
-        <v>3233</v>
+        <v>3238</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>3</v>
       </c>
@@ -2904,13 +2926,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C97" s="4">
-        <v>3234</v>
+        <v>3239</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>3</v>
       </c>
@@ -2918,13 +2940,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C98" s="4">
-        <v>3235</v>
+        <v>3240</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>3</v>
       </c>
@@ -2932,140 +2954,145 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C99" s="4">
-        <v>3236</v>
+        <v>3241</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B100" s="1">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C100" s="4">
-        <v>3237</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4.2</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B101" s="1">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C101" s="4">
-        <v>3238</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1361</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B102" s="1">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C102" s="4">
-        <v>3239</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1362</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B103" s="1">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C103" s="4">
-        <v>3240</v>
+        <v>4.2</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B104" s="1">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C104" s="4">
-        <v>3241</v>
+        <v>4.2</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B105" s="1">
         <v>4.2</v>
       </c>
-      <c r="F105" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C105" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B106" s="1">
         <v>4.2</v>
       </c>
-      <c r="C106" s="1"/>
-      <c r="F106" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C106" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B107" s="1">
         <v>4.2</v>
       </c>
-      <c r="C107" s="4">
-        <v>1361</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C107" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B108" s="1">
         <v>4.2</v>
       </c>
-      <c r="C108" s="4">
-        <v>1362</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C108" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>3</v>
       </c>
@@ -3073,13 +3100,13 @@
         <v>4.2</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>3</v>
       </c>
@@ -3087,13 +3114,13 @@
         <v>4.2</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>3</v>
       </c>
@@ -3101,13 +3128,13 @@
         <v>4.2</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>3</v>
       </c>
@@ -3115,7 +3142,7 @@
         <v>4.2</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>4</v>
@@ -3129,7 +3156,7 @@
         <v>4.2</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>4</v>
@@ -3143,7 +3170,7 @@
         <v>4.2</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>4</v>
@@ -3157,7 +3184,7 @@
         <v>4.2</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>4</v>
@@ -3171,7 +3198,7 @@
         <v>4.2</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>4</v>
@@ -3185,7 +3212,7 @@
         <v>4.2</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>4</v>
@@ -3199,7 +3226,7 @@
         <v>4.2</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>4</v>
@@ -3213,7 +3240,7 @@
         <v>4.2</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>4</v>
@@ -3227,7 +3254,7 @@
         <v>4.2</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>4</v>
@@ -3241,7 +3268,7 @@
         <v>4.2</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>4</v>
@@ -3255,7 +3282,7 @@
         <v>4.2</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>4</v>
@@ -3269,7 +3296,7 @@
         <v>4.2</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>4</v>
@@ -3283,7 +3310,7 @@
         <v>4.2</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>4</v>
@@ -3297,7 +3324,7 @@
         <v>4.2</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>4</v>
@@ -3311,7 +3338,7 @@
         <v>4.2</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>4</v>
@@ -3325,7 +3352,7 @@
         <v>4.2</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>4</v>
@@ -3339,13 +3366,13 @@
         <v>4.2</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>3</v>
       </c>
@@ -3353,13 +3380,13 @@
         <v>4.2</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>3</v>
       </c>
@@ -3367,13 +3394,13 @@
         <v>4.2</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>3</v>
       </c>
@@ -3381,13 +3408,13 @@
         <v>4.2</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>3</v>
       </c>
@@ -3395,13 +3422,13 @@
         <v>4.2</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>3</v>
       </c>
@@ -3409,131 +3436,136 @@
         <v>4.2</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B134" s="1">
-        <v>4.2</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>31</v>
+        <v>4.3</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B135" s="1">
-        <v>4.2</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B136" s="1">
-        <v>4.2</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B137" s="1">
-        <v>4.2</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B138" s="1">
-        <v>4.2</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B139" s="1">
-        <v>4.2</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B140" s="1">
-        <v>4.3</v>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B141" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F141" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C141" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B142" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C142" s="1"/>
-      <c r="F142" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C142" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>3</v>
       </c>
@@ -3541,13 +3573,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>3</v>
       </c>
@@ -3555,13 +3587,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>3</v>
       </c>
@@ -3569,13 +3601,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>3</v>
       </c>
@@ -3583,13 +3615,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>3</v>
       </c>
@@ -3597,13 +3629,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>3</v>
       </c>
@@ -3611,13 +3643,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>3</v>
       </c>
@@ -3625,13 +3657,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>3</v>
       </c>
@@ -3639,13 +3671,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>3</v>
       </c>
@@ -3653,13 +3685,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>3</v>
       </c>
@@ -3667,13 +3699,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>3</v>
       </c>
@@ -3681,13 +3713,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>3</v>
       </c>
@@ -3695,13 +3727,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>3</v>
       </c>
@@ -3709,13 +3741,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>3</v>
       </c>
@@ -3723,13 +3755,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>3</v>
       </c>
@@ -3737,13 +3769,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>3</v>
       </c>
@@ -3751,13 +3783,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>3</v>
       </c>
@@ -3765,13 +3797,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>3</v>
       </c>
@@ -3779,10 +3811,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>4</v>
+        <v>61</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -3793,7 +3828,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>4</v>
@@ -3807,10 +3842,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>4</v>
+        <v>64</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -3821,7 +3859,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>4</v>
@@ -3835,7 +3873,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>4</v>
@@ -3849,7 +3887,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>4</v>
@@ -3863,7 +3901,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>4</v>
@@ -3877,13 +3915,10 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E167" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F167" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -3894,7 +3929,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>4</v>
@@ -3908,13 +3943,10 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>62</v>
+        <v>71</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -3925,7 +3957,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>4</v>
@@ -3939,7 +3971,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>4</v>
@@ -3953,7 +3985,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>4</v>
@@ -3967,7 +3999,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>4</v>
@@ -3981,7 +4013,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>4</v>
@@ -3992,10 +4024,7 @@
         <v>3</v>
       </c>
       <c r="B175" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="C175" s="4" t="s">
-        <v>70</v>
+        <v>5.2</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>4</v>
@@ -4006,13 +4035,10 @@
         <v>3</v>
       </c>
       <c r="B176" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>4</v>
+        <v>6.1</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -4020,10 +4046,10 @@
         <v>3</v>
       </c>
       <c r="B177" s="1">
-        <v>5.0999999999999996</v>
+        <v>6.1</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>4</v>
@@ -4034,10 +4060,10 @@
         <v>3</v>
       </c>
       <c r="B178" s="1">
-        <v>5.0999999999999996</v>
+        <v>6.1</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>4</v>
@@ -4048,10 +4074,10 @@
         <v>3</v>
       </c>
       <c r="B179" s="1">
-        <v>5.0999999999999996</v>
+        <v>6.1</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>4</v>
@@ -4062,10 +4088,10 @@
         <v>3</v>
       </c>
       <c r="B180" s="1">
-        <v>5.0999999999999996</v>
+        <v>6.1</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="D180" s="1" t="s">
         <v>4</v>
@@ -4076,10 +4102,10 @@
         <v>3</v>
       </c>
       <c r="B181" s="1">
-        <v>5.0999999999999996</v>
+        <v>6.1</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>4</v>
@@ -4090,7 +4116,10 @@
         <v>3</v>
       </c>
       <c r="B182" s="1">
-        <v>5.2</v>
+        <v>6.1</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="D182" s="1" t="s">
         <v>4</v>
@@ -4103,8 +4132,14 @@
       <c r="B183" s="1">
         <v>6.1</v>
       </c>
+      <c r="C183" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F183" s="1" t="s">
-        <v>257</v>
+        <v>85</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -4115,10 +4150,13 @@
         <v>6.1</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>4</v>
+        <v>84</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -4129,7 +4167,7 @@
         <v>6.1</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>4</v>
@@ -4143,7 +4181,7 @@
         <v>6.1</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>4</v>
@@ -4157,7 +4195,7 @@
         <v>6.1</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>4</v>
@@ -4171,7 +4209,7 @@
         <v>6.1</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>4</v>
@@ -4185,7 +4223,7 @@
         <v>6.1</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D189" s="1" t="s">
         <v>4</v>
@@ -4199,13 +4237,10 @@
         <v>6.1</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F190" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -4216,13 +4251,10 @@
         <v>6.1</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F191" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -4233,7 +4265,7 @@
         <v>6.1</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>4</v>
@@ -4244,10 +4276,7 @@
         <v>3</v>
       </c>
       <c r="B193" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="C193" s="4" t="s">
-        <v>87</v>
+        <v>6.2</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>4</v>
@@ -4258,10 +4287,7 @@
         <v>3</v>
       </c>
       <c r="B194" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="C194" s="4" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>4</v>
@@ -4272,13 +4298,13 @@
         <v>3</v>
       </c>
       <c r="B195" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="C195" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -4286,10 +4312,10 @@
         <v>3</v>
       </c>
       <c r="B196" s="1">
-        <v>6.1</v>
+        <v>8</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>4</v>
@@ -4300,10 +4326,10 @@
         <v>3</v>
       </c>
       <c r="B197" s="1">
-        <v>6.1</v>
+        <v>8</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>4</v>
@@ -4314,10 +4340,10 @@
         <v>3</v>
       </c>
       <c r="B198" s="1">
-        <v>6.1</v>
+        <v>8</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>4</v>
@@ -4328,10 +4354,10 @@
         <v>3</v>
       </c>
       <c r="B199" s="1">
-        <v>6.1</v>
+        <v>8</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>4</v>
@@ -4342,10 +4368,19 @@
         <v>3</v>
       </c>
       <c r="B200" s="1">
-        <v>6.2</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G200" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -4353,7 +4388,10 @@
         <v>3</v>
       </c>
       <c r="B201" s="1">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>4</v>
@@ -4366,8 +4404,11 @@
       <c r="B202" s="1">
         <v>8</v>
       </c>
-      <c r="F202" s="1" t="s">
-        <v>262</v>
+      <c r="C202" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -4377,9 +4418,11 @@
       <c r="B203" s="1">
         <v>8</v>
       </c>
-      <c r="C203" s="1"/>
-      <c r="F203" s="1" t="s">
-        <v>261</v>
+      <c r="C203" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -4390,10 +4433,13 @@
         <v>8</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>4</v>
+        <v>104</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -4401,13 +4447,13 @@
         <v>3</v>
       </c>
       <c r="B205" s="1">
-        <v>8</v>
-      </c>
-      <c r="C205" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -4415,10 +4461,10 @@
         <v>3</v>
       </c>
       <c r="B206" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>4</v>
@@ -4429,10 +4475,10 @@
         <v>3</v>
       </c>
       <c r="B207" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>4</v>
@@ -4443,104 +4489,124 @@
         <v>3</v>
       </c>
       <c r="B208" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F208" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B209" s="1">
+        <v>9</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F209" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="G208" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A209" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B209" s="1">
-        <v>8</v>
-      </c>
-      <c r="C209" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D209" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G209" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H209" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B210" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H210" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B211" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B212" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F212" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B213" s="1">
         <v>9</v>
       </c>
+      <c r="C213" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F213" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="G213" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B214" s="1">
         <v>9</v>
       </c>
-      <c r="C214" s="1"/>
-      <c r="F214" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C214" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>3</v>
       </c>
@@ -4548,13 +4614,16 @@
         <v>9</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F215" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>3</v>
       </c>
@@ -4562,13 +4631,25 @@
         <v>9</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D216" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G216" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H216" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="I216" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>3</v>
       </c>
@@ -4576,13 +4657,13 @@
         <v>9</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>3</v>
       </c>
@@ -4590,22 +4671,16 @@
         <v>9</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E218" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D218" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G218" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H218" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>3</v>
       </c>
@@ -4613,7 +4688,7 @@
         <v>9</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>4</v>
@@ -4625,10 +4700,13 @@
         <v>114</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+      <c r="I219" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>3</v>
       </c>
@@ -4636,13 +4714,16 @@
         <v>9</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="D220" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F220" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>3</v>
       </c>
@@ -4650,13 +4731,16 @@
         <v>9</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="D221" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F221" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>3</v>
       </c>
@@ -4664,180 +4748,12 @@
         <v>9</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E222" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D222" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G222" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A223" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B223" s="1">
-        <v>9</v>
-      </c>
-      <c r="C223" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A224" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B224" s="1">
-        <v>9</v>
-      </c>
-      <c r="C224" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D224" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F224" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A225" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B225" s="1">
-        <v>9</v>
-      </c>
-      <c r="C225" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E225" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F225" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G225" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H225" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="I225" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A226" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B226" s="1">
-        <v>9</v>
-      </c>
-      <c r="C226" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D226" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A227" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B227" s="1">
-        <v>9</v>
-      </c>
-      <c r="C227" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D227" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F227" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A228" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B228" s="1">
-        <v>9</v>
-      </c>
-      <c r="C228" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E228" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F228" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G228" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H228" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="I228" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A229" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B229" s="1">
-        <v>9</v>
-      </c>
-      <c r="C229" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D229" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F229" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A230" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B230" s="1">
-        <v>9</v>
-      </c>
-      <c r="C230" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D230" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F230" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A231" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B231" s="1">
-        <v>9</v>
-      </c>
-      <c r="C231" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D231" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F231" s="1" t="s">
         <v>118</v>
       </c>
     </row>
@@ -23262,14 +23178,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c3e85fef-df06-4e67-8632-489752715f52" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6fd297-1f65-4950-8fc9-157e29c7b648">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -23522,21 +23436,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c3e85fef-df06-4e67-8632-489752715f52" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6fd297-1f65-4950-8fc9-157e29c7b648">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98411DB4-5541-4967-8DBE-AF3E324DD5F5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171B3C16-7124-4B98-87E3-5FC6A9D45406}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c3e85fef-df06-4e67-8632-489752715f52"/>
-    <ds:schemaRef ds:uri="ea6fd297-1f65-4950-8fc9-157e29c7b648"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -23561,9 +23474,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171B3C16-7124-4B98-87E3-5FC6A9D45406}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98411DB4-5541-4967-8DBE-AF3E324DD5F5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c3e85fef-df06-4e67-8632-489752715f52"/>
+    <ds:schemaRef ds:uri="ea6fd297-1f65-4950-8fc9-157e29c7b648"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/dg_list.xlsx
+++ b/dg_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ialasia.sharepoint.com/sites/IALDGDESK/Shared Documents/General/Query System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="250" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8199D398-1B17-4CC0-A177-61361D755230}"/>
+  <xr:revisionPtr revIDLastSave="287" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{859F7B5F-65CE-4ADB-870F-4ACAD3063226}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="27630" windowHeight="16440" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
   </bookViews>
   <sheets>
     <sheet name="IAL" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3455" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3397" uniqueCount="264">
   <si>
     <t>UN Number</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -662,10 +662,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Class 4.3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1183</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -674,9 +670,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Class 4.3</t>
-  </si>
-  <si>
     <t>1295</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1037,11 +1030,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Related to TRICHLOROISOCYANURIC ACID or DICHLOROISOCYANURIC ACID and their synonyms are prohibited. Only accept WHL booking on
-WHL vessel.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Batteries are prohibited,if batteries (DG/non-DG) are used, defective, damaged and waste. Only brand new batteries are accepted.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1050,12 +1038,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Including power banks, are prohibited regardless of whether they are classified as
-DG or non-DG. All customers, including Partners, shall declare non-DG UN3481 &amp; non-DG UN3552 container to WHL.
-Partners are requested to submit declaration to WHL and add remark in your CBF for any container containing non-DG UN3481 or non-DG UN3552.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Only accept brand new ELECTRIC VEHICLE with state of charge(SOC) under 30%.</t>
   </si>
   <si>
@@ -1084,6 +1066,26 @@
   </si>
   <si>
     <t>All Dangerous Goods in Reefer Containers should be approved by HQ SE &amp; DG DESK. (IAL’s booking only)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DG goods in Reefer container is prohibited except Japan export. (Wan Hai booking only)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DG goods in Thermo King (TK) Reefer container is prohibited. (regardless of whether Partners or Wan Hai shipments)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class 6.1 is PROHIBITED for all ports including Japan export. (Wan Hai booking only)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Related to TRICHLOROISOCYANURIC ACID or DICHLOROISOCYANURIC ACID and their synonyms are prohibited. Only accept WHL booking on WHL vessel.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Including power banks, are prohibited regardless of whether they are classified as DG or non-DG. All customers, including Partners, shall declare non-DG UN3481 &amp; non-DG UN3552 container to WHL. Partners are requested to submit declaration to WHL and add remark in your CBF for any container containing non-DG UN3481 or non-DG UN3552.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1238,6 +1240,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1598,7 +1604,7 @@
         <v>136</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1688,10 +1694,10 @@
         <v>2.1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1758,10 +1764,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1803,10 +1809,10 @@
         <v>5</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -2503,10 +2509,10 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -2968,10 +2974,10 @@
         <v>4.2</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -3461,10 +3467,10 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -4038,7 +4044,7 @@
         <v>6.1</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -4301,10 +4307,10 @@
         <v>8</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -4450,10 +4456,10 @@
         <v>9</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -4643,7 +4649,7 @@
         <v>114</v>
       </c>
       <c r="H216" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>124</v>
@@ -4700,7 +4706,7 @@
         <v>114</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>129</v>
@@ -4766,7 +4772,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6C51C0B-216E-42EC-81BA-73D00CDF28DF}">
-  <dimension ref="A1:H300"/>
+  <dimension ref="A1:H310"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.625" style="1" customWidth="1"/>
@@ -4891,11 +4897,11 @@
       <c r="B9" s="1">
         <v>2.1</v>
       </c>
-      <c r="C9" s="4">
-        <v>1057</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
+      <c r="F9" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -4905,14 +4911,11 @@
       <c r="B10" s="1">
         <v>2.1</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>149</v>
+      <c r="C10" s="4">
+        <v>1057</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -4922,11 +4925,14 @@
       <c r="B11" s="1">
         <v>2.1</v>
       </c>
-      <c r="C11" s="4">
-        <v>1961</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
+      <c r="C11" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -4937,7 +4943,7 @@
         <v>2.1</v>
       </c>
       <c r="C12" s="4">
-        <v>1966</v>
+        <v>1961</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>4</v>
@@ -4951,7 +4957,7 @@
         <v>2.1</v>
       </c>
       <c r="C13" s="4">
-        <v>1972</v>
+        <v>1966</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>4</v>
@@ -4964,14 +4970,11 @@
       <c r="B14" s="1">
         <v>2.1</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>149</v>
+      <c r="C14" s="4">
+        <v>1972</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -4979,10 +4982,10 @@
         <v>144</v>
       </c>
       <c r="B15" s="1">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>4</v>
@@ -4998,232 +5001,235 @@
       <c r="B16" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B17" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B18" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B19" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C19" s="4">
         <v>2455</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B18" s="1">
+      <c r="D19" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" s="1">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B19" s="1">
-        <v>3</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F19" s="1" t="s">
+      <c r="D20" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B21" s="1">
+        <v>3</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B22" s="1">
+        <v>3</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B20" s="1">
-        <v>3</v>
-      </c>
-      <c r="C20" s="4">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="1">
+        <v>3</v>
+      </c>
+      <c r="C23" s="4">
         <v>1088</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B21" s="1">
-        <v>3</v>
-      </c>
-      <c r="C21" s="4">
+      <c r="D23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B24" s="1">
+        <v>3</v>
+      </c>
+      <c r="C24" s="4">
         <v>1089</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B22" s="1">
-        <v>3</v>
-      </c>
-      <c r="C22" s="4">
+      <c r="D24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B25" s="1">
+        <v>3</v>
+      </c>
+      <c r="C25" s="4">
         <v>1090</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B23" s="1">
-        <v>3</v>
-      </c>
-      <c r="C23" s="4">
+      <c r="D25" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" s="1">
+        <v>3</v>
+      </c>
+      <c r="C26" s="4">
         <v>1100</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B24" s="1">
-        <v>3</v>
-      </c>
-      <c r="C24" s="4">
+      <c r="D26" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B27" s="1">
+        <v>3</v>
+      </c>
+      <c r="C27" s="4">
         <v>1108</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B25" s="1">
-        <v>3</v>
-      </c>
-      <c r="C25" s="4" t="s">
+      <c r="D27" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B28" s="1">
+        <v>3</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B26" s="1">
-        <v>3</v>
-      </c>
-      <c r="C26" s="4">
+      <c r="D28" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="1">
+        <v>3</v>
+      </c>
+      <c r="C29" s="4">
         <v>1131</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B27" s="1">
-        <v>3</v>
-      </c>
-      <c r="C27" s="4">
+      <c r="D29" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B30" s="1">
+        <v>3</v>
+      </c>
+      <c r="C30" s="4">
         <v>1144</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B28" s="1">
-        <v>3</v>
-      </c>
-      <c r="C28" s="4">
+      <c r="D30" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B31" s="1">
+        <v>3</v>
+      </c>
+      <c r="C31" s="4">
         <v>1146</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B29" s="1">
-        <v>3</v>
-      </c>
-      <c r="C29" s="4">
+      <c r="D31" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B32" s="1">
+        <v>3</v>
+      </c>
+      <c r="C32" s="4">
         <v>1154</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B30" s="1">
-        <v>3</v>
-      </c>
-      <c r="C30" s="4">
-        <v>1155</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B31" s="1">
-        <v>3</v>
-      </c>
-      <c r="C31" s="4">
-        <v>1159</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B32" s="1">
-        <v>3</v>
-      </c>
-      <c r="C32" s="4">
-        <v>1164</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>4</v>
@@ -5237,7 +5243,7 @@
         <v>3</v>
       </c>
       <c r="C33" s="4">
-        <v>1167</v>
+        <v>1155</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>4</v>
@@ -5251,7 +5257,7 @@
         <v>3</v>
       </c>
       <c r="C34" s="4">
-        <v>1190</v>
+        <v>1159</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>4</v>
@@ -5264,8 +5270,8 @@
       <c r="B35" s="1">
         <v>3</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>153</v>
+      <c r="C35" s="4">
+        <v>1164</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>4</v>
@@ -5279,7 +5285,7 @@
         <v>3</v>
       </c>
       <c r="C36" s="4">
-        <v>1218</v>
+        <v>1167</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>4</v>
@@ -5293,7 +5299,7 @@
         <v>3</v>
       </c>
       <c r="C37" s="4">
-        <v>1221</v>
+        <v>1190</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>4</v>
@@ -5306,8 +5312,8 @@
       <c r="B38" s="1">
         <v>3</v>
       </c>
-      <c r="C38" s="4">
-        <v>1234</v>
+      <c r="C38" s="4" t="s">
+        <v>153</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>4</v>
@@ -5321,7 +5327,7 @@
         <v>3</v>
       </c>
       <c r="C39" s="4">
-        <v>1243</v>
+        <v>1218</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>4</v>
@@ -5335,7 +5341,7 @@
         <v>3</v>
       </c>
       <c r="C40" s="4">
-        <v>1275</v>
+        <v>1221</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>4</v>
@@ -5349,7 +5355,7 @@
         <v>3</v>
       </c>
       <c r="C41" s="4">
-        <v>1277</v>
+        <v>1234</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>4</v>
@@ -5363,7 +5369,7 @@
         <v>3</v>
       </c>
       <c r="C42" s="4">
-        <v>1280</v>
+        <v>1243</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>4</v>
@@ -5377,7 +5383,7 @@
         <v>3</v>
       </c>
       <c r="C43" s="4">
-        <v>1298</v>
+        <v>1275</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>4</v>
@@ -5391,7 +5397,7 @@
         <v>3</v>
       </c>
       <c r="C44" s="4">
-        <v>1302</v>
+        <v>1277</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>4</v>
@@ -5405,7 +5411,7 @@
         <v>3</v>
       </c>
       <c r="C45" s="4">
-        <v>1303</v>
+        <v>1280</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>4</v>
@@ -5419,7 +5425,7 @@
         <v>3</v>
       </c>
       <c r="C46" s="4">
-        <v>1891</v>
+        <v>1298</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>4</v>
@@ -5433,7 +5439,7 @@
         <v>3</v>
       </c>
       <c r="C47" s="4">
-        <v>1991</v>
+        <v>1302</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>4</v>
@@ -5447,7 +5453,7 @@
         <v>3</v>
       </c>
       <c r="C48" s="4">
-        <v>1999</v>
+        <v>1303</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>4</v>
@@ -5461,7 +5467,7 @@
         <v>3</v>
       </c>
       <c r="C49" s="4">
-        <v>2045</v>
+        <v>1891</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>4</v>
@@ -5475,7 +5481,7 @@
         <v>3</v>
       </c>
       <c r="C50" s="4">
-        <v>2056</v>
+        <v>1991</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>4</v>
@@ -5489,7 +5495,7 @@
         <v>3</v>
       </c>
       <c r="C51" s="4">
-        <v>2246</v>
+        <v>1999</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>4</v>
@@ -5503,7 +5509,7 @@
         <v>3</v>
       </c>
       <c r="C52" s="4">
-        <v>2251</v>
+        <v>2045</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>4</v>
@@ -5517,7 +5523,7 @@
         <v>3</v>
       </c>
       <c r="C53" s="4">
-        <v>2301</v>
+        <v>2056</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>4</v>
@@ -5531,7 +5537,7 @@
         <v>3</v>
       </c>
       <c r="C54" s="4">
-        <v>2356</v>
+        <v>2246</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>4</v>
@@ -5545,7 +5551,7 @@
         <v>3</v>
       </c>
       <c r="C55" s="4">
-        <v>2363</v>
+        <v>2251</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>4</v>
@@ -5559,7 +5565,7 @@
         <v>3</v>
       </c>
       <c r="C56" s="4">
-        <v>2371</v>
+        <v>2301</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>4</v>
@@ -5573,7 +5579,7 @@
         <v>3</v>
       </c>
       <c r="C57" s="4">
-        <v>2384</v>
+        <v>2356</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>4</v>
@@ -5587,7 +5593,7 @@
         <v>3</v>
       </c>
       <c r="C58" s="4">
-        <v>2389</v>
+        <v>2363</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>4</v>
@@ -5601,7 +5607,7 @@
         <v>3</v>
       </c>
       <c r="C59" s="4">
-        <v>2398</v>
+        <v>2371</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>4</v>
@@ -5615,7 +5621,7 @@
         <v>3</v>
       </c>
       <c r="C60" s="4">
-        <v>2402</v>
+        <v>2384</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>4</v>
@@ -5629,7 +5635,7 @@
         <v>3</v>
       </c>
       <c r="C61" s="4">
-        <v>2456</v>
+        <v>2389</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>4</v>
@@ -5643,7 +5649,7 @@
         <v>3</v>
       </c>
       <c r="C62" s="4">
-        <v>2457</v>
+        <v>2398</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>4</v>
@@ -5657,7 +5663,7 @@
         <v>3</v>
       </c>
       <c r="C63" s="4">
-        <v>2459</v>
+        <v>2402</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>4</v>
@@ -5671,156 +5677,153 @@
         <v>3</v>
       </c>
       <c r="C64" s="4">
+        <v>2456</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B65" s="1">
+        <v>3</v>
+      </c>
+      <c r="C65" s="4">
+        <v>2457</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B66" s="1">
+        <v>3</v>
+      </c>
+      <c r="C66" s="4">
+        <v>2459</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B67" s="1">
+        <v>3</v>
+      </c>
+      <c r="C67" s="4">
         <v>2460</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B65" s="1">
-        <v>3</v>
-      </c>
-      <c r="C65" s="4">
+      <c r="D67" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B68" s="1">
+        <v>3</v>
+      </c>
+      <c r="C68" s="4">
         <v>2461</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B66" s="1">
-        <v>3</v>
-      </c>
-      <c r="C66" s="4">
+      <c r="D68" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B69" s="1">
+        <v>3</v>
+      </c>
+      <c r="C69" s="4">
         <v>2561</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B67" s="1">
-        <v>3</v>
-      </c>
-      <c r="C67" s="4">
+      <c r="D69" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B70" s="1">
+        <v>3</v>
+      </c>
+      <c r="C70" s="4">
         <v>2612</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B68" s="1">
-        <v>3</v>
-      </c>
-      <c r="C68" s="4">
+      <c r="D70" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B71" s="1">
+        <v>3</v>
+      </c>
+      <c r="C71" s="4">
         <v>2615</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B69" s="1">
-        <v>3</v>
-      </c>
-      <c r="C69" s="4">
+      <c r="D71" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B72" s="1">
+        <v>3</v>
+      </c>
+      <c r="C72" s="4">
         <v>2749</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B70" s="1">
-        <v>3</v>
-      </c>
-      <c r="C70" s="4">
+      <c r="D72" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B73" s="1">
+        <v>3</v>
+      </c>
+      <c r="C73" s="4">
         <v>2983</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B71" s="1">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C71" s="4">
-        <v>1334</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B72" s="1">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B73" s="1">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C73" s="4">
-        <v>1309</v>
-      </c>
       <c r="D73" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B74" s="1">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C74" s="4">
-        <v>1323</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F74" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>144</v>
       </c>
@@ -5828,27 +5831,30 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C75" s="4">
-        <v>1333</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1334</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B76" s="1">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C76" s="4">
-        <v>1339</v>
+      <c r="C76" s="4" t="s">
+        <v>154</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>144</v>
       </c>
@@ -5856,13 +5862,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C77" s="4">
-        <v>1343</v>
+        <v>1309</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>144</v>
       </c>
@@ -5870,13 +5876,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C78" s="4">
-        <v>1358</v>
+        <v>1323</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>144</v>
       </c>
@@ -5884,13 +5890,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C79" s="4">
-        <v>1869</v>
+        <v>1333</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>144</v>
       </c>
@@ -5898,7 +5904,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C80" s="4">
-        <v>2858</v>
+        <v>1339</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>4</v>
@@ -5912,7 +5918,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C81" s="4">
-        <v>2878</v>
+        <v>1343</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>4</v>
@@ -5926,7 +5932,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C82" s="4">
-        <v>3089</v>
+        <v>1358</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>4</v>
@@ -5940,7 +5946,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C83" s="4">
-        <v>3221</v>
+        <v>1869</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>4</v>
@@ -5954,7 +5960,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C84" s="4">
-        <v>3222</v>
+        <v>2858</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>4</v>
@@ -5968,7 +5974,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C85" s="4">
-        <v>3223</v>
+        <v>2878</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>4</v>
@@ -5982,7 +5988,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C86" s="4">
-        <v>3224</v>
+        <v>3089</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>4</v>
@@ -5996,7 +6002,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C87" s="4">
-        <v>3225</v>
+        <v>3221</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>4</v>
@@ -6010,7 +6016,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C88" s="4">
-        <v>3226</v>
+        <v>3222</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>4</v>
@@ -6024,7 +6030,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C89" s="4">
-        <v>3227</v>
+        <v>3223</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>4</v>
@@ -6038,7 +6044,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C90" s="4">
-        <v>3228</v>
+        <v>3224</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>4</v>
@@ -6052,7 +6058,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C91" s="4">
-        <v>3229</v>
+        <v>3225</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>4</v>
@@ -6066,7 +6072,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C92" s="4">
-        <v>3230</v>
+        <v>3226</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>4</v>
@@ -6080,7 +6086,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C93" s="4">
-        <v>3231</v>
+        <v>3227</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>4</v>
@@ -6094,7 +6100,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C94" s="4">
-        <v>3232</v>
+        <v>3228</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>4</v>
@@ -6108,7 +6114,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C95" s="4">
-        <v>3233</v>
+        <v>3229</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>4</v>
@@ -6122,13 +6128,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C96" s="4">
-        <v>3234</v>
+        <v>3230</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>144</v>
       </c>
@@ -6136,13 +6142,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C97" s="4">
-        <v>3235</v>
+        <v>3231</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>144</v>
       </c>
@@ -6150,13 +6156,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C98" s="4">
-        <v>3236</v>
+        <v>3232</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>144</v>
       </c>
@@ -6164,13 +6170,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C99" s="4">
-        <v>3237</v>
+        <v>3233</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>144</v>
       </c>
@@ -6178,13 +6184,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C100" s="4">
-        <v>3238</v>
+        <v>3234</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>144</v>
       </c>
@@ -6192,13 +6198,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C101" s="4">
-        <v>3239</v>
+        <v>3235</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>144</v>
       </c>
@@ -6206,13 +6212,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C102" s="4">
-        <v>3240</v>
+        <v>3236</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>144</v>
       </c>
@@ -6220,117 +6226,117 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C103" s="4">
+        <v>3237</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B104" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C104" s="4">
+        <v>3238</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B105" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C105" s="4">
+        <v>3239</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B106" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C106" s="4">
+        <v>3240</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B107" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C107" s="4">
         <v>3241</v>
       </c>
-      <c r="D103" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B104" s="1">
-        <v>4.2</v>
-      </c>
-      <c r="C104" s="4">
-        <v>1361</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F104" s="5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B105" s="1">
-        <v>4.2</v>
-      </c>
-      <c r="C105" s="4">
-        <v>1362</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F105" s="5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B106" s="1">
-        <v>4.2</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B107" s="1">
-        <v>4.2</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>7</v>
-      </c>
       <c r="D107" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B108" s="1">
         <v>4.2</v>
       </c>
-      <c r="C108" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F108" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B109" s="1">
         <v>4.2</v>
       </c>
-      <c r="C109" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C109" s="4">
+        <v>1361</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F109" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B110" s="1">
         <v>4.2</v>
       </c>
-      <c r="C110" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C110" s="4">
+        <v>1362</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>144</v>
       </c>
@@ -6338,13 +6344,13 @@
         <v>4.2</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>144</v>
       </c>
@@ -6352,7 +6358,7 @@
         <v>4.2</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>4</v>
@@ -6366,7 +6372,7 @@
         <v>4.2</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>4</v>
@@ -6380,7 +6386,7 @@
         <v>4.2</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>4</v>
@@ -6394,7 +6400,7 @@
         <v>4.2</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>4</v>
@@ -6408,7 +6414,7 @@
         <v>4.2</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>4</v>
@@ -6422,7 +6428,7 @@
         <v>4.2</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>4</v>
@@ -6436,7 +6442,7 @@
         <v>4.2</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>4</v>
@@ -6450,7 +6456,7 @@
         <v>4.2</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>4</v>
@@ -6464,7 +6470,7 @@
         <v>4.2</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>4</v>
@@ -6478,7 +6484,7 @@
         <v>4.2</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>4</v>
@@ -6492,7 +6498,7 @@
         <v>4.2</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>4</v>
@@ -6506,7 +6512,7 @@
         <v>4.2</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>4</v>
@@ -6520,7 +6526,7 @@
         <v>4.2</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>4</v>
@@ -6534,7 +6540,7 @@
         <v>4.2</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>4</v>
@@ -6548,7 +6554,7 @@
         <v>4.2</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>4</v>
@@ -6562,7 +6568,7 @@
         <v>4.2</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>4</v>
@@ -6576,13 +6582,13 @@
         <v>4.2</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>144</v>
       </c>
@@ -6590,13 +6596,13 @@
         <v>4.2</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>144</v>
       </c>
@@ -6604,13 +6610,13 @@
         <v>4.2</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>144</v>
       </c>
@@ -6618,13 +6624,13 @@
         <v>4.2</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>144</v>
       </c>
@@ -6632,13 +6638,13 @@
         <v>4.2</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>144</v>
       </c>
@@ -6646,13 +6652,13 @@
         <v>4.2</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>144</v>
       </c>
@@ -6660,13 +6666,13 @@
         <v>4.2</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>144</v>
       </c>
@@ -6674,13 +6680,13 @@
         <v>4.2</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>144</v>
       </c>
@@ -6688,119 +6694,119 @@
         <v>4.2</v>
       </c>
       <c r="C136" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B137" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B138" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B139" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B140" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B141" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C141" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B137" s="1" t="s">
+      <c r="D141" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B142" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B143" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C143" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C137" s="4" t="s">
+      <c r="D143" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B144" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C144" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A140" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A143" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A144" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>166</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>4</v>
@@ -6810,11 +6816,11 @@
       <c r="A145" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>160</v>
+      <c r="B145" s="1">
+        <v>4.3</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>4</v>
@@ -6824,11 +6830,11 @@
       <c r="A146" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="B146" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C146" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>168</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>4</v>
@@ -6838,11 +6844,11 @@
       <c r="A147" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>160</v>
+      <c r="B147" s="1">
+        <v>4.3</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>4</v>
@@ -6852,11 +6858,11 @@
       <c r="A148" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>160</v>
+      <c r="B148" s="1">
+        <v>4.3</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>4</v>
@@ -6866,11 +6872,11 @@
       <c r="A149" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>160</v>
+      <c r="B149" s="1">
+        <v>4.3</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>4</v>
@@ -6880,11 +6886,11 @@
       <c r="A150" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>160</v>
+      <c r="B150" s="1">
+        <v>4.3</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>4</v>
@@ -6894,11 +6900,11 @@
       <c r="A151" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>160</v>
+      <c r="B151" s="1">
+        <v>4.3</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>4</v>
@@ -6908,11 +6914,11 @@
       <c r="A152" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>160</v>
+      <c r="B152" s="1">
+        <v>4.3</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>4</v>
@@ -6922,11 +6928,11 @@
       <c r="A153" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>160</v>
+      <c r="B153" s="1">
+        <v>4.3</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>4</v>
@@ -6936,11 +6942,11 @@
       <c r="A154" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>160</v>
+      <c r="B154" s="1">
+        <v>4.3</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>4</v>
@@ -6950,11 +6956,11 @@
       <c r="A155" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>160</v>
+      <c r="B155" s="1">
+        <v>4.3</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>4</v>
@@ -6964,11 +6970,11 @@
       <c r="A156" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>160</v>
+      <c r="B156" s="1">
+        <v>4.3</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>4</v>
@@ -6978,11 +6984,11 @@
       <c r="A157" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>160</v>
+      <c r="B157" s="1">
+        <v>4.3</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>4</v>
@@ -6992,11 +6998,11 @@
       <c r="A158" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>160</v>
+      <c r="B158" s="1">
+        <v>4.3</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>4</v>
@@ -7006,11 +7012,11 @@
       <c r="A159" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>160</v>
+      <c r="B159" s="1">
+        <v>4.3</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>4</v>
@@ -7020,11 +7026,11 @@
       <c r="A160" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>160</v>
+      <c r="B160" s="1">
+        <v>4.3</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>4</v>
@@ -7034,11 +7040,11 @@
       <c r="A161" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>160</v>
+      <c r="B161" s="1">
+        <v>4.3</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>4</v>
@@ -7048,11 +7054,11 @@
       <c r="A162" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>160</v>
+      <c r="B162" s="1">
+        <v>4.3</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>4</v>
@@ -7062,11 +7068,11 @@
       <c r="A163" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>160</v>
+      <c r="B163" s="1">
+        <v>4.3</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>4</v>
@@ -7076,11 +7082,11 @@
       <c r="A164" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>160</v>
+      <c r="B164" s="1">
+        <v>4.3</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>4</v>
@@ -7090,11 +7096,11 @@
       <c r="A165" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>160</v>
+      <c r="B165" s="1">
+        <v>4.3</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>4</v>
@@ -7104,11 +7110,11 @@
       <c r="A166" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>160</v>
+      <c r="B166" s="1">
+        <v>4.3</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>4</v>
@@ -7118,11 +7124,11 @@
       <c r="A167" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>160</v>
+      <c r="B167" s="1">
+        <v>4.3</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D167" s="1" t="s">
         <v>4</v>
@@ -7132,11 +7138,11 @@
       <c r="A168" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>160</v>
+      <c r="B168" s="1">
+        <v>4.3</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>4</v>
@@ -7146,11 +7152,11 @@
       <c r="A169" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>160</v>
+      <c r="B169" s="1">
+        <v>4.3</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>4</v>
@@ -7160,11 +7166,11 @@
       <c r="A170" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>160</v>
+      <c r="B170" s="1">
+        <v>4.3</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>4</v>
@@ -7174,11 +7180,11 @@
       <c r="A171" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>160</v>
+      <c r="B171" s="1">
+        <v>4.3</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>4</v>
@@ -7188,11 +7194,11 @@
       <c r="A172" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>160</v>
+      <c r="B172" s="1">
+        <v>4.3</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>4</v>
@@ -7202,11 +7208,11 @@
       <c r="A173" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>160</v>
+      <c r="B173" s="1">
+        <v>4.3</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>4</v>
@@ -7216,11 +7222,11 @@
       <c r="A174" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>160</v>
+      <c r="B174" s="1">
+        <v>4.3</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>4</v>
@@ -7230,11 +7236,11 @@
       <c r="A175" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>160</v>
+      <c r="B175" s="1">
+        <v>4.3</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>4</v>
@@ -7244,11 +7250,11 @@
       <c r="A176" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>160</v>
+      <c r="B176" s="1">
+        <v>4.3</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>4</v>
@@ -7258,11 +7264,11 @@
       <c r="A177" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>160</v>
+      <c r="B177" s="1">
+        <v>4.3</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>4</v>
@@ -7272,11 +7278,11 @@
       <c r="A178" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>160</v>
+      <c r="B178" s="1">
+        <v>4.3</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>4</v>
@@ -7286,11 +7292,11 @@
       <c r="A179" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>160</v>
+      <c r="B179" s="1">
+        <v>4.3</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>4</v>
@@ -7300,11 +7306,11 @@
       <c r="A180" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>160</v>
+      <c r="B180" s="1">
+        <v>4.3</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D180" s="1" t="s">
         <v>4</v>
@@ -7314,11 +7320,11 @@
       <c r="A181" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>160</v>
+      <c r="B181" s="1">
+        <v>4.3</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>4</v>
@@ -7328,11 +7334,11 @@
       <c r="A182" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>160</v>
+      <c r="B182" s="1">
+        <v>4.3</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D182" s="1" t="s">
         <v>4</v>
@@ -7342,11 +7348,11 @@
       <c r="A183" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>160</v>
+      <c r="B183" s="1">
+        <v>4.3</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D183" s="1" t="s">
         <v>4</v>
@@ -7356,11 +7362,11 @@
       <c r="A184" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>160</v>
+      <c r="B184" s="1">
+        <v>4.3</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D184" s="1" t="s">
         <v>4</v>
@@ -7370,11 +7376,11 @@
       <c r="A185" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>160</v>
+      <c r="B185" s="1">
+        <v>4.3</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>4</v>
@@ -7384,11 +7390,11 @@
       <c r="A186" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>160</v>
+      <c r="B186" s="1">
+        <v>4.3</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>4</v>
@@ -7398,11 +7404,11 @@
       <c r="A187" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>160</v>
+      <c r="B187" s="1">
+        <v>4.3</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>4</v>
@@ -7412,11 +7418,11 @@
       <c r="A188" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>160</v>
+      <c r="B188" s="1">
+        <v>4.3</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>4</v>
@@ -7426,11 +7432,11 @@
       <c r="A189" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>160</v>
+      <c r="B189" s="1">
+        <v>4.3</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="D189" s="1" t="s">
         <v>4</v>
@@ -7440,11 +7446,11 @@
       <c r="A190" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>160</v>
+      <c r="B190" s="1">
+        <v>4.3</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>4</v>
@@ -7454,11 +7460,11 @@
       <c r="A191" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>160</v>
+      <c r="B191" s="1">
+        <v>4.3</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>4</v>
@@ -7468,11 +7474,11 @@
       <c r="A192" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B192" s="1" t="s">
-        <v>160</v>
+      <c r="B192" s="1">
+        <v>4.3</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>4</v>
@@ -7482,11 +7488,11 @@
       <c r="A193" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>160</v>
+      <c r="B193" s="1">
+        <v>4.3</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>4</v>
@@ -7496,11 +7502,11 @@
       <c r="A194" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>160</v>
+      <c r="B194" s="1">
+        <v>4.3</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>4</v>
@@ -7510,11 +7516,11 @@
       <c r="A195" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>160</v>
+      <c r="B195" s="1">
+        <v>4.3</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>4</v>
@@ -7524,11 +7530,11 @@
       <c r="A196" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>160</v>
+      <c r="B196" s="1">
+        <v>4.3</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>4</v>
@@ -7538,11 +7544,11 @@
       <c r="A197" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>160</v>
+      <c r="B197" s="1">
+        <v>4.3</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>4</v>
@@ -7552,11 +7558,11 @@
       <c r="A198" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>160</v>
+      <c r="B198" s="1">
+        <v>4.3</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>4</v>
@@ -7566,11 +7572,11 @@
       <c r="A199" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>160</v>
+      <c r="B199" s="1">
+        <v>4.3</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>4</v>
@@ -7580,11 +7586,11 @@
       <c r="A200" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>160</v>
+      <c r="B200" s="1">
+        <v>4.3</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>4</v>
@@ -7594,11 +7600,11 @@
       <c r="A201" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>160</v>
+      <c r="B201" s="1">
+        <v>4.3</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>4</v>
@@ -7608,11 +7614,11 @@
       <c r="A202" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>160</v>
+      <c r="B202" s="1">
+        <v>4.3</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>4</v>
@@ -7622,11 +7628,11 @@
       <c r="A203" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>160</v>
+      <c r="B203" s="1">
+        <v>4.3</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>4</v>
@@ -7636,11 +7642,11 @@
       <c r="A204" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>160</v>
+      <c r="B204" s="1">
+        <v>4.3</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>4</v>
@@ -7650,11 +7656,11 @@
       <c r="A205" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B205" s="1" t="s">
-        <v>160</v>
+      <c r="B205" s="1">
+        <v>4.3</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>4</v>
@@ -7664,11 +7670,11 @@
       <c r="A206" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>160</v>
+      <c r="B206" s="1">
+        <v>4.3</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>4</v>
@@ -7678,11 +7684,11 @@
       <c r="A207" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>160</v>
+      <c r="B207" s="1">
+        <v>4.3</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>4</v>
@@ -7692,11 +7698,11 @@
       <c r="A208" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>160</v>
+      <c r="B208" s="1">
+        <v>4.3</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>4</v>
@@ -7706,11 +7712,11 @@
       <c r="A209" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>160</v>
+      <c r="B209" s="1">
+        <v>4.3</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>4</v>
@@ -7720,11 +7726,11 @@
       <c r="A210" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>160</v>
+      <c r="B210" s="1">
+        <v>4.3</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>4</v>
@@ -7734,11 +7740,11 @@
       <c r="A211" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B211" s="1" t="s">
-        <v>160</v>
+      <c r="B211" s="1">
+        <v>4.3</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>4</v>
@@ -7748,11 +7754,11 @@
       <c r="A212" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B212" s="1" t="s">
-        <v>160</v>
+      <c r="B212" s="1">
+        <v>4.3</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>4</v>
@@ -7762,11 +7768,11 @@
       <c r="A213" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>160</v>
+      <c r="B213" s="1">
+        <v>4.3</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>4</v>
@@ -7776,11 +7782,11 @@
       <c r="A214" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>160</v>
+      <c r="B214" s="1">
+        <v>4.3</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>4</v>
@@ -7790,11 +7796,11 @@
       <c r="A215" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B215" s="1" t="s">
-        <v>160</v>
+      <c r="B215" s="1">
+        <v>4.3</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>4</v>
@@ -7804,11 +7810,11 @@
       <c r="A216" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>160</v>
+      <c r="B216" s="1">
+        <v>4.3</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>4</v>
@@ -7818,11 +7824,11 @@
       <c r="A217" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>160</v>
+      <c r="B217" s="1">
+        <v>4.3</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>4</v>
@@ -7832,11 +7838,11 @@
       <c r="A218" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>160</v>
+      <c r="B218" s="1">
+        <v>4.3</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="D218" s="1" t="s">
         <v>4</v>
@@ -7846,11 +7852,11 @@
       <c r="A219" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B219" s="1" t="s">
-        <v>160</v>
+      <c r="B219" s="1">
+        <v>4.3</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>4</v>
@@ -7860,11 +7866,11 @@
       <c r="A220" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B220" s="1" t="s">
-        <v>160</v>
+      <c r="B220" s="1">
+        <v>4.3</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D220" s="1" t="s">
         <v>4</v>
@@ -7874,11 +7880,11 @@
       <c r="A221" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>160</v>
+      <c r="B221" s="1">
+        <v>4.3</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D221" s="1" t="s">
         <v>4</v>
@@ -7888,11 +7894,11 @@
       <c r="A222" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>160</v>
+      <c r="B222" s="1">
+        <v>4.3</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D222" s="1" t="s">
         <v>4</v>
@@ -7902,11 +7908,11 @@
       <c r="A223" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>160</v>
+      <c r="B223" s="1">
+        <v>4.3</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>4</v>
@@ -7917,100 +7923,100 @@
         <v>144</v>
       </c>
       <c r="B224" s="1">
-        <v>5.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>37</v>
+        <v>238</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B225" s="1">
-        <v>5.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>38</v>
+        <v>239</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B226" s="1">
-        <v>5.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>39</v>
+        <v>240</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B227" s="1">
-        <v>5.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>40</v>
+        <v>241</v>
       </c>
       <c r="D227" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B228" s="1">
-        <v>5.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>41</v>
+        <v>242</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B229" s="1">
-        <v>5.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>42</v>
+        <v>243</v>
       </c>
       <c r="D229" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B230" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C230" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D230" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F230" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G230" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>144</v>
       </c>
@@ -8018,13 +8024,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>144</v>
       </c>
@@ -8032,13 +8038,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>144</v>
       </c>
@@ -8046,13 +8052,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>144</v>
       </c>
@@ -8060,13 +8066,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>144</v>
       </c>
@@ -8074,13 +8080,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>144</v>
       </c>
@@ -8088,13 +8094,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>144</v>
       </c>
@@ -8102,13 +8108,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C237" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D237" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>144</v>
       </c>
@@ -8116,13 +8122,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D238" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>144</v>
       </c>
@@ -8130,13 +8136,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C239" s="4" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>144</v>
       </c>
@@ -8144,7 +8150,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>4</v>
@@ -8158,7 +8164,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>4</v>
@@ -8172,7 +8178,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D242" s="1" t="s">
         <v>4</v>
@@ -8186,7 +8192,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C243" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>4</v>
@@ -8200,13 +8206,10 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E244" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F244" s="1" t="s">
-        <v>246</v>
+        <v>50</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -8217,13 +8220,10 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C245" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E245" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F245" s="1" t="s">
-        <v>246</v>
+        <v>51</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -8234,7 +8234,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>4</v>
@@ -8248,7 +8248,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C247" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>4</v>
@@ -8262,13 +8262,10 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E248" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F248" s="1" t="s">
-        <v>247</v>
+        <v>54</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -8279,7 +8276,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C249" s="4" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>4</v>
@@ -8293,13 +8290,10 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E250" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F250" s="1" t="s">
-        <v>247</v>
+        <v>56</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -8310,10 +8304,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D251" s="1" t="s">
-        <v>4</v>
+        <v>57</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F251" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -8324,10 +8321,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D252" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F252" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -8338,7 +8338,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C253" s="4" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D253" s="1" t="s">
         <v>4</v>
@@ -8352,7 +8352,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>4</v>
@@ -8366,10 +8366,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D255" s="1" t="s">
-        <v>4</v>
+        <v>61</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F255" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -8380,16 +8383,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="E256" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F256" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="D256" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>144</v>
       </c>
@@ -8397,13 +8397,16 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C257" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F257" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>144</v>
       </c>
@@ -8411,13 +8414,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>144</v>
       </c>
@@ -8425,13 +8428,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>144</v>
       </c>
@@ -8439,13 +8442,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>144</v>
       </c>
@@ -8453,13 +8456,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C261" s="4" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D261" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>144</v>
       </c>
@@ -8467,136 +8470,136 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C262" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B263" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C263" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F263" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A264" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B264" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C264" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A265" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B265" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C265" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B266" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A267" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B267" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A268" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B268" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A269" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B269" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C269" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D262" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A263" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B263" s="1">
+      <c r="D269" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A270" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B270" s="1">
         <v>5.2</v>
       </c>
-      <c r="D263" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A264" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B264" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="C264" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D264" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A265" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B265" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="C265" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D265" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A266" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B266" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="C266" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D266" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A267" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B267" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="C267" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="D267" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A268" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B268" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="C268" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D268" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A269" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B269" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="C269" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A270" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B270" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="C270" s="4" t="s">
-        <v>86</v>
-      </c>
       <c r="D270" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B271" s="1">
         <v>6.1</v>
       </c>
-      <c r="C271" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F271" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>144</v>
       </c>
@@ -8604,13 +8607,13 @@
         <v>6.1</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>144</v>
       </c>
@@ -8618,13 +8621,13 @@
         <v>6.1</v>
       </c>
       <c r="C273" s="4" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D273" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>144</v>
       </c>
@@ -8632,13 +8635,13 @@
         <v>6.1</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D274" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>144</v>
       </c>
@@ -8646,13 +8649,13 @@
         <v>6.1</v>
       </c>
       <c r="C275" s="4" t="s">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>144</v>
       </c>
@@ -8660,13 +8663,13 @@
         <v>6.1</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D276" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>144</v>
       </c>
@@ -8674,175 +8677,172 @@
         <v>6.1</v>
       </c>
       <c r="C277" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A278" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B278" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A279" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B279" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C279" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A280" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B280" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C280" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A281" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B281" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C281" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A282" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B282" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C282" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A283" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B283" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A284" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B284" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C284" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A285" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B285" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C285" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D277" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A278" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B278" s="1">
+      <c r="D285" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A286" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B286" s="1">
         <v>6.2</v>
       </c>
-      <c r="D278" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A279" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B279" s="1">
+      <c r="D286" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A287" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B287" s="1">
         <v>7</v>
       </c>
-      <c r="D279" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A280" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B280" s="1">
+      <c r="D287" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A288" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B288" s="1">
         <v>8</v>
       </c>
-      <c r="C280" s="4" t="s">
+      <c r="F288" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G288" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A289" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B289" s="1">
+        <v>8</v>
+      </c>
+      <c r="C289" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D280" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A281" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B281" s="1">
-        <v>8</v>
-      </c>
-      <c r="C281" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A282" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B282" s="1">
-        <v>8</v>
-      </c>
-      <c r="C282" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A283" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B283" s="1">
-        <v>8</v>
-      </c>
-      <c r="C283" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D283" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A284" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B284" s="1">
-        <v>8</v>
-      </c>
-      <c r="C284" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D284" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A285" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B285" s="1">
-        <v>8</v>
-      </c>
-      <c r="C285" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D285" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A286" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B286" s="1">
-        <v>8</v>
-      </c>
-      <c r="C286" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D286" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A287" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B287" s="1">
-        <v>8</v>
-      </c>
-      <c r="C287" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D287" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A288" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B288" s="1">
-        <v>9</v>
-      </c>
-      <c r="C288" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D288" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A289" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B289" s="1">
-        <v>9</v>
-      </c>
-      <c r="C289" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="E289" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F289" s="5" t="s">
-        <v>251</v>
+      <c r="D289" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -8850,19 +8850,13 @@
         <v>144</v>
       </c>
       <c r="B290" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E290" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F290" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="G290" s="1" t="s">
-        <v>253</v>
+        <v>95</v>
+      </c>
+      <c r="D290" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -8870,10 +8864,10 @@
         <v>144</v>
       </c>
       <c r="B291" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C291" s="4" t="s">
-        <v>115</v>
+        <v>247</v>
       </c>
       <c r="D291" s="1" t="s">
         <v>4</v>
@@ -8884,50 +8878,41 @@
         <v>144</v>
       </c>
       <c r="B292" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="D292" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B293" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C293" s="4" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="D293" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F293" s="5" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B294" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E294" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F294" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="G294" s="5" t="s">
-        <v>254</v>
+        <v>101</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
@@ -8935,50 +8920,41 @@
         <v>144</v>
       </c>
       <c r="B295" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C295" s="4" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D295" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="296" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B296" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D296" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F296" s="5" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B297" s="1">
         <v>9</v>
       </c>
-      <c r="C297" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E297" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F297" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="G297" s="5" t="s">
-        <v>254</v>
+        <v>259</v>
+      </c>
+      <c r="G297" s="1" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -8989,19 +8965,13 @@
         <v>9</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E298" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F298" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="G298" s="1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>144</v>
       </c>
@@ -9009,16 +8979,13 @@
         <v>9</v>
       </c>
       <c r="C299" s="4" t="s">
-        <v>131</v>
+        <v>248</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F299" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="G299" s="1" t="s">
-        <v>255</v>
+      <c r="F299" s="5" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
@@ -9029,16 +8996,192 @@
         <v>9</v>
       </c>
       <c r="C300" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E300" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F300" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G300" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B301" s="1">
+        <v>9</v>
+      </c>
+      <c r="C301" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A302" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B302" s="1">
+        <v>9</v>
+      </c>
+      <c r="C302" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A303" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B303" s="1">
+        <v>9</v>
+      </c>
+      <c r="C303" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F303" s="5" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A304" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B304" s="1">
+        <v>9</v>
+      </c>
+      <c r="C304" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E304" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F304" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G304" s="5" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A305" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B305" s="1">
+        <v>9</v>
+      </c>
+      <c r="C305" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A306" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B306" s="1">
+        <v>9</v>
+      </c>
+      <c r="C306" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F306" s="5" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A307" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B307" s="1">
+        <v>9</v>
+      </c>
+      <c r="C307" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E307" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F307" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G307" s="5" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A308" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B308" s="1">
+        <v>9</v>
+      </c>
+      <c r="C308" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E308" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F308" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G308" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A309" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B309" s="1">
+        <v>9</v>
+      </c>
+      <c r="C309" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E309" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F309" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G309" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A310" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B310" s="1">
+        <v>9</v>
+      </c>
+      <c r="C310" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E300" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F300" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="G300" s="1" t="s">
-        <v>255</v>
+      <c r="E310" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F310" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G310" s="1" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -23178,12 +23321,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c3e85fef-df06-4e67-8632-489752715f52" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6fd297-1f65-4950-8fc9-157e29c7b648">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -23436,44 +23581,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c3e85fef-df06-4e67-8632-489752715f52" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6fd297-1f65-4950-8fc9-157e29c7b648">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171B3C16-7124-4B98-87E3-5FC6A9D45406}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D53AE126-6F09-4BBB-AD0C-4EFC39D23541}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ea6fd297-1f65-4950-8fc9-157e29c7b648"/>
-    <ds:schemaRef ds:uri="c3e85fef-df06-4e67-8632-489752715f52"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98411DB4-5541-4967-8DBE-AF3E324DD5F5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -23482,4 +23598,16 @@
     <ds:schemaRef ds:uri="ea6fd297-1f65-4950-8fc9-157e29c7b648"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63AE68CF-3AF3-4609-BB89-D5022CA6D284}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171B3C16-7124-4B98-87E3-5FC6A9D45406}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/dg_list.xlsx
+++ b/dg_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ialasia.sharepoint.com/sites/IALDGDESK/Shared Documents/General/Query System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="492" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DACCB27-4406-40A2-8E48-B9F924657734}"/>
+  <xr:revisionPtr revIDLastSave="495" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B3ED574-85D2-475F-B819-D0ED22D3A0AC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="27630" windowHeight="16440" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
   </bookViews>
   <sheets>
     <sheet name="IAL" sheetId="1" r:id="rId1"/>
@@ -1460,10 +1460,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1831,7 +1827,7 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="4">
         <v>1</v>
       </c>
       <c r="C2" s="3"/>
@@ -1843,7 +1839,7 @@
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="4">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1854,7 +1850,7 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="4">
         <v>1.2</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -1865,7 +1861,7 @@
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="4">
         <v>1.3</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -1876,7 +1872,7 @@
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="4">
         <v>1.4</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -1887,7 +1883,7 @@
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="4">
         <v>1.5</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -1898,7 +1894,7 @@
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="4">
         <v>1.6</v>
       </c>
       <c r="C8" s="1"/>
@@ -1910,7 +1906,7 @@
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="4">
         <v>2.1</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -1924,7 +1920,7 @@
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="4">
         <v>2.1</v>
       </c>
       <c r="C10" s="4">
@@ -1938,7 +1934,7 @@
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="4">
         <v>2.1</v>
       </c>
       <c r="C11" s="4">
@@ -1952,7 +1948,7 @@
       <c r="A12" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="4">
         <v>2.1</v>
       </c>
       <c r="C12" s="4">
@@ -1966,7 +1962,7 @@
       <c r="A13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="4">
         <v>2.1</v>
       </c>
       <c r="C13" s="4">
@@ -1980,7 +1976,7 @@
       <c r="A14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="4">
         <v>2.2000000000000002</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -1994,7 +1990,7 @@
       <c r="A15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="4">
         <v>2.2000000000000002</v>
       </c>
       <c r="C15" s="4">
@@ -2008,7 +2004,7 @@
       <c r="A16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="4">
         <v>2.2999999999999998</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -2019,7 +2015,7 @@
       <c r="A17" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="4">
         <v>3</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -2039,7 +2035,7 @@
       <c r="A18" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="4">
         <v>3</v>
       </c>
       <c r="C18" s="4">
@@ -2053,7 +2049,7 @@
       <c r="A19" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="4">
         <v>3</v>
       </c>
       <c r="C19" s="4">
@@ -2067,7 +2063,7 @@
       <c r="A20" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="4">
         <v>3</v>
       </c>
       <c r="C20" s="4">
@@ -2081,7 +2077,7 @@
       <c r="A21" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="4">
         <v>3</v>
       </c>
       <c r="C21" s="4">
@@ -2095,7 +2091,7 @@
       <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="4">
         <v>3</v>
       </c>
       <c r="C22" s="4">
@@ -2109,7 +2105,7 @@
       <c r="A23" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="4">
         <v>3</v>
       </c>
       <c r="C23" s="4">
@@ -2123,7 +2119,7 @@
       <c r="A24" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="4">
         <v>3</v>
       </c>
       <c r="C24" s="4">
@@ -2137,7 +2133,7 @@
       <c r="A25" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="4">
         <v>3</v>
       </c>
       <c r="C25" s="4">
@@ -2151,7 +2147,7 @@
       <c r="A26" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="4">
         <v>3</v>
       </c>
       <c r="C26" s="4">
@@ -2165,7 +2161,7 @@
       <c r="A27" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="4">
         <v>3</v>
       </c>
       <c r="C27" s="4">
@@ -2179,7 +2175,7 @@
       <c r="A28" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="4">
         <v>3</v>
       </c>
       <c r="C28" s="4">
@@ -2193,7 +2189,7 @@
       <c r="A29" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="4">
         <v>3</v>
       </c>
       <c r="C29" s="4">
@@ -2207,7 +2203,7 @@
       <c r="A30" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="4">
         <v>3</v>
       </c>
       <c r="C30" s="4">
@@ -2221,7 +2217,7 @@
       <c r="A31" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="4">
         <v>3</v>
       </c>
       <c r="C31" s="4">
@@ -2235,7 +2231,7 @@
       <c r="A32" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="4">
         <v>3</v>
       </c>
       <c r="C32" s="4">
@@ -2249,7 +2245,7 @@
       <c r="A33" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="4">
         <v>3</v>
       </c>
       <c r="C33" s="4">
@@ -2263,7 +2259,7 @@
       <c r="A34" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="4">
         <v>3</v>
       </c>
       <c r="C34" s="4">
@@ -2277,7 +2273,7 @@
       <c r="A35" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="4">
         <v>3</v>
       </c>
       <c r="C35" s="4">
@@ -2291,7 +2287,7 @@
       <c r="A36" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="4">
         <v>3</v>
       </c>
       <c r="C36" s="4">
@@ -2305,7 +2301,7 @@
       <c r="A37" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="4">
         <v>3</v>
       </c>
       <c r="C37" s="4">
@@ -2319,7 +2315,7 @@
       <c r="A38" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="4">
         <v>3</v>
       </c>
       <c r="C38" s="4">
@@ -2333,7 +2329,7 @@
       <c r="A39" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="4">
         <v>3</v>
       </c>
       <c r="C39" s="4">
@@ -2347,7 +2343,7 @@
       <c r="A40" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="4">
         <v>3</v>
       </c>
       <c r="C40" s="4">
@@ -2361,7 +2357,7 @@
       <c r="A41" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="4">
         <v>3</v>
       </c>
       <c r="C41" s="4">
@@ -2375,7 +2371,7 @@
       <c r="A42" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="4">
         <v>3</v>
       </c>
       <c r="C42" s="4">
@@ -2389,7 +2385,7 @@
       <c r="A43" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="4">
         <v>3</v>
       </c>
       <c r="C43" s="4">
@@ -2403,7 +2399,7 @@
       <c r="A44" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="4">
         <v>3</v>
       </c>
       <c r="C44" s="4">
@@ -2417,7 +2413,7 @@
       <c r="A45" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45" s="4">
         <v>3</v>
       </c>
       <c r="C45" s="4">
@@ -2431,7 +2427,7 @@
       <c r="A46" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="4">
         <v>3</v>
       </c>
       <c r="C46" s="4">
@@ -2445,7 +2441,7 @@
       <c r="A47" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="4">
         <v>3</v>
       </c>
       <c r="C47" s="4">
@@ -2459,7 +2455,7 @@
       <c r="A48" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" s="4">
         <v>3</v>
       </c>
       <c r="C48" s="4">
@@ -2473,7 +2469,7 @@
       <c r="A49" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49" s="4">
         <v>3</v>
       </c>
       <c r="C49" s="4">
@@ -2487,7 +2483,7 @@
       <c r="A50" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="4">
         <v>3</v>
       </c>
       <c r="C50" s="4">
@@ -2501,7 +2497,7 @@
       <c r="A51" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51" s="4">
         <v>3</v>
       </c>
       <c r="C51" s="4">
@@ -2515,7 +2511,7 @@
       <c r="A52" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B52" s="4">
         <v>3</v>
       </c>
       <c r="C52" s="4">
@@ -2529,7 +2525,7 @@
       <c r="A53" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="4">
         <v>3</v>
       </c>
       <c r="C53" s="4">
@@ -2543,7 +2539,7 @@
       <c r="A54" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54" s="4">
         <v>3</v>
       </c>
       <c r="C54" s="4">
@@ -2557,7 +2553,7 @@
       <c r="A55" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="4">
         <v>3</v>
       </c>
       <c r="C55" s="4">
@@ -2571,7 +2567,7 @@
       <c r="A56" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="4">
         <v>3</v>
       </c>
       <c r="C56" s="4">
@@ -2585,7 +2581,7 @@
       <c r="A57" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57" s="4">
         <v>3</v>
       </c>
       <c r="C57" s="4">
@@ -2599,7 +2595,7 @@
       <c r="A58" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B58" s="1">
+      <c r="B58" s="4">
         <v>3</v>
       </c>
       <c r="C58" s="4">
@@ -2613,7 +2609,7 @@
       <c r="A59" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B59" s="4">
         <v>3</v>
       </c>
       <c r="C59" s="4">
@@ -2627,7 +2623,7 @@
       <c r="A60" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B60" s="4">
         <v>3</v>
       </c>
       <c r="C60" s="4">
@@ -2641,7 +2637,7 @@
       <c r="A61" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61" s="4">
         <v>3</v>
       </c>
       <c r="C61" s="4">
@@ -2655,7 +2651,7 @@
       <c r="A62" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62" s="4">
         <v>3</v>
       </c>
       <c r="C62" s="4">
@@ -2669,7 +2665,7 @@
       <c r="A63" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63" s="4">
         <v>3</v>
       </c>
       <c r="C63" s="4">
@@ -2683,7 +2679,7 @@
       <c r="A64" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64" s="4">
         <v>3</v>
       </c>
       <c r="C64" s="4">
@@ -2697,7 +2693,7 @@
       <c r="A65" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65" s="4">
         <v>3</v>
       </c>
       <c r="C65" s="4">
@@ -2711,7 +2707,7 @@
       <c r="A66" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66" s="4">
         <v>3</v>
       </c>
       <c r="C66" s="4">
@@ -2725,7 +2721,7 @@
       <c r="A67" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="F67" s="1" t="s">
@@ -2739,7 +2735,7 @@
       <c r="A68" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C68" s="4">
@@ -2756,7 +2752,7 @@
       <c r="A69" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B69" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C69" s="4">
@@ -2770,7 +2766,7 @@
       <c r="A70" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C70" s="4">
@@ -2784,7 +2780,7 @@
       <c r="A71" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C71" s="4">
@@ -2798,7 +2794,7 @@
       <c r="A72" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B72" s="1">
+      <c r="B72" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C72" s="4">
@@ -2812,7 +2808,7 @@
       <c r="A73" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B73" s="1">
+      <c r="B73" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C73" s="4">
@@ -2826,7 +2822,7 @@
       <c r="A74" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B74" s="1">
+      <c r="B74" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C74" s="4">
@@ -2840,7 +2836,7 @@
       <c r="A75" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B75" s="1">
+      <c r="B75" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C75" s="4">
@@ -2854,7 +2850,7 @@
       <c r="A76" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B76" s="1">
+      <c r="B76" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C76" s="4">
@@ -2868,7 +2864,7 @@
       <c r="A77" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B77" s="1">
+      <c r="B77" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C77" s="4">
@@ -2882,7 +2878,7 @@
       <c r="A78" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C78" s="4">
@@ -2896,7 +2892,7 @@
       <c r="A79" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B79" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C79" s="4">
@@ -2910,7 +2906,7 @@
       <c r="A80" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B80" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C80" s="4">
@@ -2924,7 +2920,7 @@
       <c r="A81" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B81" s="1">
+      <c r="B81" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C81" s="4">
@@ -2938,7 +2934,7 @@
       <c r="A82" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B82" s="1">
+      <c r="B82" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C82" s="4">
@@ -2952,7 +2948,7 @@
       <c r="A83" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B83" s="1">
+      <c r="B83" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C83" s="4">
@@ -2966,7 +2962,7 @@
       <c r="A84" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B84" s="1">
+      <c r="B84" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C84" s="4">
@@ -2980,7 +2976,7 @@
       <c r="A85" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B85" s="1">
+      <c r="B85" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C85" s="4">
@@ -2994,7 +2990,7 @@
       <c r="A86" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B86" s="1">
+      <c r="B86" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C86" s="4">
@@ -3008,7 +3004,7 @@
       <c r="A87" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B87" s="1">
+      <c r="B87" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C87" s="4">
@@ -3022,7 +3018,7 @@
       <c r="A88" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B88" s="1">
+      <c r="B88" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C88" s="4">
@@ -3036,7 +3032,7 @@
       <c r="A89" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B89" s="1">
+      <c r="B89" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C89" s="4">
@@ -3050,7 +3046,7 @@
       <c r="A90" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B90" s="1">
+      <c r="B90" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C90" s="4">
@@ -3064,7 +3060,7 @@
       <c r="A91" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B91" s="1">
+      <c r="B91" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C91" s="4">
@@ -3078,7 +3074,7 @@
       <c r="A92" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B92" s="1">
+      <c r="B92" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C92" s="4">
@@ -3092,7 +3088,7 @@
       <c r="A93" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B93" s="1">
+      <c r="B93" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C93" s="4">
@@ -3106,7 +3102,7 @@
       <c r="A94" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B94" s="1">
+      <c r="B94" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C94" s="4">
@@ -3120,7 +3116,7 @@
       <c r="A95" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B95" s="1">
+      <c r="B95" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C95" s="4">
@@ -3134,7 +3130,7 @@
       <c r="A96" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B96" s="1">
+      <c r="B96" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C96" s="4">
@@ -3148,7 +3144,7 @@
       <c r="A97" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B97" s="1">
+      <c r="B97" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C97" s="4">
@@ -3162,7 +3158,7 @@
       <c r="A98" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B98" s="1">
+      <c r="B98" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C98" s="4">
@@ -3176,7 +3172,7 @@
       <c r="A99" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B99" s="1">
+      <c r="B99" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C99" s="4">
@@ -3190,7 +3186,7 @@
       <c r="A100" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B100" s="1">
+      <c r="B100" s="4">
         <v>4.2</v>
       </c>
       <c r="F100" s="1" t="s">
@@ -3204,7 +3200,7 @@
       <c r="A101" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B101" s="1">
+      <c r="B101" s="4">
         <v>4.2</v>
       </c>
       <c r="C101" s="4">
@@ -3221,7 +3217,7 @@
       <c r="A102" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B102" s="1">
+      <c r="B102" s="4">
         <v>4.2</v>
       </c>
       <c r="C102" s="4">
@@ -3238,7 +3234,7 @@
       <c r="A103" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B103" s="1">
+      <c r="B103" s="4">
         <v>4.2</v>
       </c>
       <c r="C103" s="4" t="s">
@@ -3252,7 +3248,7 @@
       <c r="A104" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B104" s="1">
+      <c r="B104" s="4">
         <v>4.2</v>
       </c>
       <c r="C104" s="4" t="s">
@@ -3266,7 +3262,7 @@
       <c r="A105" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B105" s="1">
+      <c r="B105" s="4">
         <v>4.2</v>
       </c>
       <c r="C105" s="4" t="s">
@@ -3280,7 +3276,7 @@
       <c r="A106" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B106" s="1">
+      <c r="B106" s="4">
         <v>4.2</v>
       </c>
       <c r="C106" s="4" t="s">
@@ -3294,7 +3290,7 @@
       <c r="A107" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B107" s="1">
+      <c r="B107" s="4">
         <v>4.2</v>
       </c>
       <c r="C107" s="4" t="s">
@@ -3308,7 +3304,7 @@
       <c r="A108" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B108" s="1">
+      <c r="B108" s="4">
         <v>4.2</v>
       </c>
       <c r="C108" s="4" t="s">
@@ -3322,7 +3318,7 @@
       <c r="A109" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B109" s="1">
+      <c r="B109" s="4">
         <v>4.2</v>
       </c>
       <c r="C109" s="4" t="s">
@@ -3336,7 +3332,7 @@
       <c r="A110" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B110" s="1">
+      <c r="B110" s="4">
         <v>4.2</v>
       </c>
       <c r="C110" s="4" t="s">
@@ -3350,7 +3346,7 @@
       <c r="A111" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B111" s="1">
+      <c r="B111" s="4">
         <v>4.2</v>
       </c>
       <c r="C111" s="4" t="s">
@@ -3364,7 +3360,7 @@
       <c r="A112" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B112" s="1">
+      <c r="B112" s="4">
         <v>4.2</v>
       </c>
       <c r="C112" s="4" t="s">
@@ -3378,7 +3374,7 @@
       <c r="A113" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B113" s="1">
+      <c r="B113" s="4">
         <v>4.2</v>
       </c>
       <c r="C113" s="4" t="s">
@@ -3392,7 +3388,7 @@
       <c r="A114" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B114" s="1">
+      <c r="B114" s="4">
         <v>4.2</v>
       </c>
       <c r="C114" s="4" t="s">
@@ -3406,7 +3402,7 @@
       <c r="A115" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B115" s="1">
+      <c r="B115" s="4">
         <v>4.2</v>
       </c>
       <c r="C115" s="4" t="s">
@@ -3420,7 +3416,7 @@
       <c r="A116" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B116" s="1">
+      <c r="B116" s="4">
         <v>4.2</v>
       </c>
       <c r="C116" s="4" t="s">
@@ -3434,7 +3430,7 @@
       <c r="A117" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B117" s="1">
+      <c r="B117" s="4">
         <v>4.2</v>
       </c>
       <c r="C117" s="4" t="s">
@@ -3448,7 +3444,7 @@
       <c r="A118" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B118" s="1">
+      <c r="B118" s="4">
         <v>4.2</v>
       </c>
       <c r="C118" s="4" t="s">
@@ -3462,7 +3458,7 @@
       <c r="A119" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B119" s="1">
+      <c r="B119" s="4">
         <v>4.2</v>
       </c>
       <c r="C119" s="4" t="s">
@@ -3476,7 +3472,7 @@
       <c r="A120" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B120" s="1">
+      <c r="B120" s="4">
         <v>4.2</v>
       </c>
       <c r="C120" s="4" t="s">
@@ -3490,7 +3486,7 @@
       <c r="A121" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B121" s="1">
+      <c r="B121" s="4">
         <v>4.2</v>
       </c>
       <c r="C121" s="4" t="s">
@@ -3504,7 +3500,7 @@
       <c r="A122" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B122" s="1">
+      <c r="B122" s="4">
         <v>4.2</v>
       </c>
       <c r="C122" s="4" t="s">
@@ -3518,7 +3514,7 @@
       <c r="A123" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B123" s="1">
+      <c r="B123" s="4">
         <v>4.2</v>
       </c>
       <c r="C123" s="4" t="s">
@@ -3532,7 +3528,7 @@
       <c r="A124" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B124" s="1">
+      <c r="B124" s="4">
         <v>4.2</v>
       </c>
       <c r="C124" s="4" t="s">
@@ -3546,7 +3542,7 @@
       <c r="A125" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B125" s="1">
+      <c r="B125" s="4">
         <v>4.2</v>
       </c>
       <c r="C125" s="4" t="s">
@@ -3560,7 +3556,7 @@
       <c r="A126" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B126" s="1">
+      <c r="B126" s="4">
         <v>4.2</v>
       </c>
       <c r="C126" s="4" t="s">
@@ -3574,7 +3570,7 @@
       <c r="A127" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B127" s="1">
+      <c r="B127" s="4">
         <v>4.2</v>
       </c>
       <c r="C127" s="4" t="s">
@@ -3588,7 +3584,7 @@
       <c r="A128" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B128" s="1">
+      <c r="B128" s="4">
         <v>4.2</v>
       </c>
       <c r="C128" s="4" t="s">
@@ -3602,7 +3598,7 @@
       <c r="A129" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B129" s="1">
+      <c r="B129" s="4">
         <v>4.2</v>
       </c>
       <c r="C129" s="4" t="s">
@@ -3616,7 +3612,7 @@
       <c r="A130" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B130" s="1">
+      <c r="B130" s="4">
         <v>4.2</v>
       </c>
       <c r="C130" s="4" t="s">
@@ -3630,7 +3626,7 @@
       <c r="A131" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B131" s="1">
+      <c r="B131" s="4">
         <v>4.2</v>
       </c>
       <c r="C131" s="4" t="s">
@@ -3644,7 +3640,7 @@
       <c r="A132" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B132" s="1">
+      <c r="B132" s="4">
         <v>4.2</v>
       </c>
       <c r="C132" s="4" t="s">
@@ -3658,7 +3654,7 @@
       <c r="A133" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B133" s="1">
+      <c r="B133" s="4">
         <v>4.2</v>
       </c>
       <c r="C133" s="4" t="s">
@@ -3672,7 +3668,7 @@
       <c r="A134" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B134" s="1">
+      <c r="B134" s="4">
         <v>4.3</v>
       </c>
       <c r="D134" s="1" t="s">
@@ -3683,7 +3679,7 @@
       <c r="A135" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B135" s="1">
+      <c r="B135" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="F135" s="1" t="s">
@@ -3697,7 +3693,7 @@
       <c r="A136" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B136" s="1">
+      <c r="B136" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C136" s="4" t="s">
@@ -3711,7 +3707,7 @@
       <c r="A137" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B137" s="1">
+      <c r="B137" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C137" s="4" t="s">
@@ -3725,7 +3721,7 @@
       <c r="A138" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B138" s="1">
+      <c r="B138" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C138" s="4" t="s">
@@ -3739,7 +3735,7 @@
       <c r="A139" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B139" s="1">
+      <c r="B139" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C139" s="4" t="s">
@@ -3753,7 +3749,7 @@
       <c r="A140" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B140" s="1">
+      <c r="B140" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C140" s="4" t="s">
@@ -3767,7 +3763,7 @@
       <c r="A141" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B141" s="1">
+      <c r="B141" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C141" s="4" t="s">
@@ -3781,7 +3777,7 @@
       <c r="A142" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B142" s="1">
+      <c r="B142" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C142" s="4" t="s">
@@ -3795,7 +3791,7 @@
       <c r="A143" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B143" s="1">
+      <c r="B143" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C143" s="4" t="s">
@@ -3809,7 +3805,7 @@
       <c r="A144" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B144" s="1">
+      <c r="B144" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C144" s="4" t="s">
@@ -3823,7 +3819,7 @@
       <c r="A145" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B145" s="1">
+      <c r="B145" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C145" s="4" t="s">
@@ -3837,7 +3833,7 @@
       <c r="A146" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B146" s="1">
+      <c r="B146" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C146" s="4" t="s">
@@ -3851,7 +3847,7 @@
       <c r="A147" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B147" s="1">
+      <c r="B147" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C147" s="4" t="s">
@@ -3865,7 +3861,7 @@
       <c r="A148" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B148" s="1">
+      <c r="B148" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C148" s="4" t="s">
@@ -3879,7 +3875,7 @@
       <c r="A149" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B149" s="1">
+      <c r="B149" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C149" s="4" t="s">
@@ -3893,7 +3889,7 @@
       <c r="A150" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B150" s="1">
+      <c r="B150" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C150" s="4" t="s">
@@ -3907,7 +3903,7 @@
       <c r="A151" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B151" s="1">
+      <c r="B151" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C151" s="4" t="s">
@@ -3921,7 +3917,7 @@
       <c r="A152" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B152" s="1">
+      <c r="B152" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C152" s="4" t="s">
@@ -3935,7 +3931,7 @@
       <c r="A153" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B153" s="1">
+      <c r="B153" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C153" s="4" t="s">
@@ -3949,7 +3945,7 @@
       <c r="A154" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B154" s="1">
+      <c r="B154" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C154" s="4" t="s">
@@ -3963,7 +3959,7 @@
       <c r="A155" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B155" s="1">
+      <c r="B155" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C155" s="4" t="s">
@@ -3977,7 +3973,7 @@
       <c r="A156" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B156" s="1">
+      <c r="B156" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C156" s="4" t="s">
@@ -3991,7 +3987,7 @@
       <c r="A157" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B157" s="1">
+      <c r="B157" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C157" s="4" t="s">
@@ -4005,7 +4001,7 @@
       <c r="A158" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B158" s="1">
+      <c r="B158" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C158" s="4" t="s">
@@ -4019,7 +4015,7 @@
       <c r="A159" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B159" s="1">
+      <c r="B159" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C159" s="4" t="s">
@@ -4033,7 +4029,7 @@
       <c r="A160" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B160" s="1">
+      <c r="B160" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C160" s="4" t="s">
@@ -4050,7 +4046,7 @@
       <c r="A161" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B161" s="1">
+      <c r="B161" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C161" s="4" t="s">
@@ -4064,7 +4060,7 @@
       <c r="A162" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B162" s="1">
+      <c r="B162" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C162" s="4" t="s">
@@ -4081,7 +4077,7 @@
       <c r="A163" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B163" s="1">
+      <c r="B163" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C163" s="4" t="s">
@@ -4095,7 +4091,7 @@
       <c r="A164" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B164" s="1">
+      <c r="B164" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C164" s="4" t="s">
@@ -4109,7 +4105,7 @@
       <c r="A165" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B165" s="1">
+      <c r="B165" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C165" s="4" t="s">
@@ -4123,7 +4119,7 @@
       <c r="A166" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B166" s="1">
+      <c r="B166" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C166" s="4" t="s">
@@ -4137,7 +4133,7 @@
       <c r="A167" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B167" s="1">
+      <c r="B167" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C167" s="4" t="s">
@@ -4151,7 +4147,7 @@
       <c r="A168" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B168" s="1">
+      <c r="B168" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C168" s="4" t="s">
@@ -4165,7 +4161,7 @@
       <c r="A169" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B169" s="1">
+      <c r="B169" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C169" s="4" t="s">
@@ -4179,7 +4175,7 @@
       <c r="A170" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B170" s="1">
+      <c r="B170" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C170" s="4" t="s">
@@ -4193,7 +4189,7 @@
       <c r="A171" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B171" s="1">
+      <c r="B171" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C171" s="4" t="s">
@@ -4207,7 +4203,7 @@
       <c r="A172" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B172" s="1">
+      <c r="B172" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C172" s="4" t="s">
@@ -4221,7 +4217,7 @@
       <c r="A173" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B173" s="1">
+      <c r="B173" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C173" s="4" t="s">
@@ -4235,7 +4231,7 @@
       <c r="A174" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B174" s="1">
+      <c r="B174" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C174" s="4" t="s">
@@ -4249,7 +4245,7 @@
       <c r="A175" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B175" s="1">
+      <c r="B175" s="4">
         <v>5.2</v>
       </c>
       <c r="D175" s="1" t="s">
@@ -4260,7 +4256,7 @@
       <c r="A176" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B176" s="1">
+      <c r="B176" s="4">
         <v>6.1</v>
       </c>
       <c r="F176" s="1" t="s">
@@ -4271,7 +4267,7 @@
       <c r="A177" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B177" s="1">
+      <c r="B177" s="4">
         <v>6.1</v>
       </c>
       <c r="C177" s="4" t="s">
@@ -4285,7 +4281,7 @@
       <c r="A178" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B178" s="1">
+      <c r="B178" s="4">
         <v>6.1</v>
       </c>
       <c r="C178" s="4" t="s">
@@ -4299,7 +4295,7 @@
       <c r="A179" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B179" s="1">
+      <c r="B179" s="4">
         <v>6.1</v>
       </c>
       <c r="C179" s="4" t="s">
@@ -4313,7 +4309,7 @@
       <c r="A180" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B180" s="1">
+      <c r="B180" s="4">
         <v>6.1</v>
       </c>
       <c r="C180" s="4" t="s">
@@ -4327,7 +4323,7 @@
       <c r="A181" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B181" s="1">
+      <c r="B181" s="4">
         <v>6.1</v>
       </c>
       <c r="C181" s="4" t="s">
@@ -4341,7 +4337,7 @@
       <c r="A182" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B182" s="1">
+      <c r="B182" s="4">
         <v>6.1</v>
       </c>
       <c r="C182" s="4" t="s">
@@ -4355,7 +4351,7 @@
       <c r="A183" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B183" s="1">
+      <c r="B183" s="4">
         <v>6.1</v>
       </c>
       <c r="C183" s="4" t="s">
@@ -4372,7 +4368,7 @@
       <c r="A184" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B184" s="1">
+      <c r="B184" s="4">
         <v>6.1</v>
       </c>
       <c r="C184" s="4" t="s">
@@ -4389,7 +4385,7 @@
       <c r="A185" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B185" s="1">
+      <c r="B185" s="4">
         <v>6.1</v>
       </c>
       <c r="C185" s="4" t="s">
@@ -4403,7 +4399,7 @@
       <c r="A186" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B186" s="1">
+      <c r="B186" s="4">
         <v>6.1</v>
       </c>
       <c r="C186" s="4" t="s">
@@ -4417,7 +4413,7 @@
       <c r="A187" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B187" s="1">
+      <c r="B187" s="4">
         <v>6.1</v>
       </c>
       <c r="C187" s="4" t="s">
@@ -4431,7 +4427,7 @@
       <c r="A188" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B188" s="1">
+      <c r="B188" s="4">
         <v>6.1</v>
       </c>
       <c r="C188" s="4" t="s">
@@ -4445,7 +4441,7 @@
       <c r="A189" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B189" s="1">
+      <c r="B189" s="4">
         <v>6.1</v>
       </c>
       <c r="C189" s="4" t="s">
@@ -4459,7 +4455,7 @@
       <c r="A190" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B190" s="1">
+      <c r="B190" s="4">
         <v>6.1</v>
       </c>
       <c r="C190" s="4" t="s">
@@ -4473,7 +4469,7 @@
       <c r="A191" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B191" s="1">
+      <c r="B191" s="4">
         <v>6.1</v>
       </c>
       <c r="C191" s="4" t="s">
@@ -4487,7 +4483,7 @@
       <c r="A192" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B192" s="1">
+      <c r="B192" s="4">
         <v>6.1</v>
       </c>
       <c r="C192" s="4" t="s">
@@ -4501,7 +4497,7 @@
       <c r="A193" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B193" s="1">
+      <c r="B193" s="4">
         <v>6.2</v>
       </c>
       <c r="D193" s="1" t="s">
@@ -4512,7 +4508,7 @@
       <c r="A194" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B194" s="1">
+      <c r="B194" s="4">
         <v>7</v>
       </c>
       <c r="D194" s="1" t="s">
@@ -4523,7 +4519,7 @@
       <c r="A195" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B195" s="1">
+      <c r="B195" s="4">
         <v>8</v>
       </c>
       <c r="F195" s="1" t="s">
@@ -4537,7 +4533,7 @@
       <c r="A196" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B196" s="1">
+      <c r="B196" s="4">
         <v>8</v>
       </c>
       <c r="C196" s="4" t="s">
@@ -4551,7 +4547,7 @@
       <c r="A197" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B197" s="1">
+      <c r="B197" s="4">
         <v>8</v>
       </c>
       <c r="C197" s="4" t="s">
@@ -4565,7 +4561,7 @@
       <c r="A198" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B198" s="1">
+      <c r="B198" s="4">
         <v>8</v>
       </c>
       <c r="C198" s="4" t="s">
@@ -4579,7 +4575,7 @@
       <c r="A199" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B199" s="1">
+      <c r="B199" s="4">
         <v>8</v>
       </c>
       <c r="C199" s="4" t="s">
@@ -4593,7 +4589,7 @@
       <c r="A200" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B200" s="1">
+      <c r="B200" s="4">
         <v>8</v>
       </c>
       <c r="C200" s="4" t="s">
@@ -4613,7 +4609,7 @@
       <c r="A201" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B201" s="1">
+      <c r="B201" s="4">
         <v>8</v>
       </c>
       <c r="C201" s="4" t="s">
@@ -4627,7 +4623,7 @@
       <c r="A202" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B202" s="1">
+      <c r="B202" s="4">
         <v>8</v>
       </c>
       <c r="C202" s="4" t="s">
@@ -4641,7 +4637,7 @@
       <c r="A203" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B203" s="1">
+      <c r="B203" s="4">
         <v>8</v>
       </c>
       <c r="C203" s="4" t="s">
@@ -4655,7 +4651,7 @@
       <c r="A204" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B204" s="1">
+      <c r="B204" s="4">
         <v>8</v>
       </c>
       <c r="C204" s="4" t="s">
@@ -4672,7 +4668,7 @@
       <c r="A205" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B205" s="1">
+      <c r="B205" s="4">
         <v>9</v>
       </c>
       <c r="F205" s="1" t="s">
@@ -4686,7 +4682,7 @@
       <c r="A206" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B206" s="1">
+      <c r="B206" s="4">
         <v>9</v>
       </c>
       <c r="C206" s="4" t="s">
@@ -4700,7 +4696,7 @@
       <c r="A207" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B207" s="1">
+      <c r="B207" s="4">
         <v>9</v>
       </c>
       <c r="C207" s="4" t="s">
@@ -4714,7 +4710,7 @@
       <c r="A208" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B208" s="1">
+      <c r="B208" s="4">
         <v>9</v>
       </c>
       <c r="C208" s="4" t="s">
@@ -4728,7 +4724,7 @@
       <c r="A209" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B209" s="1">
+      <c r="B209" s="4">
         <v>9</v>
       </c>
       <c r="C209" s="4" t="s">
@@ -4751,7 +4747,7 @@
       <c r="A210" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B210" s="1">
+      <c r="B210" s="4">
         <v>9</v>
       </c>
       <c r="C210" s="4" t="s">
@@ -4774,7 +4770,7 @@
       <c r="A211" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B211" s="1">
+      <c r="B211" s="4">
         <v>9</v>
       </c>
       <c r="C211" s="4" t="s">
@@ -4788,7 +4784,7 @@
       <c r="A212" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B212" s="1">
+      <c r="B212" s="4">
         <v>9</v>
       </c>
       <c r="C212" s="4" t="s">
@@ -4802,7 +4798,7 @@
       <c r="A213" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B213" s="1">
+      <c r="B213" s="4">
         <v>9</v>
       </c>
       <c r="C213" s="4" t="s">
@@ -4822,7 +4818,7 @@
       <c r="A214" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B214" s="1">
+      <c r="B214" s="4">
         <v>9</v>
       </c>
       <c r="C214" s="4" t="s">
@@ -4836,7 +4832,7 @@
       <c r="A215" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B215" s="1">
+      <c r="B215" s="4">
         <v>9</v>
       </c>
       <c r="C215" s="4" t="s">
@@ -4853,7 +4849,7 @@
       <c r="A216" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B216" s="1">
+      <c r="B216" s="4">
         <v>9</v>
       </c>
       <c r="C216" s="4" t="s">
@@ -4879,7 +4875,7 @@
       <c r="A217" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B217" s="1">
+      <c r="B217" s="4">
         <v>9</v>
       </c>
       <c r="C217" s="4" t="s">
@@ -4893,7 +4889,7 @@
       <c r="A218" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B218" s="1">
+      <c r="B218" s="4">
         <v>9</v>
       </c>
       <c r="C218" s="4" t="s">
@@ -4910,7 +4906,7 @@
       <c r="A219" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B219" s="1">
+      <c r="B219" s="4">
         <v>9</v>
       </c>
       <c r="C219" s="4" t="s">
@@ -4936,7 +4932,7 @@
       <c r="A220" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B220" s="1">
+      <c r="B220" s="4">
         <v>9</v>
       </c>
       <c r="C220" s="4" t="s">
@@ -4953,7 +4949,7 @@
       <c r="A221" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B221" s="1">
+      <c r="B221" s="4">
         <v>9</v>
       </c>
       <c r="C221" s="4" t="s">
@@ -4970,7 +4966,7 @@
       <c r="A222" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B222" s="1">
+      <c r="B222" s="4">
         <v>9</v>
       </c>
       <c r="C222" s="4" t="s">
@@ -5035,7 +5031,7 @@
       <c r="A2" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="4">
         <v>1</v>
       </c>
       <c r="C2" s="3"/>
@@ -5047,7 +5043,7 @@
       <c r="A3" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="4">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -5058,7 +5054,7 @@
       <c r="A4" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="4">
         <v>1.2</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -5069,7 +5065,7 @@
       <c r="A5" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="4">
         <v>1.3</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -5080,7 +5076,7 @@
       <c r="A6" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="4">
         <v>1.4</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -5091,7 +5087,7 @@
       <c r="A7" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="4">
         <v>1.5</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -5102,7 +5098,7 @@
       <c r="A8" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="4">
         <v>1.6</v>
       </c>
       <c r="C8" s="1"/>
@@ -5114,7 +5110,7 @@
       <c r="A9" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="4">
         <v>2.1</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -5128,7 +5124,7 @@
       <c r="A10" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="4">
         <v>2.1</v>
       </c>
       <c r="C10" s="4">
@@ -5142,7 +5138,7 @@
       <c r="A11" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="4">
         <v>2.1</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -5159,7 +5155,7 @@
       <c r="A12" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="4">
         <v>2.1</v>
       </c>
       <c r="C12" s="4">
@@ -5173,7 +5169,7 @@
       <c r="A13" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="4">
         <v>2.1</v>
       </c>
       <c r="C13" s="4">
@@ -5187,7 +5183,7 @@
       <c r="A14" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="4">
         <v>2.1</v>
       </c>
       <c r="C14" s="4">
@@ -5201,7 +5197,7 @@
       <c r="A15" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="4">
         <v>2.1</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -5218,7 +5214,7 @@
       <c r="A16" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="4">
         <v>2.2000000000000002</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -5232,7 +5228,7 @@
       <c r="A17" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="4">
         <v>2.2000000000000002</v>
       </c>
       <c r="C17" s="4" t="s">
@@ -5249,7 +5245,7 @@
       <c r="A18" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="4">
         <v>2.2000000000000002</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -5266,7 +5262,7 @@
       <c r="A19" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="4">
         <v>2.2000000000000002</v>
       </c>
       <c r="C19" s="4">
@@ -5280,7 +5276,7 @@
       <c r="A20" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="4">
         <v>2.2999999999999998</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -5291,7 +5287,7 @@
       <c r="A21" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="4">
         <v>3</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -5305,7 +5301,7 @@
       <c r="A22" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="4">
         <v>3</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -5319,7 +5315,7 @@
       <c r="A23" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="4">
         <v>3</v>
       </c>
       <c r="C23" s="4">
@@ -5333,7 +5329,7 @@
       <c r="A24" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="4">
         <v>3</v>
       </c>
       <c r="C24" s="4">
@@ -5347,7 +5343,7 @@
       <c r="A25" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="4">
         <v>3</v>
       </c>
       <c r="C25" s="4">
@@ -5361,7 +5357,7 @@
       <c r="A26" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="4">
         <v>3</v>
       </c>
       <c r="C26" s="4">
@@ -5375,7 +5371,7 @@
       <c r="A27" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="4">
         <v>3</v>
       </c>
       <c r="C27" s="4">
@@ -5389,7 +5385,7 @@
       <c r="A28" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="4">
         <v>3</v>
       </c>
       <c r="C28" s="4" t="s">
@@ -5403,7 +5399,7 @@
       <c r="A29" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="4">
         <v>3</v>
       </c>
       <c r="C29" s="4">
@@ -5417,7 +5413,7 @@
       <c r="A30" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="4">
         <v>3</v>
       </c>
       <c r="C30" s="4">
@@ -5431,7 +5427,7 @@
       <c r="A31" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="4">
         <v>3</v>
       </c>
       <c r="C31" s="4">
@@ -5445,7 +5441,7 @@
       <c r="A32" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="4">
         <v>3</v>
       </c>
       <c r="C32" s="4">
@@ -5459,7 +5455,7 @@
       <c r="A33" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="4">
         <v>3</v>
       </c>
       <c r="C33" s="4">
@@ -5473,7 +5469,7 @@
       <c r="A34" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="4">
         <v>3</v>
       </c>
       <c r="C34" s="4">
@@ -5487,7 +5483,7 @@
       <c r="A35" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="4">
         <v>3</v>
       </c>
       <c r="C35" s="4">
@@ -5501,7 +5497,7 @@
       <c r="A36" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="4">
         <v>3</v>
       </c>
       <c r="C36" s="4">
@@ -5515,7 +5511,7 @@
       <c r="A37" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="4">
         <v>3</v>
       </c>
       <c r="C37" s="4">
@@ -5529,7 +5525,7 @@
       <c r="A38" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="4">
         <v>3</v>
       </c>
       <c r="C38" s="4" t="s">
@@ -5543,7 +5539,7 @@
       <c r="A39" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="4">
         <v>3</v>
       </c>
       <c r="C39" s="4">
@@ -5557,7 +5553,7 @@
       <c r="A40" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="4">
         <v>3</v>
       </c>
       <c r="C40" s="4">
@@ -5571,7 +5567,7 @@
       <c r="A41" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="4">
         <v>3</v>
       </c>
       <c r="C41" s="4">
@@ -5585,7 +5581,7 @@
       <c r="A42" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="4">
         <v>3</v>
       </c>
       <c r="C42" s="4">
@@ -5599,7 +5595,7 @@
       <c r="A43" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="4">
         <v>3</v>
       </c>
       <c r="C43" s="4">
@@ -5613,7 +5609,7 @@
       <c r="A44" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="4">
         <v>3</v>
       </c>
       <c r="C44" s="4">
@@ -5627,7 +5623,7 @@
       <c r="A45" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45" s="4">
         <v>3</v>
       </c>
       <c r="C45" s="4">
@@ -5641,7 +5637,7 @@
       <c r="A46" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="4">
         <v>3</v>
       </c>
       <c r="C46" s="4">
@@ -5655,7 +5651,7 @@
       <c r="A47" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="4">
         <v>3</v>
       </c>
       <c r="C47" s="4">
@@ -5669,7 +5665,7 @@
       <c r="A48" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" s="4">
         <v>3</v>
       </c>
       <c r="C48" s="4">
@@ -5683,7 +5679,7 @@
       <c r="A49" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49" s="4">
         <v>3</v>
       </c>
       <c r="C49" s="4">
@@ -5697,7 +5693,7 @@
       <c r="A50" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="4">
         <v>3</v>
       </c>
       <c r="C50" s="4">
@@ -5711,7 +5707,7 @@
       <c r="A51" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51" s="4">
         <v>3</v>
       </c>
       <c r="C51" s="4">
@@ -5725,7 +5721,7 @@
       <c r="A52" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B52" s="4">
         <v>3</v>
       </c>
       <c r="C52" s="4">
@@ -5739,7 +5735,7 @@
       <c r="A53" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="4">
         <v>3</v>
       </c>
       <c r="C53" s="4">
@@ -5753,7 +5749,7 @@
       <c r="A54" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54" s="4">
         <v>3</v>
       </c>
       <c r="C54" s="4">
@@ -5767,7 +5763,7 @@
       <c r="A55" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="4">
         <v>3</v>
       </c>
       <c r="C55" s="4">
@@ -5781,7 +5777,7 @@
       <c r="A56" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="4">
         <v>3</v>
       </c>
       <c r="C56" s="4">
@@ -5795,7 +5791,7 @@
       <c r="A57" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57" s="4">
         <v>3</v>
       </c>
       <c r="C57" s="4">
@@ -5809,7 +5805,7 @@
       <c r="A58" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B58" s="1">
+      <c r="B58" s="4">
         <v>3</v>
       </c>
       <c r="C58" s="4">
@@ -5823,7 +5819,7 @@
       <c r="A59" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B59" s="4">
         <v>3</v>
       </c>
       <c r="C59" s="4">
@@ -5837,7 +5833,7 @@
       <c r="A60" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B60" s="4">
         <v>3</v>
       </c>
       <c r="C60" s="4">
@@ -5851,7 +5847,7 @@
       <c r="A61" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61" s="4">
         <v>3</v>
       </c>
       <c r="C61" s="4">
@@ -5865,7 +5861,7 @@
       <c r="A62" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62" s="4">
         <v>3</v>
       </c>
       <c r="C62" s="4">
@@ -5879,7 +5875,7 @@
       <c r="A63" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63" s="4">
         <v>3</v>
       </c>
       <c r="C63" s="4">
@@ -5893,7 +5889,7 @@
       <c r="A64" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64" s="4">
         <v>3</v>
       </c>
       <c r="C64" s="4">
@@ -5907,7 +5903,7 @@
       <c r="A65" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65" s="4">
         <v>3</v>
       </c>
       <c r="C65" s="4">
@@ -5921,7 +5917,7 @@
       <c r="A66" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66" s="4">
         <v>3</v>
       </c>
       <c r="C66" s="4">
@@ -5935,7 +5931,7 @@
       <c r="A67" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67" s="4">
         <v>3</v>
       </c>
       <c r="C67" s="4">
@@ -5949,7 +5945,7 @@
       <c r="A68" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68" s="4">
         <v>3</v>
       </c>
       <c r="C68" s="4">
@@ -5963,7 +5959,7 @@
       <c r="A69" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B69" s="4">
         <v>3</v>
       </c>
       <c r="C69" s="4">
@@ -5977,7 +5973,7 @@
       <c r="A70" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70" s="4">
         <v>3</v>
       </c>
       <c r="C70" s="4">
@@ -5991,7 +5987,7 @@
       <c r="A71" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71" s="4">
         <v>3</v>
       </c>
       <c r="C71" s="4">
@@ -6005,7 +6001,7 @@
       <c r="A72" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B72" s="1">
+      <c r="B72" s="4">
         <v>3</v>
       </c>
       <c r="C72" s="4">
@@ -6019,7 +6015,7 @@
       <c r="A73" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B73" s="1">
+      <c r="B73" s="4">
         <v>3</v>
       </c>
       <c r="C73" s="4">
@@ -6033,7 +6029,7 @@
       <c r="A74" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B74" s="1">
+      <c r="B74" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="F74" s="1" t="s">
@@ -6047,7 +6043,7 @@
       <c r="A75" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B75" s="1">
+      <c r="B75" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C75" s="4">
@@ -6064,7 +6060,7 @@
       <c r="A76" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B76" s="1">
+      <c r="B76" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C76" s="4" t="s">
@@ -6078,7 +6074,7 @@
       <c r="A77" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B77" s="1">
+      <c r="B77" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C77" s="4">
@@ -6092,7 +6088,7 @@
       <c r="A78" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C78" s="4">
@@ -6106,7 +6102,7 @@
       <c r="A79" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B79" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C79" s="4">
@@ -6120,7 +6116,7 @@
       <c r="A80" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B80" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C80" s="4">
@@ -6134,7 +6130,7 @@
       <c r="A81" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B81" s="1">
+      <c r="B81" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C81" s="4">
@@ -6148,7 +6144,7 @@
       <c r="A82" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B82" s="1">
+      <c r="B82" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C82" s="4">
@@ -6162,7 +6158,7 @@
       <c r="A83" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B83" s="1">
+      <c r="B83" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C83" s="4">
@@ -6176,7 +6172,7 @@
       <c r="A84" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B84" s="1">
+      <c r="B84" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C84" s="4">
@@ -6190,7 +6186,7 @@
       <c r="A85" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B85" s="1">
+      <c r="B85" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C85" s="4">
@@ -6204,7 +6200,7 @@
       <c r="A86" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B86" s="1">
+      <c r="B86" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C86" s="4">
@@ -6218,7 +6214,7 @@
       <c r="A87" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B87" s="1">
+      <c r="B87" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C87" s="4">
@@ -6232,7 +6228,7 @@
       <c r="A88" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B88" s="1">
+      <c r="B88" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C88" s="4">
@@ -6246,7 +6242,7 @@
       <c r="A89" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B89" s="1">
+      <c r="B89" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C89" s="4">
@@ -6260,7 +6256,7 @@
       <c r="A90" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B90" s="1">
+      <c r="B90" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C90" s="4">
@@ -6274,7 +6270,7 @@
       <c r="A91" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B91" s="1">
+      <c r="B91" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C91" s="4">
@@ -6288,7 +6284,7 @@
       <c r="A92" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B92" s="1">
+      <c r="B92" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C92" s="4">
@@ -6302,7 +6298,7 @@
       <c r="A93" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B93" s="1">
+      <c r="B93" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C93" s="4">
@@ -6316,7 +6312,7 @@
       <c r="A94" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B94" s="1">
+      <c r="B94" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C94" s="4">
@@ -6330,7 +6326,7 @@
       <c r="A95" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B95" s="1">
+      <c r="B95" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C95" s="4">
@@ -6344,7 +6340,7 @@
       <c r="A96" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B96" s="1">
+      <c r="B96" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C96" s="4">
@@ -6358,7 +6354,7 @@
       <c r="A97" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B97" s="1">
+      <c r="B97" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C97" s="4">
@@ -6372,7 +6368,7 @@
       <c r="A98" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B98" s="1">
+      <c r="B98" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C98" s="4">
@@ -6386,7 +6382,7 @@
       <c r="A99" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B99" s="1">
+      <c r="B99" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C99" s="4">
@@ -6400,7 +6396,7 @@
       <c r="A100" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B100" s="1">
+      <c r="B100" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C100" s="4">
@@ -6414,7 +6410,7 @@
       <c r="A101" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B101" s="1">
+      <c r="B101" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C101" s="4">
@@ -6428,7 +6424,7 @@
       <c r="A102" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B102" s="1">
+      <c r="B102" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C102" s="4">
@@ -6442,7 +6438,7 @@
       <c r="A103" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B103" s="1">
+      <c r="B103" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C103" s="4">
@@ -6456,7 +6452,7 @@
       <c r="A104" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B104" s="1">
+      <c r="B104" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C104" s="4">
@@ -6470,7 +6466,7 @@
       <c r="A105" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B105" s="1">
+      <c r="B105" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C105" s="4">
@@ -6484,7 +6480,7 @@
       <c r="A106" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B106" s="1">
+      <c r="B106" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C106" s="4">
@@ -6498,7 +6494,7 @@
       <c r="A107" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B107" s="1">
+      <c r="B107" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C107" s="4">
@@ -6512,7 +6508,7 @@
       <c r="A108" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B108" s="1">
+      <c r="B108" s="4">
         <v>4.2</v>
       </c>
       <c r="F108" s="1" t="s">
@@ -6526,7 +6522,7 @@
       <c r="A109" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B109" s="1">
+      <c r="B109" s="4">
         <v>4.2</v>
       </c>
       <c r="C109" s="4">
@@ -6543,7 +6539,7 @@
       <c r="A110" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B110" s="1">
+      <c r="B110" s="4">
         <v>4.2</v>
       </c>
       <c r="C110" s="4">
@@ -6560,7 +6556,7 @@
       <c r="A111" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B111" s="1">
+      <c r="B111" s="4">
         <v>4.2</v>
       </c>
       <c r="C111" s="4" t="s">
@@ -6574,7 +6570,7 @@
       <c r="A112" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B112" s="1">
+      <c r="B112" s="4">
         <v>4.2</v>
       </c>
       <c r="C112" s="4" t="s">
@@ -6588,7 +6584,7 @@
       <c r="A113" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B113" s="1">
+      <c r="B113" s="4">
         <v>4.2</v>
       </c>
       <c r="C113" s="4" t="s">
@@ -6602,7 +6598,7 @@
       <c r="A114" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B114" s="1">
+      <c r="B114" s="4">
         <v>4.2</v>
       </c>
       <c r="C114" s="4" t="s">
@@ -6616,7 +6612,7 @@
       <c r="A115" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B115" s="1">
+      <c r="B115" s="4">
         <v>4.2</v>
       </c>
       <c r="C115" s="4" t="s">
@@ -6630,7 +6626,7 @@
       <c r="A116" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B116" s="1">
+      <c r="B116" s="4">
         <v>4.2</v>
       </c>
       <c r="C116" s="4" t="s">
@@ -6644,7 +6640,7 @@
       <c r="A117" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B117" s="1">
+      <c r="B117" s="4">
         <v>4.2</v>
       </c>
       <c r="C117" s="4" t="s">
@@ -6658,7 +6654,7 @@
       <c r="A118" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B118" s="1">
+      <c r="B118" s="4">
         <v>4.2</v>
       </c>
       <c r="C118" s="4" t="s">
@@ -6672,7 +6668,7 @@
       <c r="A119" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B119" s="1">
+      <c r="B119" s="4">
         <v>4.2</v>
       </c>
       <c r="C119" s="4" t="s">
@@ -6686,7 +6682,7 @@
       <c r="A120" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B120" s="1">
+      <c r="B120" s="4">
         <v>4.2</v>
       </c>
       <c r="C120" s="4" t="s">
@@ -6700,7 +6696,7 @@
       <c r="A121" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B121" s="1">
+      <c r="B121" s="4">
         <v>4.2</v>
       </c>
       <c r="C121" s="4" t="s">
@@ -6714,7 +6710,7 @@
       <c r="A122" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B122" s="1">
+      <c r="B122" s="4">
         <v>4.2</v>
       </c>
       <c r="C122" s="4" t="s">
@@ -6728,7 +6724,7 @@
       <c r="A123" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B123" s="1">
+      <c r="B123" s="4">
         <v>4.2</v>
       </c>
       <c r="C123" s="4" t="s">
@@ -6742,7 +6738,7 @@
       <c r="A124" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B124" s="1">
+      <c r="B124" s="4">
         <v>4.2</v>
       </c>
       <c r="C124" s="4" t="s">
@@ -6756,7 +6752,7 @@
       <c r="A125" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B125" s="1">
+      <c r="B125" s="4">
         <v>4.2</v>
       </c>
       <c r="C125" s="4" t="s">
@@ -6770,7 +6766,7 @@
       <c r="A126" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B126" s="1">
+      <c r="B126" s="4">
         <v>4.2</v>
       </c>
       <c r="C126" s="4" t="s">
@@ -6784,7 +6780,7 @@
       <c r="A127" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B127" s="1">
+      <c r="B127" s="4">
         <v>4.2</v>
       </c>
       <c r="C127" s="4" t="s">
@@ -6798,7 +6794,7 @@
       <c r="A128" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B128" s="1">
+      <c r="B128" s="4">
         <v>4.2</v>
       </c>
       <c r="C128" s="4" t="s">
@@ -6812,7 +6808,7 @@
       <c r="A129" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B129" s="1">
+      <c r="B129" s="4">
         <v>4.2</v>
       </c>
       <c r="C129" s="4" t="s">
@@ -6826,7 +6822,7 @@
       <c r="A130" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B130" s="1">
+      <c r="B130" s="4">
         <v>4.2</v>
       </c>
       <c r="C130" s="4" t="s">
@@ -6840,7 +6836,7 @@
       <c r="A131" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B131" s="1">
+      <c r="B131" s="4">
         <v>4.2</v>
       </c>
       <c r="C131" s="4" t="s">
@@ -6854,7 +6850,7 @@
       <c r="A132" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B132" s="1">
+      <c r="B132" s="4">
         <v>4.2</v>
       </c>
       <c r="C132" s="4" t="s">
@@ -6868,7 +6864,7 @@
       <c r="A133" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B133" s="1">
+      <c r="B133" s="4">
         <v>4.2</v>
       </c>
       <c r="C133" s="4" t="s">
@@ -6882,7 +6878,7 @@
       <c r="A134" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B134" s="1">
+      <c r="B134" s="4">
         <v>4.2</v>
       </c>
       <c r="C134" s="4" t="s">
@@ -6896,7 +6892,7 @@
       <c r="A135" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B135" s="1">
+      <c r="B135" s="4">
         <v>4.2</v>
       </c>
       <c r="C135" s="4" t="s">
@@ -6910,7 +6906,7 @@
       <c r="A136" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B136" s="1">
+      <c r="B136" s="4">
         <v>4.2</v>
       </c>
       <c r="C136" s="4" t="s">
@@ -6924,7 +6920,7 @@
       <c r="A137" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B137" s="1">
+      <c r="B137" s="4">
         <v>4.2</v>
       </c>
       <c r="C137" s="4" t="s">
@@ -6938,7 +6934,7 @@
       <c r="A138" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B138" s="1">
+      <c r="B138" s="4">
         <v>4.2</v>
       </c>
       <c r="C138" s="4" t="s">
@@ -6952,7 +6948,7 @@
       <c r="A139" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B139" s="1">
+      <c r="B139" s="4">
         <v>4.2</v>
       </c>
       <c r="C139" s="4" t="s">
@@ -6966,7 +6962,7 @@
       <c r="A140" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B140" s="1">
+      <c r="B140" s="4">
         <v>4.2</v>
       </c>
       <c r="C140" s="4" t="s">
@@ -6980,7 +6976,7 @@
       <c r="A141" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B141" s="1">
+      <c r="B141" s="4">
         <v>4.2</v>
       </c>
       <c r="C141" s="4" t="s">
@@ -6994,7 +6990,7 @@
       <c r="A142" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B142" s="1">
+      <c r="B142" s="4">
         <v>4.3</v>
       </c>
       <c r="F142" s="1" t="s">
@@ -7008,7 +7004,7 @@
       <c r="A143" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B143" s="1">
+      <c r="B143" s="4">
         <v>4.3</v>
       </c>
       <c r="C143" s="4" t="s">
@@ -7022,7 +7018,7 @@
       <c r="A144" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B144" s="1">
+      <c r="B144" s="4">
         <v>4.3</v>
       </c>
       <c r="C144" s="4" t="s">
@@ -7036,7 +7032,7 @@
       <c r="A145" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B145" s="1">
+      <c r="B145" s="4">
         <v>4.3</v>
       </c>
       <c r="C145" s="4" t="s">
@@ -7050,7 +7046,7 @@
       <c r="A146" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B146" s="1">
+      <c r="B146" s="4">
         <v>4.3</v>
       </c>
       <c r="C146" s="4" t="s">
@@ -7064,7 +7060,7 @@
       <c r="A147" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B147" s="1">
+      <c r="B147" s="4">
         <v>4.3</v>
       </c>
       <c r="C147" s="4" t="s">
@@ -7078,7 +7074,7 @@
       <c r="A148" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B148" s="1">
+      <c r="B148" s="4">
         <v>4.3</v>
       </c>
       <c r="C148" s="4" t="s">
@@ -7092,7 +7088,7 @@
       <c r="A149" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B149" s="1">
+      <c r="B149" s="4">
         <v>4.3</v>
       </c>
       <c r="C149" s="4" t="s">
@@ -7106,7 +7102,7 @@
       <c r="A150" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B150" s="1">
+      <c r="B150" s="4">
         <v>4.3</v>
       </c>
       <c r="C150" s="4" t="s">
@@ -7120,7 +7116,7 @@
       <c r="A151" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B151" s="1">
+      <c r="B151" s="4">
         <v>4.3</v>
       </c>
       <c r="C151" s="4" t="s">
@@ -7134,7 +7130,7 @@
       <c r="A152" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B152" s="1">
+      <c r="B152" s="4">
         <v>4.3</v>
       </c>
       <c r="C152" s="4" t="s">
@@ -7148,7 +7144,7 @@
       <c r="A153" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B153" s="1">
+      <c r="B153" s="4">
         <v>4.3</v>
       </c>
       <c r="C153" s="4" t="s">
@@ -7162,7 +7158,7 @@
       <c r="A154" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B154" s="1">
+      <c r="B154" s="4">
         <v>4.3</v>
       </c>
       <c r="C154" s="4" t="s">
@@ -7176,7 +7172,7 @@
       <c r="A155" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B155" s="1">
+      <c r="B155" s="4">
         <v>4.3</v>
       </c>
       <c r="C155" s="4" t="s">
@@ -7190,7 +7186,7 @@
       <c r="A156" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B156" s="1">
+      <c r="B156" s="4">
         <v>4.3</v>
       </c>
       <c r="C156" s="4" t="s">
@@ -7204,7 +7200,7 @@
       <c r="A157" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B157" s="1">
+      <c r="B157" s="4">
         <v>4.3</v>
       </c>
       <c r="C157" s="4" t="s">
@@ -7218,7 +7214,7 @@
       <c r="A158" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B158" s="1">
+      <c r="B158" s="4">
         <v>4.3</v>
       </c>
       <c r="C158" s="4" t="s">
@@ -7232,7 +7228,7 @@
       <c r="A159" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B159" s="1">
+      <c r="B159" s="4">
         <v>4.3</v>
       </c>
       <c r="C159" s="4" t="s">
@@ -7246,7 +7242,7 @@
       <c r="A160" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B160" s="1">
+      <c r="B160" s="4">
         <v>4.3</v>
       </c>
       <c r="C160" s="4" t="s">
@@ -7260,7 +7256,7 @@
       <c r="A161" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B161" s="1">
+      <c r="B161" s="4">
         <v>4.3</v>
       </c>
       <c r="C161" s="4" t="s">
@@ -7274,7 +7270,7 @@
       <c r="A162" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B162" s="1">
+      <c r="B162" s="4">
         <v>4.3</v>
       </c>
       <c r="C162" s="4" t="s">
@@ -7288,7 +7284,7 @@
       <c r="A163" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B163" s="1">
+      <c r="B163" s="4">
         <v>4.3</v>
       </c>
       <c r="C163" s="4" t="s">
@@ -7302,7 +7298,7 @@
       <c r="A164" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B164" s="1">
+      <c r="B164" s="4">
         <v>4.3</v>
       </c>
       <c r="C164" s="4" t="s">
@@ -7316,7 +7312,7 @@
       <c r="A165" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B165" s="1">
+      <c r="B165" s="4">
         <v>4.3</v>
       </c>
       <c r="C165" s="4" t="s">
@@ -7330,7 +7326,7 @@
       <c r="A166" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B166" s="1">
+      <c r="B166" s="4">
         <v>4.3</v>
       </c>
       <c r="C166" s="4" t="s">
@@ -7344,7 +7340,7 @@
       <c r="A167" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B167" s="1">
+      <c r="B167" s="4">
         <v>4.3</v>
       </c>
       <c r="C167" s="4" t="s">
@@ -7358,7 +7354,7 @@
       <c r="A168" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B168" s="1">
+      <c r="B168" s="4">
         <v>4.3</v>
       </c>
       <c r="C168" s="4" t="s">
@@ -7372,7 +7368,7 @@
       <c r="A169" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B169" s="1">
+      <c r="B169" s="4">
         <v>4.3</v>
       </c>
       <c r="C169" s="4" t="s">
@@ -7386,7 +7382,7 @@
       <c r="A170" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B170" s="1">
+      <c r="B170" s="4">
         <v>4.3</v>
       </c>
       <c r="C170" s="4" t="s">
@@ -7400,7 +7396,7 @@
       <c r="A171" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B171" s="1">
+      <c r="B171" s="4">
         <v>4.3</v>
       </c>
       <c r="C171" s="4" t="s">
@@ -7414,7 +7410,7 @@
       <c r="A172" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B172" s="1">
+      <c r="B172" s="4">
         <v>4.3</v>
       </c>
       <c r="C172" s="4" t="s">
@@ -7428,7 +7424,7 @@
       <c r="A173" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B173" s="1">
+      <c r="B173" s="4">
         <v>4.3</v>
       </c>
       <c r="C173" s="4" t="s">
@@ -7442,7 +7438,7 @@
       <c r="A174" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B174" s="1">
+      <c r="B174" s="4">
         <v>4.3</v>
       </c>
       <c r="C174" s="4" t="s">
@@ -7456,7 +7452,7 @@
       <c r="A175" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B175" s="1">
+      <c r="B175" s="4">
         <v>4.3</v>
       </c>
       <c r="C175" s="4" t="s">
@@ -7470,7 +7466,7 @@
       <c r="A176" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B176" s="1">
+      <c r="B176" s="4">
         <v>4.3</v>
       </c>
       <c r="C176" s="4" t="s">
@@ -7484,7 +7480,7 @@
       <c r="A177" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B177" s="1">
+      <c r="B177" s="4">
         <v>4.3</v>
       </c>
       <c r="C177" s="4" t="s">
@@ -7498,7 +7494,7 @@
       <c r="A178" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B178" s="1">
+      <c r="B178" s="4">
         <v>4.3</v>
       </c>
       <c r="C178" s="4" t="s">
@@ -7512,7 +7508,7 @@
       <c r="A179" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B179" s="1">
+      <c r="B179" s="4">
         <v>4.3</v>
       </c>
       <c r="C179" s="4" t="s">
@@ -7526,7 +7522,7 @@
       <c r="A180" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B180" s="1">
+      <c r="B180" s="4">
         <v>4.3</v>
       </c>
       <c r="C180" s="4" t="s">
@@ -7540,7 +7536,7 @@
       <c r="A181" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B181" s="1">
+      <c r="B181" s="4">
         <v>4.3</v>
       </c>
       <c r="C181" s="4" t="s">
@@ -7554,7 +7550,7 @@
       <c r="A182" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B182" s="1">
+      <c r="B182" s="4">
         <v>4.3</v>
       </c>
       <c r="C182" s="4" t="s">
@@ -7568,7 +7564,7 @@
       <c r="A183" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B183" s="1">
+      <c r="B183" s="4">
         <v>4.3</v>
       </c>
       <c r="C183" s="4" t="s">
@@ -7582,7 +7578,7 @@
       <c r="A184" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B184" s="1">
+      <c r="B184" s="4">
         <v>4.3</v>
       </c>
       <c r="C184" s="4" t="s">
@@ -7596,7 +7592,7 @@
       <c r="A185" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B185" s="1">
+      <c r="B185" s="4">
         <v>4.3</v>
       </c>
       <c r="C185" s="4" t="s">
@@ -7610,7 +7606,7 @@
       <c r="A186" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B186" s="1">
+      <c r="B186" s="4">
         <v>4.3</v>
       </c>
       <c r="C186" s="4" t="s">
@@ -7624,7 +7620,7 @@
       <c r="A187" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B187" s="1">
+      <c r="B187" s="4">
         <v>4.3</v>
       </c>
       <c r="C187" s="4" t="s">
@@ -7638,7 +7634,7 @@
       <c r="A188" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B188" s="1">
+      <c r="B188" s="4">
         <v>4.3</v>
       </c>
       <c r="C188" s="4" t="s">
@@ -7652,7 +7648,7 @@
       <c r="A189" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B189" s="1">
+      <c r="B189" s="4">
         <v>4.3</v>
       </c>
       <c r="C189" s="4" t="s">
@@ -7666,7 +7662,7 @@
       <c r="A190" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B190" s="1">
+      <c r="B190" s="4">
         <v>4.3</v>
       </c>
       <c r="C190" s="4" t="s">
@@ -7680,7 +7676,7 @@
       <c r="A191" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B191" s="1">
+      <c r="B191" s="4">
         <v>4.3</v>
       </c>
       <c r="C191" s="4" t="s">
@@ -7694,7 +7690,7 @@
       <c r="A192" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B192" s="1">
+      <c r="B192" s="4">
         <v>4.3</v>
       </c>
       <c r="C192" s="4" t="s">
@@ -7708,7 +7704,7 @@
       <c r="A193" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B193" s="1">
+      <c r="B193" s="4">
         <v>4.3</v>
       </c>
       <c r="C193" s="4" t="s">
@@ -7722,7 +7718,7 @@
       <c r="A194" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B194" s="1">
+      <c r="B194" s="4">
         <v>4.3</v>
       </c>
       <c r="C194" s="4" t="s">
@@ -7736,7 +7732,7 @@
       <c r="A195" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B195" s="1">
+      <c r="B195" s="4">
         <v>4.3</v>
       </c>
       <c r="C195" s="4" t="s">
@@ -7750,7 +7746,7 @@
       <c r="A196" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B196" s="1">
+      <c r="B196" s="4">
         <v>4.3</v>
       </c>
       <c r="C196" s="4" t="s">
@@ -7764,7 +7760,7 @@
       <c r="A197" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B197" s="1">
+      <c r="B197" s="4">
         <v>4.3</v>
       </c>
       <c r="C197" s="4" t="s">
@@ -7778,7 +7774,7 @@
       <c r="A198" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B198" s="1">
+      <c r="B198" s="4">
         <v>4.3</v>
       </c>
       <c r="C198" s="4" t="s">
@@ -7792,7 +7788,7 @@
       <c r="A199" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B199" s="1">
+      <c r="B199" s="4">
         <v>4.3</v>
       </c>
       <c r="C199" s="4" t="s">
@@ -7806,7 +7802,7 @@
       <c r="A200" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B200" s="1">
+      <c r="B200" s="4">
         <v>4.3</v>
       </c>
       <c r="C200" s="4" t="s">
@@ -7820,7 +7816,7 @@
       <c r="A201" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B201" s="1">
+      <c r="B201" s="4">
         <v>4.3</v>
       </c>
       <c r="C201" s="4" t="s">
@@ -7834,7 +7830,7 @@
       <c r="A202" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B202" s="1">
+      <c r="B202" s="4">
         <v>4.3</v>
       </c>
       <c r="C202" s="4" t="s">
@@ -7848,7 +7844,7 @@
       <c r="A203" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B203" s="1">
+      <c r="B203" s="4">
         <v>4.3</v>
       </c>
       <c r="C203" s="4" t="s">
@@ -7862,7 +7858,7 @@
       <c r="A204" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B204" s="1">
+      <c r="B204" s="4">
         <v>4.3</v>
       </c>
       <c r="C204" s="4" t="s">
@@ -7876,7 +7872,7 @@
       <c r="A205" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B205" s="1">
+      <c r="B205" s="4">
         <v>4.3</v>
       </c>
       <c r="C205" s="4" t="s">
@@ -7890,7 +7886,7 @@
       <c r="A206" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B206" s="1">
+      <c r="B206" s="4">
         <v>4.3</v>
       </c>
       <c r="C206" s="4" t="s">
@@ -7904,7 +7900,7 @@
       <c r="A207" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B207" s="1">
+      <c r="B207" s="4">
         <v>4.3</v>
       </c>
       <c r="C207" s="4" t="s">
@@ -7918,7 +7914,7 @@
       <c r="A208" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B208" s="1">
+      <c r="B208" s="4">
         <v>4.3</v>
       </c>
       <c r="C208" s="4" t="s">
@@ -7932,7 +7928,7 @@
       <c r="A209" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B209" s="1">
+      <c r="B209" s="4">
         <v>4.3</v>
       </c>
       <c r="C209" s="4" t="s">
@@ -7946,7 +7942,7 @@
       <c r="A210" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B210" s="1">
+      <c r="B210" s="4">
         <v>4.3</v>
       </c>
       <c r="C210" s="4" t="s">
@@ -7960,7 +7956,7 @@
       <c r="A211" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B211" s="1">
+      <c r="B211" s="4">
         <v>4.3</v>
       </c>
       <c r="C211" s="4" t="s">
@@ -7974,7 +7970,7 @@
       <c r="A212" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B212" s="1">
+      <c r="B212" s="4">
         <v>4.3</v>
       </c>
       <c r="C212" s="4" t="s">
@@ -7988,7 +7984,7 @@
       <c r="A213" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B213" s="1">
+      <c r="B213" s="4">
         <v>4.3</v>
       </c>
       <c r="C213" s="4" t="s">
@@ -8002,7 +7998,7 @@
       <c r="A214" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B214" s="1">
+      <c r="B214" s="4">
         <v>4.3</v>
       </c>
       <c r="C214" s="4" t="s">
@@ -8016,7 +8012,7 @@
       <c r="A215" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B215" s="1">
+      <c r="B215" s="4">
         <v>4.3</v>
       </c>
       <c r="C215" s="4" t="s">
@@ -8030,7 +8026,7 @@
       <c r="A216" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B216" s="1">
+      <c r="B216" s="4">
         <v>4.3</v>
       </c>
       <c r="C216" s="4" t="s">
@@ -8044,7 +8040,7 @@
       <c r="A217" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B217" s="1">
+      <c r="B217" s="4">
         <v>4.3</v>
       </c>
       <c r="C217" s="4" t="s">
@@ -8058,7 +8054,7 @@
       <c r="A218" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B218" s="1">
+      <c r="B218" s="4">
         <v>4.3</v>
       </c>
       <c r="C218" s="4" t="s">
@@ -8072,7 +8068,7 @@
       <c r="A219" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B219" s="1">
+      <c r="B219" s="4">
         <v>4.3</v>
       </c>
       <c r="C219" s="4" t="s">
@@ -8086,7 +8082,7 @@
       <c r="A220" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B220" s="1">
+      <c r="B220" s="4">
         <v>4.3</v>
       </c>
       <c r="C220" s="4" t="s">
@@ -8100,7 +8096,7 @@
       <c r="A221" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B221" s="1">
+      <c r="B221" s="4">
         <v>4.3</v>
       </c>
       <c r="C221" s="4" t="s">
@@ -8114,7 +8110,7 @@
       <c r="A222" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B222" s="1">
+      <c r="B222" s="4">
         <v>4.3</v>
       </c>
       <c r="C222" s="4" t="s">
@@ -8128,7 +8124,7 @@
       <c r="A223" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B223" s="1">
+      <c r="B223" s="4">
         <v>4.3</v>
       </c>
       <c r="C223" s="4" t="s">
@@ -8142,7 +8138,7 @@
       <c r="A224" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B224" s="1">
+      <c r="B224" s="4">
         <v>4.3</v>
       </c>
       <c r="C224" s="4" t="s">
@@ -8156,7 +8152,7 @@
       <c r="A225" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B225" s="1">
+      <c r="B225" s="4">
         <v>4.3</v>
       </c>
       <c r="C225" s="4" t="s">
@@ -8170,7 +8166,7 @@
       <c r="A226" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B226" s="1">
+      <c r="B226" s="4">
         <v>4.3</v>
       </c>
       <c r="C226" s="4" t="s">
@@ -8184,7 +8180,7 @@
       <c r="A227" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B227" s="1">
+      <c r="B227" s="4">
         <v>4.3</v>
       </c>
       <c r="C227" s="4" t="s">
@@ -8198,7 +8194,7 @@
       <c r="A228" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B228" s="1">
+      <c r="B228" s="4">
         <v>4.3</v>
       </c>
       <c r="C228" s="4" t="s">
@@ -8212,7 +8208,7 @@
       <c r="A229" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B229" s="1">
+      <c r="B229" s="4">
         <v>4.3</v>
       </c>
       <c r="C229" s="4" t="s">
@@ -8226,7 +8222,7 @@
       <c r="A230" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B230" s="1">
+      <c r="B230" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="F230" s="1" t="s">
@@ -8240,7 +8236,7 @@
       <c r="A231" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B231" s="1">
+      <c r="B231" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C231" s="4" t="s">
@@ -8254,7 +8250,7 @@
       <c r="A232" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B232" s="1">
+      <c r="B232" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C232" s="4" t="s">
@@ -8268,7 +8264,7 @@
       <c r="A233" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B233" s="1">
+      <c r="B233" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C233" s="4" t="s">
@@ -8282,7 +8278,7 @@
       <c r="A234" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B234" s="1">
+      <c r="B234" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C234" s="4" t="s">
@@ -8296,7 +8292,7 @@
       <c r="A235" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B235" s="1">
+      <c r="B235" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C235" s="4" t="s">
@@ -8310,7 +8306,7 @@
       <c r="A236" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B236" s="1">
+      <c r="B236" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C236" s="4" t="s">
@@ -8324,7 +8320,7 @@
       <c r="A237" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B237" s="1">
+      <c r="B237" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C237" s="4" t="s">
@@ -8338,7 +8334,7 @@
       <c r="A238" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B238" s="1">
+      <c r="B238" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C238" s="4" t="s">
@@ -8352,7 +8348,7 @@
       <c r="A239" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B239" s="1">
+      <c r="B239" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C239" s="4" t="s">
@@ -8366,7 +8362,7 @@
       <c r="A240" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B240" s="1">
+      <c r="B240" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C240" s="4" t="s">
@@ -8380,7 +8376,7 @@
       <c r="A241" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B241" s="1">
+      <c r="B241" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C241" s="4" t="s">
@@ -8394,7 +8390,7 @@
       <c r="A242" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B242" s="1">
+      <c r="B242" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C242" s="4" t="s">
@@ -8408,7 +8404,7 @@
       <c r="A243" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B243" s="1">
+      <c r="B243" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C243" s="4" t="s">
@@ -8422,7 +8418,7 @@
       <c r="A244" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B244" s="1">
+      <c r="B244" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C244" s="4" t="s">
@@ -8436,7 +8432,7 @@
       <c r="A245" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B245" s="1">
+      <c r="B245" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C245" s="4" t="s">
@@ -8450,7 +8446,7 @@
       <c r="A246" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B246" s="1">
+      <c r="B246" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C246" s="4" t="s">
@@ -8464,7 +8460,7 @@
       <c r="A247" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B247" s="1">
+      <c r="B247" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C247" s="4" t="s">
@@ -8478,7 +8474,7 @@
       <c r="A248" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B248" s="1">
+      <c r="B248" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C248" s="4" t="s">
@@ -8492,7 +8488,7 @@
       <c r="A249" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B249" s="1">
+      <c r="B249" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C249" s="4" t="s">
@@ -8506,7 +8502,7 @@
       <c r="A250" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B250" s="1">
+      <c r="B250" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C250" s="4" t="s">
@@ -8520,7 +8516,7 @@
       <c r="A251" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B251" s="1">
+      <c r="B251" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C251" s="4" t="s">
@@ -8537,7 +8533,7 @@
       <c r="A252" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B252" s="1">
+      <c r="B252" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C252" s="4" t="s">
@@ -8554,7 +8550,7 @@
       <c r="A253" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B253" s="1">
+      <c r="B253" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C253" s="4" t="s">
@@ -8568,7 +8564,7 @@
       <c r="A254" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B254" s="1">
+      <c r="B254" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C254" s="4" t="s">
@@ -8582,7 +8578,7 @@
       <c r="A255" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B255" s="1">
+      <c r="B255" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C255" s="4" t="s">
@@ -8599,7 +8595,7 @@
       <c r="A256" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B256" s="1">
+      <c r="B256" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C256" s="4" t="s">
@@ -8613,7 +8609,7 @@
       <c r="A257" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B257" s="1">
+      <c r="B257" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C257" s="4" t="s">
@@ -8630,7 +8626,7 @@
       <c r="A258" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B258" s="1">
+      <c r="B258" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C258" s="4" t="s">
@@ -8644,7 +8640,7 @@
       <c r="A259" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B259" s="1">
+      <c r="B259" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C259" s="4" t="s">
@@ -8658,7 +8654,7 @@
       <c r="A260" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B260" s="1">
+      <c r="B260" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C260" s="4" t="s">
@@ -8672,7 +8668,7 @@
       <c r="A261" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B261" s="1">
+      <c r="B261" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C261" s="4" t="s">
@@ -8686,7 +8682,7 @@
       <c r="A262" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B262" s="1">
+      <c r="B262" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C262" s="4" t="s">
@@ -8700,7 +8696,7 @@
       <c r="A263" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B263" s="1">
+      <c r="B263" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C263" s="4" t="s">
@@ -8717,7 +8713,7 @@
       <c r="A264" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B264" s="1">
+      <c r="B264" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C264" s="4" t="s">
@@ -8731,7 +8727,7 @@
       <c r="A265" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B265" s="1">
+      <c r="B265" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C265" s="4" t="s">
@@ -8745,7 +8741,7 @@
       <c r="A266" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B266" s="1">
+      <c r="B266" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C266" s="4" t="s">
@@ -8759,7 +8755,7 @@
       <c r="A267" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B267" s="1">
+      <c r="B267" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C267" s="4" t="s">
@@ -8773,7 +8769,7 @@
       <c r="A268" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B268" s="1">
+      <c r="B268" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C268" s="4" t="s">
@@ -8787,7 +8783,7 @@
       <c r="A269" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B269" s="1">
+      <c r="B269" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C269" s="4" t="s">
@@ -8801,7 +8797,7 @@
       <c r="A270" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B270" s="1">
+      <c r="B270" s="4">
         <v>5.2</v>
       </c>
       <c r="D270" s="1" t="s">
@@ -8812,7 +8808,7 @@
       <c r="A271" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B271" s="1">
+      <c r="B271" s="4">
         <v>6.1</v>
       </c>
       <c r="F271" s="1" t="s">
@@ -8823,7 +8819,7 @@
       <c r="A272" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B272" s="1">
+      <c r="B272" s="4">
         <v>6.1</v>
       </c>
       <c r="C272" s="4" t="s">
@@ -8837,7 +8833,7 @@
       <c r="A273" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B273" s="1">
+      <c r="B273" s="4">
         <v>6.1</v>
       </c>
       <c r="C273" s="4" t="s">
@@ -8851,7 +8847,7 @@
       <c r="A274" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B274" s="1">
+      <c r="B274" s="4">
         <v>6.1</v>
       </c>
       <c r="C274" s="4" t="s">
@@ -8865,7 +8861,7 @@
       <c r="A275" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B275" s="1">
+      <c r="B275" s="4">
         <v>6.1</v>
       </c>
       <c r="C275" s="4" t="s">
@@ -8879,7 +8875,7 @@
       <c r="A276" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B276" s="1">
+      <c r="B276" s="4">
         <v>6.1</v>
       </c>
       <c r="C276" s="4" t="s">
@@ -8893,7 +8889,7 @@
       <c r="A277" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B277" s="1">
+      <c r="B277" s="4">
         <v>6.1</v>
       </c>
       <c r="C277" s="4" t="s">
@@ -8907,7 +8903,7 @@
       <c r="A278" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B278" s="1">
+      <c r="B278" s="4">
         <v>6.1</v>
       </c>
       <c r="C278" s="4" t="s">
@@ -8921,7 +8917,7 @@
       <c r="A279" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B279" s="1">
+      <c r="B279" s="4">
         <v>6.1</v>
       </c>
       <c r="C279" s="4" t="s">
@@ -8935,7 +8931,7 @@
       <c r="A280" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B280" s="1">
+      <c r="B280" s="4">
         <v>6.1</v>
       </c>
       <c r="C280" s="4" t="s">
@@ -8949,7 +8945,7 @@
       <c r="A281" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B281" s="1">
+      <c r="B281" s="4">
         <v>6.1</v>
       </c>
       <c r="C281" s="4" t="s">
@@ -8963,7 +8959,7 @@
       <c r="A282" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B282" s="1">
+      <c r="B282" s="4">
         <v>6.1</v>
       </c>
       <c r="C282" s="4" t="s">
@@ -8977,7 +8973,7 @@
       <c r="A283" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B283" s="1">
+      <c r="B283" s="4">
         <v>6.1</v>
       </c>
       <c r="C283" s="4" t="s">
@@ -8991,7 +8987,7 @@
       <c r="A284" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B284" s="1">
+      <c r="B284" s="4">
         <v>6.1</v>
       </c>
       <c r="C284" s="4" t="s">
@@ -9005,7 +9001,7 @@
       <c r="A285" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B285" s="1">
+      <c r="B285" s="4">
         <v>6.1</v>
       </c>
       <c r="C285" s="4" t="s">
@@ -9019,7 +9015,7 @@
       <c r="A286" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B286" s="1">
+      <c r="B286" s="4">
         <v>6.2</v>
       </c>
       <c r="D286" s="1" t="s">
@@ -9030,7 +9026,7 @@
       <c r="A287" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B287" s="1">
+      <c r="B287" s="4">
         <v>7</v>
       </c>
       <c r="D287" s="1" t="s">
@@ -9041,7 +9037,7 @@
       <c r="A288" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B288" s="1">
+      <c r="B288" s="4">
         <v>8</v>
       </c>
       <c r="F288" s="1" t="s">
@@ -9055,7 +9051,7 @@
       <c r="A289" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B289" s="1">
+      <c r="B289" s="4">
         <v>8</v>
       </c>
       <c r="C289" s="4" t="s">
@@ -9069,7 +9065,7 @@
       <c r="A290" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B290" s="1">
+      <c r="B290" s="4">
         <v>8</v>
       </c>
       <c r="C290" s="4" t="s">
@@ -9083,7 +9079,7 @@
       <c r="A291" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B291" s="1">
+      <c r="B291" s="4">
         <v>8</v>
       </c>
       <c r="C291" s="4" t="s">
@@ -9097,7 +9093,7 @@
       <c r="A292" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B292" s="1">
+      <c r="B292" s="4">
         <v>8</v>
       </c>
       <c r="C292" s="4" t="s">
@@ -9111,7 +9107,7 @@
       <c r="A293" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B293" s="1">
+      <c r="B293" s="4">
         <v>8</v>
       </c>
       <c r="C293" s="4" t="s">
@@ -9125,7 +9121,7 @@
       <c r="A294" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B294" s="1">
+      <c r="B294" s="4">
         <v>8</v>
       </c>
       <c r="C294" s="4" t="s">
@@ -9139,7 +9135,7 @@
       <c r="A295" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B295" s="1">
+      <c r="B295" s="4">
         <v>8</v>
       </c>
       <c r="C295" s="4" t="s">
@@ -9153,7 +9149,7 @@
       <c r="A296" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B296" s="1">
+      <c r="B296" s="4">
         <v>8</v>
       </c>
       <c r="C296" s="4" t="s">
@@ -9167,7 +9163,7 @@
       <c r="A297" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B297" s="1">
+      <c r="B297" s="4">
         <v>9</v>
       </c>
       <c r="F297" s="1" t="s">
@@ -9181,7 +9177,7 @@
       <c r="A298" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B298" s="1">
+      <c r="B298" s="4">
         <v>9</v>
       </c>
       <c r="C298" s="4" t="s">
@@ -9195,7 +9191,7 @@
       <c r="A299" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B299" s="1">
+      <c r="B299" s="4">
         <v>9</v>
       </c>
       <c r="C299" s="4" t="s">
@@ -9212,7 +9208,7 @@
       <c r="A300" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B300" s="1">
+      <c r="B300" s="4">
         <v>9</v>
       </c>
       <c r="C300" s="4" t="s">
@@ -9232,7 +9228,7 @@
       <c r="A301" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B301" s="1">
+      <c r="B301" s="4">
         <v>9</v>
       </c>
       <c r="C301" s="4" t="s">
@@ -9246,7 +9242,7 @@
       <c r="A302" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B302" s="1">
+      <c r="B302" s="4">
         <v>9</v>
       </c>
       <c r="C302" s="4" t="s">
@@ -9260,7 +9256,7 @@
       <c r="A303" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B303" s="1">
+      <c r="B303" s="4">
         <v>9</v>
       </c>
       <c r="C303" s="4" t="s">
@@ -9277,7 +9273,7 @@
       <c r="A304" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B304" s="1">
+      <c r="B304" s="4">
         <v>9</v>
       </c>
       <c r="C304" s="4" t="s">
@@ -9297,7 +9293,7 @@
       <c r="A305" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B305" s="1">
+      <c r="B305" s="4">
         <v>9</v>
       </c>
       <c r="C305" s="4" t="s">
@@ -9311,7 +9307,7 @@
       <c r="A306" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B306" s="1">
+      <c r="B306" s="4">
         <v>9</v>
       </c>
       <c r="C306" s="4" t="s">
@@ -9328,7 +9324,7 @@
       <c r="A307" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B307" s="1">
+      <c r="B307" s="4">
         <v>9</v>
       </c>
       <c r="C307" s="4" t="s">
@@ -9348,7 +9344,7 @@
       <c r="A308" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B308" s="1">
+      <c r="B308" s="4">
         <v>9</v>
       </c>
       <c r="C308" s="4" t="s">
@@ -9368,7 +9364,7 @@
       <c r="A309" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B309" s="1">
+      <c r="B309" s="4">
         <v>9</v>
       </c>
       <c r="C309" s="4" t="s">
@@ -9388,7 +9384,7 @@
       <c r="A310" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B310" s="1">
+      <c r="B310" s="4">
         <v>9</v>
       </c>
       <c r="C310" s="4" t="s">
@@ -9563,7 +9559,7 @@
       <c r="A3" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="4">
         <v>1.1000000000000001</v>
       </c>
       <c r="C3" s="1"/>
@@ -9575,7 +9571,7 @@
       <c r="A4" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="4">
         <v>1.2</v>
       </c>
       <c r="C4" s="1"/>
@@ -9587,7 +9583,7 @@
       <c r="A5" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="4">
         <v>1.3</v>
       </c>
       <c r="C5" s="1"/>
@@ -9599,7 +9595,7 @@
       <c r="A6" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="4">
         <v>1.4</v>
       </c>
       <c r="C6" s="1"/>
@@ -9611,7 +9607,7 @@
       <c r="A7" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="4">
         <v>1.5</v>
       </c>
       <c r="C7" s="1"/>
@@ -9623,7 +9619,7 @@
       <c r="A8" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="4">
         <v>1.6</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -9634,7 +9630,7 @@
       <c r="A9" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="4">
         <v>2.1</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -9723,7 +9719,7 @@
       <c r="A10" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="4">
         <v>2.1</v>
       </c>
       <c r="C10" s="1">
@@ -9737,7 +9733,7 @@
       <c r="A11" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="4">
         <v>2.1</v>
       </c>
       <c r="C11" s="1">
@@ -9751,7 +9747,7 @@
       <c r="A12" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="4">
         <v>2.1</v>
       </c>
       <c r="C12" s="1">
@@ -9765,7 +9761,7 @@
       <c r="A13" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="4">
         <v>2.1</v>
       </c>
       <c r="C13" s="1">
@@ -9779,7 +9775,7 @@
       <c r="A14" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="4">
         <v>2.1</v>
       </c>
       <c r="C14" s="1">
@@ -9793,7 +9789,7 @@
       <c r="A15" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="4">
         <v>2.1</v>
       </c>
       <c r="C15" s="1">
@@ -9807,7 +9803,7 @@
       <c r="A16" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="4">
         <v>2.1</v>
       </c>
       <c r="C16" s="1">
@@ -9817,11 +9813,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="17" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="4">
         <v>2.1</v>
       </c>
       <c r="C17" s="1">
@@ -9831,11 +9827,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="18" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="4">
         <v>2.1</v>
       </c>
       <c r="C18" s="1">
@@ -9845,11 +9841,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="4">
         <v>2.1</v>
       </c>
       <c r="C19" s="1">
@@ -9859,11 +9855,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="20" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="4">
         <v>2.1</v>
       </c>
       <c r="C20" s="1">
@@ -9873,11 +9869,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="4">
         <v>2.1</v>
       </c>
       <c r="C21" s="1">
@@ -9887,11 +9883,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="22" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="4">
         <v>2.1</v>
       </c>
       <c r="C22" s="1">
@@ -9901,11 +9897,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="23" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="4">
         <v>2.1</v>
       </c>
       <c r="C23" s="1">
@@ -9915,11 +9911,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="4">
         <v>2.1</v>
       </c>
       <c r="C24" s="1">
@@ -9929,11 +9925,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="25" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="4">
         <v>2.1</v>
       </c>
       <c r="C25" s="1">
@@ -9943,11 +9939,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="26" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="4">
         <v>2.1</v>
       </c>
       <c r="C26" s="1">
@@ -9957,11 +9953,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="27" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="4">
         <v>2.1</v>
       </c>
       <c r="C27" s="1">
@@ -9971,11 +9967,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="4">
         <v>2.1</v>
       </c>
       <c r="C28" s="1">
@@ -9985,11 +9981,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="29" spans="1:32" s="1" customFormat="1" ht="252" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" ht="252" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="4">
         <v>2.2000000000000002</v>
       </c>
       <c r="F29" s="1" t="s">
@@ -10074,11 +10070,11 @@
         <v>300</v>
       </c>
     </row>
-    <row r="30" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="4">
         <v>2.2000000000000002</v>
       </c>
       <c r="C30" s="1">
@@ -10088,22 +10084,22 @@
         <v>138</v>
       </c>
     </row>
-    <row r="31" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="4">
         <v>2.2999999999999998</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="32" spans="1:32" s="1" customFormat="1" ht="252" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" ht="252" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="4">
         <v>3</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -10188,11 +10184,11 @@
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="4">
         <v>3</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -10205,11 +10201,11 @@
         <v>267</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="4">
         <v>3</v>
       </c>
       <c r="C34" s="1">
@@ -10219,11 +10215,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="4">
         <v>3</v>
       </c>
       <c r="C35" s="1">
@@ -10233,11 +10229,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="4">
         <v>3</v>
       </c>
       <c r="C36" s="1">
@@ -10247,11 +10243,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="4">
         <v>3</v>
       </c>
       <c r="C37" s="1">
@@ -10261,11 +10257,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="4">
         <v>3</v>
       </c>
       <c r="C38" s="1">
@@ -10275,11 +10271,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="4">
         <v>3</v>
       </c>
       <c r="C39" s="1">
@@ -10289,11 +10285,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="4">
         <v>3</v>
       </c>
       <c r="C40" s="1">
@@ -10303,11 +10299,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="4">
         <v>3</v>
       </c>
       <c r="C41" s="1">
@@ -10317,11 +10313,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="4">
         <v>3</v>
       </c>
       <c r="C42" s="1">
@@ -10331,11 +10327,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="4">
         <v>3</v>
       </c>
       <c r="C43" s="1">
@@ -10345,11 +10341,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="4">
         <v>3</v>
       </c>
       <c r="C44" s="1">
@@ -10359,11 +10355,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45" s="4">
         <v>3</v>
       </c>
       <c r="C45" s="1">
@@ -10373,11 +10369,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="4">
         <v>3</v>
       </c>
       <c r="C46" s="1">
@@ -10387,11 +10383,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="4">
         <v>3</v>
       </c>
       <c r="C47" s="1">
@@ -10401,11 +10397,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" s="4">
         <v>3</v>
       </c>
       <c r="C48" s="1">
@@ -10415,11 +10411,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="49" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49" s="4">
         <v>3</v>
       </c>
       <c r="C49" s="1">
@@ -10429,11 +10425,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="50" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="4">
         <v>3</v>
       </c>
       <c r="C50" s="1">
@@ -10443,11 +10439,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="51" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51" s="4">
         <v>3</v>
       </c>
       <c r="C51" s="1">
@@ -10457,11 +10453,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="52" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B52" s="4">
         <v>3</v>
       </c>
       <c r="C52" s="1">
@@ -10471,11 +10467,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="53" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="4">
         <v>3</v>
       </c>
       <c r="C53" s="1">
@@ -10485,11 +10481,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="54" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54" s="4">
         <v>3</v>
       </c>
       <c r="C54" s="1">
@@ -10499,11 +10495,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="55" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="4">
         <v>3</v>
       </c>
       <c r="C55" s="1">
@@ -10513,11 +10509,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="56" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="4">
         <v>3</v>
       </c>
       <c r="C56" s="1">
@@ -10527,11 +10523,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="57" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57" s="4">
         <v>3</v>
       </c>
       <c r="C57" s="1">
@@ -10541,11 +10537,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="58" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B58" s="1">
+      <c r="B58" s="4">
         <v>3</v>
       </c>
       <c r="C58" s="1">
@@ -10555,11 +10551,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="59" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B59" s="4">
         <v>3</v>
       </c>
       <c r="C59" s="1">
@@ -10569,11 +10565,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="60" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B60" s="4">
         <v>3</v>
       </c>
       <c r="C60" s="1">
@@ -10583,11 +10579,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="61" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61" s="4">
         <v>3</v>
       </c>
       <c r="C61" s="1">
@@ -10597,11 +10593,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="62" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62" s="4">
         <v>3</v>
       </c>
       <c r="C62" s="1">
@@ -10611,11 +10607,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63" s="4">
         <v>3</v>
       </c>
       <c r="C63" s="1">
@@ -10625,11 +10621,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="64" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64" s="4">
         <v>3</v>
       </c>
       <c r="C64" s="1">
@@ -10639,11 +10635,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="65" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65" s="4">
         <v>3</v>
       </c>
       <c r="C65" s="1">
@@ -10653,11 +10649,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="66" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66" s="4">
         <v>3</v>
       </c>
       <c r="C66" s="1">
@@ -10667,11 +10663,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="67" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67" s="4">
         <v>3</v>
       </c>
       <c r="C67" s="1">
@@ -10681,11 +10677,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="68" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68" s="4">
         <v>3</v>
       </c>
       <c r="C68" s="1">
@@ -10695,11 +10691,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="69" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B69" s="4">
         <v>3</v>
       </c>
       <c r="C69" s="1">
@@ -10709,11 +10705,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="70" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70" s="4">
         <v>3</v>
       </c>
       <c r="C70" s="1">
@@ -10723,11 +10719,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="71" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71" s="4">
         <v>3</v>
       </c>
       <c r="C71" s="1">
@@ -10737,11 +10733,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="72" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B72" s="1">
+      <c r="B72" s="4">
         <v>3</v>
       </c>
       <c r="C72" s="1">
@@ -10751,11 +10747,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="73" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B73" s="1">
+      <c r="B73" s="4">
         <v>3</v>
       </c>
       <c r="C73" s="1">
@@ -10765,11 +10761,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="74" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B74" s="1">
+      <c r="B74" s="4">
         <v>3</v>
       </c>
       <c r="C74" s="1">
@@ -10779,11 +10775,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="75" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B75" s="1">
+      <c r="B75" s="4">
         <v>3</v>
       </c>
       <c r="C75" s="1">
@@ -10793,11 +10789,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="76" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B76" s="1">
+      <c r="B76" s="4">
         <v>3</v>
       </c>
       <c r="C76" s="1">
@@ -10807,11 +10803,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="77" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B77" s="1">
+      <c r="B77" s="4">
         <v>3</v>
       </c>
       <c r="C77" s="1">
@@ -10821,11 +10817,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="78" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78" s="4">
         <v>3</v>
       </c>
       <c r="C78" s="1">
@@ -10835,11 +10831,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="79" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B79" s="4">
         <v>3</v>
       </c>
       <c r="C79" s="1">
@@ -10849,11 +10845,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="80" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B80" s="4">
         <v>3</v>
       </c>
       <c r="C80" s="1">
@@ -10863,11 +10859,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="81" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B81" s="1">
+      <c r="B81" s="4">
         <v>3</v>
       </c>
       <c r="C81" s="1">
@@ -10877,11 +10873,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="82" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B82" s="1">
+      <c r="B82" s="4">
         <v>3</v>
       </c>
       <c r="C82" s="1">
@@ -10891,11 +10887,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="83" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B83" s="1">
+      <c r="B83" s="4">
         <v>3</v>
       </c>
       <c r="C83" s="1">
@@ -10905,11 +10901,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="84" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B84" s="1">
+      <c r="B84" s="4">
         <v>3</v>
       </c>
       <c r="C84" s="1">
@@ -10919,11 +10915,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="85" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B85" s="1">
+      <c r="B85" s="4">
         <v>3</v>
       </c>
       <c r="C85" s="1">
@@ -10933,11 +10929,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="86" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B86" s="1">
+      <c r="B86" s="4">
         <v>3</v>
       </c>
       <c r="C86" s="1">
@@ -10947,11 +10943,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="87" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B87" s="1">
+      <c r="B87" s="4">
         <v>3</v>
       </c>
       <c r="C87" s="1">
@@ -10961,11 +10957,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="88" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B88" s="1">
+      <c r="B88" s="4">
         <v>3</v>
       </c>
       <c r="C88" s="1">
@@ -10975,11 +10971,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="89" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B89" s="1">
+      <c r="B89" s="4">
         <v>3</v>
       </c>
       <c r="C89" s="1">
@@ -10989,11 +10985,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="90" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B90" s="1">
+      <c r="B90" s="4">
         <v>3</v>
       </c>
       <c r="C90" s="1">
@@ -11003,11 +10999,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="91" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B91" s="1">
+      <c r="B91" s="4">
         <v>3</v>
       </c>
       <c r="C91" s="1">
@@ -11017,11 +11013,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="92" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B92" s="1">
+      <c r="B92" s="4">
         <v>3</v>
       </c>
       <c r="C92" s="1">
@@ -11031,11 +11027,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="93" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B93" s="1">
+      <c r="B93" s="4">
         <v>3</v>
       </c>
       <c r="C93" s="1">
@@ -11045,11 +11041,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="94" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B94" s="1">
+      <c r="B94" s="4">
         <v>3</v>
       </c>
       <c r="C94" s="1">
@@ -11059,11 +11055,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="95" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B95" s="1">
+      <c r="B95" s="4">
         <v>3</v>
       </c>
       <c r="C95" s="1">
@@ -11073,11 +11069,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="96" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B96" s="1">
+      <c r="B96" s="4">
         <v>3</v>
       </c>
       <c r="C96" s="1">
@@ -11087,11 +11083,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="97" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B97" s="1">
+      <c r="B97" s="4">
         <v>3</v>
       </c>
       <c r="C97" s="1">
@@ -11101,11 +11097,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="98" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B98" s="1">
+      <c r="B98" s="4">
         <v>3</v>
       </c>
       <c r="C98" s="1">
@@ -11115,11 +11111,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="99" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B99" s="1">
+      <c r="B99" s="4">
         <v>3</v>
       </c>
       <c r="C99" s="1">
@@ -11129,11 +11125,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="100" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B100" s="1">
+      <c r="B100" s="4">
         <v>3</v>
       </c>
       <c r="C100" s="1">
@@ -11143,11 +11139,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="101" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B101" s="1">
+      <c r="B101" s="4">
         <v>3</v>
       </c>
       <c r="C101" s="1">
@@ -11157,11 +11153,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="102" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B102" s="1">
+      <c r="B102" s="4">
         <v>3</v>
       </c>
       <c r="C102" s="1">
@@ -11171,11 +11167,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="103" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B103" s="1">
+      <c r="B103" s="4">
         <v>3</v>
       </c>
       <c r="C103" s="1">
@@ -11185,11 +11181,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="104" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B104" s="1">
+      <c r="B104" s="4">
         <v>3</v>
       </c>
       <c r="C104" s="1">
@@ -11199,11 +11195,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="105" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B105" s="1">
+      <c r="B105" s="4">
         <v>3</v>
       </c>
       <c r="C105" s="1">
@@ -11213,11 +11209,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="106" spans="1:32" s="1" customFormat="1" ht="252" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:32" ht="252" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B106" s="1">
+      <c r="B106" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="F106" s="1" t="s">
@@ -11302,11 +11298,11 @@
         <v>300</v>
       </c>
     </row>
-    <row r="107" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B107" s="1">
+      <c r="B107" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C107" s="1">
@@ -11316,11 +11312,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="108" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B108" s="1">
+      <c r="B108" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C108" s="1">
@@ -11330,11 +11326,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="109" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B109" s="1">
+      <c r="B109" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C109" s="1">
@@ -11344,11 +11340,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="110" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B110" s="1">
+      <c r="B110" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C110" s="1">
@@ -11358,11 +11354,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="111" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B111" s="1">
+      <c r="B111" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C111" s="1">
@@ -11372,11 +11368,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="112" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B112" s="1">
+      <c r="B112" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C112" s="1">
@@ -11386,11 +11382,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="113" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B113" s="1">
+      <c r="B113" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C113" s="1">
@@ -11400,11 +11396,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="114" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B114" s="1">
+      <c r="B114" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C114" s="1">
@@ -11414,11 +11410,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="115" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B115" s="1">
+      <c r="B115" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C115" s="1">
@@ -11428,11 +11424,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="116" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B116" s="1">
+      <c r="B116" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C116" s="1">
@@ -11442,11 +11438,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="117" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B117" s="1">
+      <c r="B117" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C117" s="1">
@@ -11456,11 +11452,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="118" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B118" s="1">
+      <c r="B118" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C118" s="1">
@@ -11470,11 +11466,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="119" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B119" s="1">
+      <c r="B119" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C119" s="1">
@@ -11484,11 +11480,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="120" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B120" s="1">
+      <c r="B120" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C120" s="1">
@@ -11498,11 +11494,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B121" s="1">
+      <c r="B121" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C121" s="1">
@@ -11512,11 +11508,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="122" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B122" s="1">
+      <c r="B122" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C122" s="1">
@@ -11526,11 +11522,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="123" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B123" s="1">
+      <c r="B123" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C123" s="1">
@@ -11540,11 +11536,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="124" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B124" s="1">
+      <c r="B124" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C124" s="1">
@@ -11554,11 +11550,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="125" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B125" s="1">
+      <c r="B125" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C125" s="1">
@@ -11568,11 +11564,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="126" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B126" s="1">
+      <c r="B126" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C126" s="1">
@@ -11582,11 +11578,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="127" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B127" s="1">
+      <c r="B127" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C127" s="1">
@@ -11596,11 +11592,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="128" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B128" s="1">
+      <c r="B128" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C128" s="1">
@@ -11610,11 +11606,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="129" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B129" s="1">
+      <c r="B129" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C129" s="1">
@@ -11624,11 +11620,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="130" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B130" s="1">
+      <c r="B130" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C130" s="1">
@@ -11638,11 +11634,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="131" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B131" s="1">
+      <c r="B131" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C131" s="1">
@@ -11652,11 +11648,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="132" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B132" s="1">
+      <c r="B132" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C132" s="1">
@@ -11666,11 +11662,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="133" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B133" s="1">
+      <c r="B133" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C133" s="1">
@@ -11680,11 +11676,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="134" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B134" s="1">
+      <c r="B134" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C134" s="1">
@@ -11694,11 +11690,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="135" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B135" s="1">
+      <c r="B135" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C135" s="1">
@@ -11708,11 +11704,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="136" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B136" s="1">
+      <c r="B136" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C136" s="1">
@@ -11722,11 +11718,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="137" spans="1:32" s="1" customFormat="1" ht="252" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:32" ht="252" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B137" s="1">
+      <c r="B137" s="4">
         <v>4.2</v>
       </c>
       <c r="F137" s="1" t="s">
@@ -11811,11 +11807,11 @@
         <v>300</v>
       </c>
     </row>
-    <row r="138" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B138" s="1">
+      <c r="B138" s="4">
         <v>4.2</v>
       </c>
       <c r="C138" s="1">
@@ -11825,11 +11821,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="139" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B139" s="1">
+      <c r="B139" s="4">
         <v>4.2</v>
       </c>
       <c r="C139" s="1">
@@ -11839,11 +11835,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B140" s="1">
+      <c r="B140" s="4">
         <v>4.2</v>
       </c>
       <c r="C140" s="1">
@@ -11853,11 +11849,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="141" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B141" s="1">
+      <c r="B141" s="4">
         <v>4.2</v>
       </c>
       <c r="C141" s="1">
@@ -11867,11 +11863,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="142" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B142" s="1">
+      <c r="B142" s="4">
         <v>4.2</v>
       </c>
       <c r="C142" s="1">
@@ -11884,11 +11880,11 @@
         <v>286</v>
       </c>
     </row>
-    <row r="143" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B143" s="1">
+      <c r="B143" s="4">
         <v>4.2</v>
       </c>
       <c r="C143" s="1">
@@ -11898,11 +11894,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="144" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B144" s="1">
+      <c r="B144" s="4">
         <v>4.2</v>
       </c>
       <c r="C144" s="1">
@@ -11912,11 +11908,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="145" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B145" s="1">
+      <c r="B145" s="4">
         <v>4.2</v>
       </c>
       <c r="C145" s="1">
@@ -11926,11 +11922,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="146" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B146" s="1">
+      <c r="B146" s="4">
         <v>4.2</v>
       </c>
       <c r="C146" s="1">
@@ -11940,11 +11936,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="147" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B147" s="1">
+      <c r="B147" s="4">
         <v>4.2</v>
       </c>
       <c r="C147" s="1">
@@ -11954,11 +11950,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="148" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B148" s="1">
+      <c r="B148" s="4">
         <v>4.2</v>
       </c>
       <c r="C148" s="1">
@@ -11968,11 +11964,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="149" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B149" s="1">
+      <c r="B149" s="4">
         <v>4.2</v>
       </c>
       <c r="C149" s="1">
@@ -11982,11 +11978,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="150" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B150" s="1">
+      <c r="B150" s="4">
         <v>4.2</v>
       </c>
       <c r="C150" s="1">
@@ -11996,11 +11992,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="151" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B151" s="1">
+      <c r="B151" s="4">
         <v>4.2</v>
       </c>
       <c r="C151" s="1">
@@ -12010,11 +12006,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="152" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B152" s="1">
+      <c r="B152" s="4">
         <v>4.2</v>
       </c>
       <c r="C152" s="1">
@@ -12024,11 +12020,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="153" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B153" s="1">
+      <c r="B153" s="4">
         <v>4.2</v>
       </c>
       <c r="C153" s="1">
@@ -12038,11 +12034,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="154" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B154" s="1">
+      <c r="B154" s="4">
         <v>4.2</v>
       </c>
       <c r="C154" s="1">
@@ -12052,11 +12048,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="155" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B155" s="1">
+      <c r="B155" s="4">
         <v>4.2</v>
       </c>
       <c r="C155" s="1">
@@ -12066,11 +12062,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="156" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B156" s="1">
+      <c r="B156" s="4">
         <v>4.2</v>
       </c>
       <c r="C156" s="1">
@@ -12080,11 +12076,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="157" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B157" s="1">
+      <c r="B157" s="4">
         <v>4.2</v>
       </c>
       <c r="C157" s="1">
@@ -12094,11 +12090,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="158" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B158" s="1">
+      <c r="B158" s="4">
         <v>4.2</v>
       </c>
       <c r="C158" s="1">
@@ -12108,11 +12104,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="159" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B159" s="1">
+      <c r="B159" s="4">
         <v>4.2</v>
       </c>
       <c r="C159" s="1">
@@ -12122,11 +12118,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="160" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B160" s="1">
+      <c r="B160" s="4">
         <v>4.2</v>
       </c>
       <c r="C160" s="1">
@@ -12136,11 +12132,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="161" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B161" s="1">
+      <c r="B161" s="4">
         <v>4.2</v>
       </c>
       <c r="C161" s="1">
@@ -12150,11 +12146,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="162" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B162" s="1">
+      <c r="B162" s="4">
         <v>4.2</v>
       </c>
       <c r="C162" s="1">
@@ -12164,11 +12160,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="163" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B163" s="1">
+      <c r="B163" s="4">
         <v>4.2</v>
       </c>
       <c r="C163" s="1">
@@ -12178,11 +12174,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="164" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B164" s="1">
+      <c r="B164" s="4">
         <v>4.2</v>
       </c>
       <c r="C164" s="1">
@@ -12195,11 +12191,11 @@
         <v>286</v>
       </c>
     </row>
-    <row r="165" spans="1:32" s="1" customFormat="1" ht="252" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:32" ht="252" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B165" s="1">
+      <c r="B165" s="4">
         <v>4.3</v>
       </c>
       <c r="F165" s="1" t="s">
@@ -12284,11 +12280,11 @@
         <v>300</v>
       </c>
     </row>
-    <row r="166" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B166" s="1">
+      <c r="B166" s="4">
         <v>4.3</v>
       </c>
       <c r="E166" s="1" t="s">
@@ -12301,11 +12297,11 @@
         <v>265</v>
       </c>
     </row>
-    <row r="167" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B167" s="1">
+      <c r="B167" s="4">
         <v>4.3</v>
       </c>
       <c r="C167" s="1">
@@ -12315,11 +12311,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="168" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B168" s="1">
+      <c r="B168" s="4">
         <v>4.3</v>
       </c>
       <c r="C168" s="1">
@@ -12329,11 +12325,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="169" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B169" s="1">
+      <c r="B169" s="4">
         <v>4.3</v>
       </c>
       <c r="C169" s="1">
@@ -12343,11 +12339,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="170" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B170" s="1">
+      <c r="B170" s="4">
         <v>4.3</v>
       </c>
       <c r="C170" s="1">
@@ -12357,11 +12353,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="171" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B171" s="1">
+      <c r="B171" s="4">
         <v>4.3</v>
       </c>
       <c r="C171" s="1">
@@ -12371,11 +12367,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="172" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B172" s="1">
+      <c r="B172" s="4">
         <v>4.3</v>
       </c>
       <c r="C172" s="1">
@@ -12385,11 +12381,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="173" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B173" s="1">
+      <c r="B173" s="4">
         <v>4.3</v>
       </c>
       <c r="C173" s="1">
@@ -12399,11 +12395,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="174" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B174" s="1">
+      <c r="B174" s="4">
         <v>4.3</v>
       </c>
       <c r="C174" s="1">
@@ -12413,11 +12409,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="175" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B175" s="1">
+      <c r="B175" s="4">
         <v>4.3</v>
       </c>
       <c r="C175" s="1">
@@ -12427,11 +12423,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="176" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B176" s="1">
+      <c r="B176" s="4">
         <v>4.3</v>
       </c>
       <c r="C176" s="1">
@@ -12441,11 +12437,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="177" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B177" s="1">
+      <c r="B177" s="4">
         <v>4.3</v>
       </c>
       <c r="C177" s="1">
@@ -12455,11 +12451,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="178" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B178" s="1">
+      <c r="B178" s="4">
         <v>4.3</v>
       </c>
       <c r="C178" s="1">
@@ -12469,11 +12465,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="179" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B179" s="1">
+      <c r="B179" s="4">
         <v>4.3</v>
       </c>
       <c r="C179" s="1">
@@ -12483,11 +12479,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="180" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B180" s="1">
+      <c r="B180" s="4">
         <v>4.3</v>
       </c>
       <c r="C180" s="1">
@@ -12497,11 +12493,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="181" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B181" s="1">
+      <c r="B181" s="4">
         <v>4.3</v>
       </c>
       <c r="C181" s="1">
@@ -12511,11 +12507,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="182" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B182" s="1">
+      <c r="B182" s="4">
         <v>4.3</v>
       </c>
       <c r="C182" s="1">
@@ -12525,11 +12521,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="183" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B183" s="1">
+      <c r="B183" s="4">
         <v>4.3</v>
       </c>
       <c r="C183" s="1">
@@ -12539,11 +12535,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="184" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B184" s="1">
+      <c r="B184" s="4">
         <v>4.3</v>
       </c>
       <c r="C184" s="1">
@@ -12553,11 +12549,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="185" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B185" s="1">
+      <c r="B185" s="4">
         <v>4.3</v>
       </c>
       <c r="C185" s="1">
@@ -12567,11 +12563,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="186" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B186" s="1">
+      <c r="B186" s="4">
         <v>4.3</v>
       </c>
       <c r="C186" s="1">
@@ -12581,11 +12577,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="187" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B187" s="1">
+      <c r="B187" s="4">
         <v>4.3</v>
       </c>
       <c r="C187" s="1">
@@ -12595,11 +12591,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="188" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B188" s="1">
+      <c r="B188" s="4">
         <v>4.3</v>
       </c>
       <c r="C188" s="1">
@@ -12609,11 +12605,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="189" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B189" s="1">
+      <c r="B189" s="4">
         <v>4.3</v>
       </c>
       <c r="C189" s="1">
@@ -12623,11 +12619,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="190" spans="1:32" s="1" customFormat="1" ht="252" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:32" ht="252" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B190" s="1">
+      <c r="B190" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="F190" s="1" t="s">
@@ -12712,11 +12708,11 @@
         <v>300</v>
       </c>
     </row>
-    <row r="191" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B191" s="1">
+      <c r="B191" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C191" s="1">
@@ -12726,11 +12722,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="192" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B192" s="1">
+      <c r="B192" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C192" s="1">
@@ -12740,11 +12736,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="193" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B193" s="1">
+      <c r="B193" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C193" s="1">
@@ -12754,11 +12750,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="194" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B194" s="1">
+      <c r="B194" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C194" s="1">
@@ -12768,11 +12764,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="195" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B195" s="1">
+      <c r="B195" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C195" s="1">
@@ -12782,11 +12778,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="196" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B196" s="1">
+      <c r="B196" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C196" s="1">
@@ -12796,11 +12792,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="197" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B197" s="1">
+      <c r="B197" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C197" s="1">
@@ -12810,11 +12806,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="198" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B198" s="1">
+      <c r="B198" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C198" s="1">
@@ -12830,11 +12826,11 @@
         <v>269</v>
       </c>
     </row>
-    <row r="199" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B199" s="1">
+      <c r="B199" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C199" s="1">
@@ -12844,11 +12840,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="200" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B200" s="1">
+      <c r="B200" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C200" s="1">
@@ -12858,11 +12854,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="201" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B201" s="1">
+      <c r="B201" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C201" s="1">
@@ -12872,11 +12868,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="202" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B202" s="1">
+      <c r="B202" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C202" s="1">
@@ -12886,11 +12882,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="203" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B203" s="1">
+      <c r="B203" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C203" s="1">
@@ -12900,11 +12896,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="204" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B204" s="1">
+      <c r="B204" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C204" s="1">
@@ -12914,11 +12910,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="205" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B205" s="1">
+      <c r="B205" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C205" s="1">
@@ -12928,11 +12924,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="206" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B206" s="1">
+      <c r="B206" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C206" s="1">
@@ -12942,11 +12938,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="207" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B207" s="1">
+      <c r="B207" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C207" s="1">
@@ -12956,11 +12952,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="208" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B208" s="1">
+      <c r="B208" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C208" s="1">
@@ -12970,11 +12966,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="209" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B209" s="1">
+      <c r="B209" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C209" s="1">
@@ -12984,11 +12980,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="210" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B210" s="1">
+      <c r="B210" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C210" s="1">
@@ -12998,11 +12994,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="211" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B211" s="1">
+      <c r="B211" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C211" s="1">
@@ -13012,11 +13008,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="212" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B212" s="1">
+      <c r="B212" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C212" s="1">
@@ -13029,11 +13025,11 @@
         <v>270</v>
       </c>
     </row>
-    <row r="213" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B213" s="1">
+      <c r="B213" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C213" s="1">
@@ -13046,11 +13042,11 @@
         <v>270</v>
       </c>
     </row>
-    <row r="214" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B214" s="1">
+      <c r="B214" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C214" s="1">
@@ -13060,11 +13056,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="215" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B215" s="1">
+      <c r="B215" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C215" s="1">
@@ -13074,11 +13070,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="216" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B216" s="1">
+      <c r="B216" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C216" s="1">
@@ -13088,11 +13084,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="217" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B217" s="1">
+      <c r="B217" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C217" s="1">
@@ -13102,11 +13098,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="218" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B218" s="1">
+      <c r="B218" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C218" s="1">
@@ -13116,11 +13112,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="219" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B219" s="1">
+      <c r="B219" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C219" s="1">
@@ -13136,11 +13132,11 @@
         <v>269</v>
       </c>
     </row>
-    <row r="220" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B220" s="1">
+      <c r="B220" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C220" s="1">
@@ -13150,11 +13146,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="221" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B221" s="1">
+      <c r="B221" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C221" s="1">
@@ -13164,11 +13160,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="222" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B222" s="1">
+      <c r="B222" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C222" s="1">
@@ -13178,11 +13174,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="223" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B223" s="1">
+      <c r="B223" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C223" s="1">
@@ -13192,11 +13188,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="224" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B224" s="1">
+      <c r="B224" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C224" s="1">
@@ -13206,11 +13202,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="225" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B225" s="1">
+      <c r="B225" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C225" s="1">
@@ -13220,11 +13216,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="226" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B226" s="1">
+      <c r="B226" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C226" s="1">
@@ -13234,11 +13230,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="227" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B227" s="1">
+      <c r="B227" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C227" s="1">
@@ -13248,11 +13244,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="228" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B228" s="1">
+      <c r="B228" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C228" s="1">
@@ -13262,11 +13258,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="229" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B229" s="1">
+      <c r="B229" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C229" s="1">
@@ -13276,11 +13272,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="230" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B230" s="1">
+      <c r="B230" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C230" s="1">
@@ -13290,11 +13286,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="231" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B231" s="1">
+      <c r="B231" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C231" s="1">
@@ -13304,11 +13300,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="232" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B232" s="1">
+      <c r="B232" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C232" s="1">
@@ -13318,11 +13314,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="233" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B233" s="1">
+      <c r="B233" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C233" s="1">
@@ -13332,11 +13328,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="234" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B234" s="1">
+      <c r="B234" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C234" s="1">
@@ -13346,11 +13342,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="235" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B235" s="1">
+      <c r="B235" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C235" s="1">
@@ -13360,11 +13356,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="236" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B236" s="1">
+      <c r="B236" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C236" s="1">
@@ -13374,22 +13370,22 @@
         <v>138</v>
       </c>
     </row>
-    <row r="237" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B237" s="1">
+      <c r="B237" s="4">
         <v>5.2</v>
       </c>
       <c r="D237" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="238" spans="1:32" s="1" customFormat="1" ht="252" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:32" ht="252" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B238" s="1">
+      <c r="B238" s="4">
         <v>6.1</v>
       </c>
       <c r="F238" s="1" t="s">
@@ -13474,11 +13470,11 @@
         <v>300</v>
       </c>
     </row>
-    <row r="239" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B239" s="1">
+      <c r="B239" s="4">
         <v>6.1</v>
       </c>
       <c r="E239" s="1" t="s">
@@ -13491,11 +13487,11 @@
         <v>265</v>
       </c>
     </row>
-    <row r="240" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B240" s="1">
+      <c r="B240" s="4">
         <v>6.1</v>
       </c>
       <c r="C240" s="1">
@@ -13505,11 +13501,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="241" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B241" s="1">
+      <c r="B241" s="4">
         <v>6.1</v>
       </c>
       <c r="C241" s="1">
@@ -13519,11 +13515,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="242" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B242" s="1">
+      <c r="B242" s="4">
         <v>6.1</v>
       </c>
       <c r="C242" s="1">
@@ -13533,11 +13529,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="243" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B243" s="1">
+      <c r="B243" s="4">
         <v>6.1</v>
       </c>
       <c r="C243" s="1">
@@ -13547,11 +13543,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="244" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B244" s="1">
+      <c r="B244" s="4">
         <v>6.1</v>
       </c>
       <c r="C244" s="1">
@@ -13561,11 +13557,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="245" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B245" s="1">
+      <c r="B245" s="4">
         <v>6.1</v>
       </c>
       <c r="C245" s="1">
@@ -13575,11 +13571,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="246" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B246" s="1">
+      <c r="B246" s="4">
         <v>6.1</v>
       </c>
       <c r="C246" s="1">
@@ -13589,11 +13585,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="247" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B247" s="1">
+      <c r="B247" s="4">
         <v>6.1</v>
       </c>
       <c r="C247" s="1">
@@ -13603,11 +13599,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="248" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B248" s="1">
+      <c r="B248" s="4">
         <v>6.1</v>
       </c>
       <c r="C248" s="1">
@@ -13617,11 +13613,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="249" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B249" s="1">
+      <c r="B249" s="4">
         <v>6.1</v>
       </c>
       <c r="C249" s="1">
@@ -13631,11 +13627,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="250" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B250" s="1">
+      <c r="B250" s="4">
         <v>6.1</v>
       </c>
       <c r="C250" s="1">
@@ -13645,11 +13641,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="251" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B251" s="1">
+      <c r="B251" s="4">
         <v>6.1</v>
       </c>
       <c r="C251" s="1">
@@ -13659,11 +13655,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="252" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B252" s="1">
+      <c r="B252" s="4">
         <v>6.1</v>
       </c>
       <c r="C252" s="1">
@@ -13673,11 +13669,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="253" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B253" s="1">
+      <c r="B253" s="4">
         <v>6.1</v>
       </c>
       <c r="C253" s="1">
@@ -13687,11 +13683,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="254" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B254" s="1">
+      <c r="B254" s="4">
         <v>6.1</v>
       </c>
       <c r="C254" s="1">
@@ -13701,11 +13697,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="255" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B255" s="1">
+      <c r="B255" s="4">
         <v>6.1</v>
       </c>
       <c r="C255" s="1">
@@ -13715,11 +13711,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="256" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B256" s="1">
+      <c r="B256" s="4">
         <v>6.1</v>
       </c>
       <c r="C256" s="1">
@@ -13729,11 +13725,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="257" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B257" s="1">
+      <c r="B257" s="4">
         <v>6.1</v>
       </c>
       <c r="C257" s="1">
@@ -13743,11 +13739,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="258" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B258" s="1">
+      <c r="B258" s="4">
         <v>6.1</v>
       </c>
       <c r="C258" s="1">
@@ -13757,11 +13753,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="259" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B259" s="1">
+      <c r="B259" s="4">
         <v>6.1</v>
       </c>
       <c r="C259" s="1">
@@ -13771,33 +13767,33 @@
         <v>138</v>
       </c>
     </row>
-    <row r="260" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B260" s="1">
+      <c r="B260" s="4">
         <v>6.2</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="261" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B261" s="1">
+      <c r="B261" s="4">
         <v>7</v>
       </c>
       <c r="D261" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="262" spans="1:32" s="1" customFormat="1" ht="252" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:32" ht="252" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B262" s="1">
+      <c r="B262" s="4">
         <v>8</v>
       </c>
       <c r="F262" s="1" t="s">
@@ -13882,11 +13878,11 @@
         <v>300</v>
       </c>
     </row>
-    <row r="263" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B263" s="1">
+      <c r="B263" s="4">
         <v>8</v>
       </c>
       <c r="E263" s="1" t="s">
@@ -13899,11 +13895,11 @@
         <v>265</v>
       </c>
     </row>
-    <row r="264" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B264" s="1">
+      <c r="B264" s="4">
         <v>8</v>
       </c>
       <c r="C264" s="1">
@@ -13919,11 +13915,11 @@
         <v>269</v>
       </c>
     </row>
-    <row r="265" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B265" s="1">
+      <c r="B265" s="4">
         <v>8</v>
       </c>
       <c r="C265" s="1">
@@ -13933,11 +13929,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="266" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B266" s="1">
+      <c r="B266" s="4">
         <v>8</v>
       </c>
       <c r="C266" s="1">
@@ -13947,11 +13943,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="267" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B267" s="1">
+      <c r="B267" s="4">
         <v>8</v>
       </c>
       <c r="C267" s="1">
@@ -13961,11 +13957,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="268" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B268" s="1">
+      <c r="B268" s="4">
         <v>8</v>
       </c>
       <c r="C268" s="1">
@@ -13975,11 +13971,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="269" spans="1:32" s="1" customFormat="1" ht="252" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:32" ht="252" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B269" s="1">
+      <c r="B269" s="4">
         <v>9</v>
       </c>
       <c r="F269" s="1" t="s">
@@ -14064,11 +14060,11 @@
         <v>300</v>
       </c>
     </row>
-    <row r="270" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B270" s="1">
+      <c r="B270" s="4">
         <v>9</v>
       </c>
       <c r="C270" s="1">
@@ -14078,11 +14074,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="271" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B271" s="1">
+      <c r="B271" s="4">
         <v>9</v>
       </c>
       <c r="C271" s="1">
@@ -14095,11 +14091,11 @@
         <v>286</v>
       </c>
     </row>
-    <row r="272" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B272" s="1">
+      <c r="B272" s="4">
         <v>9</v>
       </c>
       <c r="C272" s="1">
@@ -14109,11 +14105,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="273" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B273" s="1">
+      <c r="B273" s="4">
         <v>9</v>
       </c>
       <c r="C273" s="1">
@@ -14123,11 +14119,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="274" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B274" s="1">
+      <c r="B274" s="4">
         <v>9</v>
       </c>
       <c r="C274" s="1">
@@ -14137,11 +14133,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="275" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B275" s="1">
+      <c r="B275" s="4">
         <v>9</v>
       </c>
       <c r="C275" s="1">
@@ -14151,11 +14147,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="276" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B276" s="1">
+      <c r="B276" s="4">
         <v>9</v>
       </c>
       <c r="C276" s="1">
@@ -14165,11 +14161,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="277" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B277" s="1">
+      <c r="B277" s="4">
         <v>9</v>
       </c>
       <c r="C277" s="1">
@@ -14182,11 +14178,11 @@
         <v>271</v>
       </c>
     </row>
-    <row r="278" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B278" s="1">
+      <c r="B278" s="4">
         <v>9</v>
       </c>
       <c r="C278" s="1">
@@ -14199,11 +14195,11 @@
         <v>272</v>
       </c>
     </row>
-    <row r="279" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B279" s="1">
+      <c r="B279" s="4">
         <v>9</v>
       </c>
       <c r="C279" s="1">
@@ -14216,11 +14212,11 @@
         <v>272</v>
       </c>
     </row>
-    <row r="280" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B280" s="1">
+      <c r="B280" s="4">
         <v>9</v>
       </c>
       <c r="C280" s="1">
@@ -14230,11 +14226,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="281" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B281" s="1">
+      <c r="B281" s="4">
         <v>9</v>
       </c>
       <c r="C281" s="1">
@@ -14244,11 +14240,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="282" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B282" s="1">
+      <c r="B282" s="4">
         <v>9</v>
       </c>
       <c r="C282" s="1">
@@ -14258,11 +14254,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="283" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B283" s="1">
+      <c r="B283" s="4">
         <v>9</v>
       </c>
       <c r="C283" s="1">
@@ -14275,11 +14271,6 @@
         <v>271</v>
       </c>
     </row>
-    <row r="284" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="285" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="286" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="287" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="288" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="289" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="290" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="291" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -24690,14 +24681,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c3e85fef-df06-4e67-8632-489752715f52" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6fd297-1f65-4950-8fc9-157e29c7b648">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24950,21 +24939,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c3e85fef-df06-4e67-8632-489752715f52" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6fd297-1f65-4950-8fc9-157e29c7b648">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98411DB4-5541-4967-8DBE-AF3E324DD5F5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171B3C16-7124-4B98-87E3-5FC6A9D45406}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c3e85fef-df06-4e67-8632-489752715f52"/>
-    <ds:schemaRef ds:uri="ea6fd297-1f65-4950-8fc9-157e29c7b648"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -24989,9 +24977,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171B3C16-7124-4B98-87E3-5FC6A9D45406}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98411DB4-5541-4967-8DBE-AF3E324DD5F5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c3e85fef-df06-4e67-8632-489752715f52"/>
+    <ds:schemaRef ds:uri="ea6fd297-1f65-4950-8fc9-157e29c7b648"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/dg_list.xlsx
+++ b/dg_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ialasia.sharepoint.com/sites/IALDGDESK/Shared Documents/General/Query System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="495" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B3ED574-85D2-475F-B819-D0ED22D3A0AC}"/>
+  <xr:revisionPtr revIDLastSave="500" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B22458AF-3C5A-4DE5-B6B6-808327CFB01C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="27630" windowHeight="16440" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="27630" windowHeight="16440" activeTab="6" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
   </bookViews>
   <sheets>
     <sheet name="IAL" sheetId="1" r:id="rId1"/>
@@ -1427,9 +1427,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1444,6 +1441,9 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9547,7 +9547,7 @@
       <c r="A2" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="4">
         <v>1</v>
       </c>
       <c r="C2" s="1"/>
@@ -14323,7 +14323,7 @@
       <c r="A2" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="14">
         <v>1</v>
       </c>
       <c r="C2" s="7"/>
@@ -14340,7 +14340,7 @@
       <c r="B3" s="9">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C3" s="10"/>
+      <c r="C3" s="9"/>
       <c r="D3" s="7" t="s">
         <v>138</v>
       </c>
@@ -14354,7 +14354,7 @@
       <c r="B4" s="9">
         <v>1.2</v>
       </c>
-      <c r="C4" s="10"/>
+      <c r="C4" s="9"/>
       <c r="D4" s="7" t="s">
         <v>138</v>
       </c>
@@ -14368,7 +14368,7 @@
       <c r="B5" s="9">
         <v>1.3</v>
       </c>
-      <c r="C5" s="10"/>
+      <c r="C5" s="9"/>
       <c r="D5" s="7" t="s">
         <v>138</v>
       </c>
@@ -14382,7 +14382,7 @@
       <c r="B6" s="9">
         <v>1.4</v>
       </c>
-      <c r="C6" s="10"/>
+      <c r="C6" s="9"/>
       <c r="D6" s="7" t="s">
         <v>138</v>
       </c>
@@ -14396,7 +14396,7 @@
       <c r="B7" s="9">
         <v>1.5</v>
       </c>
-      <c r="C7" s="10"/>
+      <c r="C7" s="9"/>
       <c r="D7" s="7" t="s">
         <v>138</v>
       </c>
@@ -14410,7 +14410,7 @@
       <c r="B8" s="9">
         <v>1.6</v>
       </c>
-      <c r="C8" s="11"/>
+      <c r="C8" s="10"/>
       <c r="D8" s="7" t="s">
         <v>138</v>
       </c>
@@ -14421,7 +14421,7 @@
       <c r="A9" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="14">
         <v>2.1</v>
       </c>
       <c r="C9" s="7">
@@ -14437,7 +14437,7 @@
       <c r="A10" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="14">
         <v>2.1</v>
       </c>
       <c r="C10" s="7">
@@ -14453,7 +14453,7 @@
       <c r="A11" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="14">
         <v>2.1</v>
       </c>
       <c r="C11" s="7">
@@ -14469,7 +14469,7 @@
       <c r="A12" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="14">
         <v>2.1</v>
       </c>
       <c r="C12" s="7">
@@ -14485,7 +14485,7 @@
       <c r="A13" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="14">
         <v>2.1</v>
       </c>
       <c r="C13" s="7">
@@ -14501,7 +14501,7 @@
       <c r="A14" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="14">
         <v>2.1</v>
       </c>
       <c r="C14" s="7">
@@ -14517,7 +14517,7 @@
       <c r="A15" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="14">
         <v>2.1</v>
       </c>
       <c r="C15" s="7">
@@ -14533,7 +14533,7 @@
       <c r="A16" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="14">
         <v>2.1</v>
       </c>
       <c r="C16" s="7">
@@ -14549,7 +14549,7 @@
       <c r="A17" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="14">
         <v>2.1</v>
       </c>
       <c r="C17" s="7">
@@ -14565,7 +14565,7 @@
       <c r="A18" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="14">
         <v>2.1</v>
       </c>
       <c r="C18" s="7">
@@ -14581,7 +14581,7 @@
       <c r="A19" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="14">
         <v>2.1</v>
       </c>
       <c r="C19" s="7">
@@ -14597,7 +14597,7 @@
       <c r="A20" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="14">
         <v>2.1</v>
       </c>
       <c r="C20" s="7">
@@ -14613,7 +14613,7 @@
       <c r="A21" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="14">
         <v>2.1</v>
       </c>
       <c r="C21" s="7">
@@ -14629,7 +14629,7 @@
       <c r="A22" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="14">
         <v>2.1</v>
       </c>
       <c r="C22" s="7">
@@ -14645,7 +14645,7 @@
       <c r="A23" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="14">
         <v>2.1</v>
       </c>
       <c r="C23" s="7">
@@ -14661,7 +14661,7 @@
       <c r="A24" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="14">
         <v>2.1</v>
       </c>
       <c r="C24" s="7">
@@ -14677,7 +14677,7 @@
       <c r="A25" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="14">
         <v>2.1</v>
       </c>
       <c r="C25" s="7">
@@ -14693,7 +14693,7 @@
       <c r="A26" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="14">
         <v>2.1</v>
       </c>
       <c r="C26" s="7">
@@ -14709,7 +14709,7 @@
       <c r="A27" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="14">
         <v>2.1</v>
       </c>
       <c r="C27" s="7">
@@ -14725,7 +14725,7 @@
       <c r="A28" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="14">
         <v>2.1</v>
       </c>
       <c r="C28" s="7">
@@ -14741,7 +14741,7 @@
       <c r="A29" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="14">
         <v>2.1</v>
       </c>
       <c r="C29" s="7">
@@ -14757,7 +14757,7 @@
       <c r="A30" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="14">
         <v>2.1</v>
       </c>
       <c r="C30" s="7">
@@ -14773,7 +14773,7 @@
       <c r="A31" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="14">
         <v>2.1</v>
       </c>
       <c r="C31" s="7">
@@ -14789,7 +14789,7 @@
       <c r="A32" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="14">
         <v>2.1</v>
       </c>
       <c r="C32" s="7">
@@ -14805,7 +14805,7 @@
       <c r="A33" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="14">
         <v>2.1</v>
       </c>
       <c r="C33" s="7">
@@ -14821,7 +14821,7 @@
       <c r="A34" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="14">
         <v>2.1</v>
       </c>
       <c r="C34" s="7">
@@ -14837,7 +14837,7 @@
       <c r="A35" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="14">
         <v>2.1</v>
       </c>
       <c r="C35" s="7">
@@ -14853,7 +14853,7 @@
       <c r="A36" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="14">
         <v>2.2000000000000002</v>
       </c>
       <c r="C36" s="7"/>
@@ -14869,7 +14869,7 @@
       <c r="A37" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C37" s="7"/>
@@ -14883,7 +14883,7 @@
       <c r="A38" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="14">
         <v>3</v>
       </c>
       <c r="C38" s="7">
@@ -14899,7 +14899,7 @@
       <c r="A39" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="14">
         <v>3</v>
       </c>
       <c r="C39" s="7">
@@ -14915,7 +14915,7 @@
       <c r="A40" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="14">
         <v>3</v>
       </c>
       <c r="C40" s="7">
@@ -14931,7 +14931,7 @@
       <c r="A41" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="14">
         <v>3</v>
       </c>
       <c r="C41" s="7">
@@ -14947,7 +14947,7 @@
       <c r="A42" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="14">
         <v>3</v>
       </c>
       <c r="C42" s="7">
@@ -14963,7 +14963,7 @@
       <c r="A43" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43" s="14">
         <v>3</v>
       </c>
       <c r="C43" s="7">
@@ -14979,7 +14979,7 @@
       <c r="A44" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="14">
         <v>3</v>
       </c>
       <c r="C44" s="7">
@@ -14995,7 +14995,7 @@
       <c r="A45" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="14">
         <v>3</v>
       </c>
       <c r="C45" s="7">
@@ -15011,7 +15011,7 @@
       <c r="A46" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46" s="14">
         <v>3</v>
       </c>
       <c r="C46" s="7">
@@ -15027,7 +15027,7 @@
       <c r="A47" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="14">
         <v>3</v>
       </c>
       <c r="C47" s="7">
@@ -15043,7 +15043,7 @@
       <c r="A48" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48" s="14">
         <v>3</v>
       </c>
       <c r="C48" s="7">
@@ -15059,7 +15059,7 @@
       <c r="A49" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="14">
         <v>3</v>
       </c>
       <c r="C49" s="7">
@@ -15075,7 +15075,7 @@
       <c r="A50" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="14">
         <v>3</v>
       </c>
       <c r="C50" s="7">
@@ -15091,7 +15091,7 @@
       <c r="A51" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B51" s="14">
         <v>3</v>
       </c>
       <c r="C51" s="7">
@@ -15107,7 +15107,7 @@
       <c r="A52" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="14">
         <v>3</v>
       </c>
       <c r="C52" s="7">
@@ -15123,7 +15123,7 @@
       <c r="A53" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B53" s="14">
         <v>3</v>
       </c>
       <c r="C53" s="7">
@@ -15139,7 +15139,7 @@
       <c r="A54" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="14">
         <v>3</v>
       </c>
       <c r="C54" s="7">
@@ -15155,7 +15155,7 @@
       <c r="A55" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="14">
         <v>3</v>
       </c>
       <c r="C55" s="7">
@@ -15171,7 +15171,7 @@
       <c r="A56" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="14">
         <v>3</v>
       </c>
       <c r="C56" s="7">
@@ -15187,7 +15187,7 @@
       <c r="A57" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B57" s="7">
+      <c r="B57" s="14">
         <v>3</v>
       </c>
       <c r="C57" s="7">
@@ -15203,7 +15203,7 @@
       <c r="A58" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B58" s="7">
+      <c r="B58" s="14">
         <v>3</v>
       </c>
       <c r="C58" s="7">
@@ -15219,7 +15219,7 @@
       <c r="A59" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B59" s="7">
+      <c r="B59" s="14">
         <v>3</v>
       </c>
       <c r="C59" s="7">
@@ -15235,7 +15235,7 @@
       <c r="A60" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="14">
         <v>3</v>
       </c>
       <c r="C60" s="7">
@@ -15251,7 +15251,7 @@
       <c r="A61" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B61" s="7">
+      <c r="B61" s="14">
         <v>3</v>
       </c>
       <c r="C61" s="7">
@@ -15267,7 +15267,7 @@
       <c r="A62" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B62" s="7">
+      <c r="B62" s="14">
         <v>3</v>
       </c>
       <c r="C62" s="7">
@@ -15283,7 +15283,7 @@
       <c r="A63" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B63" s="7">
+      <c r="B63" s="14">
         <v>3</v>
       </c>
       <c r="C63" s="7">
@@ -15299,7 +15299,7 @@
       <c r="A64" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B64" s="7">
+      <c r="B64" s="14">
         <v>3</v>
       </c>
       <c r="C64" s="7">
@@ -15315,7 +15315,7 @@
       <c r="A65" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B65" s="7">
+      <c r="B65" s="14">
         <v>3</v>
       </c>
       <c r="C65" s="7">
@@ -15331,7 +15331,7 @@
       <c r="A66" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B66" s="7">
+      <c r="B66" s="14">
         <v>3</v>
       </c>
       <c r="C66" s="7">
@@ -15347,7 +15347,7 @@
       <c r="A67" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B67" s="7">
+      <c r="B67" s="14">
         <v>3</v>
       </c>
       <c r="C67" s="7">
@@ -15363,7 +15363,7 @@
       <c r="A68" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B68" s="7">
+      <c r="B68" s="14">
         <v>3</v>
       </c>
       <c r="C68" s="7">
@@ -15379,7 +15379,7 @@
       <c r="A69" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B69" s="7">
+      <c r="B69" s="14">
         <v>3</v>
       </c>
       <c r="C69" s="7">
@@ -15395,7 +15395,7 @@
       <c r="A70" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="7">
+      <c r="B70" s="14">
         <v>3</v>
       </c>
       <c r="C70" s="7">
@@ -15411,7 +15411,7 @@
       <c r="A71" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B71" s="7">
+      <c r="B71" s="14">
         <v>3</v>
       </c>
       <c r="C71" s="7">
@@ -15427,7 +15427,7 @@
       <c r="A72" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B72" s="7">
+      <c r="B72" s="14">
         <v>3</v>
       </c>
       <c r="C72" s="7">
@@ -15443,7 +15443,7 @@
       <c r="A73" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B73" s="7">
+      <c r="B73" s="14">
         <v>3</v>
       </c>
       <c r="C73" s="7">
@@ -15459,7 +15459,7 @@
       <c r="A74" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B74" s="7">
+      <c r="B74" s="14">
         <v>3</v>
       </c>
       <c r="C74" s="7">
@@ -15475,7 +15475,7 @@
       <c r="A75" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B75" s="7">
+      <c r="B75" s="14">
         <v>3</v>
       </c>
       <c r="C75" s="7">
@@ -15491,7 +15491,7 @@
       <c r="A76" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B76" s="7">
+      <c r="B76" s="14">
         <v>3</v>
       </c>
       <c r="C76" s="7">
@@ -15507,7 +15507,7 @@
       <c r="A77" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B77" s="7">
+      <c r="B77" s="14">
         <v>3</v>
       </c>
       <c r="C77" s="7">
@@ -15523,7 +15523,7 @@
       <c r="A78" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B78" s="7">
+      <c r="B78" s="14">
         <v>3</v>
       </c>
       <c r="C78" s="7">
@@ -15539,7 +15539,7 @@
       <c r="A79" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B79" s="7">
+      <c r="B79" s="14">
         <v>3</v>
       </c>
       <c r="C79" s="7">
@@ -15555,7 +15555,7 @@
       <c r="A80" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B80" s="7">
+      <c r="B80" s="14">
         <v>3</v>
       </c>
       <c r="C80" s="7">
@@ -15571,7 +15571,7 @@
       <c r="A81" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B81" s="7">
+      <c r="B81" s="14">
         <v>3</v>
       </c>
       <c r="C81" s="7">
@@ -15587,7 +15587,7 @@
       <c r="A82" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B82" s="7">
+      <c r="B82" s="14">
         <v>3</v>
       </c>
       <c r="C82" s="7">
@@ -15603,7 +15603,7 @@
       <c r="A83" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B83" s="7">
+      <c r="B83" s="14">
         <v>3</v>
       </c>
       <c r="C83" s="7">
@@ -15619,7 +15619,7 @@
       <c r="A84" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B84" s="7">
+      <c r="B84" s="14">
         <v>3</v>
       </c>
       <c r="C84" s="7">
@@ -15635,7 +15635,7 @@
       <c r="A85" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B85" s="7">
+      <c r="B85" s="14">
         <v>3</v>
       </c>
       <c r="C85" s="7">
@@ -15651,7 +15651,7 @@
       <c r="A86" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B86" s="7">
+      <c r="B86" s="14">
         <v>3</v>
       </c>
       <c r="C86" s="7">
@@ -15667,7 +15667,7 @@
       <c r="A87" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B87" s="7">
+      <c r="B87" s="14">
         <v>3</v>
       </c>
       <c r="C87" s="7">
@@ -15683,7 +15683,7 @@
       <c r="A88" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B88" s="7">
+      <c r="B88" s="14">
         <v>3</v>
       </c>
       <c r="C88" s="7">
@@ -15699,7 +15699,7 @@
       <c r="A89" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B89" s="7">
+      <c r="B89" s="14">
         <v>3</v>
       </c>
       <c r="C89" s="7">
@@ -15715,7 +15715,7 @@
       <c r="A90" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B90" s="7">
+      <c r="B90" s="14">
         <v>3</v>
       </c>
       <c r="C90" s="7">
@@ -15731,7 +15731,7 @@
       <c r="A91" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B91" s="7">
+      <c r="B91" s="14">
         <v>3</v>
       </c>
       <c r="C91" s="7">
@@ -15747,7 +15747,7 @@
       <c r="A92" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B92" s="7">
+      <c r="B92" s="14">
         <v>3</v>
       </c>
       <c r="C92" s="7">
@@ -15763,7 +15763,7 @@
       <c r="A93" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B93" s="7">
+      <c r="B93" s="14">
         <v>3</v>
       </c>
       <c r="C93" s="7">
@@ -15779,7 +15779,7 @@
       <c r="A94" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B94" s="7">
+      <c r="B94" s="14">
         <v>3</v>
       </c>
       <c r="C94" s="7">
@@ -15795,7 +15795,7 @@
       <c r="A95" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B95" s="7">
+      <c r="B95" s="14">
         <v>3</v>
       </c>
       <c r="C95" s="7">
@@ -15811,7 +15811,7 @@
       <c r="A96" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B96" s="7">
+      <c r="B96" s="14">
         <v>3</v>
       </c>
       <c r="C96" s="7">
@@ -15827,7 +15827,7 @@
       <c r="A97" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B97" s="7">
+      <c r="B97" s="14">
         <v>3</v>
       </c>
       <c r="C97" s="7">
@@ -15843,7 +15843,7 @@
       <c r="A98" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B98" s="7">
+      <c r="B98" s="14">
         <v>3</v>
       </c>
       <c r="C98" s="7">
@@ -15859,7 +15859,7 @@
       <c r="A99" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B99" s="7">
+      <c r="B99" s="14">
         <v>3</v>
       </c>
       <c r="C99" s="7">
@@ -15875,7 +15875,7 @@
       <c r="A100" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B100" s="7">
+      <c r="B100" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C100" s="7">
@@ -15891,7 +15891,7 @@
       <c r="A101" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B101" s="7">
+      <c r="B101" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C101" s="7">
@@ -15907,7 +15907,7 @@
       <c r="A102" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B102" s="7">
+      <c r="B102" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C102" s="7">
@@ -15923,7 +15923,7 @@
       <c r="A103" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B103" s="7">
+      <c r="B103" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C103" s="7">
@@ -15939,7 +15939,7 @@
       <c r="A104" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B104" s="7">
+      <c r="B104" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C104" s="7">
@@ -15955,7 +15955,7 @@
       <c r="A105" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B105" s="7">
+      <c r="B105" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C105" s="7">
@@ -15971,7 +15971,7 @@
       <c r="A106" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B106" s="7">
+      <c r="B106" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C106" s="7">
@@ -15987,7 +15987,7 @@
       <c r="A107" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B107" s="7">
+      <c r="B107" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C107" s="7">
@@ -16003,7 +16003,7 @@
       <c r="A108" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B108" s="7">
+      <c r="B108" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C108" s="7">
@@ -16019,7 +16019,7 @@
       <c r="A109" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B109" s="7">
+      <c r="B109" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C109" s="7">
@@ -16035,7 +16035,7 @@
       <c r="A110" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B110" s="7">
+      <c r="B110" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C110" s="7">
@@ -16051,7 +16051,7 @@
       <c r="A111" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B111" s="7">
+      <c r="B111" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C111" s="7">
@@ -16067,7 +16067,7 @@
       <c r="A112" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B112" s="7">
+      <c r="B112" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C112" s="7">
@@ -16083,7 +16083,7 @@
       <c r="A113" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B113" s="7">
+      <c r="B113" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C113" s="7">
@@ -16099,7 +16099,7 @@
       <c r="A114" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B114" s="7">
+      <c r="B114" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C114" s="7">
@@ -16115,7 +16115,7 @@
       <c r="A115" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B115" s="7">
+      <c r="B115" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C115" s="7">
@@ -16131,7 +16131,7 @@
       <c r="A116" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B116" s="7">
+      <c r="B116" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C116" s="7">
@@ -16147,7 +16147,7 @@
       <c r="A117" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B117" s="7">
+      <c r="B117" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C117" s="7">
@@ -16163,7 +16163,7 @@
       <c r="A118" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B118" s="7">
+      <c r="B118" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C118" s="7">
@@ -16179,7 +16179,7 @@
       <c r="A119" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B119" s="7">
+      <c r="B119" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C119" s="7">
@@ -16195,7 +16195,7 @@
       <c r="A120" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B120" s="7">
+      <c r="B120" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C120" s="7">
@@ -16211,7 +16211,7 @@
       <c r="A121" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B121" s="7">
+      <c r="B121" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C121" s="7">
@@ -16227,7 +16227,7 @@
       <c r="A122" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B122" s="7">
+      <c r="B122" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C122" s="7">
@@ -16243,7 +16243,7 @@
       <c r="A123" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B123" s="7">
+      <c r="B123" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C123" s="7">
@@ -16259,7 +16259,7 @@
       <c r="A124" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B124" s="7">
+      <c r="B124" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C124" s="7">
@@ -16275,7 +16275,7 @@
       <c r="A125" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B125" s="7">
+      <c r="B125" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C125" s="7">
@@ -16291,7 +16291,7 @@
       <c r="A126" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B126" s="7">
+      <c r="B126" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C126" s="7">
@@ -16307,7 +16307,7 @@
       <c r="A127" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B127" s="7">
+      <c r="B127" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C127" s="7">
@@ -16323,7 +16323,7 @@
       <c r="A128" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B128" s="7">
+      <c r="B128" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C128" s="7">
@@ -16339,7 +16339,7 @@
       <c r="A129" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B129" s="7">
+      <c r="B129" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C129" s="7">
@@ -16355,7 +16355,7 @@
       <c r="A130" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B130" s="7">
+      <c r="B130" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C130" s="7">
@@ -16371,7 +16371,7 @@
       <c r="A131" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B131" s="7">
+      <c r="B131" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C131" s="7">
@@ -16387,7 +16387,7 @@
       <c r="A132" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B132" s="7">
+      <c r="B132" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C132" s="7">
@@ -16403,7 +16403,7 @@
       <c r="A133" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B133" s="7">
+      <c r="B133" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C133" s="7">
@@ -16419,7 +16419,7 @@
       <c r="A134" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B134" s="7">
+      <c r="B134" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C134" s="7">
@@ -16435,7 +16435,7 @@
       <c r="A135" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B135" s="7">
+      <c r="B135" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C135" s="7">
@@ -16451,7 +16451,7 @@
       <c r="A136" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B136" s="7">
+      <c r="B136" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C136" s="7">
@@ -16467,7 +16467,7 @@
       <c r="A137" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B137" s="7">
+      <c r="B137" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C137" s="7">
@@ -16483,7 +16483,7 @@
       <c r="A138" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B138" s="7">
+      <c r="B138" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C138" s="7">
@@ -16499,7 +16499,7 @@
       <c r="A139" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B139" s="7">
+      <c r="B139" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C139" s="7">
@@ -16515,7 +16515,7 @@
       <c r="A140" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B140" s="7">
+      <c r="B140" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C140" s="7">
@@ -16531,7 +16531,7 @@
       <c r="A141" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B141" s="7">
+      <c r="B141" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C141" s="7">
@@ -16547,7 +16547,7 @@
       <c r="A142" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B142" s="7">
+      <c r="B142" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C142" s="7">
@@ -16563,7 +16563,7 @@
       <c r="A143" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B143" s="7">
+      <c r="B143" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C143" s="7">
@@ -16579,7 +16579,7 @@
       <c r="A144" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B144" s="7">
+      <c r="B144" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C144" s="7">
@@ -16595,7 +16595,7 @@
       <c r="A145" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B145" s="7">
+      <c r="B145" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C145" s="7">
@@ -16611,7 +16611,7 @@
       <c r="A146" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B146" s="7">
+      <c r="B146" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C146" s="7">
@@ -16627,7 +16627,7 @@
       <c r="A147" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B147" s="7">
+      <c r="B147" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C147" s="7">
@@ -16643,7 +16643,7 @@
       <c r="A148" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B148" s="7">
+      <c r="B148" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C148" s="7">
@@ -16659,7 +16659,7 @@
       <c r="A149" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B149" s="7">
+      <c r="B149" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C149" s="7">
@@ -16675,7 +16675,7 @@
       <c r="A150" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B150" s="7">
+      <c r="B150" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C150" s="7">
@@ -16691,7 +16691,7 @@
       <c r="A151" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B151" s="7">
+      <c r="B151" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C151" s="7">
@@ -16707,7 +16707,7 @@
       <c r="A152" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B152" s="7">
+      <c r="B152" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C152" s="7">
@@ -16723,7 +16723,7 @@
       <c r="A153" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B153" s="7">
+      <c r="B153" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C153" s="7">
@@ -16739,7 +16739,7 @@
       <c r="A154" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B154" s="7">
+      <c r="B154" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C154" s="7">
@@ -16755,7 +16755,7 @@
       <c r="A155" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B155" s="7">
+      <c r="B155" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C155" s="7">
@@ -16771,7 +16771,7 @@
       <c r="A156" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B156" s="7">
+      <c r="B156" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C156" s="7">
@@ -16787,7 +16787,7 @@
       <c r="A157" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B157" s="7">
+      <c r="B157" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C157" s="7">
@@ -16803,7 +16803,7 @@
       <c r="A158" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B158" s="7">
+      <c r="B158" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C158" s="7">
@@ -16819,7 +16819,7 @@
       <c r="A159" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B159" s="7">
+      <c r="B159" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C159" s="7">
@@ -16835,7 +16835,7 @@
       <c r="A160" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B160" s="7">
+      <c r="B160" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C160" s="7">
@@ -16851,7 +16851,7 @@
       <c r="A161" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B161" s="7">
+      <c r="B161" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C161" s="7">
@@ -16867,7 +16867,7 @@
       <c r="A162" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B162" s="7">
+      <c r="B162" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C162" s="7">
@@ -16883,7 +16883,7 @@
       <c r="A163" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B163" s="7">
+      <c r="B163" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C163" s="7">
@@ -16899,7 +16899,7 @@
       <c r="A164" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B164" s="7">
+      <c r="B164" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C164" s="7">
@@ -16915,7 +16915,7 @@
       <c r="A165" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B165" s="7">
+      <c r="B165" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C165" s="7">
@@ -16931,7 +16931,7 @@
       <c r="A166" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B166" s="7">
+      <c r="B166" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C166" s="7">
@@ -16947,7 +16947,7 @@
       <c r="A167" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B167" s="7">
+      <c r="B167" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C167" s="7">
@@ -16963,7 +16963,7 @@
       <c r="A168" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B168" s="7">
+      <c r="B168" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C168" s="7">
@@ -16979,7 +16979,7 @@
       <c r="A169" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B169" s="7">
+      <c r="B169" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C169" s="7">
@@ -16995,7 +16995,7 @@
       <c r="A170" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B170" s="7">
+      <c r="B170" s="14">
         <v>4.2</v>
       </c>
       <c r="C170" s="7">
@@ -17011,7 +17011,7 @@
       <c r="A171" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B171" s="7">
+      <c r="B171" s="14">
         <v>4.2</v>
       </c>
       <c r="C171" s="7">
@@ -17027,7 +17027,7 @@
       <c r="A172" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B172" s="7">
+      <c r="B172" s="14">
         <v>4.2</v>
       </c>
       <c r="C172" s="7">
@@ -17043,7 +17043,7 @@
       <c r="A173" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B173" s="7">
+      <c r="B173" s="14">
         <v>4.2</v>
       </c>
       <c r="C173" s="7">
@@ -17059,7 +17059,7 @@
       <c r="A174" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B174" s="7">
+      <c r="B174" s="14">
         <v>4.2</v>
       </c>
       <c r="C174" s="7">
@@ -17075,7 +17075,7 @@
       <c r="A175" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B175" s="7">
+      <c r="B175" s="14">
         <v>4.2</v>
       </c>
       <c r="C175" s="7">
@@ -17091,7 +17091,7 @@
       <c r="A176" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B176" s="7">
+      <c r="B176" s="14">
         <v>4.2</v>
       </c>
       <c r="C176" s="7">
@@ -17107,7 +17107,7 @@
       <c r="A177" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B177" s="7">
+      <c r="B177" s="14">
         <v>4.2</v>
       </c>
       <c r="C177" s="7">
@@ -17123,7 +17123,7 @@
       <c r="A178" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B178" s="7">
+      <c r="B178" s="14">
         <v>4.2</v>
       </c>
       <c r="C178" s="7">
@@ -17139,7 +17139,7 @@
       <c r="A179" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B179" s="7">
+      <c r="B179" s="14">
         <v>4.2</v>
       </c>
       <c r="C179" s="7">
@@ -17155,7 +17155,7 @@
       <c r="A180" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B180" s="7">
+      <c r="B180" s="14">
         <v>4.2</v>
       </c>
       <c r="C180" s="7">
@@ -17171,7 +17171,7 @@
       <c r="A181" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B181" s="7">
+      <c r="B181" s="14">
         <v>4.2</v>
       </c>
       <c r="C181" s="7">
@@ -17187,7 +17187,7 @@
       <c r="A182" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B182" s="7">
+      <c r="B182" s="14">
         <v>4.2</v>
       </c>
       <c r="C182" s="7">
@@ -17203,7 +17203,7 @@
       <c r="A183" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B183" s="7">
+      <c r="B183" s="14">
         <v>4.2</v>
       </c>
       <c r="C183" s="7">
@@ -17219,7 +17219,7 @@
       <c r="A184" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B184" s="7">
+      <c r="B184" s="14">
         <v>4.2</v>
       </c>
       <c r="C184" s="7">
@@ -17235,7 +17235,7 @@
       <c r="A185" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B185" s="7">
+      <c r="B185" s="14">
         <v>4.2</v>
       </c>
       <c r="C185" s="7">
@@ -17251,7 +17251,7 @@
       <c r="A186" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B186" s="7">
+      <c r="B186" s="14">
         <v>4.2</v>
       </c>
       <c r="C186" s="7">
@@ -17267,7 +17267,7 @@
       <c r="A187" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B187" s="7">
+      <c r="B187" s="14">
         <v>4.2</v>
       </c>
       <c r="C187" s="7">
@@ -17283,7 +17283,7 @@
       <c r="A188" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B188" s="7">
+      <c r="B188" s="14">
         <v>4.2</v>
       </c>
       <c r="C188" s="7">
@@ -17299,7 +17299,7 @@
       <c r="A189" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B189" s="7">
+      <c r="B189" s="14">
         <v>4.2</v>
       </c>
       <c r="C189" s="7">
@@ -17315,7 +17315,7 @@
       <c r="A190" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B190" s="7">
+      <c r="B190" s="14">
         <v>4.2</v>
       </c>
       <c r="C190" s="7">
@@ -17331,7 +17331,7 @@
       <c r="A191" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B191" s="7">
+      <c r="B191" s="14">
         <v>4.2</v>
       </c>
       <c r="C191" s="7">
@@ -17347,7 +17347,7 @@
       <c r="A192" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B192" s="7">
+      <c r="B192" s="14">
         <v>4.2</v>
       </c>
       <c r="C192" s="7">
@@ -17363,7 +17363,7 @@
       <c r="A193" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B193" s="7">
+      <c r="B193" s="14">
         <v>4.2</v>
       </c>
       <c r="C193" s="7">
@@ -17379,7 +17379,7 @@
       <c r="A194" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B194" s="7">
+      <c r="B194" s="14">
         <v>4.2</v>
       </c>
       <c r="C194" s="7">
@@ -17395,7 +17395,7 @@
       <c r="A195" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B195" s="7">
+      <c r="B195" s="14">
         <v>4.2</v>
       </c>
       <c r="C195" s="7">
@@ -17411,7 +17411,7 @@
       <c r="A196" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B196" s="7">
+      <c r="B196" s="14">
         <v>4.2</v>
       </c>
       <c r="C196" s="7">
@@ -17427,7 +17427,7 @@
       <c r="A197" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B197" s="7">
+      <c r="B197" s="14">
         <v>4.2</v>
       </c>
       <c r="C197" s="7">
@@ -17443,7 +17443,7 @@
       <c r="A198" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B198" s="7">
+      <c r="B198" s="14">
         <v>4.2</v>
       </c>
       <c r="C198" s="7">
@@ -17459,7 +17459,7 @@
       <c r="A199" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B199" s="7">
+      <c r="B199" s="14">
         <v>4.2</v>
       </c>
       <c r="C199" s="7">
@@ -17475,7 +17475,7 @@
       <c r="A200" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B200" s="7">
+      <c r="B200" s="14">
         <v>4.2</v>
       </c>
       <c r="C200" s="7">
@@ -17491,7 +17491,7 @@
       <c r="A201" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B201" s="7">
+      <c r="B201" s="14">
         <v>4.2</v>
       </c>
       <c r="C201" s="7">
@@ -17507,7 +17507,7 @@
       <c r="A202" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B202" s="7">
+      <c r="B202" s="14">
         <v>4.3</v>
       </c>
       <c r="C202" s="7"/>
@@ -17521,7 +17521,7 @@
       <c r="A203" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B203" s="7">
+      <c r="B203" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C203" s="7">
@@ -17537,7 +17537,7 @@
       <c r="A204" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B204" s="7">
+      <c r="B204" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C204" s="7">
@@ -17553,7 +17553,7 @@
       <c r="A205" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B205" s="7">
+      <c r="B205" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C205" s="7">
@@ -17569,7 +17569,7 @@
       <c r="A206" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B206" s="7">
+      <c r="B206" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C206" s="7">
@@ -17585,7 +17585,7 @@
       <c r="A207" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B207" s="7">
+      <c r="B207" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C207" s="7">
@@ -17601,7 +17601,7 @@
       <c r="A208" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B208" s="7">
+      <c r="B208" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C208" s="7">
@@ -17617,7 +17617,7 @@
       <c r="A209" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B209" s="7">
+      <c r="B209" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C209" s="7">
@@ -17633,7 +17633,7 @@
       <c r="A210" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B210" s="7">
+      <c r="B210" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C210" s="7">
@@ -17649,7 +17649,7 @@
       <c r="A211" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B211" s="7">
+      <c r="B211" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C211" s="7">
@@ -17665,7 +17665,7 @@
       <c r="A212" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B212" s="7">
+      <c r="B212" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C212" s="7">
@@ -17681,7 +17681,7 @@
       <c r="A213" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B213" s="7">
+      <c r="B213" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C213" s="7">
@@ -17697,7 +17697,7 @@
       <c r="A214" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B214" s="7">
+      <c r="B214" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C214" s="7">
@@ -17713,7 +17713,7 @@
       <c r="A215" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B215" s="7">
+      <c r="B215" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C215" s="7">
@@ -17729,7 +17729,7 @@
       <c r="A216" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B216" s="7">
+      <c r="B216" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C216" s="7">
@@ -17745,7 +17745,7 @@
       <c r="A217" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B217" s="7">
+      <c r="B217" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C217" s="7">
@@ -17761,7 +17761,7 @@
       <c r="A218" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B218" s="7">
+      <c r="B218" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C218" s="7">
@@ -17777,7 +17777,7 @@
       <c r="A219" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B219" s="7">
+      <c r="B219" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C219" s="7">
@@ -17793,7 +17793,7 @@
       <c r="A220" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B220" s="7">
+      <c r="B220" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C220" s="7">
@@ -17809,7 +17809,7 @@
       <c r="A221" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B221" s="7">
+      <c r="B221" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C221" s="7">
@@ -17825,7 +17825,7 @@
       <c r="A222" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B222" s="7">
+      <c r="B222" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C222" s="7">
@@ -17841,7 +17841,7 @@
       <c r="A223" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B223" s="7">
+      <c r="B223" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C223" s="7">
@@ -17857,7 +17857,7 @@
       <c r="A224" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B224" s="7">
+      <c r="B224" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C224" s="7">
@@ -17873,7 +17873,7 @@
       <c r="A225" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B225" s="7">
+      <c r="B225" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C225" s="7">
@@ -17889,7 +17889,7 @@
       <c r="A226" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B226" s="7">
+      <c r="B226" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C226" s="7">
@@ -17905,7 +17905,7 @@
       <c r="A227" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B227" s="7">
+      <c r="B227" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C227" s="7">
@@ -17921,7 +17921,7 @@
       <c r="A228" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B228" s="7">
+      <c r="B228" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C228" s="7">
@@ -17937,7 +17937,7 @@
       <c r="A229" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B229" s="7">
+      <c r="B229" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C229" s="7">
@@ -17953,7 +17953,7 @@
       <c r="A230" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B230" s="7">
+      <c r="B230" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C230" s="7">
@@ -17969,7 +17969,7 @@
       <c r="A231" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B231" s="7">
+      <c r="B231" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C231" s="7">
@@ -17985,7 +17985,7 @@
       <c r="A232" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B232" s="7">
+      <c r="B232" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C232" s="7">
@@ -18001,7 +18001,7 @@
       <c r="A233" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B233" s="7">
+      <c r="B233" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C233" s="7">
@@ -18017,7 +18017,7 @@
       <c r="A234" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B234" s="7">
+      <c r="B234" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C234" s="7">
@@ -18033,7 +18033,7 @@
       <c r="A235" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B235" s="7">
+      <c r="B235" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C235" s="7">
@@ -18049,7 +18049,7 @@
       <c r="A236" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B236" s="7">
+      <c r="B236" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C236" s="7">
@@ -18065,7 +18065,7 @@
       <c r="A237" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B237" s="7">
+      <c r="B237" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C237" s="7">
@@ -18081,7 +18081,7 @@
       <c r="A238" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B238" s="7">
+      <c r="B238" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C238" s="7">
@@ -18097,7 +18097,7 @@
       <c r="A239" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B239" s="7">
+      <c r="B239" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C239" s="7">
@@ -18113,7 +18113,7 @@
       <c r="A240" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B240" s="7">
+      <c r="B240" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C240" s="7">
@@ -18129,7 +18129,7 @@
       <c r="A241" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B241" s="7">
+      <c r="B241" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C241" s="7">
@@ -18145,7 +18145,7 @@
       <c r="A242" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B242" s="7">
+      <c r="B242" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C242" s="7">
@@ -18161,7 +18161,7 @@
       <c r="A243" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B243" s="7">
+      <c r="B243" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C243" s="7">
@@ -18177,7 +18177,7 @@
       <c r="A244" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B244" s="7">
+      <c r="B244" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C244" s="7">
@@ -18193,7 +18193,7 @@
       <c r="A245" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B245" s="7">
+      <c r="B245" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C245" s="7">
@@ -18209,7 +18209,7 @@
       <c r="A246" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B246" s="7">
+      <c r="B246" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C246" s="7">
@@ -18225,7 +18225,7 @@
       <c r="A247" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B247" s="7">
+      <c r="B247" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C247" s="7">
@@ -18241,7 +18241,7 @@
       <c r="A248" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B248" s="7">
+      <c r="B248" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C248" s="7">
@@ -18257,7 +18257,7 @@
       <c r="A249" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B249" s="7">
+      <c r="B249" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C249" s="7">
@@ -18273,7 +18273,7 @@
       <c r="A250" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B250" s="7">
+      <c r="B250" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C250" s="7">
@@ -18289,7 +18289,7 @@
       <c r="A251" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B251" s="7">
+      <c r="B251" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C251" s="7">
@@ -18305,7 +18305,7 @@
       <c r="A252" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B252" s="7">
+      <c r="B252" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C252" s="7">
@@ -18321,7 +18321,7 @@
       <c r="A253" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B253" s="7">
+      <c r="B253" s="14">
         <v>5.2</v>
       </c>
       <c r="C253" s="7"/>
@@ -18335,7 +18335,7 @@
       <c r="A254" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B254" s="7">
+      <c r="B254" s="14">
         <v>6.1</v>
       </c>
       <c r="C254" s="7">
@@ -18351,7 +18351,7 @@
       <c r="A255" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B255" s="7">
+      <c r="B255" s="14">
         <v>6.1</v>
       </c>
       <c r="C255" s="7">
@@ -18367,7 +18367,7 @@
       <c r="A256" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B256" s="7">
+      <c r="B256" s="14">
         <v>6.1</v>
       </c>
       <c r="C256" s="7">
@@ -18383,7 +18383,7 @@
       <c r="A257" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B257" s="7">
+      <c r="B257" s="14">
         <v>6.1</v>
       </c>
       <c r="C257" s="7">
@@ -18399,7 +18399,7 @@
       <c r="A258" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B258" s="7">
+      <c r="B258" s="14">
         <v>6.1</v>
       </c>
       <c r="C258" s="7">
@@ -18415,7 +18415,7 @@
       <c r="A259" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B259" s="7">
+      <c r="B259" s="14">
         <v>6.1</v>
       </c>
       <c r="C259" s="7">
@@ -18431,7 +18431,7 @@
       <c r="A260" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B260" s="7">
+      <c r="B260" s="14">
         <v>6.1</v>
       </c>
       <c r="C260" s="7">
@@ -18447,7 +18447,7 @@
       <c r="A261" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B261" s="7">
+      <c r="B261" s="14">
         <v>6.1</v>
       </c>
       <c r="C261" s="7">
@@ -18463,7 +18463,7 @@
       <c r="A262" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B262" s="7">
+      <c r="B262" s="14">
         <v>6.1</v>
       </c>
       <c r="C262" s="7">
@@ -18479,7 +18479,7 @@
       <c r="A263" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B263" s="7">
+      <c r="B263" s="14">
         <v>6.1</v>
       </c>
       <c r="C263" s="7">
@@ -18495,7 +18495,7 @@
       <c r="A264" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B264" s="7">
+      <c r="B264" s="14">
         <v>6.1</v>
       </c>
       <c r="C264" s="7">
@@ -18511,7 +18511,7 @@
       <c r="A265" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B265" s="7">
+      <c r="B265" s="14">
         <v>6.1</v>
       </c>
       <c r="C265" s="7">
@@ -18527,7 +18527,7 @@
       <c r="A266" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B266" s="7">
+      <c r="B266" s="14">
         <v>6.1</v>
       </c>
       <c r="C266" s="7">
@@ -18543,7 +18543,7 @@
       <c r="A267" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B267" s="7">
+      <c r="B267" s="14">
         <v>6.1</v>
       </c>
       <c r="C267" s="7">
@@ -18559,7 +18559,7 @@
       <c r="A268" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B268" s="7">
+      <c r="B268" s="14">
         <v>6.1</v>
       </c>
       <c r="C268" s="7">
@@ -18575,7 +18575,7 @@
       <c r="A269" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B269" s="7">
+      <c r="B269" s="14">
         <v>6.1</v>
       </c>
       <c r="C269" s="7">
@@ -18591,7 +18591,7 @@
       <c r="A270" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B270" s="7">
+      <c r="B270" s="14">
         <v>6.1</v>
       </c>
       <c r="C270" s="7">
@@ -18607,7 +18607,7 @@
       <c r="A271" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B271" s="7">
+      <c r="B271" s="14">
         <v>6.1</v>
       </c>
       <c r="C271" s="7">
@@ -18623,7 +18623,7 @@
       <c r="A272" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B272" s="7">
+      <c r="B272" s="14">
         <v>6.1</v>
       </c>
       <c r="C272" s="7">
@@ -18639,7 +18639,7 @@
       <c r="A273" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B273" s="7">
+      <c r="B273" s="14">
         <v>6.1</v>
       </c>
       <c r="C273" s="7">
@@ -18655,7 +18655,7 @@
       <c r="A274" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B274" s="7">
+      <c r="B274" s="14">
         <v>6.1</v>
       </c>
       <c r="C274" s="7">
@@ -18671,7 +18671,7 @@
       <c r="A275" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B275" s="7">
+      <c r="B275" s="14">
         <v>6.1</v>
       </c>
       <c r="C275" s="7">
@@ -18687,7 +18687,7 @@
       <c r="A276" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B276" s="7">
+      <c r="B276" s="14">
         <v>6.1</v>
       </c>
       <c r="C276" s="7">
@@ -18703,7 +18703,7 @@
       <c r="A277" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B277" s="7">
+      <c r="B277" s="14">
         <v>6.1</v>
       </c>
       <c r="C277" s="7">
@@ -18719,7 +18719,7 @@
       <c r="A278" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B278" s="7">
+      <c r="B278" s="14">
         <v>6.1</v>
       </c>
       <c r="C278" s="7">
@@ -18735,7 +18735,7 @@
       <c r="A279" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B279" s="7">
+      <c r="B279" s="14">
         <v>6.1</v>
       </c>
       <c r="C279" s="7">
@@ -18751,7 +18751,7 @@
       <c r="A280" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B280" s="7">
+      <c r="B280" s="14">
         <v>6.1</v>
       </c>
       <c r="C280" s="7">
@@ -18767,7 +18767,7 @@
       <c r="A281" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B281" s="7">
+      <c r="B281" s="14">
         <v>6.1</v>
       </c>
       <c r="C281" s="7">
@@ -18783,7 +18783,7 @@
       <c r="A282" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B282" s="7">
+      <c r="B282" s="14">
         <v>6.1</v>
       </c>
       <c r="C282" s="7">
@@ -18799,7 +18799,7 @@
       <c r="A283" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B283" s="7">
+      <c r="B283" s="14">
         <v>6.1</v>
       </c>
       <c r="C283" s="7">
@@ -18815,7 +18815,7 @@
       <c r="A284" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B284" s="7">
+      <c r="B284" s="14">
         <v>6.1</v>
       </c>
       <c r="C284" s="7">
@@ -18831,7 +18831,7 @@
       <c r="A285" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B285" s="7">
+      <c r="B285" s="14">
         <v>6.1</v>
       </c>
       <c r="C285" s="7">
@@ -18847,7 +18847,7 @@
       <c r="A286" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B286" s="7">
+      <c r="B286" s="14">
         <v>6.1</v>
       </c>
       <c r="C286" s="7">
@@ -18863,7 +18863,7 @@
       <c r="A287" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B287" s="7">
+      <c r="B287" s="14">
         <v>6.1</v>
       </c>
       <c r="C287" s="7">
@@ -18879,7 +18879,7 @@
       <c r="A288" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B288" s="7">
+      <c r="B288" s="14">
         <v>6.1</v>
       </c>
       <c r="C288" s="7">
@@ -18895,7 +18895,7 @@
       <c r="A289" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B289" s="7">
+      <c r="B289" s="14">
         <v>6.1</v>
       </c>
       <c r="C289" s="7">
@@ -18911,7 +18911,7 @@
       <c r="A290" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B290" s="7">
+      <c r="B290" s="14">
         <v>6.1</v>
       </c>
       <c r="C290" s="7">
@@ -18927,7 +18927,7 @@
       <c r="A291" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B291" s="7">
+      <c r="B291" s="14">
         <v>6.1</v>
       </c>
       <c r="C291" s="7">
@@ -18943,7 +18943,7 @@
       <c r="A292" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B292" s="7">
+      <c r="B292" s="14">
         <v>6.1</v>
       </c>
       <c r="C292" s="7">
@@ -18959,7 +18959,7 @@
       <c r="A293" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B293" s="7">
+      <c r="B293" s="14">
         <v>6.1</v>
       </c>
       <c r="C293" s="7">
@@ -18975,7 +18975,7 @@
       <c r="A294" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B294" s="7">
+      <c r="B294" s="14">
         <v>6.1</v>
       </c>
       <c r="C294" s="7">
@@ -18991,7 +18991,7 @@
       <c r="A295" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B295" s="7">
+      <c r="B295" s="14">
         <v>6.1</v>
       </c>
       <c r="C295" s="7">
@@ -19007,7 +19007,7 @@
       <c r="A296" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B296" s="7">
+      <c r="B296" s="14">
         <v>6.1</v>
       </c>
       <c r="C296" s="7">
@@ -19023,7 +19023,7 @@
       <c r="A297" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B297" s="7">
+      <c r="B297" s="14">
         <v>6.1</v>
       </c>
       <c r="C297" s="7">
@@ -19039,7 +19039,7 @@
       <c r="A298" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B298" s="7">
+      <c r="B298" s="14">
         <v>6.1</v>
       </c>
       <c r="C298" s="7">
@@ -19055,7 +19055,7 @@
       <c r="A299" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B299" s="7">
+      <c r="B299" s="14">
         <v>6.1</v>
       </c>
       <c r="C299" s="7">
@@ -19071,7 +19071,7 @@
       <c r="A300" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B300" s="7">
+      <c r="B300" s="14">
         <v>6.1</v>
       </c>
       <c r="C300" s="7">
@@ -19087,7 +19087,7 @@
       <c r="A301" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B301" s="7">
+      <c r="B301" s="14">
         <v>6.2</v>
       </c>
       <c r="C301" s="7"/>
@@ -19101,7 +19101,7 @@
       <c r="A302" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B302" s="7">
+      <c r="B302" s="14">
         <v>7</v>
       </c>
       <c r="C302" s="7"/>
@@ -19115,7 +19115,7 @@
       <c r="A303" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B303" s="7">
+      <c r="B303" s="14">
         <v>8</v>
       </c>
       <c r="C303" s="7">
@@ -19131,7 +19131,7 @@
       <c r="A304" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B304" s="7">
+      <c r="B304" s="14">
         <v>8</v>
       </c>
       <c r="C304" s="7">
@@ -19147,7 +19147,7 @@
       <c r="A305" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B305" s="7">
+      <c r="B305" s="14">
         <v>8</v>
       </c>
       <c r="C305" s="7">
@@ -19163,7 +19163,7 @@
       <c r="A306" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B306" s="7">
+      <c r="B306" s="14">
         <v>8</v>
       </c>
       <c r="C306" s="7">
@@ -19179,7 +19179,7 @@
       <c r="A307" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B307" s="7">
+      <c r="B307" s="14">
         <v>8</v>
       </c>
       <c r="C307" s="7">
@@ -19195,7 +19195,7 @@
       <c r="A308" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B308" s="7">
+      <c r="B308" s="14">
         <v>8</v>
       </c>
       <c r="C308" s="7">
@@ -19211,7 +19211,7 @@
       <c r="A309" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B309" s="7">
+      <c r="B309" s="14">
         <v>8</v>
       </c>
       <c r="C309" s="7">
@@ -19227,7 +19227,7 @@
       <c r="A310" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B310" s="7">
+      <c r="B310" s="14">
         <v>8</v>
       </c>
       <c r="C310" s="7">
@@ -19243,7 +19243,7 @@
       <c r="A311" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B311" s="7">
+      <c r="B311" s="14">
         <v>8</v>
       </c>
       <c r="C311" s="7">
@@ -19259,7 +19259,7 @@
       <c r="A312" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B312" s="7">
+      <c r="B312" s="14">
         <v>8</v>
       </c>
       <c r="C312" s="7">
@@ -19275,7 +19275,7 @@
       <c r="A313" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B313" s="7">
+      <c r="B313" s="14">
         <v>8</v>
       </c>
       <c r="C313" s="7">
@@ -19291,7 +19291,7 @@
       <c r="A314" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B314" s="7">
+      <c r="B314" s="14">
         <v>8</v>
       </c>
       <c r="C314" s="7">
@@ -19307,7 +19307,7 @@
       <c r="A315" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B315" s="7">
+      <c r="B315" s="14">
         <v>8</v>
       </c>
       <c r="C315" s="7">
@@ -19323,7 +19323,7 @@
       <c r="A316" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B316" s="7">
+      <c r="B316" s="14">
         <v>8</v>
       </c>
       <c r="C316" s="7">
@@ -19339,7 +19339,7 @@
       <c r="A317" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B317" s="7">
+      <c r="B317" s="14">
         <v>9</v>
       </c>
       <c r="C317" s="7">
@@ -19357,7 +19357,7 @@
       <c r="A318" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B318" s="7">
+      <c r="B318" s="14">
         <v>9</v>
       </c>
       <c r="C318" s="7">
@@ -19373,7 +19373,7 @@
       <c r="A319" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B319" s="7">
+      <c r="B319" s="14">
         <v>9</v>
       </c>
       <c r="C319" s="7">
@@ -19389,7 +19389,7 @@
       <c r="A320" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B320" s="7">
+      <c r="B320" s="14">
         <v>9</v>
       </c>
       <c r="C320" s="7">
@@ -19405,7 +19405,7 @@
       <c r="A321" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B321" s="7">
+      <c r="B321" s="14">
         <v>9</v>
       </c>
       <c r="C321" s="7">
@@ -19421,7 +19421,7 @@
       <c r="A322" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B322" s="7">
+      <c r="B322" s="14">
         <v>9</v>
       </c>
       <c r="C322" s="7">
@@ -19437,7 +19437,7 @@
       <c r="A323" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B323" s="7">
+      <c r="B323" s="14">
         <v>9</v>
       </c>
       <c r="C323" s="7">
@@ -19453,7 +19453,7 @@
       <c r="A324" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B324" s="7">
+      <c r="B324" s="14">
         <v>9</v>
       </c>
       <c r="C324" s="7">
@@ -19469,7 +19469,7 @@
       <c r="A325" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B325" s="7">
+      <c r="B325" s="14">
         <v>9</v>
       </c>
       <c r="C325" s="7">
@@ -19485,7 +19485,7 @@
       <c r="A326" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B326" s="7">
+      <c r="B326" s="14">
         <v>9</v>
       </c>
       <c r="C326" s="7">
@@ -19501,7 +19501,7 @@
       <c r="A327" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B327" s="7">
+      <c r="B327" s="14">
         <v>9</v>
       </c>
       <c r="C327" s="7">
@@ -19517,7 +19517,7 @@
       <c r="A328" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B328" s="7">
+      <c r="B328" s="14">
         <v>9</v>
       </c>
       <c r="C328" s="7">
@@ -19535,7 +19535,7 @@
       <c r="A329" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B329" s="7">
+      <c r="B329" s="14">
         <v>9</v>
       </c>
       <c r="C329" s="7">
@@ -19551,7 +19551,7 @@
       <c r="A330" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B330" s="7">
+      <c r="B330" s="14">
         <v>9</v>
       </c>
       <c r="C330" s="7">
@@ -19567,7 +19567,7 @@
       <c r="A331" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B331" s="7">
+      <c r="B331" s="14">
         <v>9</v>
       </c>
       <c r="C331" s="7">
@@ -19583,7 +19583,7 @@
       <c r="A332" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B332" s="7">
+      <c r="B332" s="14">
         <v>9</v>
       </c>
       <c r="C332" s="7">
@@ -19599,7 +19599,7 @@
       <c r="A333" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B333" s="7">
+      <c r="B333" s="14">
         <v>9</v>
       </c>
       <c r="C333" s="7">
@@ -19617,7 +19617,7 @@
       <c r="A334" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B334" s="7">
+      <c r="B334" s="14">
         <v>9</v>
       </c>
       <c r="C334" s="7">
@@ -19633,7 +19633,7 @@
       <c r="A335" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B335" s="7">
+      <c r="B335" s="14">
         <v>9</v>
       </c>
       <c r="C335" s="7">
@@ -19651,7 +19651,7 @@
       <c r="A336" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B336" s="7">
+      <c r="B336" s="14">
         <v>9</v>
       </c>
       <c r="C336" s="7">
@@ -19667,7 +19667,7 @@
       <c r="A337" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B337" s="7">
+      <c r="B337" s="14">
         <v>9</v>
       </c>
       <c r="C337" s="7">
@@ -19703,7 +19703,7 @@
       <c r="B1" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="8" t="s">
@@ -19726,10 +19726,10 @@
       <c r="A2" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="14">
         <v>1</v>
       </c>
-      <c r="C2" s="12"/>
+      <c r="C2" s="11"/>
       <c r="D2" s="7" t="s">
         <v>138</v>
       </c>
@@ -19738,7 +19738,7 @@
       <c r="A3" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="14">
         <v>1.1000000000000001</v>
       </c>
       <c r="C3" s="7"/>
@@ -19750,7 +19750,7 @@
       <c r="A4" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="14">
         <v>1.2</v>
       </c>
       <c r="C4" s="7"/>
@@ -19762,7 +19762,7 @@
       <c r="A5" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="14">
         <v>1.3</v>
       </c>
       <c r="C5" s="7"/>
@@ -19774,7 +19774,7 @@
       <c r="A6" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="14">
         <v>1.4</v>
       </c>
       <c r="C6" s="7"/>
@@ -19786,7 +19786,7 @@
       <c r="A7" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="14">
         <v>1.5</v>
       </c>
       <c r="C7" s="7"/>
@@ -19798,7 +19798,7 @@
       <c r="A8" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="14">
         <v>1.6</v>
       </c>
       <c r="C8" s="7"/>
@@ -19810,7 +19810,7 @@
       <c r="A9" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="14">
         <v>2.1</v>
       </c>
       <c r="C9" s="7"/>
@@ -19822,7 +19822,7 @@
       <c r="A10" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="14">
         <v>2.1</v>
       </c>
       <c r="C10" s="7">
@@ -19836,7 +19836,7 @@
       <c r="A11" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="14">
         <v>2.1</v>
       </c>
       <c r="C11" s="7">
@@ -19850,7 +19850,7 @@
       <c r="A12" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="14">
         <v>2.1</v>
       </c>
       <c r="C12" s="7">
@@ -19864,7 +19864,7 @@
       <c r="A13" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="14">
         <v>2.1</v>
       </c>
       <c r="C13" s="7">
@@ -19878,7 +19878,7 @@
       <c r="A14" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="14">
         <v>2.1</v>
       </c>
       <c r="C14" s="7">
@@ -19892,7 +19892,7 @@
       <c r="A15" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="14">
         <v>2.2000000000000002</v>
       </c>
       <c r="C15" s="7">
@@ -19906,7 +19906,7 @@
       <c r="A16" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C16" s="7">
@@ -19920,7 +19920,7 @@
       <c r="A17" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C17" s="7">
@@ -19934,7 +19934,7 @@
       <c r="A18" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C18" s="7">
@@ -19948,7 +19948,7 @@
       <c r="A19" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C19" s="7">
@@ -19962,7 +19962,7 @@
       <c r="A20" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C20" s="7">
@@ -19976,7 +19976,7 @@
       <c r="A21" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C21" s="7">
@@ -19990,7 +19990,7 @@
       <c r="A22" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C22" s="7">
@@ -20004,7 +20004,7 @@
       <c r="A23" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C23" s="7">
@@ -20018,7 +20018,7 @@
       <c r="A24" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C24" s="7">
@@ -20032,7 +20032,7 @@
       <c r="A25" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C25" s="7">
@@ -20046,7 +20046,7 @@
       <c r="A26" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C26" s="7">
@@ -20060,7 +20060,7 @@
       <c r="A27" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C27" s="7">
@@ -20074,7 +20074,7 @@
       <c r="A28" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C28" s="7">
@@ -20088,7 +20088,7 @@
       <c r="A29" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="14">
         <v>3</v>
       </c>
       <c r="C29" s="7"/>
@@ -20100,7 +20100,7 @@
       <c r="A30" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="14">
         <v>3</v>
       </c>
       <c r="C30" s="7">
@@ -20114,7 +20114,7 @@
       <c r="A31" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="14">
         <v>3</v>
       </c>
       <c r="C31" s="7">
@@ -20128,7 +20128,7 @@
       <c r="A32" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="14">
         <v>3</v>
       </c>
       <c r="C32" s="7">
@@ -20142,7 +20142,7 @@
       <c r="A33" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C33" s="7">
@@ -20156,7 +20156,7 @@
       <c r="A34" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C34" s="7">
@@ -20170,7 +20170,7 @@
       <c r="A35" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C35" s="7">
@@ -20184,7 +20184,7 @@
       <c r="A36" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C36" s="7">
@@ -20198,7 +20198,7 @@
       <c r="A37" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C37" s="7">
@@ -20212,7 +20212,7 @@
       <c r="A38" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C38" s="7">
@@ -20226,7 +20226,7 @@
       <c r="A39" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C39" s="7">
@@ -20240,7 +20240,7 @@
       <c r="A40" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C40" s="7">
@@ -20254,7 +20254,7 @@
       <c r="A41" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C41" s="7">
@@ -20268,7 +20268,7 @@
       <c r="A42" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C42" s="7">
@@ -20282,7 +20282,7 @@
       <c r="A43" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C43" s="7">
@@ -20296,7 +20296,7 @@
       <c r="A44" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C44" s="7">
@@ -20310,7 +20310,7 @@
       <c r="A45" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C45" s="7">
@@ -20324,7 +20324,7 @@
       <c r="A46" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C46" s="7">
@@ -20338,7 +20338,7 @@
       <c r="A47" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C47" s="7">
@@ -20352,7 +20352,7 @@
       <c r="A48" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C48" s="7">
@@ -20366,7 +20366,7 @@
       <c r="A49" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="14">
         <v>4.2</v>
       </c>
       <c r="C49" s="7"/>
@@ -20378,7 +20378,7 @@
       <c r="A50" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="14">
         <v>4.2</v>
       </c>
       <c r="C50" s="7">
@@ -20392,7 +20392,7 @@
       <c r="A51" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B51" s="14">
         <v>4.2</v>
       </c>
       <c r="C51" s="7">
@@ -20406,7 +20406,7 @@
       <c r="A52" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="14">
         <v>4.2</v>
       </c>
       <c r="C52" s="7">
@@ -20420,7 +20420,7 @@
       <c r="A53" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B53" s="14">
         <v>4.2</v>
       </c>
       <c r="C53" s="7">
@@ -20434,7 +20434,7 @@
       <c r="A54" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="14">
         <v>4.2</v>
       </c>
       <c r="C54" s="7">
@@ -20448,7 +20448,7 @@
       <c r="A55" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="14">
         <v>4.2</v>
       </c>
       <c r="C55" s="7">
@@ -20462,7 +20462,7 @@
       <c r="A56" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="14">
         <v>4.2</v>
       </c>
       <c r="C56" s="7">
@@ -20476,7 +20476,7 @@
       <c r="A57" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B57" s="7">
+      <c r="B57" s="14">
         <v>4.2</v>
       </c>
       <c r="C57" s="7">
@@ -20490,7 +20490,7 @@
       <c r="A58" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B58" s="7">
+      <c r="B58" s="14">
         <v>4.2</v>
       </c>
       <c r="C58" s="7">
@@ -20504,7 +20504,7 @@
       <c r="A59" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B59" s="7">
+      <c r="B59" s="14">
         <v>4.2</v>
       </c>
       <c r="C59" s="7">
@@ -20518,7 +20518,7 @@
       <c r="A60" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="14">
         <v>4.2</v>
       </c>
       <c r="C60" s="7">
@@ -20532,7 +20532,7 @@
       <c r="A61" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B61" s="7">
+      <c r="B61" s="14">
         <v>4.3</v>
       </c>
       <c r="C61" s="7">
@@ -20546,7 +20546,7 @@
       <c r="A62" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B62" s="7">
+      <c r="B62" s="14">
         <v>4.3</v>
       </c>
       <c r="C62" s="7">
@@ -20560,7 +20560,7 @@
       <c r="A63" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B63" s="7">
+      <c r="B63" s="14">
         <v>4.3</v>
       </c>
       <c r="C63" s="7">
@@ -20574,7 +20574,7 @@
       <c r="A64" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B64" s="7">
+      <c r="B64" s="14">
         <v>4.3</v>
       </c>
       <c r="C64" s="7">
@@ -20588,7 +20588,7 @@
       <c r="A65" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B65" s="7">
+      <c r="B65" s="14">
         <v>4.3</v>
       </c>
       <c r="C65" s="7">
@@ -20602,7 +20602,7 @@
       <c r="A66" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B66" s="7">
+      <c r="B66" s="14">
         <v>4.3</v>
       </c>
       <c r="C66" s="7">
@@ -20616,7 +20616,7 @@
       <c r="A67" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B67" s="7">
+      <c r="B67" s="14">
         <v>4.3</v>
       </c>
       <c r="C67" s="7">
@@ -20630,7 +20630,7 @@
       <c r="A68" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B68" s="7">
+      <c r="B68" s="14">
         <v>4.3</v>
       </c>
       <c r="C68" s="7">
@@ -20644,7 +20644,7 @@
       <c r="A69" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B69" s="7">
+      <c r="B69" s="14">
         <v>4.3</v>
       </c>
       <c r="C69" s="7">
@@ -20658,7 +20658,7 @@
       <c r="A70" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B70" s="7">
+      <c r="B70" s="14">
         <v>4.3</v>
       </c>
       <c r="C70" s="7">
@@ -20672,7 +20672,7 @@
       <c r="A71" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B71" s="7">
+      <c r="B71" s="14">
         <v>4.3</v>
       </c>
       <c r="C71" s="7">
@@ -20686,7 +20686,7 @@
       <c r="A72" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B72" s="7">
+      <c r="B72" s="14">
         <v>4.3</v>
       </c>
       <c r="C72" s="7">
@@ -20700,7 +20700,7 @@
       <c r="A73" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B73" s="7">
+      <c r="B73" s="14">
         <v>4.3</v>
       </c>
       <c r="C73" s="7">
@@ -20714,7 +20714,7 @@
       <c r="A74" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B74" s="7">
+      <c r="B74" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C74" s="7">
@@ -20728,7 +20728,7 @@
       <c r="A75" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B75" s="7">
+      <c r="B75" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C75" s="7">
@@ -20742,7 +20742,7 @@
       <c r="A76" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B76" s="7">
+      <c r="B76" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C76" s="7">
@@ -20756,7 +20756,7 @@
       <c r="A77" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B77" s="7">
+      <c r="B77" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C77" s="7">
@@ -20770,7 +20770,7 @@
       <c r="A78" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B78" s="7">
+      <c r="B78" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C78" s="7">
@@ -20784,7 +20784,7 @@
       <c r="A79" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B79" s="7">
+      <c r="B79" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C79" s="7">
@@ -20798,7 +20798,7 @@
       <c r="A80" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B80" s="7">
+      <c r="B80" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C80" s="7">
@@ -20812,7 +20812,7 @@
       <c r="A81" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B81" s="7">
+      <c r="B81" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C81" s="7">
@@ -20826,7 +20826,7 @@
       <c r="A82" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B82" s="7">
+      <c r="B82" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C82" s="7">
@@ -20840,7 +20840,7 @@
       <c r="A83" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B83" s="7">
+      <c r="B83" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C83" s="7">
@@ -20854,7 +20854,7 @@
       <c r="A84" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B84" s="7">
+      <c r="B84" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C84" s="7">
@@ -20868,7 +20868,7 @@
       <c r="A85" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B85" s="7">
+      <c r="B85" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C85" s="7">
@@ -20882,7 +20882,7 @@
       <c r="A86" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B86" s="7">
+      <c r="B86" s="14">
         <v>5.2</v>
       </c>
       <c r="C86" s="7"/>
@@ -20894,7 +20894,7 @@
       <c r="A87" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B87" s="7">
+      <c r="B87" s="14">
         <v>5.2</v>
       </c>
       <c r="C87" s="7">
@@ -20908,7 +20908,7 @@
       <c r="A88" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B88" s="7">
+      <c r="B88" s="14">
         <v>5.2</v>
       </c>
       <c r="C88" s="7">
@@ -20922,7 +20922,7 @@
       <c r="A89" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B89" s="7">
+      <c r="B89" s="14">
         <v>5.2</v>
       </c>
       <c r="C89" s="7">
@@ -20936,7 +20936,7 @@
       <c r="A90" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B90" s="7">
+      <c r="B90" s="14">
         <v>5.2</v>
       </c>
       <c r="C90" s="7">
@@ -20950,7 +20950,7 @@
       <c r="A91" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B91" s="7">
+      <c r="B91" s="14">
         <v>5.2</v>
       </c>
       <c r="C91" s="7">
@@ -20964,7 +20964,7 @@
       <c r="A92" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B92" s="7">
+      <c r="B92" s="14">
         <v>5.2</v>
       </c>
       <c r="C92" s="7">
@@ -20978,7 +20978,7 @@
       <c r="A93" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B93" s="7">
+      <c r="B93" s="14">
         <v>5.2</v>
       </c>
       <c r="C93" s="7">
@@ -20992,7 +20992,7 @@
       <c r="A94" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B94" s="7">
+      <c r="B94" s="14">
         <v>5.2</v>
       </c>
       <c r="C94" s="7">
@@ -21006,7 +21006,7 @@
       <c r="A95" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B95" s="7">
+      <c r="B95" s="14">
         <v>5.2</v>
       </c>
       <c r="C95" s="7">
@@ -21020,7 +21020,7 @@
       <c r="A96" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B96" s="7">
+      <c r="B96" s="14">
         <v>5.2</v>
       </c>
       <c r="C96" s="7">
@@ -21034,7 +21034,7 @@
       <c r="A97" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B97" s="7">
+      <c r="B97" s="14">
         <v>5.2</v>
       </c>
       <c r="C97" s="7">
@@ -21048,7 +21048,7 @@
       <c r="A98" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B98" s="7">
+      <c r="B98" s="14">
         <v>5.2</v>
       </c>
       <c r="C98" s="7">
@@ -21062,7 +21062,7 @@
       <c r="A99" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B99" s="7">
+      <c r="B99" s="14">
         <v>5.2</v>
       </c>
       <c r="C99" s="7">
@@ -21076,7 +21076,7 @@
       <c r="A100" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B100" s="7">
+      <c r="B100" s="14">
         <v>6.1</v>
       </c>
       <c r="C100" s="7">
@@ -21090,7 +21090,7 @@
       <c r="A101" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B101" s="7">
+      <c r="B101" s="14">
         <v>6.1</v>
       </c>
       <c r="C101" s="7">
@@ -21104,7 +21104,7 @@
       <c r="A102" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B102" s="7">
+      <c r="B102" s="14">
         <v>6.1</v>
       </c>
       <c r="C102" s="7">
@@ -21118,7 +21118,7 @@
       <c r="A103" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B103" s="7">
+      <c r="B103" s="14">
         <v>6.1</v>
       </c>
       <c r="C103" s="7">
@@ -21132,7 +21132,7 @@
       <c r="A104" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B104" s="7">
+      <c r="B104" s="14">
         <v>6.1</v>
       </c>
       <c r="C104" s="7">
@@ -21146,7 +21146,7 @@
       <c r="A105" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B105" s="7">
+      <c r="B105" s="14">
         <v>6.1</v>
       </c>
       <c r="C105" s="7">
@@ -21160,7 +21160,7 @@
       <c r="A106" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B106" s="7">
+      <c r="B106" s="14">
         <v>6.1</v>
       </c>
       <c r="C106" s="7">
@@ -21174,7 +21174,7 @@
       <c r="A107" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B107" s="7">
+      <c r="B107" s="14">
         <v>6.1</v>
       </c>
       <c r="C107" s="7">
@@ -21188,7 +21188,7 @@
       <c r="A108" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B108" s="7">
+      <c r="B108" s="14">
         <v>6.2</v>
       </c>
       <c r="C108" s="7"/>
@@ -21200,7 +21200,7 @@
       <c r="A109" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B109" s="7">
+      <c r="B109" s="14">
         <v>7</v>
       </c>
       <c r="C109" s="7"/>
@@ -21212,7 +21212,7 @@
       <c r="A110" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B110" s="7">
+      <c r="B110" s="14">
         <v>8</v>
       </c>
       <c r="C110" s="7">
@@ -21226,7 +21226,7 @@
       <c r="A111" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B111" s="7">
+      <c r="B111" s="14">
         <v>8</v>
       </c>
       <c r="C111" s="7">
@@ -21240,7 +21240,7 @@
       <c r="A112" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B112" s="7">
+      <c r="B112" s="14">
         <v>8</v>
       </c>
       <c r="C112" s="7">
@@ -21254,7 +21254,7 @@
       <c r="A113" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B113" s="7">
+      <c r="B113" s="14">
         <v>8</v>
       </c>
       <c r="C113" s="7">
@@ -21268,7 +21268,7 @@
       <c r="A114" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B114" s="7">
+      <c r="B114" s="14">
         <v>8</v>
       </c>
       <c r="C114" s="7">
@@ -21282,7 +21282,7 @@
       <c r="A115" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B115" s="7">
+      <c r="B115" s="14">
         <v>8</v>
       </c>
       <c r="C115" s="7">
@@ -21296,7 +21296,7 @@
       <c r="A116" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B116" s="7">
+      <c r="B116" s="14">
         <v>9</v>
       </c>
       <c r="C116" s="7">
@@ -21310,7 +21310,7 @@
       <c r="A117" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B117" s="7">
+      <c r="B117" s="14">
         <v>9</v>
       </c>
       <c r="C117" s="7">
@@ -21324,7 +21324,7 @@
       <c r="A118" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B118" s="7">
+      <c r="B118" s="14">
         <v>9</v>
       </c>
       <c r="C118" s="7">
@@ -21338,7 +21338,7 @@
       <c r="A119" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B119" s="7">
+      <c r="B119" s="14">
         <v>9</v>
       </c>
       <c r="C119" s="7">
@@ -21352,7 +21352,7 @@
       <c r="A120" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B120" s="7">
+      <c r="B120" s="14">
         <v>9</v>
       </c>
       <c r="C120" s="7">
@@ -21366,7 +21366,7 @@
       <c r="A121" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B121" s="7">
+      <c r="B121" s="14">
         <v>9</v>
       </c>
       <c r="C121" s="7">
@@ -21380,7 +21380,7 @@
       <c r="A122" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B122" s="7">
+      <c r="B122" s="14">
         <v>9</v>
       </c>
       <c r="C122" s="7">
@@ -21394,7 +21394,7 @@
       <c r="A123" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B123" s="7">
+      <c r="B123" s="14">
         <v>9</v>
       </c>
       <c r="C123" s="7">
@@ -21408,7 +21408,7 @@
       <c r="A124" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B124" s="7">
+      <c r="B124" s="14">
         <v>9</v>
       </c>
       <c r="C124" s="7">
@@ -21422,7 +21422,7 @@
       <c r="A125" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B125" s="7">
+      <c r="B125" s="14">
         <v>9</v>
       </c>
       <c r="C125" s="7">
@@ -21436,7 +21436,7 @@
       <c r="A126" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B126" s="7">
+      <c r="B126" s="14">
         <v>9</v>
       </c>
       <c r="C126" s="7">
@@ -21450,7 +21450,7 @@
       <c r="A127" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B127" s="7">
+      <c r="B127" s="14">
         <v>9</v>
       </c>
       <c r="C127" s="7">
@@ -21464,7 +21464,7 @@
       <c r="A128" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B128" s="7">
+      <c r="B128" s="14">
         <v>9</v>
       </c>
       <c r="C128" s="7">
@@ -21478,7 +21478,7 @@
       <c r="A129" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B129" s="7">
+      <c r="B129" s="14">
         <v>9</v>
       </c>
       <c r="C129" s="7">
@@ -21492,7 +21492,7 @@
       <c r="A130" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B130" s="7">
+      <c r="B130" s="14">
         <v>9</v>
       </c>
       <c r="C130" s="7">
@@ -21506,7 +21506,7 @@
       <c r="A131" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B131" s="7">
+      <c r="B131" s="14">
         <v>9</v>
       </c>
       <c r="C131" s="7">
@@ -21520,7 +21520,7 @@
       <c r="A132" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B132" s="7">
+      <c r="B132" s="14">
         <v>9</v>
       </c>
       <c r="C132" s="7">
@@ -21534,7 +21534,7 @@
       <c r="A133" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B133" s="7">
+      <c r="B133" s="14">
         <v>9</v>
       </c>
       <c r="C133" s="7">
@@ -21548,7 +21548,7 @@
       <c r="A134" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B134" s="7">
+      <c r="B134" s="14">
         <v>9</v>
       </c>
       <c r="C134" s="7">
@@ -21562,7 +21562,7 @@
       <c r="A135" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B135" s="7">
+      <c r="B135" s="14">
         <v>9</v>
       </c>
       <c r="C135" s="7">
@@ -21746,7 +21746,7 @@
       <c r="B1" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="8" t="s">
@@ -21769,7 +21769,7 @@
       <c r="A2" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="4">
         <v>1</v>
       </c>
       <c r="C2" s="3"/>
@@ -21781,7 +21781,7 @@
       <c r="A3" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="4">
         <v>1.1000000000000001</v>
       </c>
       <c r="C3" s="1"/>
@@ -21793,7 +21793,7 @@
       <c r="A4" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="4">
         <v>1.2</v>
       </c>
       <c r="C4" s="1"/>
@@ -21805,7 +21805,7 @@
       <c r="A5" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="4">
         <v>1.3</v>
       </c>
       <c r="C5" s="1"/>
@@ -21817,7 +21817,7 @@
       <c r="A6" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="4">
         <v>1.4</v>
       </c>
       <c r="C6" s="1"/>
@@ -21829,7 +21829,7 @@
       <c r="A7" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="4">
         <v>1.5</v>
       </c>
       <c r="C7" s="1"/>
@@ -21841,7 +21841,7 @@
       <c r="A8" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="4">
         <v>1.6</v>
       </c>
       <c r="C8" s="1"/>
@@ -21853,7 +21853,7 @@
       <c r="A9" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="4">
         <v>2.1</v>
       </c>
       <c r="C9" s="1">
@@ -21867,7 +21867,7 @@
       <c r="A10" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="4">
         <v>2.1</v>
       </c>
       <c r="C10" s="1">
@@ -21881,7 +21881,7 @@
       <c r="A11" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="4">
         <v>2.2000000000000002</v>
       </c>
       <c r="C11" s="1">
@@ -21895,7 +21895,7 @@
       <c r="A12" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="4">
         <v>2.2999999999999998</v>
       </c>
       <c r="C12" s="1"/>
@@ -21907,7 +21907,7 @@
       <c r="A13" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C13" s="1"/>
@@ -21919,7 +21919,7 @@
       <c r="A14" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C14" s="1">
@@ -21933,7 +21933,7 @@
       <c r="A15" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C15" s="1">
@@ -21947,7 +21947,7 @@
       <c r="A16" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C16" s="1">
@@ -21961,7 +21961,7 @@
       <c r="A17" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C17" s="1">
@@ -21975,7 +21975,7 @@
       <c r="A18" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="C18" s="1">
@@ -21989,7 +21989,7 @@
       <c r="A19" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="4">
         <v>4.2</v>
       </c>
       <c r="C19" s="1">
@@ -22003,7 +22003,7 @@
       <c r="A20" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="4">
         <v>4.2</v>
       </c>
       <c r="C20" s="1">
@@ -22017,7 +22017,7 @@
       <c r="A21" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="4">
         <v>4.2</v>
       </c>
       <c r="C21" s="1">
@@ -22031,7 +22031,7 @@
       <c r="A22" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="4">
         <v>4.2</v>
       </c>
       <c r="C22" s="1">
@@ -22045,7 +22045,7 @@
       <c r="A23" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="4">
         <v>4.3</v>
       </c>
       <c r="C23" s="1">
@@ -22059,7 +22059,7 @@
       <c r="A24" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="4">
         <v>4.3</v>
       </c>
       <c r="C24" s="1">
@@ -22073,7 +22073,7 @@
       <c r="A25" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C25" s="1">
@@ -22087,7 +22087,7 @@
       <c r="A26" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C26" s="1">
@@ -22101,7 +22101,7 @@
       <c r="A27" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C27" s="1">
@@ -22115,7 +22115,7 @@
       <c r="A28" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C28" s="1">
@@ -22129,7 +22129,7 @@
       <c r="A29" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C29" s="1">
@@ -22143,7 +22143,7 @@
       <c r="A30" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C30" s="1">
@@ -22157,7 +22157,7 @@
       <c r="A31" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C31" s="1">
@@ -22171,7 +22171,7 @@
       <c r="A32" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C32" s="1">
@@ -22185,7 +22185,7 @@
       <c r="A33" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C33" s="1">
@@ -22199,7 +22199,7 @@
       <c r="A34" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="4">
         <v>5.0999999999999996</v>
       </c>
       <c r="C34" s="1">
@@ -22213,7 +22213,7 @@
       <c r="A35" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="4">
         <v>5.2</v>
       </c>
       <c r="C35" s="1"/>
@@ -22225,7 +22225,7 @@
       <c r="A36" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="4">
         <v>5.2</v>
       </c>
       <c r="C36" s="1">
@@ -22239,7 +22239,7 @@
       <c r="A37" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="4">
         <v>5.2</v>
       </c>
       <c r="C37" s="1">
@@ -22253,7 +22253,7 @@
       <c r="A38" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="4">
         <v>5.2</v>
       </c>
       <c r="C38" s="1">
@@ -22267,7 +22267,7 @@
       <c r="A39" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="4">
         <v>5.2</v>
       </c>
       <c r="C39" s="1">
@@ -22281,7 +22281,7 @@
       <c r="A40" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="4">
         <v>5.2</v>
       </c>
       <c r="C40" s="1">
@@ -22295,7 +22295,7 @@
       <c r="A41" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="4">
         <v>5.2</v>
       </c>
       <c r="C41" s="1">
@@ -22309,7 +22309,7 @@
       <c r="A42" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="4">
         <v>5.2</v>
       </c>
       <c r="C42" s="1">
@@ -22323,7 +22323,7 @@
       <c r="A43" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="4">
         <v>5.2</v>
       </c>
       <c r="C43" s="1">
@@ -22337,7 +22337,7 @@
       <c r="A44" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="4">
         <v>5.2</v>
       </c>
       <c r="C44" s="1">
@@ -22351,7 +22351,7 @@
       <c r="A45" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45" s="4">
         <v>5.2</v>
       </c>
       <c r="C45" s="1">
@@ -22365,7 +22365,7 @@
       <c r="A46" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="4">
         <v>6.1</v>
       </c>
       <c r="C46" s="1">
@@ -22379,7 +22379,7 @@
       <c r="A47" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="4">
         <v>6.1</v>
       </c>
       <c r="C47" s="1">
@@ -22393,7 +22393,7 @@
       <c r="A48" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" s="4">
         <v>6.1</v>
       </c>
       <c r="C48" s="1">
@@ -22407,7 +22407,7 @@
       <c r="A49" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49" s="4">
         <v>6.2</v>
       </c>
       <c r="C49" s="1"/>
@@ -22419,7 +22419,7 @@
       <c r="A50" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="4">
         <v>7</v>
       </c>
       <c r="C50" s="1"/>
@@ -22431,7 +22431,7 @@
       <c r="A51" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51" s="4">
         <v>8</v>
       </c>
       <c r="C51" s="1">
@@ -22445,7 +22445,7 @@
       <c r="A52" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B52" s="4">
         <v>8</v>
       </c>
       <c r="C52" s="1">
@@ -22459,7 +22459,7 @@
       <c r="A53" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="4">
         <v>8</v>
       </c>
       <c r="C53" s="1">
@@ -22473,7 +22473,7 @@
       <c r="A54" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54" s="4">
         <v>8</v>
       </c>
       <c r="C54" s="1">
@@ -22487,7 +22487,7 @@
       <c r="A55" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="4">
         <v>9</v>
       </c>
       <c r="C55" s="1">
@@ -22501,7 +22501,7 @@
       <c r="A56" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="4">
         <v>9</v>
       </c>
       <c r="C56" s="1">
@@ -22515,7 +22515,7 @@
       <c r="A57" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57" s="4">
         <v>9</v>
       </c>
       <c r="C57" s="1">
@@ -22529,7 +22529,7 @@
       <c r="A58" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B58" s="1">
+      <c r="B58" s="4">
         <v>9</v>
       </c>
       <c r="C58" s="1">
@@ -22543,7 +22543,7 @@
       <c r="A59" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B59" s="4">
         <v>9</v>
       </c>
       <c r="C59" s="1">
@@ -22557,7 +22557,7 @@
       <c r="A60" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B60" s="4">
         <v>9</v>
       </c>
       <c r="C60" s="1">
@@ -22571,7 +22571,7 @@
       <c r="A61" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61" s="4">
         <v>9</v>
       </c>
       <c r="C61" s="1">
@@ -22585,7 +22585,7 @@
       <c r="A62" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62" s="4">
         <v>9</v>
       </c>
       <c r="C62" s="1">
@@ -22599,7 +22599,7 @@
       <c r="A63" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63" s="4">
         <v>9</v>
       </c>
       <c r="C63" s="1">
@@ -22613,7 +22613,7 @@
       <c r="A64" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64" s="4">
         <v>9</v>
       </c>
       <c r="C64" s="1">
@@ -22627,7 +22627,7 @@
       <c r="A65" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65" s="4">
         <v>9</v>
       </c>
       <c r="C65" s="1">
@@ -22641,7 +22641,7 @@
       <c r="A66" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66" s="4">
         <v>9</v>
       </c>
       <c r="C66" s="1">
@@ -22655,7 +22655,7 @@
       <c r="A67" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67" s="4">
         <v>9</v>
       </c>
       <c r="C67" s="1">
@@ -22669,7 +22669,7 @@
       <c r="A68" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68" s="4">
         <v>9</v>
       </c>
       <c r="C68" s="1">
@@ -22683,7 +22683,7 @@
       <c r="A69" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B69" s="4">
         <v>9</v>
       </c>
       <c r="C69" s="1">
@@ -22697,7 +22697,7 @@
       <c r="A70" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70" s="4">
         <v>9</v>
       </c>
       <c r="C70" s="1">
@@ -22711,7 +22711,7 @@
       <c r="A71" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71" s="4">
         <v>9</v>
       </c>
       <c r="C71" s="1">
@@ -22725,7 +22725,7 @@
       <c r="A72" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B72" s="1">
+      <c r="B72" s="4">
         <v>9</v>
       </c>
       <c r="C72" s="1">
@@ -22739,7 +22739,7 @@
       <c r="A73" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B73" s="1">
+      <c r="B73" s="4">
         <v>9</v>
       </c>
       <c r="C73" s="1">
@@ -22753,7 +22753,7 @@
       <c r="A74" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B74" s="1">
+      <c r="B74" s="4">
         <v>9</v>
       </c>
       <c r="C74" s="1">
@@ -22767,7 +22767,7 @@
       <c r="A75" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B75" s="1">
+      <c r="B75" s="4">
         <v>9</v>
       </c>
       <c r="C75" s="1">
@@ -22781,7 +22781,7 @@
       <c r="A76" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B76" s="1">
+      <c r="B76" s="4">
         <v>9</v>
       </c>
       <c r="C76" s="1">
@@ -22795,7 +22795,7 @@
       <c r="A77" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B77" s="1">
+      <c r="B77" s="4">
         <v>9</v>
       </c>
       <c r="C77" s="1">
@@ -22823,16 +22823,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -22852,7 +22852,7 @@
       <c r="A2" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="14">
         <v>1</v>
       </c>
       <c r="C2" s="7"/>
@@ -22864,7 +22864,7 @@
       <c r="A3" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="14">
         <v>1.1000000000000001</v>
       </c>
       <c r="C3" s="7"/>
@@ -22876,7 +22876,7 @@
       <c r="A4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="14">
         <v>1.2</v>
       </c>
       <c r="C4" s="7"/>
@@ -22888,7 +22888,7 @@
       <c r="A5" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="14">
         <v>1.3</v>
       </c>
       <c r="C5" s="7"/>
@@ -22900,7 +22900,7 @@
       <c r="A6" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="14">
         <v>1.4</v>
       </c>
       <c r="C6" s="7"/>
@@ -22912,7 +22912,7 @@
       <c r="A7" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="14">
         <v>1.5</v>
       </c>
       <c r="C7" s="7"/>
@@ -22924,7 +22924,7 @@
       <c r="A8" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="14">
         <v>1.6</v>
       </c>
       <c r="C8" s="7"/>
@@ -22936,7 +22936,7 @@
       <c r="A9" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="14">
         <v>2.2000000000000002</v>
       </c>
       <c r="C9" s="7">
@@ -22950,7 +22950,7 @@
       <c r="A10" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C10" s="7"/>
@@ -22962,7 +22962,7 @@
       <c r="A11" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C11" s="7">
@@ -22976,7 +22976,7 @@
       <c r="A12" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C12" s="7">
@@ -22990,7 +22990,7 @@
       <c r="A13" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C13" s="7">
@@ -23004,7 +23004,7 @@
       <c r="A14" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C14" s="7">
@@ -23018,7 +23018,7 @@
       <c r="A15" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C15" s="7">
@@ -23032,7 +23032,7 @@
       <c r="A16" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C16" s="7">
@@ -23046,7 +23046,7 @@
       <c r="A17" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C17" s="7">
@@ -23060,7 +23060,7 @@
       <c r="A18" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C18" s="7">
@@ -23074,7 +23074,7 @@
       <c r="A19" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="14">
         <v>2.2999999999999998</v>
       </c>
       <c r="C19" s="7">
@@ -23088,7 +23088,7 @@
       <c r="A20" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="14">
         <v>3</v>
       </c>
       <c r="C20" s="7"/>
@@ -23100,7 +23100,7 @@
       <c r="A21" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="14">
         <v>3</v>
       </c>
       <c r="C21" s="7">
@@ -23114,7 +23114,7 @@
       <c r="A22" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="14">
         <v>3</v>
       </c>
       <c r="C22" s="7">
@@ -23128,7 +23128,7 @@
       <c r="A23" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="14">
         <v>3</v>
       </c>
       <c r="C23" s="7">
@@ -23142,7 +23142,7 @@
       <c r="A24" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C24" s="7">
@@ -23156,7 +23156,7 @@
       <c r="A25" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C25" s="7">
@@ -23170,7 +23170,7 @@
       <c r="A26" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C26" s="7">
@@ -23184,7 +23184,7 @@
       <c r="A27" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C27" s="7">
@@ -23198,7 +23198,7 @@
       <c r="A28" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C28" s="7">
@@ -23212,7 +23212,7 @@
       <c r="A29" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C29" s="7">
@@ -23226,7 +23226,7 @@
       <c r="A30" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C30" s="7">
@@ -23240,7 +23240,7 @@
       <c r="A31" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C31" s="7">
@@ -23254,7 +23254,7 @@
       <c r="A32" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C32" s="7">
@@ -23268,7 +23268,7 @@
       <c r="A33" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C33" s="7">
@@ -23282,7 +23282,7 @@
       <c r="A34" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C34" s="7">
@@ -23296,7 +23296,7 @@
       <c r="A35" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C35" s="7">
@@ -23310,7 +23310,7 @@
       <c r="A36" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C36" s="7">
@@ -23324,7 +23324,7 @@
       <c r="A37" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C37" s="7">
@@ -23338,7 +23338,7 @@
       <c r="A38" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C38" s="7">
@@ -23352,7 +23352,7 @@
       <c r="A39" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C39" s="7">
@@ -23366,7 +23366,7 @@
       <c r="A40" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C40" s="7">
@@ -23380,7 +23380,7 @@
       <c r="A41" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C41" s="7">
@@ -23394,7 +23394,7 @@
       <c r="A42" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C42" s="7">
@@ -23408,7 +23408,7 @@
       <c r="A43" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C43" s="7">
@@ -23422,7 +23422,7 @@
       <c r="A44" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C44" s="7">
@@ -23436,7 +23436,7 @@
       <c r="A45" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C45" s="7">
@@ -23450,7 +23450,7 @@
       <c r="A46" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C46" s="7">
@@ -23464,7 +23464,7 @@
       <c r="A47" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C47" s="7">
@@ -23478,7 +23478,7 @@
       <c r="A48" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C48" s="7">
@@ -23492,7 +23492,7 @@
       <c r="A49" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C49" s="7">
@@ -23506,7 +23506,7 @@
       <c r="A50" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C50" s="7">
@@ -23520,7 +23520,7 @@
       <c r="A51" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B51" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="C51" s="7">
@@ -23534,7 +23534,7 @@
       <c r="A52" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="14">
         <v>4.2</v>
       </c>
       <c r="C52" s="7">
@@ -23548,7 +23548,7 @@
       <c r="A53" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B53" s="14">
         <v>4.2</v>
       </c>
       <c r="C53" s="7">
@@ -23562,7 +23562,7 @@
       <c r="A54" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="14">
         <v>4.2</v>
       </c>
       <c r="C54" s="7">
@@ -23576,7 +23576,7 @@
       <c r="A55" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="14">
         <v>4.2</v>
       </c>
       <c r="C55" s="7">
@@ -23590,7 +23590,7 @@
       <c r="A56" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="14">
         <v>4.2</v>
       </c>
       <c r="C56" s="7">
@@ -23604,7 +23604,7 @@
       <c r="A57" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B57" s="7">
+      <c r="B57" s="14">
         <v>4.2</v>
       </c>
       <c r="C57" s="7">
@@ -23618,7 +23618,7 @@
       <c r="A58" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B58" s="7">
+      <c r="B58" s="14">
         <v>4.2</v>
       </c>
       <c r="C58" s="7">
@@ -23632,7 +23632,7 @@
       <c r="A59" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B59" s="7">
+      <c r="B59" s="14">
         <v>4.2</v>
       </c>
       <c r="C59" s="7">
@@ -23646,7 +23646,7 @@
       <c r="A60" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="14">
         <v>4.2</v>
       </c>
       <c r="C60" s="7">
@@ -23660,7 +23660,7 @@
       <c r="A61" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B61" s="7">
+      <c r="B61" s="14">
         <v>4.2</v>
       </c>
       <c r="C61" s="7">
@@ -23674,7 +23674,7 @@
       <c r="A62" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B62" s="7">
+      <c r="B62" s="14">
         <v>4.3</v>
       </c>
       <c r="C62" s="7">
@@ -23688,7 +23688,7 @@
       <c r="A63" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B63" s="7">
+      <c r="B63" s="14">
         <v>4.3</v>
       </c>
       <c r="C63" s="7">
@@ -23702,7 +23702,7 @@
       <c r="A64" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B64" s="7">
+      <c r="B64" s="14">
         <v>4.3</v>
       </c>
       <c r="C64" s="7">
@@ -23716,7 +23716,7 @@
       <c r="A65" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B65" s="7">
+      <c r="B65" s="14">
         <v>4.3</v>
       </c>
       <c r="C65" s="7">
@@ -23730,7 +23730,7 @@
       <c r="A66" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B66" s="7">
+      <c r="B66" s="14">
         <v>4.3</v>
       </c>
       <c r="C66" s="7">
@@ -23744,7 +23744,7 @@
       <c r="A67" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B67" s="7">
+      <c r="B67" s="14">
         <v>4.3</v>
       </c>
       <c r="C67" s="7">
@@ -23758,7 +23758,7 @@
       <c r="A68" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B68" s="7">
+      <c r="B68" s="14">
         <v>4.3</v>
       </c>
       <c r="C68" s="7">
@@ -23772,7 +23772,7 @@
       <c r="A69" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B69" s="7">
+      <c r="B69" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C69" s="7">
@@ -23786,7 +23786,7 @@
       <c r="A70" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B70" s="7">
+      <c r="B70" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C70" s="7">
@@ -23800,7 +23800,7 @@
       <c r="A71" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B71" s="7">
+      <c r="B71" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C71" s="7">
@@ -23814,7 +23814,7 @@
       <c r="A72" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B72" s="7">
+      <c r="B72" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C72" s="7">
@@ -23828,7 +23828,7 @@
       <c r="A73" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B73" s="7">
+      <c r="B73" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C73" s="7">
@@ -23842,7 +23842,7 @@
       <c r="A74" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B74" s="7">
+      <c r="B74" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C74" s="7">
@@ -23856,7 +23856,7 @@
       <c r="A75" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B75" s="7">
+      <c r="B75" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C75" s="7">
@@ -23870,7 +23870,7 @@
       <c r="A76" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B76" s="7">
+      <c r="B76" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C76" s="7">
@@ -23884,7 +23884,7 @@
       <c r="A77" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B77" s="7">
+      <c r="B77" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C77" s="7">
@@ -23898,7 +23898,7 @@
       <c r="A78" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B78" s="7">
+      <c r="B78" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C78" s="7">
@@ -23912,7 +23912,7 @@
       <c r="A79" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B79" s="7">
+      <c r="B79" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C79" s="7">
@@ -23926,7 +23926,7 @@
       <c r="A80" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B80" s="7">
+      <c r="B80" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C80" s="7">
@@ -23940,7 +23940,7 @@
       <c r="A81" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B81" s="7">
+      <c r="B81" s="14">
         <v>5.0999999999999996</v>
       </c>
       <c r="C81" s="7">
@@ -23954,7 +23954,7 @@
       <c r="A82" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B82" s="7">
+      <c r="B82" s="14">
         <v>5.2</v>
       </c>
       <c r="C82" s="7">
@@ -23968,7 +23968,7 @@
       <c r="A83" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B83" s="7">
+      <c r="B83" s="14">
         <v>5.2</v>
       </c>
       <c r="C83" s="7">
@@ -23982,7 +23982,7 @@
       <c r="A84" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B84" s="7">
+      <c r="B84" s="14">
         <v>5.2</v>
       </c>
       <c r="C84" s="7">
@@ -23996,7 +23996,7 @@
       <c r="A85" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B85" s="7">
+      <c r="B85" s="14">
         <v>5.2</v>
       </c>
       <c r="C85" s="7">
@@ -24010,7 +24010,7 @@
       <c r="A86" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B86" s="7">
+      <c r="B86" s="14">
         <v>5.2</v>
       </c>
       <c r="C86" s="7">
@@ -24024,7 +24024,7 @@
       <c r="A87" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B87" s="7">
+      <c r="B87" s="14">
         <v>5.2</v>
       </c>
       <c r="C87" s="7">
@@ -24038,7 +24038,7 @@
       <c r="A88" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B88" s="7">
+      <c r="B88" s="14">
         <v>5.2</v>
       </c>
       <c r="C88" s="7">
@@ -24052,7 +24052,7 @@
       <c r="A89" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B89" s="7">
+      <c r="B89" s="14">
         <v>5.2</v>
       </c>
       <c r="C89" s="7">
@@ -24066,7 +24066,7 @@
       <c r="A90" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B90" s="7">
+      <c r="B90" s="14">
         <v>5.2</v>
       </c>
       <c r="C90" s="7">
@@ -24080,7 +24080,7 @@
       <c r="A91" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B91" s="7">
+      <c r="B91" s="14">
         <v>5.2</v>
       </c>
       <c r="C91" s="7">
@@ -24094,7 +24094,7 @@
       <c r="A92" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B92" s="7">
+      <c r="B92" s="14">
         <v>5.2</v>
       </c>
       <c r="C92" s="7">
@@ -24108,7 +24108,7 @@
       <c r="A93" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B93" s="7">
+      <c r="B93" s="14">
         <v>5.2</v>
       </c>
       <c r="C93" s="7">
@@ -24122,7 +24122,7 @@
       <c r="A94" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B94" s="7">
+      <c r="B94" s="14">
         <v>5.2</v>
       </c>
       <c r="C94" s="7">
@@ -24136,7 +24136,7 @@
       <c r="A95" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B95" s="7">
+      <c r="B95" s="14">
         <v>5.2</v>
       </c>
       <c r="C95" s="7">
@@ -24150,7 +24150,7 @@
       <c r="A96" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B96" s="7">
+      <c r="B96" s="14">
         <v>5.2</v>
       </c>
       <c r="C96" s="7">
@@ -24164,7 +24164,7 @@
       <c r="A97" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B97" s="7">
+      <c r="B97" s="14">
         <v>5.2</v>
       </c>
       <c r="C97" s="7">
@@ -24178,7 +24178,7 @@
       <c r="A98" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B98" s="7">
+      <c r="B98" s="14">
         <v>5.2</v>
       </c>
       <c r="C98" s="7">
@@ -24192,7 +24192,7 @@
       <c r="A99" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B99" s="7">
+      <c r="B99" s="14">
         <v>5.2</v>
       </c>
       <c r="C99" s="7">
@@ -24206,7 +24206,7 @@
       <c r="A100" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B100" s="7">
+      <c r="B100" s="14">
         <v>5.2</v>
       </c>
       <c r="C100" s="7">
@@ -24220,7 +24220,7 @@
       <c r="A101" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B101" s="7">
+      <c r="B101" s="14">
         <v>5.2</v>
       </c>
       <c r="C101" s="7">
@@ -24234,7 +24234,7 @@
       <c r="A102" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B102" s="7">
+      <c r="B102" s="14">
         <v>6.1</v>
       </c>
       <c r="C102" s="7">
@@ -24248,7 +24248,7 @@
       <c r="A103" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B103" s="7">
+      <c r="B103" s="14">
         <v>6.1</v>
       </c>
       <c r="C103" s="7">
@@ -24262,7 +24262,7 @@
       <c r="A104" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B104" s="7">
+      <c r="B104" s="14">
         <v>6.1</v>
       </c>
       <c r="C104" s="7">
@@ -24276,7 +24276,7 @@
       <c r="A105" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B105" s="7">
+      <c r="B105" s="14">
         <v>6.1</v>
       </c>
       <c r="C105" s="7">
@@ -24290,7 +24290,7 @@
       <c r="A106" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B106" s="7">
+      <c r="B106" s="14">
         <v>6.2</v>
       </c>
       <c r="C106" s="7"/>
@@ -24302,7 +24302,7 @@
       <c r="A107" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B107" s="7">
+      <c r="B107" s="14">
         <v>7</v>
       </c>
       <c r="C107" s="7"/>
@@ -24314,7 +24314,7 @@
       <c r="A108" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B108" s="7">
+      <c r="B108" s="14">
         <v>8</v>
       </c>
       <c r="C108" s="7">
@@ -24328,7 +24328,7 @@
       <c r="A109" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B109" s="7">
+      <c r="B109" s="14">
         <v>8</v>
       </c>
       <c r="C109" s="7">
@@ -24342,7 +24342,7 @@
       <c r="A110" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B110" s="7">
+      <c r="B110" s="14">
         <v>8</v>
       </c>
       <c r="C110" s="7">
@@ -24356,7 +24356,7 @@
       <c r="A111" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B111" s="7">
+      <c r="B111" s="14">
         <v>9</v>
       </c>
       <c r="C111" s="7">
@@ -24370,7 +24370,7 @@
       <c r="A112" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B112" s="7">
+      <c r="B112" s="14">
         <v>9</v>
       </c>
       <c r="C112" s="7">
@@ -24384,7 +24384,7 @@
       <c r="A113" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B113" s="7">
+      <c r="B113" s="14">
         <v>9</v>
       </c>
       <c r="C113" s="7">
@@ -24398,7 +24398,7 @@
       <c r="A114" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B114" s="7">
+      <c r="B114" s="14">
         <v>9</v>
       </c>
       <c r="C114" s="7">
@@ -24412,7 +24412,7 @@
       <c r="A115" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B115" s="7">
+      <c r="B115" s="14">
         <v>9</v>
       </c>
       <c r="C115" s="7">
@@ -24426,7 +24426,7 @@
       <c r="A116" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B116" s="7">
+      <c r="B116" s="14">
         <v>9</v>
       </c>
       <c r="C116" s="7">
@@ -24440,7 +24440,7 @@
       <c r="A117" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B117" s="7">
+      <c r="B117" s="14">
         <v>9</v>
       </c>
       <c r="C117" s="7">
@@ -24454,7 +24454,7 @@
       <c r="A118" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B118" s="7">
+      <c r="B118" s="14">
         <v>9</v>
       </c>
       <c r="C118" s="7">
@@ -24468,7 +24468,7 @@
       <c r="A119" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B119" s="7">
+      <c r="B119" s="14">
         <v>9</v>
       </c>
       <c r="C119" s="7">
@@ -24482,7 +24482,7 @@
       <c r="A120" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B120" s="7">
+      <c r="B120" s="14">
         <v>9</v>
       </c>
       <c r="C120" s="7">
@@ -24496,7 +24496,7 @@
       <c r="A121" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B121" s="7">
+      <c r="B121" s="14">
         <v>9</v>
       </c>
       <c r="C121" s="7">
@@ -24510,7 +24510,7 @@
       <c r="A122" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B122" s="7">
+      <c r="B122" s="14">
         <v>9</v>
       </c>
       <c r="C122" s="7">
@@ -24524,7 +24524,7 @@
       <c r="A123" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B123" s="7">
+      <c r="B123" s="14">
         <v>9</v>
       </c>
       <c r="C123" s="7">
@@ -24538,7 +24538,7 @@
       <c r="A124" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B124" s="7">
+      <c r="B124" s="14">
         <v>9</v>
       </c>
       <c r="C124" s="7">
@@ -24552,7 +24552,7 @@
       <c r="A125" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B125" s="7">
+      <c r="B125" s="14">
         <v>9</v>
       </c>
       <c r="C125" s="7">
@@ -24566,7 +24566,7 @@
       <c r="A126" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B126" s="7">
+      <c r="B126" s="14">
         <v>9</v>
       </c>
       <c r="C126" s="7">
@@ -24580,7 +24580,7 @@
       <c r="A127" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B127" s="7">
+      <c r="B127" s="14">
         <v>9</v>
       </c>
       <c r="C127" s="7">
@@ -24594,7 +24594,7 @@
       <c r="A128" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B128" s="7">
+      <c r="B128" s="14">
         <v>9</v>
       </c>
       <c r="C128" s="7">
@@ -24608,7 +24608,7 @@
       <c r="A129" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B129" s="7">
+      <c r="B129" s="14">
         <v>9</v>
       </c>
       <c r="C129" s="7">
@@ -24622,7 +24622,7 @@
       <c r="A130" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B130" s="7">
+      <c r="B130" s="14">
         <v>9</v>
       </c>
       <c r="C130" s="7">
@@ -24636,7 +24636,7 @@
       <c r="A131" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B131" s="7">
+      <c r="B131" s="14">
         <v>9</v>
       </c>
       <c r="C131" s="7">
@@ -24650,7 +24650,7 @@
       <c r="A132" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B132" s="7">
+      <c r="B132" s="14">
         <v>9</v>
       </c>
       <c r="C132" s="7">
@@ -24664,7 +24664,7 @@
       <c r="A133" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B133" s="7">
+      <c r="B133" s="14">
         <v>9</v>
       </c>
       <c r="C133" s="7">
@@ -24681,12 +24681,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c3e85fef-df06-4e67-8632-489752715f52" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6fd297-1f65-4950-8fc9-157e29c7b648">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24939,20 +24941,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c3e85fef-df06-4e67-8632-489752715f52" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6fd297-1f65-4950-8fc9-157e29c7b648">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171B3C16-7124-4B98-87E3-5FC6A9D45406}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98411DB4-5541-4967-8DBE-AF3E324DD5F5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c3e85fef-df06-4e67-8632-489752715f52"/>
+    <ds:schemaRef ds:uri="ea6fd297-1f65-4950-8fc9-157e29c7b648"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -24977,12 +24980,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98411DB4-5541-4967-8DBE-AF3E324DD5F5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171B3C16-7124-4B98-87E3-5FC6A9D45406}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c3e85fef-df06-4e67-8632-489752715f52"/>
-    <ds:schemaRef ds:uri="ea6fd297-1f65-4950-8fc9-157e29c7b648"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/dg_list.xlsx
+++ b/dg_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ialasia.sharepoint.com/sites/IALDGDESK/Shared Documents/General/Query System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="545" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A424F4E-F6CC-46D3-863C-BBD24AE8B541}"/>
+  <xr:revisionPtr revIDLastSave="953" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D75CC56C-FF13-4508-B3C1-933254F95F07}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
   </bookViews>
   <sheets>
     <sheet name="IAL" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3447" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3536" uniqueCount="352">
   <si>
     <t>UN Number</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1318,6 +1318,102 @@
   </si>
   <si>
     <t>WHL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All Flammable liquid substances initial boiling point below / equal to 35°C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All Flammable liquid substances FLASH POINT below -18°C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flash point BELOW -18 °C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>For TSL Booking on TSL Vessel can be loaded in GP, but Partner's booking only be loaded in reefer.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All lithium ion / metal and sodium ion batteries cargos are ON deck.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TSL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dangerous goods packed by flexitank container are prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All substances with IMDG CODE SP 76/349/350/351/352/353/900 is prohitbited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All "MOLTEN " type DG are prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DG in reefer only accept Class 3, 4.1 and 9 (not include any sub risk). If Class 3 substances which flash point&lt;23°C, the RF which maximum setting temperatures are less than 10°C below the flashpoint.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> UN 2216 sould provide fishmeal certificate comply with IMDG CODE SP 907</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TSL only accept all kinds of new batteries. Any waste/recycled/used batteries are prohibited. Such as UN2794, 2800, 3090, 3091, 3171, 3480, 3481, 3536 or any other UN number which are related to "battery"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">TSL only accept all kinds of new batteries. Any waste/recycled/used batteries are prohibited. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dangerous Goods which is assigned SP386 (1)50°C&lt;SAPT&lt;75°C in the package of IBC, if less than 50°C is prohibited. (2) 45°C &lt;SAPT&lt; 75°C in the portable tank, if less than 45°C is prohibited. (3) SDS is required in order to verify the SAPT of the cargo (4) Letter of idemnity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dangerous Goods requiring temperature control by IMDG Code is prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Any Dangerous "WASTE" as per IMDG Code is not accepted.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DIVINYLBENZENE (DVB) is prohibited.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bitumen cargo is not acceptable in flexitank or in hot state.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sodium Dichloroisocyanurate Dihydrate (SDID) is prohibited.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>For commodity Fish meal(Fish scrap), we accept DG with Class 9 UN2216 only.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fishmeal declares as non-dg which is complied with IMDG Code SP928 will not be admitted. Partners are requesting for acceptance of loading fishmeals shall be in a DG of Class 9 UN2216, Fishmeals with classifying as Class 4.2 UN1374 is prohibited.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reject all of Class 5.1 or sub Class 5.1 export from India.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Any kinds of charcoal &amp; Carbon covered by this entry is produced by pyrolysis of an organic material are not acceptable.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lithium ion / metal battery (UN 3480 / UN 3090, DG or non-DG,including power bank) are not acceptable even if they comply with SP 188</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1457,11 +1553,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -13314,17 +13410,28 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC47445C-7012-4511-9F13-234CFD25521A}">
-  <dimension ref="A1:H337"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q364"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.625" style="16" customWidth="1"/>
-    <col min="2" max="2" width="15" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="11.625" style="16" customWidth="1"/>
-    <col min="6" max="8" width="50.625" style="16" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="16"/>
+    <col min="1" max="1" width="7.625" style="15" customWidth="1"/>
+    <col min="2" max="2" width="15" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.625" style="15" customWidth="1"/>
+    <col min="6" max="6" width="121.625" style="15" customWidth="1"/>
+    <col min="7" max="7" width="86" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="102.625" style="15" customWidth="1"/>
+    <col min="9" max="9" width="169" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="178.25" style="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="235.75" style="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="65.5" style="15" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="53.875" style="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="36.875" style="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="51.625" style="15" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="49.125" style="15" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="101.875" style="15" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>2</v>
       </c>
@@ -13350,100 +13457,129 @@
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="B2" s="17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="C2" s="16"/>
+      <c r="F2" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="17">
         <v>1</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="B3" s="15">
+      <c r="C3" s="14"/>
+      <c r="D3" s="14" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="16">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="14" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="B4" s="15">
+      <c r="C4" s="16"/>
+      <c r="D4" s="14" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B5" s="16">
         <v>1.2</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="14" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="B5" s="15">
+      <c r="C5" s="16"/>
+      <c r="D5" s="14" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B6" s="16">
         <v>1.3</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="14" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="B6" s="15">
+      <c r="C6" s="16"/>
+      <c r="D6" s="14" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B7" s="16">
         <v>1.4</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="14" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="B7" s="15">
+      <c r="C7" s="16"/>
+      <c r="D7" s="14" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" s="16">
         <v>1.5</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="14" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="B8" s="15">
+      <c r="C8" s="16"/>
+      <c r="D8" s="14" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B9" s="16">
         <v>1.6</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="B9" s="17">
-        <v>2.1</v>
-      </c>
-      <c r="C9" s="14">
-        <v>1012</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>138</v>
@@ -13451,7 +13587,7 @@
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>140</v>
       </c>
@@ -13459,7 +13595,7 @@
         <v>2.1</v>
       </c>
       <c r="C10" s="14">
-        <v>1027</v>
+        <v>1001</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>138</v>
@@ -13467,7 +13603,7 @@
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>140</v>
       </c>
@@ -13475,7 +13611,7 @@
         <v>2.1</v>
       </c>
       <c r="C11" s="14">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>138</v>
@@ -13483,7 +13619,7 @@
       <c r="E11" s="14"/>
       <c r="F11" s="14"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>140</v>
       </c>
@@ -13491,7 +13627,7 @@
         <v>2.1</v>
       </c>
       <c r="C12" s="14">
-        <v>1033</v>
+        <v>1011</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>138</v>
@@ -13499,7 +13635,7 @@
       <c r="E12" s="14"/>
       <c r="F12" s="14"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>140</v>
       </c>
@@ -13507,7 +13643,7 @@
         <v>2.1</v>
       </c>
       <c r="C13" s="14">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>138</v>
@@ -13515,7 +13651,7 @@
       <c r="E13" s="14"/>
       <c r="F13" s="14"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>140</v>
       </c>
@@ -13523,7 +13659,7 @@
         <v>2.1</v>
       </c>
       <c r="C14" s="14">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>138</v>
@@ -13531,7 +13667,7 @@
       <c r="E14" s="14"/>
       <c r="F14" s="14"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>140</v>
       </c>
@@ -13539,7 +13675,7 @@
         <v>2.1</v>
       </c>
       <c r="C15" s="14">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>138</v>
@@ -13547,7 +13683,7 @@
       <c r="E15" s="14"/>
       <c r="F15" s="14"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>140</v>
       </c>
@@ -13555,7 +13691,7 @@
         <v>2.1</v>
       </c>
       <c r="C16" s="14">
-        <v>1039</v>
+        <v>1049</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>138</v>
@@ -13571,7 +13707,7 @@
         <v>2.1</v>
       </c>
       <c r="C17" s="14">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>138</v>
@@ -13587,7 +13723,7 @@
         <v>2.1</v>
       </c>
       <c r="C18" s="14">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>138</v>
@@ -13603,7 +13739,7 @@
         <v>2.1</v>
       </c>
       <c r="C19" s="14">
-        <v>1950</v>
+        <v>1075</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>138</v>
@@ -13619,7 +13755,7 @@
         <v>2.1</v>
       </c>
       <c r="C20" s="14">
-        <v>1050</v>
+        <v>1077</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>138</v>
@@ -13635,7 +13771,7 @@
         <v>2.1</v>
       </c>
       <c r="C21" s="14">
-        <v>1962</v>
+        <v>1081</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>138</v>
@@ -13651,7 +13787,7 @@
         <v>2.1</v>
       </c>
       <c r="C22" s="14">
-        <v>1969</v>
+        <v>1083</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>138</v>
@@ -13667,7 +13803,7 @@
         <v>2.1</v>
       </c>
       <c r="C23" s="14">
-        <v>1978</v>
+        <v>1085</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>138</v>
@@ -13683,7 +13819,7 @@
         <v>2.1</v>
       </c>
       <c r="C24" s="14">
-        <v>2035</v>
+        <v>1086</v>
       </c>
       <c r="D24" s="14" t="s">
         <v>138</v>
@@ -13699,7 +13835,7 @@
         <v>2.1</v>
       </c>
       <c r="C25" s="14">
-        <v>2037</v>
+        <v>1087</v>
       </c>
       <c r="D25" s="14" t="s">
         <v>138</v>
@@ -13715,7 +13851,7 @@
         <v>2.1</v>
       </c>
       <c r="C26" s="14">
-        <v>2044</v>
+        <v>1860</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>138</v>
@@ -13731,7 +13867,7 @@
         <v>2.1</v>
       </c>
       <c r="C27" s="14">
-        <v>2419</v>
+        <v>1912</v>
       </c>
       <c r="D27" s="14" t="s">
         <v>138</v>
@@ -13747,7 +13883,7 @@
         <v>2.1</v>
       </c>
       <c r="C28" s="14">
-        <v>2453</v>
+        <v>1954</v>
       </c>
       <c r="D28" s="14" t="s">
         <v>138</v>
@@ -13763,7 +13899,7 @@
         <v>2.1</v>
       </c>
       <c r="C29" s="14">
-        <v>2454</v>
+        <v>1957</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>138</v>
@@ -13779,7 +13915,7 @@
         <v>2.1</v>
       </c>
       <c r="C30" s="14">
-        <v>2517</v>
+        <v>1959</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>138</v>
@@ -13795,7 +13931,7 @@
         <v>2.1</v>
       </c>
       <c r="C31" s="14">
-        <v>2601</v>
+        <v>1961</v>
       </c>
       <c r="D31" s="14" t="s">
         <v>138</v>
@@ -13811,7 +13947,7 @@
         <v>2.1</v>
       </c>
       <c r="C32" s="14">
-        <v>3153</v>
+        <v>1964</v>
       </c>
       <c r="D32" s="14" t="s">
         <v>138</v>
@@ -13827,7 +13963,7 @@
         <v>2.1</v>
       </c>
       <c r="C33" s="14">
-        <v>3154</v>
+        <v>1965</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>138</v>
@@ -13843,7 +13979,7 @@
         <v>2.1</v>
       </c>
       <c r="C34" s="14">
-        <v>3252</v>
+        <v>1966</v>
       </c>
       <c r="D34" s="14" t="s">
         <v>138</v>
@@ -13859,7 +13995,7 @@
         <v>2.1</v>
       </c>
       <c r="C35" s="14">
-        <v>3358</v>
+        <v>1971</v>
       </c>
       <c r="D35" s="14" t="s">
         <v>138</v>
@@ -13872,15 +14008,15 @@
         <v>140</v>
       </c>
       <c r="B36" s="17">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="C36" s="14"/>
+        <v>2.1</v>
+      </c>
+      <c r="C36" s="14">
+        <v>1972</v>
+      </c>
       <c r="D36" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="E36" s="14" t="s">
-        <v>138</v>
-      </c>
+      <c r="E36" s="14"/>
       <c r="F36" s="14"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -13888,9 +14024,11 @@
         <v>140</v>
       </c>
       <c r="B37" s="17">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="C37" s="14"/>
+        <v>2.1</v>
+      </c>
+      <c r="C37" s="14">
+        <v>2034</v>
+      </c>
       <c r="D37" s="14" t="s">
         <v>138</v>
       </c>
@@ -13902,10 +14040,10 @@
         <v>140</v>
       </c>
       <c r="B38" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C38" s="14">
-        <v>1113</v>
+        <v>2200</v>
       </c>
       <c r="D38" s="14" t="s">
         <v>138</v>
@@ -13918,10 +14056,10 @@
         <v>140</v>
       </c>
       <c r="B39" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C39" s="14">
-        <v>1090</v>
+        <v>2203</v>
       </c>
       <c r="D39" s="14" t="s">
         <v>138</v>
@@ -13934,10 +14072,10 @@
         <v>140</v>
       </c>
       <c r="B40" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C40" s="14">
-        <v>1089</v>
+        <v>2452</v>
       </c>
       <c r="D40" s="14" t="s">
         <v>138</v>
@@ -13950,10 +14088,10 @@
         <v>140</v>
       </c>
       <c r="B41" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C41" s="14">
-        <v>1108</v>
+        <v>3138</v>
       </c>
       <c r="D41" s="14" t="s">
         <v>138</v>
@@ -13966,10 +14104,10 @@
         <v>140</v>
       </c>
       <c r="B42" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C42" s="14">
-        <v>1088</v>
+        <v>3150</v>
       </c>
       <c r="D42" s="14" t="s">
         <v>138</v>
@@ -13982,10 +14120,10 @@
         <v>140</v>
       </c>
       <c r="B43" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C43" s="14">
-        <v>1127</v>
+        <v>3161</v>
       </c>
       <c r="D43" s="14" t="s">
         <v>138</v>
@@ -13998,10 +14136,10 @@
         <v>140</v>
       </c>
       <c r="B44" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C44" s="14">
-        <v>1100</v>
+        <v>3167</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>138</v>
@@ -14014,10 +14152,10 @@
         <v>140</v>
       </c>
       <c r="B45" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C45" s="14">
-        <v>1131</v>
+        <v>3312</v>
       </c>
       <c r="D45" s="14" t="s">
         <v>138</v>
@@ -14030,10 +14168,10 @@
         <v>140</v>
       </c>
       <c r="B46" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C46" s="14">
-        <v>1146</v>
+        <v>3354</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>138</v>
@@ -14046,10 +14184,10 @@
         <v>140</v>
       </c>
       <c r="B47" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C47" s="14">
-        <v>1154</v>
+        <v>3374</v>
       </c>
       <c r="D47" s="14" t="s">
         <v>138</v>
@@ -14062,10 +14200,10 @@
         <v>140</v>
       </c>
       <c r="B48" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C48" s="14">
-        <v>1155</v>
+        <v>3468</v>
       </c>
       <c r="D48" s="14" t="s">
         <v>138</v>
@@ -14073,15 +14211,15 @@
       <c r="E48" s="14"/>
       <c r="F48" s="14"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B49" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C49" s="14">
-        <v>1144</v>
+        <v>3478</v>
       </c>
       <c r="D49" s="14" t="s">
         <v>138</v>
@@ -14089,15 +14227,15 @@
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B50" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C50" s="14">
-        <v>1159</v>
+        <v>3479</v>
       </c>
       <c r="D50" s="14" t="s">
         <v>138</v>
@@ -14105,15 +14243,15 @@
       <c r="E50" s="14"/>
       <c r="F50" s="14"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B51" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C51" s="14">
-        <v>1160</v>
+        <v>3501</v>
       </c>
       <c r="D51" s="14" t="s">
         <v>138</v>
@@ -14121,15 +14259,15 @@
       <c r="E51" s="14"/>
       <c r="F51" s="14"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B52" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C52" s="14">
-        <v>1164</v>
+        <v>3504</v>
       </c>
       <c r="D52" s="14" t="s">
         <v>138</v>
@@ -14137,15 +14275,15 @@
       <c r="E52" s="14"/>
       <c r="F52" s="14"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B53" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C53" s="14">
-        <v>1190</v>
+        <v>3505</v>
       </c>
       <c r="D53" s="14" t="s">
         <v>138</v>
@@ -14153,15 +14291,15 @@
       <c r="E53" s="14"/>
       <c r="F53" s="14"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B54" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C54" s="14">
-        <v>1167</v>
+        <v>3510</v>
       </c>
       <c r="D54" s="14" t="s">
         <v>138</v>
@@ -14169,15 +14307,15 @@
       <c r="E54" s="14"/>
       <c r="F54" s="14"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B55" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C55" s="14">
-        <v>1194</v>
+        <v>3529</v>
       </c>
       <c r="D55" s="14" t="s">
         <v>138</v>
@@ -14185,15 +14323,15 @@
       <c r="E55" s="14"/>
       <c r="F55" s="14"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B56" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C56" s="14">
-        <v>1203</v>
+        <v>3537</v>
       </c>
       <c r="D56" s="14" t="s">
         <v>138</v>
@@ -14201,15 +14339,15 @@
       <c r="E56" s="14"/>
       <c r="F56" s="14"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B57" s="17">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C57" s="14">
-        <v>1208</v>
+        <v>3553</v>
       </c>
       <c r="D57" s="14" t="s">
         <v>138</v>
@@ -14217,15 +14355,15 @@
       <c r="E57" s="14"/>
       <c r="F57" s="14"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B58" s="17">
-        <v>3</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="C58" s="14">
-        <v>1218</v>
+        <v>2455</v>
       </c>
       <c r="D58" s="14" t="s">
         <v>138</v>
@@ -14233,39 +14371,40 @@
       <c r="E58" s="14"/>
       <c r="F58" s="14"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B59" s="17">
-        <v>3</v>
-      </c>
-      <c r="C59" s="14">
-        <v>1234</v>
-      </c>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C59" s="14"/>
       <c r="D59" s="14" t="s">
         <v>138</v>
       </c>
       <c r="E59" s="14"/>
       <c r="F59" s="14"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B60" s="17">
         <v>3</v>
       </c>
-      <c r="C60" s="14">
-        <v>1243</v>
-      </c>
-      <c r="D60" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C60" s="14"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F60" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="G60" s="15" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
         <v>140</v>
       </c>
@@ -14273,7 +14412,7 @@
         <v>3</v>
       </c>
       <c r="C61" s="14">
-        <v>1275</v>
+        <v>1088</v>
       </c>
       <c r="D61" s="14" t="s">
         <v>138</v>
@@ -14281,7 +14420,7 @@
       <c r="E61" s="14"/>
       <c r="F61" s="14"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
         <v>140</v>
       </c>
@@ -14289,7 +14428,7 @@
         <v>3</v>
       </c>
       <c r="C62" s="14">
-        <v>1221</v>
+        <v>1089</v>
       </c>
       <c r="D62" s="14" t="s">
         <v>138</v>
@@ -14297,7 +14436,7 @@
       <c r="E62" s="14"/>
       <c r="F62" s="14"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
         <v>140</v>
       </c>
@@ -14305,7 +14444,7 @@
         <v>3</v>
       </c>
       <c r="C63" s="14">
-        <v>1265</v>
+        <v>1090</v>
       </c>
       <c r="D63" s="14" t="s">
         <v>138</v>
@@ -14313,7 +14452,7 @@
       <c r="E63" s="14"/>
       <c r="F63" s="14"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="14" t="s">
         <v>140</v>
       </c>
@@ -14321,7 +14460,7 @@
         <v>3</v>
       </c>
       <c r="C64" s="14">
-        <v>1280</v>
+        <v>1100</v>
       </c>
       <c r="D64" s="14" t="s">
         <v>138</v>
@@ -14337,7 +14476,7 @@
         <v>3</v>
       </c>
       <c r="C65" s="14">
-        <v>1298</v>
+        <v>1108</v>
       </c>
       <c r="D65" s="14" t="s">
         <v>138</v>
@@ -14353,7 +14492,7 @@
         <v>3</v>
       </c>
       <c r="C66" s="14">
-        <v>1303</v>
+        <v>1113</v>
       </c>
       <c r="D66" s="14" t="s">
         <v>138</v>
@@ -14369,7 +14508,7 @@
         <v>3</v>
       </c>
       <c r="C67" s="14">
-        <v>1277</v>
+        <v>1127</v>
       </c>
       <c r="D67" s="14" t="s">
         <v>138</v>
@@ -14385,7 +14524,7 @@
         <v>3</v>
       </c>
       <c r="C68" s="14">
-        <v>1302</v>
+        <v>1131</v>
       </c>
       <c r="D68" s="14" t="s">
         <v>138</v>
@@ -14401,7 +14540,7 @@
         <v>3</v>
       </c>
       <c r="C69" s="14">
-        <v>1991</v>
+        <v>1144</v>
       </c>
       <c r="D69" s="14" t="s">
         <v>138</v>
@@ -14417,7 +14556,7 @@
         <v>3</v>
       </c>
       <c r="C70" s="14">
-        <v>1717</v>
+        <v>1146</v>
       </c>
       <c r="D70" s="14" t="s">
         <v>138</v>
@@ -14433,7 +14572,7 @@
         <v>3</v>
       </c>
       <c r="C71" s="14">
-        <v>1999</v>
+        <v>1154</v>
       </c>
       <c r="D71" s="14" t="s">
         <v>138</v>
@@ -14449,7 +14588,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="14">
-        <v>2045</v>
+        <v>1155</v>
       </c>
       <c r="D72" s="14" t="s">
         <v>138</v>
@@ -14465,7 +14604,7 @@
         <v>3</v>
       </c>
       <c r="C73" s="14">
-        <v>2056</v>
+        <v>1159</v>
       </c>
       <c r="D73" s="14" t="s">
         <v>138</v>
@@ -14481,7 +14620,7 @@
         <v>3</v>
       </c>
       <c r="C74" s="14">
-        <v>2246</v>
+        <v>1160</v>
       </c>
       <c r="D74" s="14" t="s">
         <v>138</v>
@@ -14497,7 +14636,7 @@
         <v>3</v>
       </c>
       <c r="C75" s="14">
-        <v>2251</v>
+        <v>1164</v>
       </c>
       <c r="D75" s="14" t="s">
         <v>138</v>
@@ -14513,7 +14652,7 @@
         <v>3</v>
       </c>
       <c r="C76" s="14">
-        <v>2384</v>
+        <v>1167</v>
       </c>
       <c r="D76" s="14" t="s">
         <v>138</v>
@@ -14529,7 +14668,7 @@
         <v>3</v>
       </c>
       <c r="C77" s="14">
-        <v>2389</v>
+        <v>1190</v>
       </c>
       <c r="D77" s="14" t="s">
         <v>138</v>
@@ -14545,7 +14684,7 @@
         <v>3</v>
       </c>
       <c r="C78" s="14">
-        <v>2356</v>
+        <v>1194</v>
       </c>
       <c r="D78" s="14" t="s">
         <v>138</v>
@@ -14561,7 +14700,7 @@
         <v>3</v>
       </c>
       <c r="C79" s="14">
-        <v>2301</v>
+        <v>1203</v>
       </c>
       <c r="D79" s="14" t="s">
         <v>138</v>
@@ -14577,7 +14716,7 @@
         <v>3</v>
       </c>
       <c r="C80" s="14">
-        <v>2347</v>
+        <v>1208</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>138</v>
@@ -14593,7 +14732,7 @@
         <v>3</v>
       </c>
       <c r="C81" s="14">
-        <v>2363</v>
+        <v>1218</v>
       </c>
       <c r="D81" s="14" t="s">
         <v>138</v>
@@ -14609,7 +14748,7 @@
         <v>3</v>
       </c>
       <c r="C82" s="14">
-        <v>2371</v>
+        <v>1221</v>
       </c>
       <c r="D82" s="14" t="s">
         <v>138</v>
@@ -14625,7 +14764,7 @@
         <v>3</v>
       </c>
       <c r="C83" s="14">
-        <v>2458</v>
+        <v>1234</v>
       </c>
       <c r="D83" s="14" t="s">
         <v>138</v>
@@ -14641,7 +14780,7 @@
         <v>3</v>
       </c>
       <c r="C84" s="14">
-        <v>2398</v>
+        <v>1243</v>
       </c>
       <c r="D84" s="14" t="s">
         <v>138</v>
@@ -14657,7 +14796,7 @@
         <v>3</v>
       </c>
       <c r="C85" s="14">
-        <v>2402</v>
+        <v>1265</v>
       </c>
       <c r="D85" s="14" t="s">
         <v>138</v>
@@ -14673,7 +14812,7 @@
         <v>3</v>
       </c>
       <c r="C86" s="14">
-        <v>2457</v>
+        <v>1275</v>
       </c>
       <c r="D86" s="14" t="s">
         <v>138</v>
@@ -14689,7 +14828,7 @@
         <v>3</v>
       </c>
       <c r="C87" s="14">
-        <v>2456</v>
+        <v>1277</v>
       </c>
       <c r="D87" s="14" t="s">
         <v>138</v>
@@ -14705,7 +14844,7 @@
         <v>3</v>
       </c>
       <c r="C88" s="14">
-        <v>2460</v>
+        <v>1280</v>
       </c>
       <c r="D88" s="14" t="s">
         <v>138</v>
@@ -14721,7 +14860,7 @@
         <v>3</v>
       </c>
       <c r="C89" s="14">
-        <v>2461</v>
+        <v>1298</v>
       </c>
       <c r="D89" s="14" t="s">
         <v>138</v>
@@ -14737,7 +14876,7 @@
         <v>3</v>
       </c>
       <c r="C90" s="14">
-        <v>2459</v>
+        <v>1302</v>
       </c>
       <c r="D90" s="14" t="s">
         <v>138</v>
@@ -14753,7 +14892,7 @@
         <v>3</v>
       </c>
       <c r="C91" s="14">
-        <v>2561</v>
+        <v>1303</v>
       </c>
       <c r="D91" s="14" t="s">
         <v>138</v>
@@ -14769,7 +14908,7 @@
         <v>3</v>
       </c>
       <c r="C92" s="14">
-        <v>2612</v>
+        <v>1717</v>
       </c>
       <c r="D92" s="14" t="s">
         <v>138</v>
@@ -14785,7 +14924,7 @@
         <v>3</v>
       </c>
       <c r="C93" s="14">
-        <v>2615</v>
+        <v>1991</v>
       </c>
       <c r="D93" s="14" t="s">
         <v>138</v>
@@ -14801,7 +14940,7 @@
         <v>3</v>
       </c>
       <c r="C94" s="14">
-        <v>2749</v>
+        <v>1999</v>
       </c>
       <c r="D94" s="14" t="s">
         <v>138</v>
@@ -14817,7 +14956,7 @@
         <v>3</v>
       </c>
       <c r="C95" s="14">
-        <v>3379</v>
+        <v>2045</v>
       </c>
       <c r="D95" s="14" t="s">
         <v>138</v>
@@ -14833,7 +14972,7 @@
         <v>3</v>
       </c>
       <c r="C96" s="14">
-        <v>2983</v>
+        <v>2056</v>
       </c>
       <c r="D96" s="14" t="s">
         <v>138</v>
@@ -14849,7 +14988,7 @@
         <v>3</v>
       </c>
       <c r="C97" s="14">
-        <v>3494</v>
+        <v>2246</v>
       </c>
       <c r="D97" s="14" t="s">
         <v>138</v>
@@ -14865,7 +15004,7 @@
         <v>3</v>
       </c>
       <c r="C98" s="14">
-        <v>3343</v>
+        <v>2251</v>
       </c>
       <c r="D98" s="14" t="s">
         <v>138</v>
@@ -14881,7 +15020,7 @@
         <v>3</v>
       </c>
       <c r="C99" s="14">
-        <v>3357</v>
+        <v>2301</v>
       </c>
       <c r="D99" s="14" t="s">
         <v>138</v>
@@ -14894,10 +15033,10 @@
         <v>140</v>
       </c>
       <c r="B100" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C100" s="14">
-        <v>1320</v>
+        <v>2347</v>
       </c>
       <c r="D100" s="14" t="s">
         <v>138</v>
@@ -14910,10 +15049,10 @@
         <v>140</v>
       </c>
       <c r="B101" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C101" s="14">
-        <v>1310</v>
+        <v>2356</v>
       </c>
       <c r="D101" s="14" t="s">
         <v>138</v>
@@ -14926,10 +15065,10 @@
         <v>140</v>
       </c>
       <c r="B102" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C102" s="14">
-        <v>1331</v>
+        <v>2363</v>
       </c>
       <c r="D102" s="14" t="s">
         <v>138</v>
@@ -14942,10 +15081,10 @@
         <v>140</v>
       </c>
       <c r="B103" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C103" s="14">
-        <v>1336</v>
+        <v>2371</v>
       </c>
       <c r="D103" s="14" t="s">
         <v>138</v>
@@ -14958,10 +15097,10 @@
         <v>140</v>
       </c>
       <c r="B104" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C104" s="14">
-        <v>1337</v>
+        <v>2384</v>
       </c>
       <c r="D104" s="14" t="s">
         <v>138</v>
@@ -14974,10 +15113,10 @@
         <v>140</v>
       </c>
       <c r="B105" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C105" s="14">
-        <v>1321</v>
+        <v>2389</v>
       </c>
       <c r="D105" s="14" t="s">
         <v>138</v>
@@ -14990,10 +15129,10 @@
         <v>140</v>
       </c>
       <c r="B106" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C106" s="14">
-        <v>1322</v>
+        <v>2398</v>
       </c>
       <c r="D106" s="14" t="s">
         <v>138</v>
@@ -15006,10 +15145,10 @@
         <v>140</v>
       </c>
       <c r="B107" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C107" s="14">
-        <v>1348</v>
+        <v>2402</v>
       </c>
       <c r="D107" s="14" t="s">
         <v>138</v>
@@ -15022,10 +15161,10 @@
         <v>140</v>
       </c>
       <c r="B108" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C108" s="14">
-        <v>1349</v>
+        <v>2456</v>
       </c>
       <c r="D108" s="14" t="s">
         <v>138</v>
@@ -15038,10 +15177,10 @@
         <v>140</v>
       </c>
       <c r="B109" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C109" s="14">
-        <v>1344</v>
+        <v>2457</v>
       </c>
       <c r="D109" s="14" t="s">
         <v>138</v>
@@ -15054,10 +15193,10 @@
         <v>140</v>
       </c>
       <c r="B110" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C110" s="14">
-        <v>1347</v>
+        <v>2458</v>
       </c>
       <c r="D110" s="14" t="s">
         <v>138</v>
@@ -15070,10 +15209,10 @@
         <v>140</v>
       </c>
       <c r="B111" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C111" s="14">
-        <v>1354</v>
+        <v>2459</v>
       </c>
       <c r="D111" s="14" t="s">
         <v>138</v>
@@ -15086,10 +15225,10 @@
         <v>140</v>
       </c>
       <c r="B112" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C112" s="14">
-        <v>1357</v>
+        <v>2460</v>
       </c>
       <c r="D112" s="14" t="s">
         <v>138</v>
@@ -15102,10 +15241,10 @@
         <v>140</v>
       </c>
       <c r="B113" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C113" s="14">
-        <v>1356</v>
+        <v>2461</v>
       </c>
       <c r="D113" s="14" t="s">
         <v>138</v>
@@ -15118,10 +15257,10 @@
         <v>140</v>
       </c>
       <c r="B114" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C114" s="14">
-        <v>1355</v>
+        <v>2561</v>
       </c>
       <c r="D114" s="14" t="s">
         <v>138</v>
@@ -15134,10 +15273,10 @@
         <v>140</v>
       </c>
       <c r="B115" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C115" s="14">
-        <v>1517</v>
+        <v>2612</v>
       </c>
       <c r="D115" s="14" t="s">
         <v>138</v>
@@ -15150,10 +15289,10 @@
         <v>140</v>
       </c>
       <c r="B116" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C116" s="14">
-        <v>1571</v>
+        <v>2615</v>
       </c>
       <c r="D116" s="14" t="s">
         <v>138</v>
@@ -15166,10 +15305,10 @@
         <v>140</v>
       </c>
       <c r="B117" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C117" s="14">
-        <v>1944</v>
+        <v>2749</v>
       </c>
       <c r="D117" s="14" t="s">
         <v>138</v>
@@ -15182,10 +15321,10 @@
         <v>140</v>
       </c>
       <c r="B118" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C118" s="14">
-        <v>1945</v>
+        <v>2983</v>
       </c>
       <c r="D118" s="14" t="s">
         <v>138</v>
@@ -15198,10 +15337,10 @@
         <v>140</v>
       </c>
       <c r="B119" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C119" s="14">
-        <v>2304</v>
+        <v>3343</v>
       </c>
       <c r="D119" s="14" t="s">
         <v>138</v>
@@ -15214,10 +15353,10 @@
         <v>140</v>
       </c>
       <c r="B120" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C120" s="14">
-        <v>2555</v>
+        <v>3357</v>
       </c>
       <c r="D120" s="14" t="s">
         <v>138</v>
@@ -15230,10 +15369,10 @@
         <v>140</v>
       </c>
       <c r="B121" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C121" s="14">
-        <v>2557</v>
+        <v>3379</v>
       </c>
       <c r="D121" s="14" t="s">
         <v>138</v>
@@ -15246,10 +15385,10 @@
         <v>140</v>
       </c>
       <c r="B122" s="17">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C122" s="14">
-        <v>2254</v>
+        <v>3494</v>
       </c>
       <c r="D122" s="14" t="s">
         <v>138</v>
@@ -15265,7 +15404,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C123" s="14">
-        <v>2852</v>
+        <v>1310</v>
       </c>
       <c r="D123" s="14" t="s">
         <v>138</v>
@@ -15281,7 +15420,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C124" s="14">
-        <v>2448</v>
+        <v>1320</v>
       </c>
       <c r="D124" s="14" t="s">
         <v>138</v>
@@ -15297,7 +15436,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C125" s="14">
-        <v>2556</v>
+        <v>1321</v>
       </c>
       <c r="D125" s="14" t="s">
         <v>138</v>
@@ -15313,7 +15452,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C126" s="14">
-        <v>3097</v>
+        <v>1322</v>
       </c>
       <c r="D126" s="14" t="s">
         <v>138</v>
@@ -15329,7 +15468,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C127" s="14">
-        <v>2907</v>
+        <v>1331</v>
       </c>
       <c r="D127" s="14" t="s">
         <v>138</v>
@@ -15345,7 +15484,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C128" s="14">
-        <v>3176</v>
+        <v>1336</v>
       </c>
       <c r="D128" s="14" t="s">
         <v>138</v>
@@ -15361,7 +15500,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C129" s="14">
-        <v>3221</v>
+        <v>1337</v>
       </c>
       <c r="D129" s="14" t="s">
         <v>138</v>
@@ -15377,7 +15516,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C130" s="14">
-        <v>2956</v>
+        <v>1344</v>
       </c>
       <c r="D130" s="14" t="s">
         <v>138</v>
@@ -15393,7 +15532,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C131" s="14">
-        <v>3222</v>
+        <v>1347</v>
       </c>
       <c r="D131" s="14" t="s">
         <v>138</v>
@@ -15409,7 +15548,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C132" s="14">
-        <v>3224</v>
+        <v>1348</v>
       </c>
       <c r="D132" s="14" t="s">
         <v>138</v>
@@ -15425,7 +15564,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C133" s="14">
-        <v>3223</v>
+        <v>1349</v>
       </c>
       <c r="D133" s="14" t="s">
         <v>138</v>
@@ -15441,7 +15580,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C134" s="14">
-        <v>3226</v>
+        <v>1354</v>
       </c>
       <c r="D134" s="14" t="s">
         <v>138</v>
@@ -15457,7 +15596,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C135" s="14">
-        <v>3225</v>
+        <v>1355</v>
       </c>
       <c r="D135" s="14" t="s">
         <v>138</v>
@@ -15473,7 +15612,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C136" s="14">
-        <v>3227</v>
+        <v>1356</v>
       </c>
       <c r="D136" s="14" t="s">
         <v>138</v>
@@ -15489,7 +15628,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C137" s="14">
-        <v>3228</v>
+        <v>1357</v>
       </c>
       <c r="D137" s="14" t="s">
         <v>138</v>
@@ -15505,7 +15644,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C138" s="14">
-        <v>3235</v>
+        <v>1517</v>
       </c>
       <c r="D138" s="14" t="s">
         <v>138</v>
@@ -15521,7 +15660,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C139" s="14">
-        <v>3232</v>
+        <v>1571</v>
       </c>
       <c r="D139" s="14" t="s">
         <v>138</v>
@@ -15537,7 +15676,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C140" s="14">
-        <v>3231</v>
+        <v>1944</v>
       </c>
       <c r="D140" s="14" t="s">
         <v>138</v>
@@ -15553,7 +15692,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C141" s="14">
-        <v>3229</v>
+        <v>1945</v>
       </c>
       <c r="D141" s="14" t="s">
         <v>138</v>
@@ -15569,7 +15708,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C142" s="14">
-        <v>3234</v>
+        <v>2254</v>
       </c>
       <c r="D142" s="14" t="s">
         <v>138</v>
@@ -15585,7 +15724,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C143" s="14">
-        <v>3233</v>
+        <v>2304</v>
       </c>
       <c r="D143" s="14" t="s">
         <v>138</v>
@@ -15601,7 +15740,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C144" s="14">
-        <v>3230</v>
+        <v>2448</v>
       </c>
       <c r="D144" s="14" t="s">
         <v>138</v>
@@ -15617,7 +15756,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C145" s="14">
-        <v>3238</v>
+        <v>2555</v>
       </c>
       <c r="D145" s="14" t="s">
         <v>138</v>
@@ -15633,7 +15772,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C146" s="14">
-        <v>3240</v>
+        <v>2556</v>
       </c>
       <c r="D146" s="14" t="s">
         <v>138</v>
@@ -15649,7 +15788,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C147" s="14">
-        <v>3237</v>
+        <v>2557</v>
       </c>
       <c r="D147" s="14" t="s">
         <v>138</v>
@@ -15665,7 +15804,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C148" s="14">
-        <v>3239</v>
+        <v>2852</v>
       </c>
       <c r="D148" s="14" t="s">
         <v>138</v>
@@ -15681,7 +15820,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C149" s="14">
-        <v>3236</v>
+        <v>2907</v>
       </c>
       <c r="D149" s="14" t="s">
         <v>138</v>
@@ -15697,7 +15836,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C150" s="14">
-        <v>3251</v>
+        <v>2956</v>
       </c>
       <c r="D150" s="14" t="s">
         <v>138</v>
@@ -15713,7 +15852,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C151" s="14">
-        <v>3241</v>
+        <v>3097</v>
       </c>
       <c r="D151" s="14" t="s">
         <v>138</v>
@@ -15729,7 +15868,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C152" s="14">
-        <v>3242</v>
+        <v>3176</v>
       </c>
       <c r="D152" s="14" t="s">
         <v>138</v>
@@ -15745,7 +15884,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C153" s="14">
-        <v>3317</v>
+        <v>3221</v>
       </c>
       <c r="D153" s="14" t="s">
         <v>138</v>
@@ -15761,7 +15900,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C154" s="14">
-        <v>3319</v>
+        <v>3222</v>
       </c>
       <c r="D154" s="14" t="s">
         <v>138</v>
@@ -15777,7 +15916,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C155" s="14">
-        <v>3344</v>
+        <v>3223</v>
       </c>
       <c r="D155" s="14" t="s">
         <v>138</v>
@@ -15793,7 +15932,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C156" s="14">
-        <v>3364</v>
+        <v>3224</v>
       </c>
       <c r="D156" s="14" t="s">
         <v>138</v>
@@ -15809,7 +15948,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C157" s="14">
-        <v>3366</v>
+        <v>3225</v>
       </c>
       <c r="D157" s="14" t="s">
         <v>138</v>
@@ -15825,7 +15964,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C158" s="14">
-        <v>3370</v>
+        <v>3226</v>
       </c>
       <c r="D158" s="14" t="s">
         <v>138</v>
@@ -15841,7 +15980,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C159" s="14">
-        <v>3369</v>
+        <v>3227</v>
       </c>
       <c r="D159" s="14" t="s">
         <v>138</v>
@@ -15857,7 +15996,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C160" s="14">
-        <v>3368</v>
+        <v>3228</v>
       </c>
       <c r="D160" s="14" t="s">
         <v>138</v>
@@ -15873,7 +16012,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C161" s="14">
-        <v>3367</v>
+        <v>3229</v>
       </c>
       <c r="D161" s="14" t="s">
         <v>138</v>
@@ -15889,7 +16028,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C162" s="14">
-        <v>3376</v>
+        <v>3230</v>
       </c>
       <c r="D162" s="14" t="s">
         <v>138</v>
@@ -15905,7 +16044,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C163" s="14">
-        <v>3365</v>
+        <v>3231</v>
       </c>
       <c r="D163" s="14" t="s">
         <v>138</v>
@@ -15921,7 +16060,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C164" s="14">
-        <v>3380</v>
+        <v>3232</v>
       </c>
       <c r="D164" s="14" t="s">
         <v>138</v>
@@ -15937,7 +16076,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C165" s="14">
-        <v>3533</v>
+        <v>3233</v>
       </c>
       <c r="D165" s="14" t="s">
         <v>138</v>
@@ -15953,7 +16092,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C166" s="14">
-        <v>3531</v>
+        <v>3234</v>
       </c>
       <c r="D166" s="14" t="s">
         <v>138</v>
@@ -15969,7 +16108,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C167" s="14">
-        <v>3532</v>
+        <v>3235</v>
       </c>
       <c r="D167" s="14" t="s">
         <v>138</v>
@@ -15985,7 +16124,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C168" s="14">
-        <v>3474</v>
+        <v>3236</v>
       </c>
       <c r="D168" s="14" t="s">
         <v>138</v>
@@ -16001,7 +16140,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C169" s="14">
-        <v>3534</v>
+        <v>3237</v>
       </c>
       <c r="D169" s="14" t="s">
         <v>138</v>
@@ -16014,10 +16153,10 @@
         <v>140</v>
       </c>
       <c r="B170" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C170" s="14">
-        <v>1381</v>
+        <v>3238</v>
       </c>
       <c r="D170" s="14" t="s">
         <v>138</v>
@@ -16030,10 +16169,10 @@
         <v>140</v>
       </c>
       <c r="B171" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C171" s="14">
-        <v>1380</v>
+        <v>3239</v>
       </c>
       <c r="D171" s="14" t="s">
         <v>138</v>
@@ -16046,10 +16185,10 @@
         <v>140</v>
       </c>
       <c r="B172" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C172" s="14">
-        <v>1361</v>
+        <v>3240</v>
       </c>
       <c r="D172" s="14" t="s">
         <v>138</v>
@@ -16062,10 +16201,10 @@
         <v>140</v>
       </c>
       <c r="B173" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C173" s="14">
-        <v>1362</v>
+        <v>3241</v>
       </c>
       <c r="D173" s="14" t="s">
         <v>138</v>
@@ -16078,10 +16217,10 @@
         <v>140</v>
       </c>
       <c r="B174" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C174" s="14">
-        <v>1374</v>
+        <v>3242</v>
       </c>
       <c r="D174" s="14" t="s">
         <v>138</v>
@@ -16094,10 +16233,10 @@
         <v>140</v>
       </c>
       <c r="B175" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C175" s="14">
-        <v>1376</v>
+        <v>3251</v>
       </c>
       <c r="D175" s="14" t="s">
         <v>138</v>
@@ -16110,10 +16249,10 @@
         <v>140</v>
       </c>
       <c r="B176" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C176" s="14">
-        <v>1383</v>
+        <v>3317</v>
       </c>
       <c r="D176" s="14" t="s">
         <v>138</v>
@@ -16126,10 +16265,10 @@
         <v>140</v>
       </c>
       <c r="B177" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C177" s="14">
-        <v>2210</v>
+        <v>3319</v>
       </c>
       <c r="D177" s="14" t="s">
         <v>138</v>
@@ -16142,10 +16281,10 @@
         <v>140</v>
       </c>
       <c r="B178" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C178" s="14">
-        <v>1385</v>
+        <v>3344</v>
       </c>
       <c r="D178" s="14" t="s">
         <v>138</v>
@@ -16158,10 +16297,10 @@
         <v>140</v>
       </c>
       <c r="B179" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C179" s="14">
-        <v>1384</v>
+        <v>3364</v>
       </c>
       <c r="D179" s="14" t="s">
         <v>138</v>
@@ -16174,10 +16313,10 @@
         <v>140</v>
       </c>
       <c r="B180" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C180" s="14">
-        <v>1387</v>
+        <v>3365</v>
       </c>
       <c r="D180" s="14" t="s">
         <v>138</v>
@@ -16190,10 +16329,10 @@
         <v>140</v>
       </c>
       <c r="B181" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C181" s="14">
-        <v>2447</v>
+        <v>3366</v>
       </c>
       <c r="D181" s="14" t="s">
         <v>138</v>
@@ -16206,10 +16345,10 @@
         <v>140</v>
       </c>
       <c r="B182" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C182" s="14">
-        <v>2845</v>
+        <v>3367</v>
       </c>
       <c r="D182" s="14" t="s">
         <v>138</v>
@@ -16222,10 +16361,10 @@
         <v>140</v>
       </c>
       <c r="B183" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C183" s="14">
-        <v>2846</v>
+        <v>3368</v>
       </c>
       <c r="D183" s="14" t="s">
         <v>138</v>
@@ -16238,10 +16377,10 @@
         <v>140</v>
       </c>
       <c r="B184" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C184" s="14">
-        <v>2870</v>
+        <v>3369</v>
       </c>
       <c r="D184" s="14" t="s">
         <v>138</v>
@@ -16254,10 +16393,10 @@
         <v>140</v>
       </c>
       <c r="B185" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C185" s="14">
-        <v>2881</v>
+        <v>3370</v>
       </c>
       <c r="D185" s="14" t="s">
         <v>138</v>
@@ -16270,10 +16409,10 @@
         <v>140</v>
       </c>
       <c r="B186" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C186" s="14">
-        <v>3088</v>
+        <v>3376</v>
       </c>
       <c r="D186" s="14" t="s">
         <v>138</v>
@@ -16286,10 +16425,10 @@
         <v>140</v>
       </c>
       <c r="B187" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C187" s="14">
-        <v>3126</v>
+        <v>3380</v>
       </c>
       <c r="D187" s="14" t="s">
         <v>138</v>
@@ -16302,10 +16441,10 @@
         <v>140</v>
       </c>
       <c r="B188" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C188" s="14">
-        <v>3127</v>
+        <v>3474</v>
       </c>
       <c r="D188" s="14" t="s">
         <v>138</v>
@@ -16318,10 +16457,10 @@
         <v>140</v>
       </c>
       <c r="B189" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C189" s="14">
-        <v>3192</v>
+        <v>3531</v>
       </c>
       <c r="D189" s="14" t="s">
         <v>138</v>
@@ -16334,10 +16473,10 @@
         <v>140</v>
       </c>
       <c r="B190" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C190" s="14">
-        <v>3194</v>
+        <v>3532</v>
       </c>
       <c r="D190" s="14" t="s">
         <v>138</v>
@@ -16350,10 +16489,10 @@
         <v>140</v>
       </c>
       <c r="B191" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C191" s="14">
-        <v>3128</v>
+        <v>3533</v>
       </c>
       <c r="D191" s="14" t="s">
         <v>138</v>
@@ -16366,10 +16505,10 @@
         <v>140</v>
       </c>
       <c r="B192" s="17">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C192" s="14">
-        <v>3200</v>
+        <v>3534</v>
       </c>
       <c r="D192" s="14" t="s">
         <v>138</v>
@@ -16385,7 +16524,7 @@
         <v>4.2</v>
       </c>
       <c r="C193" s="14">
-        <v>3191</v>
+        <v>1361</v>
       </c>
       <c r="D193" s="14" t="s">
         <v>138</v>
@@ -16401,7 +16540,7 @@
         <v>4.2</v>
       </c>
       <c r="C194" s="14">
-        <v>3255</v>
+        <v>1362</v>
       </c>
       <c r="D194" s="14" t="s">
         <v>138</v>
@@ -16417,7 +16556,7 @@
         <v>4.2</v>
       </c>
       <c r="C195" s="14">
-        <v>3341</v>
+        <v>1374</v>
       </c>
       <c r="D195" s="14" t="s">
         <v>138</v>
@@ -16433,7 +16572,7 @@
         <v>4.2</v>
       </c>
       <c r="C196" s="14">
-        <v>3393</v>
+        <v>1376</v>
       </c>
       <c r="D196" s="14" t="s">
         <v>138</v>
@@ -16449,7 +16588,7 @@
         <v>4.2</v>
       </c>
       <c r="C197" s="14">
-        <v>3391</v>
+        <v>1380</v>
       </c>
       <c r="D197" s="14" t="s">
         <v>138</v>
@@ -16465,7 +16604,7 @@
         <v>4.2</v>
       </c>
       <c r="C198" s="14">
-        <v>3394</v>
+        <v>1381</v>
       </c>
       <c r="D198" s="14" t="s">
         <v>138</v>
@@ -16481,7 +16620,7 @@
         <v>4.2</v>
       </c>
       <c r="C199" s="14">
-        <v>3392</v>
+        <v>1383</v>
       </c>
       <c r="D199" s="14" t="s">
         <v>138</v>
@@ -16497,7 +16636,7 @@
         <v>4.2</v>
       </c>
       <c r="C200" s="14">
-        <v>3342</v>
+        <v>1384</v>
       </c>
       <c r="D200" s="14" t="s">
         <v>138</v>
@@ -16513,7 +16652,7 @@
         <v>4.2</v>
       </c>
       <c r="C201" s="14">
-        <v>3400</v>
+        <v>1385</v>
       </c>
       <c r="D201" s="14" t="s">
         <v>138</v>
@@ -16526,9 +16665,11 @@
         <v>140</v>
       </c>
       <c r="B202" s="17">
-        <v>4.3</v>
-      </c>
-      <c r="C202" s="14"/>
+        <v>4.2</v>
+      </c>
+      <c r="C202" s="14">
+        <v>1387</v>
+      </c>
       <c r="D202" s="14" t="s">
         <v>138</v>
       </c>
@@ -16540,10 +16681,10 @@
         <v>140</v>
       </c>
       <c r="B203" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C203" s="14">
-        <v>1462</v>
+        <v>2210</v>
       </c>
       <c r="D203" s="14" t="s">
         <v>138</v>
@@ -16556,10 +16697,10 @@
         <v>140</v>
       </c>
       <c r="B204" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C204" s="14">
-        <v>1461</v>
+        <v>2447</v>
       </c>
       <c r="D204" s="14" t="s">
         <v>138</v>
@@ -16572,10 +16713,10 @@
         <v>140</v>
       </c>
       <c r="B205" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C205" s="14">
-        <v>1459</v>
+        <v>2845</v>
       </c>
       <c r="D205" s="14" t="s">
         <v>138</v>
@@ -16588,10 +16729,10 @@
         <v>140</v>
       </c>
       <c r="B206" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C206" s="14">
-        <v>1458</v>
+        <v>2846</v>
       </c>
       <c r="D206" s="14" t="s">
         <v>138</v>
@@ -16604,10 +16745,10 @@
         <v>140</v>
       </c>
       <c r="B207" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C207" s="14">
-        <v>1454</v>
+        <v>2870</v>
       </c>
       <c r="D207" s="14" t="s">
         <v>138</v>
@@ -16620,10 +16761,10 @@
         <v>140</v>
       </c>
       <c r="B208" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C208" s="14">
-        <v>1450</v>
+        <v>2881</v>
       </c>
       <c r="D208" s="14" t="s">
         <v>138</v>
@@ -16636,10 +16777,10 @@
         <v>140</v>
       </c>
       <c r="B209" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C209" s="14">
-        <v>1442</v>
+        <v>3088</v>
       </c>
       <c r="D209" s="14" t="s">
         <v>138</v>
@@ -16652,10 +16793,10 @@
         <v>140</v>
       </c>
       <c r="B210" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C210" s="14">
-        <v>1463</v>
+        <v>3126</v>
       </c>
       <c r="D210" s="14" t="s">
         <v>138</v>
@@ -16668,10 +16809,10 @@
         <v>140</v>
       </c>
       <c r="B211" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C211" s="14">
-        <v>1481</v>
+        <v>3127</v>
       </c>
       <c r="D211" s="14" t="s">
         <v>138</v>
@@ -16684,10 +16825,10 @@
         <v>140</v>
       </c>
       <c r="B212" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C212" s="14">
-        <v>1477</v>
+        <v>3128</v>
       </c>
       <c r="D212" s="14" t="s">
         <v>138</v>
@@ -16700,10 +16841,10 @@
         <v>140</v>
       </c>
       <c r="B213" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C213" s="14">
-        <v>1479</v>
+        <v>3191</v>
       </c>
       <c r="D213" s="14" t="s">
         <v>138</v>
@@ -16716,10 +16857,10 @@
         <v>140</v>
       </c>
       <c r="B214" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C214" s="14">
-        <v>1482</v>
+        <v>3192</v>
       </c>
       <c r="D214" s="14" t="s">
         <v>138</v>
@@ -16732,10 +16873,10 @@
         <v>140</v>
       </c>
       <c r="B215" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C215" s="14">
-        <v>1483</v>
+        <v>3194</v>
       </c>
       <c r="D215" s="14" t="s">
         <v>138</v>
@@ -16748,10 +16889,10 @@
         <v>140</v>
       </c>
       <c r="B216" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C216" s="14">
-        <v>1490</v>
+        <v>3200</v>
       </c>
       <c r="D216" s="14" t="s">
         <v>138</v>
@@ -16764,10 +16905,10 @@
         <v>140</v>
       </c>
       <c r="B217" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C217" s="14">
-        <v>1512</v>
+        <v>3255</v>
       </c>
       <c r="D217" s="14" t="s">
         <v>138</v>
@@ -16780,10 +16921,10 @@
         <v>140</v>
       </c>
       <c r="B218" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C218" s="14">
-        <v>1746</v>
+        <v>3341</v>
       </c>
       <c r="D218" s="14" t="s">
         <v>138</v>
@@ -16796,10 +16937,10 @@
         <v>140</v>
       </c>
       <c r="B219" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C219" s="14">
-        <v>1745</v>
+        <v>3342</v>
       </c>
       <c r="D219" s="14" t="s">
         <v>138</v>
@@ -16812,10 +16953,10 @@
         <v>140</v>
       </c>
       <c r="B220" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C220" s="14">
-        <v>1748</v>
+        <v>3391</v>
       </c>
       <c r="D220" s="14" t="s">
         <v>138</v>
@@ -16828,10 +16969,10 @@
         <v>140</v>
       </c>
       <c r="B221" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C221" s="14">
-        <v>1873</v>
+        <v>3392</v>
       </c>
       <c r="D221" s="14" t="s">
         <v>138</v>
@@ -16844,10 +16985,10 @@
         <v>140</v>
       </c>
       <c r="B222" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C222" s="14">
-        <v>2208</v>
+        <v>3393</v>
       </c>
       <c r="D222" s="14" t="s">
         <v>138</v>
@@ -16860,10 +17001,10 @@
         <v>140</v>
       </c>
       <c r="B223" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C223" s="14">
-        <v>1942</v>
+        <v>3394</v>
       </c>
       <c r="D223" s="14" t="s">
         <v>138</v>
@@ -16876,10 +17017,10 @@
         <v>140</v>
       </c>
       <c r="B224" s="17">
-        <v>5.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C224" s="14">
-        <v>2015</v>
+        <v>3400</v>
       </c>
       <c r="D224" s="14" t="s">
         <v>138</v>
@@ -16892,11 +17033,9 @@
         <v>140</v>
       </c>
       <c r="B225" s="17">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="C225" s="14">
-        <v>2468</v>
-      </c>
+        <v>4.3</v>
+      </c>
+      <c r="C225" s="14"/>
       <c r="D225" s="14" t="s">
         <v>138</v>
       </c>
@@ -16910,14 +17049,12 @@
       <c r="B226" s="17">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C226" s="14">
-        <v>2465</v>
-      </c>
-      <c r="D226" s="14" t="s">
-        <v>138</v>
-      </c>
+      <c r="C226" s="14"/>
+      <c r="D226" s="14"/>
       <c r="E226" s="14"/>
-      <c r="F226" s="14"/>
+      <c r="F226" s="14" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="14" t="s">
@@ -16927,7 +17064,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C227" s="14">
-        <v>2426</v>
+        <v>1442</v>
       </c>
       <c r="D227" s="14" t="s">
         <v>138</v>
@@ -16943,7 +17080,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C228" s="14">
-        <v>2067</v>
+        <v>1450</v>
       </c>
       <c r="D228" s="14" t="s">
         <v>138</v>
@@ -16959,7 +17096,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C229" s="14">
-        <v>3211</v>
+        <v>1454</v>
       </c>
       <c r="D229" s="14" t="s">
         <v>138</v>
@@ -16975,7 +17112,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C230" s="14">
-        <v>3375</v>
+        <v>1458</v>
       </c>
       <c r="D230" s="14" t="s">
         <v>138</v>
@@ -16991,7 +17128,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C231" s="14">
-        <v>3218</v>
+        <v>1459</v>
       </c>
       <c r="D231" s="14" t="s">
         <v>138</v>
@@ -17007,7 +17144,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C232" s="14">
-        <v>3212</v>
+        <v>1461</v>
       </c>
       <c r="D232" s="14" t="s">
         <v>138</v>
@@ -17023,7 +17160,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C233" s="14">
-        <v>3213</v>
+        <v>1462</v>
       </c>
       <c r="D233" s="14" t="s">
         <v>138</v>
@@ -17039,7 +17176,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C234" s="14">
-        <v>3214</v>
+        <v>1463</v>
       </c>
       <c r="D234" s="14" t="s">
         <v>138</v>
@@ -17055,7 +17192,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C235" s="14">
-        <v>3219</v>
+        <v>1477</v>
       </c>
       <c r="D235" s="14" t="s">
         <v>138</v>
@@ -17071,7 +17208,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C236" s="14">
-        <v>2880</v>
+        <v>1479</v>
       </c>
       <c r="D236" s="14" t="s">
         <v>138</v>
@@ -17087,7 +17224,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C237" s="14">
-        <v>2626</v>
+        <v>1481</v>
       </c>
       <c r="D237" s="14" t="s">
         <v>138</v>
@@ -17103,7 +17240,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C238" s="14">
-        <v>3087</v>
+        <v>1482</v>
       </c>
       <c r="D238" s="14" t="s">
         <v>138</v>
@@ -17119,7 +17256,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C239" s="14">
-        <v>3085</v>
+        <v>1483</v>
       </c>
       <c r="D239" s="14" t="s">
         <v>138</v>
@@ -17135,7 +17272,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C240" s="14">
-        <v>2627</v>
+        <v>1490</v>
       </c>
       <c r="D240" s="14" t="s">
         <v>138</v>
@@ -17151,7 +17288,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C241" s="14">
-        <v>3487</v>
+        <v>1512</v>
       </c>
       <c r="D241" s="14" t="s">
         <v>138</v>
@@ -17167,7 +17304,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C242" s="14">
-        <v>3485</v>
+        <v>1745</v>
       </c>
       <c r="D242" s="14" t="s">
         <v>138</v>
@@ -17183,7 +17320,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C243" s="14">
-        <v>3378</v>
+        <v>1746</v>
       </c>
       <c r="D243" s="14" t="s">
         <v>138</v>
@@ -17199,7 +17336,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C244" s="14">
-        <v>3486</v>
+        <v>1748</v>
       </c>
       <c r="D244" s="14" t="s">
         <v>138</v>
@@ -17215,7 +17352,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C245" s="14">
-        <v>3377</v>
+        <v>1873</v>
       </c>
       <c r="D245" s="14" t="s">
         <v>138</v>
@@ -17231,7 +17368,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C246" s="14">
-        <v>3099</v>
+        <v>1942</v>
       </c>
       <c r="D246" s="14" t="s">
         <v>138</v>
@@ -17247,7 +17384,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C247" s="14">
-        <v>3098</v>
+        <v>2015</v>
       </c>
       <c r="D247" s="14" t="s">
         <v>138</v>
@@ -17263,7 +17400,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C248" s="14">
-        <v>3100</v>
+        <v>2067</v>
       </c>
       <c r="D248" s="14" t="s">
         <v>138</v>
@@ -17279,7 +17416,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C249" s="14">
-        <v>3137</v>
+        <v>2208</v>
       </c>
       <c r="D249" s="14" t="s">
         <v>138</v>
@@ -17295,7 +17432,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C250" s="14">
-        <v>3121</v>
+        <v>2426</v>
       </c>
       <c r="D250" s="14" t="s">
         <v>138</v>
@@ -17311,7 +17448,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C251" s="14">
-        <v>3139</v>
+        <v>2465</v>
       </c>
       <c r="D251" s="14" t="s">
         <v>138</v>
@@ -17327,7 +17464,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C252" s="14">
-        <v>3210</v>
+        <v>2468</v>
       </c>
       <c r="D252" s="14" t="s">
         <v>138</v>
@@ -17340,9 +17477,11 @@
         <v>140</v>
       </c>
       <c r="B253" s="17">
-        <v>5.2</v>
-      </c>
-      <c r="C253" s="14"/>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C253" s="14">
+        <v>2626</v>
+      </c>
       <c r="D253" s="14" t="s">
         <v>138</v>
       </c>
@@ -17354,10 +17493,10 @@
         <v>140</v>
       </c>
       <c r="B254" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C254" s="14">
-        <v>1613</v>
+        <v>2627</v>
       </c>
       <c r="D254" s="14" t="s">
         <v>138</v>
@@ -17370,10 +17509,10 @@
         <v>140</v>
       </c>
       <c r="B255" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C255" s="14">
-        <v>1560</v>
+        <v>2880</v>
       </c>
       <c r="D255" s="14" t="s">
         <v>138</v>
@@ -17386,10 +17525,10 @@
         <v>140</v>
       </c>
       <c r="B256" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C256" s="14">
-        <v>1510</v>
+        <v>3085</v>
       </c>
       <c r="D256" s="14" t="s">
         <v>138</v>
@@ -17402,10 +17541,10 @@
         <v>140</v>
       </c>
       <c r="B257" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C257" s="14">
-        <v>1092</v>
+        <v>3087</v>
       </c>
       <c r="D257" s="14" t="s">
         <v>138</v>
@@ -17418,10 +17557,10 @@
         <v>140</v>
       </c>
       <c r="B258" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C258" s="14">
-        <v>1259</v>
+        <v>3098</v>
       </c>
       <c r="D258" s="14" t="s">
         <v>138</v>
@@ -17434,10 +17573,10 @@
         <v>140</v>
       </c>
       <c r="B259" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C259" s="14">
-        <v>1239</v>
+        <v>3099</v>
       </c>
       <c r="D259" s="14" t="s">
         <v>138</v>
@@ -17450,10 +17589,10 @@
         <v>140</v>
       </c>
       <c r="B260" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C260" s="14">
-        <v>1163</v>
+        <v>3100</v>
       </c>
       <c r="D260" s="14" t="s">
         <v>138</v>
@@ -17466,10 +17605,10 @@
         <v>140</v>
       </c>
       <c r="B261" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C261" s="14">
-        <v>1649</v>
+        <v>3121</v>
       </c>
       <c r="D261" s="14" t="s">
         <v>138</v>
@@ -17482,10 +17621,10 @@
         <v>140</v>
       </c>
       <c r="B262" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C262" s="14">
-        <v>2321</v>
+        <v>3137</v>
       </c>
       <c r="D262" s="14" t="s">
         <v>138</v>
@@ -17498,10 +17637,10 @@
         <v>140</v>
       </c>
       <c r="B263" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C263" s="14">
-        <v>2312</v>
+        <v>3139</v>
       </c>
       <c r="D263" s="14" t="s">
         <v>138</v>
@@ -17514,10 +17653,10 @@
         <v>140</v>
       </c>
       <c r="B264" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C264" s="14">
-        <v>1642</v>
+        <v>3210</v>
       </c>
       <c r="D264" s="14" t="s">
         <v>138</v>
@@ -17530,10 +17669,10 @@
         <v>140</v>
       </c>
       <c r="B265" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C265" s="14">
-        <v>2249</v>
+        <v>3211</v>
       </c>
       <c r="D265" s="14" t="s">
         <v>138</v>
@@ -17546,10 +17685,10 @@
         <v>140</v>
       </c>
       <c r="B266" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C266" s="14">
-        <v>2480</v>
+        <v>3212</v>
       </c>
       <c r="D266" s="14" t="s">
         <v>138</v>
@@ -17562,10 +17701,10 @@
         <v>140</v>
       </c>
       <c r="B267" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C267" s="14">
-        <v>2334</v>
+        <v>3213</v>
       </c>
       <c r="D267" s="14" t="s">
         <v>138</v>
@@ -17578,10 +17717,10 @@
         <v>140</v>
       </c>
       <c r="B268" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C268" s="14">
-        <v>2481</v>
+        <v>3214</v>
       </c>
       <c r="D268" s="14" t="s">
         <v>138</v>
@@ -17594,10 +17733,10 @@
         <v>140</v>
       </c>
       <c r="B269" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C269" s="14">
-        <v>3123</v>
+        <v>3218</v>
       </c>
       <c r="D269" s="14" t="s">
         <v>138</v>
@@ -17610,10 +17749,10 @@
         <v>140</v>
       </c>
       <c r="B270" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C270" s="14">
-        <v>3124</v>
+        <v>3219</v>
       </c>
       <c r="D270" s="14" t="s">
         <v>138</v>
@@ -17626,10 +17765,10 @@
         <v>140</v>
       </c>
       <c r="B271" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C271" s="14">
-        <v>3125</v>
+        <v>3375</v>
       </c>
       <c r="D271" s="14" t="s">
         <v>138</v>
@@ -17642,10 +17781,10 @@
         <v>140</v>
       </c>
       <c r="B272" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C272" s="14">
-        <v>3250</v>
+        <v>3377</v>
       </c>
       <c r="D272" s="14" t="s">
         <v>138</v>
@@ -17653,15 +17792,15 @@
       <c r="E272" s="14"/>
       <c r="F272" s="14"/>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B273" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C273" s="14">
-        <v>3383</v>
+        <v>3378</v>
       </c>
       <c r="D273" s="14" t="s">
         <v>138</v>
@@ -17669,15 +17808,15 @@
       <c r="E273" s="14"/>
       <c r="F273" s="14"/>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B274" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C274" s="14">
-        <v>3385</v>
+        <v>3485</v>
       </c>
       <c r="D274" s="14" t="s">
         <v>138</v>
@@ -17685,15 +17824,15 @@
       <c r="E274" s="14"/>
       <c r="F274" s="14"/>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B275" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C275" s="14">
-        <v>3382</v>
+        <v>3486</v>
       </c>
       <c r="D275" s="14" t="s">
         <v>138</v>
@@ -17701,15 +17840,15 @@
       <c r="E275" s="14"/>
       <c r="F275" s="14"/>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B276" s="17">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C276" s="14">
-        <v>3384</v>
+        <v>3487</v>
       </c>
       <c r="D276" s="14" t="s">
         <v>138</v>
@@ -17717,39 +17856,40 @@
       <c r="E276" s="14"/>
       <c r="F276" s="14"/>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B277" s="17">
-        <v>6.1</v>
-      </c>
-      <c r="C277" s="14">
-        <v>3381</v>
-      </c>
+        <v>5.2</v>
+      </c>
+      <c r="C277" s="14"/>
       <c r="D277" s="14" t="s">
         <v>138</v>
       </c>
       <c r="E277" s="14"/>
       <c r="F277" s="14"/>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B278" s="17">
         <v>6.1</v>
       </c>
-      <c r="C278" s="14">
-        <v>3386</v>
-      </c>
-      <c r="D278" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="E278" s="14"/>
-      <c r="F278" s="14"/>
-    </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C278" s="14"/>
+      <c r="D278" s="14"/>
+      <c r="E278" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="F278" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G278" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" s="14" t="s">
         <v>140</v>
       </c>
@@ -17757,7 +17897,7 @@
         <v>6.1</v>
       </c>
       <c r="C279" s="14">
-        <v>3294</v>
+        <v>1092</v>
       </c>
       <c r="D279" s="14" t="s">
         <v>138</v>
@@ -17765,7 +17905,7 @@
       <c r="E279" s="14"/>
       <c r="F279" s="14"/>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" s="14" t="s">
         <v>140</v>
       </c>
@@ -17773,7 +17913,7 @@
         <v>6.1</v>
       </c>
       <c r="C280" s="14">
-        <v>3413</v>
+        <v>1163</v>
       </c>
       <c r="D280" s="14" t="s">
         <v>138</v>
@@ -17781,7 +17921,7 @@
       <c r="E280" s="14"/>
       <c r="F280" s="14"/>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" s="14" t="s">
         <v>140</v>
       </c>
@@ -17789,7 +17929,7 @@
         <v>6.1</v>
       </c>
       <c r="C281" s="14">
-        <v>3390</v>
+        <v>1239</v>
       </c>
       <c r="D281" s="14" t="s">
         <v>138</v>
@@ -17797,7 +17937,7 @@
       <c r="E281" s="14"/>
       <c r="F281" s="14"/>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" s="14" t="s">
         <v>140</v>
       </c>
@@ -17805,7 +17945,7 @@
         <v>6.1</v>
       </c>
       <c r="C282" s="14">
-        <v>3387</v>
+        <v>1259</v>
       </c>
       <c r="D282" s="14" t="s">
         <v>138</v>
@@ -17813,7 +17953,7 @@
       <c r="E282" s="14"/>
       <c r="F282" s="14"/>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" s="14" t="s">
         <v>140</v>
       </c>
@@ -17821,7 +17961,7 @@
         <v>6.1</v>
       </c>
       <c r="C283" s="14">
-        <v>3388</v>
+        <v>1510</v>
       </c>
       <c r="D283" s="14" t="s">
         <v>138</v>
@@ -17829,7 +17969,7 @@
       <c r="E283" s="14"/>
       <c r="F283" s="14"/>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="14" t="s">
         <v>140</v>
       </c>
@@ -17837,7 +17977,7 @@
         <v>6.1</v>
       </c>
       <c r="C284" s="14">
-        <v>3389</v>
+        <v>1560</v>
       </c>
       <c r="D284" s="14" t="s">
         <v>138</v>
@@ -17845,7 +17985,7 @@
       <c r="E284" s="14"/>
       <c r="F284" s="14"/>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="14" t="s">
         <v>140</v>
       </c>
@@ -17853,7 +17993,7 @@
         <v>6.1</v>
       </c>
       <c r="C285" s="14">
-        <v>3448</v>
+        <v>1613</v>
       </c>
       <c r="D285" s="14" t="s">
         <v>138</v>
@@ -17861,7 +18001,7 @@
       <c r="E285" s="14"/>
       <c r="F285" s="14"/>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" s="14" t="s">
         <v>140</v>
       </c>
@@ -17869,7 +18009,7 @@
         <v>6.1</v>
       </c>
       <c r="C286" s="14">
-        <v>3414</v>
+        <v>1642</v>
       </c>
       <c r="D286" s="14" t="s">
         <v>138</v>
@@ -17877,7 +18017,7 @@
       <c r="E286" s="14"/>
       <c r="F286" s="14"/>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" s="14" t="s">
         <v>140</v>
       </c>
@@ -17885,7 +18025,7 @@
         <v>6.1</v>
       </c>
       <c r="C287" s="14">
-        <v>3440</v>
+        <v>1649</v>
       </c>
       <c r="D287" s="14" t="s">
         <v>138</v>
@@ -17893,7 +18033,7 @@
       <c r="E287" s="14"/>
       <c r="F287" s="14"/>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" s="14" t="s">
         <v>140</v>
       </c>
@@ -17901,7 +18041,7 @@
         <v>6.1</v>
       </c>
       <c r="C288" s="14">
-        <v>3449</v>
+        <v>2249</v>
       </c>
       <c r="D288" s="14" t="s">
         <v>138</v>
@@ -17917,7 +18057,7 @@
         <v>6.1</v>
       </c>
       <c r="C289" s="14">
-        <v>3450</v>
+        <v>2312</v>
       </c>
       <c r="D289" s="14" t="s">
         <v>138</v>
@@ -17933,7 +18073,7 @@
         <v>6.1</v>
       </c>
       <c r="C290" s="14">
-        <v>3462</v>
+        <v>2321</v>
       </c>
       <c r="D290" s="14" t="s">
         <v>138</v>
@@ -17949,7 +18089,7 @@
         <v>6.1</v>
       </c>
       <c r="C291" s="14">
-        <v>3464</v>
+        <v>2334</v>
       </c>
       <c r="D291" s="14" t="s">
         <v>138</v>
@@ -17965,7 +18105,7 @@
         <v>6.1</v>
       </c>
       <c r="C292" s="14">
-        <v>3490</v>
+        <v>2480</v>
       </c>
       <c r="D292" s="14" t="s">
         <v>138</v>
@@ -17981,7 +18121,7 @@
         <v>6.1</v>
       </c>
       <c r="C293" s="14">
-        <v>3489</v>
+        <v>2481</v>
       </c>
       <c r="D293" s="14" t="s">
         <v>138</v>
@@ -17997,7 +18137,7 @@
         <v>6.1</v>
       </c>
       <c r="C294" s="14">
-        <v>3488</v>
+        <v>3123</v>
       </c>
       <c r="D294" s="14" t="s">
         <v>138</v>
@@ -18013,7 +18153,7 @@
         <v>6.1</v>
       </c>
       <c r="C295" s="14">
-        <v>3483</v>
+        <v>3124</v>
       </c>
       <c r="D295" s="14" t="s">
         <v>138</v>
@@ -18029,7 +18169,7 @@
         <v>6.1</v>
       </c>
       <c r="C296" s="14">
-        <v>3465</v>
+        <v>3125</v>
       </c>
       <c r="D296" s="14" t="s">
         <v>138</v>
@@ -18045,7 +18185,7 @@
         <v>6.1</v>
       </c>
       <c r="C297" s="14">
-        <v>3467</v>
+        <v>3250</v>
       </c>
       <c r="D297" s="14" t="s">
         <v>138</v>
@@ -18061,7 +18201,7 @@
         <v>6.1</v>
       </c>
       <c r="C298" s="14">
-        <v>3466</v>
+        <v>3294</v>
       </c>
       <c r="D298" s="14" t="s">
         <v>138</v>
@@ -18077,7 +18217,7 @@
         <v>6.1</v>
       </c>
       <c r="C299" s="14">
-        <v>3491</v>
+        <v>3381</v>
       </c>
       <c r="D299" s="14" t="s">
         <v>138</v>
@@ -18093,7 +18233,7 @@
         <v>6.1</v>
       </c>
       <c r="C300" s="14">
-        <v>3507</v>
+        <v>3382</v>
       </c>
       <c r="D300" s="14" t="s">
         <v>138</v>
@@ -18106,9 +18246,11 @@
         <v>140</v>
       </c>
       <c r="B301" s="17">
-        <v>6.2</v>
-      </c>
-      <c r="C301" s="14"/>
+        <v>6.1</v>
+      </c>
+      <c r="C301" s="14">
+        <v>3383</v>
+      </c>
       <c r="D301" s="14" t="s">
         <v>138</v>
       </c>
@@ -18120,9 +18262,11 @@
         <v>140</v>
       </c>
       <c r="B302" s="17">
-        <v>7</v>
-      </c>
-      <c r="C302" s="14"/>
+        <v>6.1</v>
+      </c>
+      <c r="C302" s="14">
+        <v>3384</v>
+      </c>
       <c r="D302" s="14" t="s">
         <v>138</v>
       </c>
@@ -18134,10 +18278,10 @@
         <v>140</v>
       </c>
       <c r="B303" s="17">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="C303" s="14">
-        <v>1744</v>
+        <v>3385</v>
       </c>
       <c r="D303" s="14" t="s">
         <v>138</v>
@@ -18150,10 +18294,10 @@
         <v>140</v>
       </c>
       <c r="B304" s="17">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="C304" s="14">
-        <v>1826</v>
+        <v>3386</v>
       </c>
       <c r="D304" s="14" t="s">
         <v>138</v>
@@ -18166,10 +18310,10 @@
         <v>140</v>
       </c>
       <c r="B305" s="17">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="C305" s="14">
-        <v>2032</v>
+        <v>3387</v>
       </c>
       <c r="D305" s="14" t="s">
         <v>138</v>
@@ -18182,10 +18326,10 @@
         <v>140</v>
       </c>
       <c r="B306" s="17">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="C306" s="14">
-        <v>1796</v>
+        <v>3388</v>
       </c>
       <c r="D306" s="14" t="s">
         <v>138</v>
@@ -18198,10 +18342,10 @@
         <v>140</v>
       </c>
       <c r="B307" s="17">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="C307" s="14">
-        <v>1849</v>
+        <v>3389</v>
       </c>
       <c r="D307" s="14" t="s">
         <v>138</v>
@@ -18214,10 +18358,10 @@
         <v>140</v>
       </c>
       <c r="B308" s="17">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="C308" s="14">
-        <v>2031</v>
+        <v>3390</v>
       </c>
       <c r="D308" s="14" t="s">
         <v>138</v>
@@ -18230,10 +18374,10 @@
         <v>140</v>
       </c>
       <c r="B309" s="17">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="C309" s="14">
-        <v>1791</v>
+        <v>3413</v>
       </c>
       <c r="D309" s="14" t="s">
         <v>138</v>
@@ -18246,10 +18390,10 @@
         <v>140</v>
       </c>
       <c r="B310" s="17">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="C310" s="14">
-        <v>3096</v>
+        <v>3414</v>
       </c>
       <c r="D310" s="14" t="s">
         <v>138</v>
@@ -18262,10 +18406,10 @@
         <v>140</v>
       </c>
       <c r="B311" s="17">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="C311" s="14">
-        <v>3301</v>
+        <v>3440</v>
       </c>
       <c r="D311" s="14" t="s">
         <v>138</v>
@@ -18278,10 +18422,10 @@
         <v>140</v>
       </c>
       <c r="B312" s="17">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="C312" s="14">
-        <v>3095</v>
+        <v>3448</v>
       </c>
       <c r="D312" s="14" t="s">
         <v>138</v>
@@ -18294,10 +18438,10 @@
         <v>140</v>
       </c>
       <c r="B313" s="17">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="C313" s="14">
-        <v>3094</v>
+        <v>3449</v>
       </c>
       <c r="D313" s="14" t="s">
         <v>138</v>
@@ -18310,10 +18454,10 @@
         <v>140</v>
       </c>
       <c r="B314" s="17">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="C314" s="14">
-        <v>2576</v>
+        <v>3450</v>
       </c>
       <c r="D314" s="14" t="s">
         <v>138</v>
@@ -18326,10 +18470,10 @@
         <v>140</v>
       </c>
       <c r="B315" s="17">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="C315" s="14">
-        <v>3484</v>
+        <v>3462</v>
       </c>
       <c r="D315" s="14" t="s">
         <v>138</v>
@@ -18342,10 +18486,10 @@
         <v>140</v>
       </c>
       <c r="B316" s="17">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="C316" s="14">
-        <v>3498</v>
+        <v>3464</v>
       </c>
       <c r="D316" s="14" t="s">
         <v>138</v>
@@ -18358,17 +18502,15 @@
         <v>140</v>
       </c>
       <c r="B317" s="17">
-        <v>9</v>
+        <v>6.1</v>
       </c>
       <c r="C317" s="14">
-        <v>3090</v>
+        <v>3465</v>
       </c>
       <c r="D317" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="E317" s="14" t="s">
-        <v>138</v>
-      </c>
+      <c r="E317" s="14"/>
       <c r="F317" s="14"/>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -18376,10 +18518,10 @@
         <v>140</v>
       </c>
       <c r="B318" s="17">
-        <v>9</v>
+        <v>6.1</v>
       </c>
       <c r="C318" s="14">
-        <v>2590</v>
+        <v>3466</v>
       </c>
       <c r="D318" s="14" t="s">
         <v>138</v>
@@ -18392,10 +18534,10 @@
         <v>140</v>
       </c>
       <c r="B319" s="17">
-        <v>9</v>
+        <v>6.1</v>
       </c>
       <c r="C319" s="14">
-        <v>3151</v>
+        <v>3467</v>
       </c>
       <c r="D319" s="14" t="s">
         <v>138</v>
@@ -18408,10 +18550,10 @@
         <v>140</v>
       </c>
       <c r="B320" s="17">
-        <v>9</v>
+        <v>6.1</v>
       </c>
       <c r="C320" s="14">
-        <v>2071</v>
+        <v>3483</v>
       </c>
       <c r="D320" s="14" t="s">
         <v>138</v>
@@ -18419,15 +18561,15 @@
       <c r="E320" s="14"/>
       <c r="F320" s="14"/>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B321" s="17">
-        <v>9</v>
+        <v>6.1</v>
       </c>
       <c r="C321" s="14">
-        <v>2212</v>
+        <v>3488</v>
       </c>
       <c r="D321" s="14" t="s">
         <v>138</v>
@@ -18435,15 +18577,15 @@
       <c r="E321" s="14"/>
       <c r="F321" s="14"/>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B322" s="17">
-        <v>9</v>
+        <v>6.1</v>
       </c>
       <c r="C322" s="14">
-        <v>2315</v>
+        <v>3489</v>
       </c>
       <c r="D322" s="14" t="s">
         <v>138</v>
@@ -18451,15 +18593,15 @@
       <c r="E322" s="14"/>
       <c r="F322" s="14"/>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B323" s="17">
-        <v>9</v>
+        <v>6.1</v>
       </c>
       <c r="C323" s="14">
-        <v>2211</v>
+        <v>3490</v>
       </c>
       <c r="D323" s="14" t="s">
         <v>138</v>
@@ -18467,15 +18609,15 @@
       <c r="E323" s="14"/>
       <c r="F323" s="14"/>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B324" s="17">
-        <v>9</v>
+        <v>6.1</v>
       </c>
       <c r="C324" s="14">
-        <v>3359</v>
+        <v>3491</v>
       </c>
       <c r="D324" s="14" t="s">
         <v>138</v>
@@ -18483,15 +18625,15 @@
       <c r="E324" s="14"/>
       <c r="F324" s="14"/>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B325" s="17">
-        <v>9</v>
+        <v>6.1</v>
       </c>
       <c r="C325" s="14">
-        <v>3152</v>
+        <v>3507</v>
       </c>
       <c r="D325" s="14" t="s">
         <v>138</v>
@@ -18499,65 +18641,62 @@
       <c r="E325" s="14"/>
       <c r="F325" s="14"/>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B326" s="17">
-        <v>9</v>
-      </c>
-      <c r="C326" s="14">
-        <v>3314</v>
-      </c>
+        <v>6.2</v>
+      </c>
+      <c r="C326" s="14"/>
       <c r="D326" s="14" t="s">
         <v>138</v>
       </c>
       <c r="E326" s="14"/>
       <c r="F326" s="14"/>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B327" s="17">
-        <v>9</v>
-      </c>
-      <c r="C327" s="14">
-        <v>3432</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C327" s="14"/>
       <c r="D327" s="14" t="s">
         <v>138</v>
       </c>
       <c r="E327" s="14"/>
       <c r="F327" s="14"/>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A328" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B328" s="17">
-        <v>9</v>
-      </c>
-      <c r="C328" s="14">
-        <v>3480</v>
-      </c>
-      <c r="D328" s="14" t="s">
-        <v>138</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C328" s="14"/>
+      <c r="D328" s="14"/>
       <c r="E328" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="F328" s="14"/>
-    </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F328" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G328" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B329" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C329" s="14">
-        <v>3509</v>
+        <v>1744</v>
       </c>
       <c r="D329" s="14" t="s">
         <v>138</v>
@@ -18565,15 +18704,15 @@
       <c r="E329" s="14"/>
       <c r="F329" s="14"/>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B330" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C330" s="14">
-        <v>3551</v>
+        <v>1791</v>
       </c>
       <c r="D330" s="14" t="s">
         <v>138</v>
@@ -18581,15 +18720,15 @@
       <c r="E330" s="14"/>
       <c r="F330" s="14"/>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B331" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C331" s="14">
-        <v>3552</v>
+        <v>1796</v>
       </c>
       <c r="D331" s="14" t="s">
         <v>138</v>
@@ -18597,15 +18736,15 @@
       <c r="E331" s="14"/>
       <c r="F331" s="14"/>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A332" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B332" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C332" s="14">
-        <v>3171</v>
+        <v>1826</v>
       </c>
       <c r="D332" s="14" t="s">
         <v>138</v>
@@ -18613,33 +18752,31 @@
       <c r="E332" s="14"/>
       <c r="F332" s="14"/>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B333" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C333" s="14">
-        <v>3091</v>
+        <v>1849</v>
       </c>
       <c r="D333" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="E333" s="14" t="s">
-        <v>138</v>
-      </c>
+      <c r="E333" s="14"/>
       <c r="F333" s="14"/>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A334" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B334" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C334" s="14">
-        <v>3556</v>
+        <v>2031</v>
       </c>
       <c r="D334" s="14" t="s">
         <v>138</v>
@@ -18647,33 +18784,31 @@
       <c r="E334" s="14"/>
       <c r="F334" s="14"/>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A335" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B335" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C335" s="14">
-        <v>3481</v>
+        <v>2032</v>
       </c>
       <c r="D335" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="E335" s="14" t="s">
-        <v>138</v>
-      </c>
+      <c r="E335" s="14"/>
       <c r="F335" s="14"/>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A336" s="14" t="s">
         <v>140</v>
       </c>
       <c r="B336" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C336" s="14">
-        <v>3558</v>
+        <v>2576</v>
       </c>
       <c r="D336" s="14" t="s">
         <v>138</v>
@@ -18686,16 +18821,504 @@
         <v>140</v>
       </c>
       <c r="B337" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C337" s="14">
-        <v>3557</v>
+        <v>3094</v>
       </c>
       <c r="D337" s="14" t="s">
         <v>138</v>
       </c>
       <c r="E337" s="14"/>
       <c r="F337" s="14"/>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A338" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B338" s="17">
+        <v>8</v>
+      </c>
+      <c r="C338" s="14">
+        <v>3095</v>
+      </c>
+      <c r="D338" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E338" s="14"/>
+      <c r="F338" s="14"/>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A339" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B339" s="17">
+        <v>8</v>
+      </c>
+      <c r="C339" s="14">
+        <v>3096</v>
+      </c>
+      <c r="D339" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E339" s="14"/>
+      <c r="F339" s="14"/>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A340" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B340" s="17">
+        <v>8</v>
+      </c>
+      <c r="C340" s="14">
+        <v>3301</v>
+      </c>
+      <c r="D340" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E340" s="14"/>
+      <c r="F340" s="14"/>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A341" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B341" s="17">
+        <v>8</v>
+      </c>
+      <c r="C341" s="14">
+        <v>3484</v>
+      </c>
+      <c r="D341" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E341" s="14"/>
+      <c r="F341" s="14"/>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A342" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B342" s="17">
+        <v>8</v>
+      </c>
+      <c r="C342" s="14">
+        <v>3498</v>
+      </c>
+      <c r="D342" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E342" s="14"/>
+      <c r="F342" s="14"/>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A343" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B343" s="17">
+        <v>9</v>
+      </c>
+      <c r="C343" s="14">
+        <v>2071</v>
+      </c>
+      <c r="D343" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E343" s="14"/>
+      <c r="F343" s="14"/>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A344" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B344" s="17">
+        <v>9</v>
+      </c>
+      <c r="C344" s="14">
+        <v>2211</v>
+      </c>
+      <c r="D344" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E344" s="14"/>
+      <c r="F344" s="14"/>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A345" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B345" s="17">
+        <v>9</v>
+      </c>
+      <c r="C345" s="14">
+        <v>2212</v>
+      </c>
+      <c r="D345" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E345" s="14"/>
+      <c r="F345" s="14"/>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A346" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B346" s="17">
+        <v>9</v>
+      </c>
+      <c r="C346" s="14">
+        <v>2315</v>
+      </c>
+      <c r="D346" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E346" s="14"/>
+      <c r="F346" s="14"/>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A347" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B347" s="17">
+        <v>9</v>
+      </c>
+      <c r="C347" s="14">
+        <v>2590</v>
+      </c>
+      <c r="D347" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E347" s="14"/>
+      <c r="F347" s="14"/>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A348" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B348" s="17">
+        <v>9</v>
+      </c>
+      <c r="C348" s="14">
+        <v>3090</v>
+      </c>
+      <c r="D348" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E348" s="14"/>
+      <c r="F348" s="14" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A349" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B349" s="17">
+        <v>9</v>
+      </c>
+      <c r="C349" s="14">
+        <v>3151</v>
+      </c>
+      <c r="D349" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E349" s="14"/>
+      <c r="F349" s="14"/>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A350" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B350" s="17">
+        <v>9</v>
+      </c>
+      <c r="C350" s="14">
+        <v>3152</v>
+      </c>
+      <c r="D350" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E350" s="14"/>
+      <c r="F350" s="14"/>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A351" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B351" s="17">
+        <v>9</v>
+      </c>
+      <c r="C351" s="14">
+        <v>3314</v>
+      </c>
+      <c r="D351" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E351" s="14"/>
+      <c r="F351" s="14"/>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A352" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B352" s="17">
+        <v>9</v>
+      </c>
+      <c r="C352" s="14">
+        <v>3359</v>
+      </c>
+      <c r="D352" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E352" s="14"/>
+      <c r="F352" s="14"/>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A353" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B353" s="17">
+        <v>9</v>
+      </c>
+      <c r="C353" s="14">
+        <v>3432</v>
+      </c>
+      <c r="D353" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E353" s="14"/>
+      <c r="F353" s="14"/>
+    </row>
+    <row r="354" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A354" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B354" s="17">
+        <v>9</v>
+      </c>
+      <c r="C354" s="14">
+        <v>3480</v>
+      </c>
+      <c r="D354" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E354" s="14"/>
+      <c r="F354" s="14" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A355" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B355" s="17">
+        <v>9</v>
+      </c>
+      <c r="C355" s="14">
+        <v>3509</v>
+      </c>
+      <c r="D355" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E355" s="14"/>
+      <c r="F355" s="14"/>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A356" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B356" s="17">
+        <v>9</v>
+      </c>
+      <c r="C356" s="14">
+        <v>3551</v>
+      </c>
+      <c r="D356" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E356" s="14"/>
+      <c r="F356" s="14"/>
+    </row>
+    <row r="357" spans="1:8" ht="63" x14ac:dyDescent="0.25">
+      <c r="A357" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B357" s="17">
+        <v>9</v>
+      </c>
+      <c r="C357" s="14">
+        <v>2216</v>
+      </c>
+      <c r="D357" s="14"/>
+      <c r="E357" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F357" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="G357" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="H357" s="14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A358" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B358" s="17">
+        <v>9</v>
+      </c>
+      <c r="C358" s="14">
+        <v>3091</v>
+      </c>
+      <c r="D358" s="14"/>
+      <c r="E358" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F358" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="G358" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="H358" s="15" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A359" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B359" s="17">
+        <v>9</v>
+      </c>
+      <c r="C359" s="14">
+        <v>3171</v>
+      </c>
+      <c r="D359" s="14"/>
+      <c r="E359" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F359" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="H359" s="15" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A360" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B360" s="17">
+        <v>9</v>
+      </c>
+      <c r="C360" s="14">
+        <v>3481</v>
+      </c>
+      <c r="D360" s="14"/>
+      <c r="E360" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F360" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="G360" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="H360" s="15" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A361" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B361" s="17">
+        <v>9</v>
+      </c>
+      <c r="C361" s="14">
+        <v>3552</v>
+      </c>
+      <c r="D361" s="14"/>
+      <c r="E361" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F361" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="G361" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="H361" s="15" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A362" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B362" s="17">
+        <v>9</v>
+      </c>
+      <c r="C362" s="14">
+        <v>3556</v>
+      </c>
+      <c r="D362" s="14"/>
+      <c r="E362" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F362" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="H362" s="15" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A363" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B363" s="17">
+        <v>9</v>
+      </c>
+      <c r="C363" s="14">
+        <v>3557</v>
+      </c>
+      <c r="D363" s="14"/>
+      <c r="E363" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F363" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="H363" s="15" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A364" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B364" s="17">
+        <v>9</v>
+      </c>
+      <c r="C364" s="14">
+        <v>3558</v>
+      </c>
+      <c r="D364" s="14"/>
+      <c r="E364" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F364" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="H364" s="15" t="s">
+        <v>332</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -23710,8 +24333,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000EE87651FA4E794C9F9EBAB47B2914A1" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e3b55ab03191701fac28f92542a127ea">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ea6fd297-1f65-4950-8fc9-157e29c7b648" xmlns:ns3="c3e85fef-df06-4e67-8632-489752715f52" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fefe44c3222484af0f545068bb015341" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文件" ma:contentTypeID="0x0101000EE87651FA4E794C9F9EBAB47B2914A1" ma:contentTypeVersion="17" ma:contentTypeDescription="建立新的文件。" ma:contentTypeScope="" ma:versionID="9c09e6d34a2a63fd0a91c0d4c1bf4f8b">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ea6fd297-1f65-4950-8fc9-157e29c7b648" xmlns:ns3="c3e85fef-df06-4e67-8632-489752715f52" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="425bb3ba415c7c22851a56042b3a2c83" ns2:_="" ns3:_="">
     <xsd:import namespace="ea6fd297-1f65-4950-8fc9-157e29c7b648"/>
     <xsd:import namespace="c3e85fef-df06-4e67-8632-489752715f52"/>
     <xsd:element name="properties">
@@ -23810,7 +24433,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="7f7e4587-cf63-4ff3-92d6-48abe44d80a4" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="影像標籤" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="7f7e4587-cf63-4ff3-92d6-48abe44d80a4" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -23821,7 +24444,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c3e85fef-df06-4e67-8632-489752715f52" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="共用對象:" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -23840,7 +24463,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="共用詳細資料" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -23868,8 +24491,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="內容類型"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="標題"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -23979,22 +24602,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33DC095D-896E-4513-BAFC-A565BB613637}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ea6fd297-1f65-4950-8fc9-157e29c7b648"/>
-    <ds:schemaRef ds:uri="c3e85fef-df06-4e67-8632-489752715f52"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47124226-01FC-4F64-B1AA-64A0F8830A37}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/dg_list.xlsx
+++ b/dg_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ialasia.sharepoint.com/sites/IALDGDESK/Shared Documents/General/Query System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1122" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D0E813D-25F7-42EC-88AD-4BAE0D219339}"/>
+  <xr:revisionPtr revIDLastSave="1176" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43D180FF-C22E-4F12-BFD0-D6DA5514C5A2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="27630" windowHeight="16440" activeTab="3" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="27630" windowHeight="16440" activeTab="4" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
   </bookViews>
   <sheets>
     <sheet name="IAL" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3638" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3638" uniqueCount="408">
   <si>
     <t>UN Number</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1513,18 +1513,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>The below restrictions apply to Laden tanks only.
- a) Stowage: 1st or 2nd tier for monitoring purpose
- b) The following acceptance requirement is applicable only for ISO Tank Refrigerated Liquid Helium
-Shipment with below MAX PSI 91 (≤91):
- - At the time of loading from the Port of Origin (POR/POL), the PSI reading for the shipment must
- be below 10 PSI (≤10).
- - At the time of loading from T/S Port, the PSI reading must be below 35 PSI (≤35) unless exempted.
- - Shipper should make arrangements with the terminal (POR/POL or T/S) to release the pressure
- when container is in the yard before loading.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Following items shall be provided to GDG, if its origin is China including Hong Kong
  a) In Dry Container (not applicable for empty receptacles)
  - Vanning survey report
@@ -1543,64 +1531,12 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1. If loading in "Live" reefers to maintain temperature for stabilization (not for quality purpose), refer to
-"Temperature Controlled DG (SOC - Live Dual Reefer)"
-2. Technical name: Divinylbenzene (DVB) (Diethenylbenzene/Vinylstyrene.) should be classified under
-Class 4.1/UN 3532 or Class 4.1/UN 3534</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. If loading in "Live" reefers to maintain temperature for stabilization (not for quality purpose), refer to
-"Temperature Controlled DG (SOC - Live Dual Reefer)"
-2. Technical name: Divinylbenzene (DVB) (Diethenylbenzene/Vinylstyrene.) should be classified under
-Class 4.1/UN 3532 or Class 4.1/UN 3535</t>
-  </si>
-  <si>
-    <t>1. If loading in "Live" reefers to maintain temperature for stabilization (not for quality purpose), refer to
-"Temperature Controlled DG (SOC - Live Dual Reefer)"
-2. Technical name: Divinylbenzene (DVB) (Diethenylbenzene/Vinylstyrene.) should be classified under
-Class 4.1/UN 3532 or Class 4.1/UN 3536</t>
-  </si>
-  <si>
-    <t>1. If loading in "Live" reefers to maintain temperature for stabilization (not for quality purpose), refer to
-"Temperature Controlled DG (SOC - Live Dual Reefer)"
-2. Technical name: Divinylbenzene (DVB) (Diethenylbenzene/Vinylstyrene.) should be classified under
-Class 4.1/UN 3532 or Class 4.1/UN 3537</t>
-  </si>
-  <si>
-    <t>1. Charcoal from Indonesia is prohibited
-2. 20ft Dry Container only (not packed together with charcoal lighter or other ignition source inside the
-container)
-3. Following items shall be provided to GDG:
- a) SDS
- b) Vanning survey report, including photos, confirming compliance with SP 978.
-4. Stowage: ODAB - On deck away from heat source / 1st tier shaded from direct sunlight</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. Raw (unfinished products) Chemically Activated Carbon MUST be declared as DG regardless of
-SP979.
-2. (DG &amp; Non-DG) Stowage: ODAB - On deck away from heat source / 1st tier shaded from direct sunlight</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1. Stowage: OD - On deck
 2. In case of Dry Container :
  a) Acceptable only in new steel drums
  b) The cargo shall be stuffed one tier only
  c) Vanning survey report is required to proof item a) and b)</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. Fire fighting material Lithium chloride powder, dry sodium chloride or graphite powder must be provided
-on board as per IMDG requirement. 20 kgs per 20ft container (1 TEU) under the care of master.
-2. Acceptable for 1st leg vessel only (if require 2nd leg vessel, shall consult GDG)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. Fire fighting material Lithium chloride powder, dry sodium chloride or graphite powder must be provided
-on board as per IMDG requirement. 20 kgs per 20ft container (1 TEU) under the care of master.
-2. Acceptable for 1st leg vessel only (if require 3nd leg vessel, shall consult GDG)</t>
   </si>
   <si>
     <t>1. Japan origin only
@@ -1685,24 +1621,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1. Prohibited from origin Bangladesh
-2. If its origin is from India, the following items shall be provided to GDG:
- a) Vanning survey report
- b) Valid IIP(Indian Institute of Packaging), ERRL (Enviro Remediation &amp; Research Laboratory) &amp; TUV
-UN certificate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Acceptable only in tank</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. Prohibited in Non-Operating Reefer (NOR)
-2. Acceptable only ONE bookings on ONE operated vessels
-3. Refer to "Temperature Controlled DG (SOC - Live Dual Reefer)" for temperature controlled DG loaded
-in live reefers for safety purpose.
-4. SADT is required for all Class 5.2
-5. All subrisk Class 1, see Class 1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1715,78 +1634,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1. SDS shall be provided to GDG in order to check technical name.
-2. Stowage:
- a) protect from radiant heat which includes direct sunlight
- b) away from living quarter
-3. Transhipment is prohibited.
-4. Prohibited if SADT is less than or equal to 56°C.</t>
-  </si>
-  <si>
-    <t>1. SDS shall be provided to GDG in order to check technical name.
-2. Stowage:
- a) protect from radiant heat which includes direct sunlight
- b) away from living quarter
-3. Transhipment is prohibited.
-4. Prohibited if SADT is less than or equal to 57°C.</t>
-  </si>
-  <si>
-    <t>1. SDS shall be provided to GDG in order to check technical name.
-2. Stowage:
- a) protect from radiant heat which includes direct sunlight
- b) away from living quarter
-3. Transhipment is prohibited.
-4. Prohibited if SADT is less than or equal to 58°C.</t>
-  </si>
-  <si>
-    <t>1. SDS shall be provided to GDG in order to check technical name.
-2. Stowage:
- a) protect from radiant heat which includes direct sunlight
- b) away from living quarter
-3. Transhipment is prohibited.
-4. Prohibited if SADT is less than or equal to 59°C.</t>
-  </si>
-  <si>
-    <t>1. SDS shall be provided to GDG in order to check technical name.
-2. Stowage:
- a) protect from radiant heat which includes direct sunlight
- b) away from living quarter
-3. Transhipment is prohibited.
-4. Prohibited if SADT is less than or equal to 60°C.</t>
-  </si>
-  <si>
-    <t>1. SDS shall be provided to GDG in order to check technical name.
-2. Stowage:
- a) protect from radiant heat which includes direct sunlight
- b) away from living quarter
-3. Transhipment is prohibited.
-4. Prohibited if SADT is less than or equal to 61°C.</t>
-  </si>
-  <si>
-    <t>1. SDS shall be provided to GDG in order to check technical name.
-2. Stowage:
- a) protect from radiant heat which includes direct sunlight
- b) away from living quarter
-3. Transhipment is prohibited.
-4. Prohibited if SADT is less than or equal to 62°C.</t>
-  </si>
-  <si>
-    <t>1. SDS shall be provided to GDG in order to check technical name.
-2. Stowage:
- a) protect from radiant heat which includes direct sunlight
- b) away from living quarter
-3. Transhipment is prohibited.
-4. Prohibited if SADT is less than or equal to 63°C.</t>
-  </si>
-  <si>
-    <t>1. SDS shall be provided to GDG in order to check technical name.
-2. Stowage:
- a) protect from radiant heat which includes direct sunlight
- b) away from living quarter
-3. Transhipment is prohibited.
-4. Prohibited if SADT is less than or equal to 64°C.</t>
-  </si>
-  <si>
     <t>Must be packed in a new package, stuffed max in 1 tier high only</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1799,10 +1646,86 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Following items shall be provided to GDG in order to verify the moisture &amp; fat contents:
+ a) SDS
+ b) Fishmeal certificate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vehicles with Used and/or damaged/defective/waste Lithium Batteries are prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Must be declared as DG.
+2. Stowage : (LIB) On deck away from heat source</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicles with Used and/or damaged/defective/waste Sodium Batteries are prohibited </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Must be declared as DG.
+2. Stowage: (LIB) On deck away from heat source</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Used (not damaged/defective) batteries shall be confirmed if they are waste.
+If it is waste, refer to "Waste (DG)". </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The below restrictions apply to Laden tanks only.
+ a) Stowage: 1st or 2nd tier for monitoring purpose
+ b) The following acceptance requirement is applicable only for ISO Tank Refrigerated Liquid Helium Shipment with below MAX PSI 91 (≤91):
+ - At the time of loading from the Port of Origin (POR/POL), the PSI reading for the shipment must be below 10 PSI (≤10).
+ - At the time of loading from T/S Port, the PSI reading must be below 35 PSI (≤35) unless exempted.
+ - Shipper should make arrangements with the terminal (POR/POL or T/S) to release the pressure when container is in the yard before loading.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. If loading in "Live" reefers to maintain temperature for stabilization (not for quality purpose), refer to "Temperature Controlled DG (SOC - Live Dual Reefer)"
+2. Technical name: Divinylbenzene (DVB) (Diethenylbenzene/Vinylstyrene.) should be classified under Class 4.1/UN 3532 or Class 4.1/UN 3534</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Charcoal from Indonesia is prohibited
+2. 20ft Dry Container only (not packed together with charcoal lighter or other ignition source inside the container)
+3. Following items shall be provided to GDG:
+ a) SDS
+ b) Vanning survey report, including photos, confirming compliance with SP 978.
+4. Stowage: ODAB - On deck away from heat source / 1st tier shaded from direct sunlight</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Raw (unfinished products) Chemically Activated Carbon MUST be declared as DG regardless of SP979.
+2. (DG &amp; Non-DG) Stowage: ODAB - On deck away from heat source / 1st tier shaded from direct sunlight</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Fire fighting material Lithium chloride powder, dry sodium chloride or graphite powder must be provided on board as per IMDG requirement. 20 kgs per 20ft container (1 TEU) under the care of master.
+2. Acceptable for 1st leg vessel only (if require 2nd leg vessel, shall consult GDG)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Prohibited from origin Bangladesh
+2. If its origin is from India, the following items shall be provided to GDG:
+ a) Vanning survey report
+ b) Valid IIP(Indian Institute of Packaging), ERRL (Enviro Remediation &amp; Research Laboratory) &amp; TUV UN certificate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Prohibited in Non-Operating Reefer (NOR)
+2. Acceptable only ONE bookings on ONE operated vessels
+3. Refer to "Temperature Controlled DG (SOC - Live Dual Reefer)" for temperature controlled DG loaded in live reefers for safety purpose.
+4. SADT is required for all Class 5.2
+5. All subrisk Class 1, see Class 1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>1. Acceptable basically in an open-top container or ventilated container.
  a) One door off container is prohibited
- b) As per IMDG Code, if the shipper want to load in closed container without adequate exchange of air
-in the unit, IMDG code SP 965.2 shall be complied.
+ b) As per IMDG Code, if the shipper want to load in closed container without adequate exchange of air in the unit, IMDG code SP 965.2 shall be complied.
  c) Flexible bags are not acceptable in closed container
  d) In case of Live Reefer, only acceptable in explosion-proof type for quality purposes
 2. Stowage: ODAB - On deck away from heat source</t>
@@ -1811,48 +1734,22 @@
   <si>
     <t>1. Acceptable basically in an open-top container or ventilated container.
  a) One door off container is prohibited
- b) As per IMDG Code, if the shipper want to load in closed container without adequate exchange of air
-in the unit, IMDG code SP 965.2 shall be complied.
+ b) As per IMDG Code, if the shipper want to load in closed container without adequate exchange of air in the unit, IMDG code SP 965.2 shall be complied.
  c) Flexible bags are not acceptable in closed container
  d) In case of Live Reefer, only acceptable in explosion-proof type for quality purposes
 3. Stowage: ODAB - On deck away from heat source</t>
-  </si>
-  <si>
-    <t>Following items shall be provided to GDG in order to verify the moisture &amp; fat contents:
- a) SDS
- b) Fishmeal certificate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. Used and/or damaged/defective/waste Lithium Batteries are prohibited. Only new lithium batteries are
-acceptable.
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Used and/or damaged/defective/waste Lithium Batteries are prohibited. Only new lithium batteries are acceptable.
 2. Stowage : (LIB) On deck away from heat source
 3. UN3090/UN3480 (only for origin from China including Hong Kong) - SDS shall be provided.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1. Used and/or damaged/defective/waste Lithium Batteries are prohibited. Only new lithium batteries are
-acceptable.
-2. Stowage : (LIB) On deck away from heat source
-3. UN3090/UN3481 (only for origin from China including Hong Kong) - SDS shall be provided.</t>
-  </si>
-  <si>
-    <t>1. Used and/or damaged/defective/waste Lithium Batteries are prohibited. Only new lithium batteries are
-acceptable.
-2. Stowage : (LIB) On deck away from heat source
-3. UN3090/UN3482 (only for origin from China including Hong Kong) - SDS shall be provided.</t>
-  </si>
-  <si>
-    <t>1. Used and/or damaged/defective/waste Lithium Batteries are prohibited. Only new lithium batteries are
-acceptable.
-2. Stowage : (LIB) On deck away from heat source
-3. UN3090/UN3483 (only for origin from China including Hong Kong) - SDS shall be provided.</t>
-  </si>
-  <si>
     <t>1. All Lithium or Sodium Battery Powered HV must be declared as DG.
 2. Used Lithium or Used Sodium Battery Powered HV are prohibited.
-Exception for Used Lithium or Used Sodium Battery Powered HV is below condition for ONE &amp; Partner's
-booking.
+Exception for Used Lithium or Used Sodium Battery Powered HV is below condition for ONE &amp; Partner's booking.
  a) The vehicle is manufactured and exported from Japan for resale only.
  b) The HV has not been involved in an accident, and the batteries are undamaged.
  c) Letter of Guarantee (L/G) to be submitted for proof of above a) &amp; b) conditions
@@ -1861,50 +1758,24 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Vehicles with Used and/or damaged/defective/waste Lithium Batteries are prohibited</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. Must be declared as DG.
-2. Stowage : (LIB) On deck away from heat source</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. Used and/or damaged/defective/waste lithium batteries are prohibited. Only new lithium batteries are
-acceptable.
+    <t>1. Used and/or damaged/defective/waste lithium batteries are prohibited. Only new lithium batteries are acceptable.
 2. Stowage : (LIB) On deck away from heat source
 3. Exceeding 45 tons container weight of BESS (Battery Energy Storage System) is prohibited.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1. Used and/or damaged/defective/waste sodium batteries are prohibited. Only new sodium batteries are
-acceptable.
+    <t>1. Used and/or damaged/defective/waste sodium batteries are prohibited. Only new sodium batteries are acceptable.
 2. Stowage : (LIB) On deck away from heat source</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1. Used and/or damaged/defective/waste sodium batteries are prohibited. Only new sodium batteries are
-acceptable.
+    <t>1. Used and/or damaged/defective/waste sodium batteries are prohibited. Only new sodium batteries are acceptable.
 3. Stowage : (LIB) On deck away from heat source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vehicles with Used and/or damaged/defective/waste Sodium Batteries are prohibited </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. Must be declared as DG.
-2. Stowage: (LIB) On deck away from heat source</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1. Stowage: (OD) On deck
-2. If under deck stowage is required, equipments suitable for detecting the fumigant gas or gases used
-should be carried on board as per IMO (MSC.1/Circ.1361/Rev.1).</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Used (not damaged/defective) batteries shall be confirmed if they are waste.
-If it is waste, refer to "Waste (DG)". </t>
+2. If under deck stowage is required, equipments suitable for detecting the fumigant gas or gases used should be carried on board as per IMO (MSC.1/Circ.1361/Rev.1).</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1912,8 +1783,7 @@
  a) Stowage: (OP) On deck &amp; protected from sources of heat.
  b) Prohibit if origin from China including Hong Kong.
  c) Must be declared as DG.
-2. Calcium hypochlorite, trichloroisocyanuric acid, symclosene, TCCA, and their synonyms are prohibited
-when declared as Class 9 under UN 3077.</t>
+2. Calcium hypochlorite, trichloroisocyanuric acid, symclosene, TCCA, and their synonyms are prohibited when declared as Class 9 under UN 3077.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2001,7 +1871,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2048,6 +1918,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -19857,7 +19730,7 @@
     <col min="2" max="2" width="15" style="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.625" style="15" customWidth="1"/>
     <col min="4" max="5" width="11.625" style="13" customWidth="1"/>
-    <col min="6" max="6" width="70.125" style="13" customWidth="1"/>
+    <col min="6" max="6" width="160.125" style="13" customWidth="1"/>
     <col min="7" max="7" width="50.625" style="13" customWidth="1"/>
     <col min="8" max="8" width="57.75" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="57.125" style="13" bestFit="1" customWidth="1"/>
@@ -20104,7 +19977,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="204.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>142</v>
       </c>
@@ -20118,10 +19991,10 @@
         <v>138</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="110.25" x14ac:dyDescent="0.25">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>142</v>
       </c>
@@ -20133,7 +20006,7 @@
         <v>138</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="31.5" x14ac:dyDescent="0.25">
@@ -20148,7 +20021,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -20165,10 +20038,10 @@
         <v>138</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="94.5" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>142</v>
       </c>
@@ -20182,10 +20055,10 @@
         <v>138</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>142</v>
       </c>
@@ -20199,10 +20072,10 @@
         <v>138</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>142</v>
       </c>
@@ -20216,10 +20089,10 @@
         <v>138</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>142</v>
       </c>
@@ -20233,10 +20106,10 @@
         <v>138</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="126" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>142</v>
       </c>
@@ -20250,10 +20123,10 @@
         <v>138</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>142</v>
       </c>
@@ -20267,7 +20140,7 @@
         <v>138</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
@@ -20284,7 +20157,7 @@
         <v>138</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -20301,7 +20174,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>142</v>
       </c>
@@ -20315,10 +20188,10 @@
         <v>138</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>142</v>
       </c>
@@ -20332,10 +20205,10 @@
         <v>138</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="173.25" x14ac:dyDescent="0.25">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>142</v>
       </c>
@@ -20349,10 +20222,10 @@
         <v>138</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="173.25" x14ac:dyDescent="0.25">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>142</v>
       </c>
@@ -20366,10 +20239,10 @@
         <v>138</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="173.25" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>142</v>
       </c>
@@ -20383,10 +20256,10 @@
         <v>138</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="173.25" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>142</v>
       </c>
@@ -20400,10 +20273,10 @@
         <v>138</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="173.25" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>142</v>
       </c>
@@ -20417,10 +20290,10 @@
         <v>138</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="173.25" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>142</v>
       </c>
@@ -20434,10 +20307,10 @@
         <v>138</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="173.25" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>142</v>
       </c>
@@ -20451,7 +20324,7 @@
         <v>138</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -20468,10 +20341,10 @@
         <v>138</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="63" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>142</v>
       </c>
@@ -20485,7 +20358,7 @@
         <v>138</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -20502,10 +20375,10 @@
         <v>138</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="110.25" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>142</v>
       </c>
@@ -20517,7 +20390,7 @@
         <v>138</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -20534,7 +20407,7 @@
         <v>138</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -20551,7 +20424,7 @@
         <v>138</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -20568,7 +20441,7 @@
         <v>138</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -20585,7 +20458,7 @@
         <v>138</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -20602,7 +20475,7 @@
         <v>138</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -20619,7 +20492,7 @@
         <v>138</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -20636,7 +20509,7 @@
         <v>138</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -20653,7 +20526,7 @@
         <v>138</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -20670,7 +20543,7 @@
         <v>138</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>401</v>
+        <v>382</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -20687,7 +20560,7 @@
         <v>138</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>402</v>
+        <v>382</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -20704,7 +20577,7 @@
         <v>138</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>403</v>
+        <v>383</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -20721,7 +20594,7 @@
         <v>138</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>404</v>
+        <v>384</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -20776,7 +20649,7 @@
         <v>138</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>405</v>
+        <v>385</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -20793,7 +20666,7 @@
         <v>138</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>405</v>
+        <v>385</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -20810,7 +20683,7 @@
         <v>138</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>405</v>
+        <v>385</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -20827,10 +20700,10 @@
         <v>138</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="126" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>142</v>
       </c>
@@ -20844,10 +20717,10 @@
         <v>4</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="126" x14ac:dyDescent="0.25">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>142</v>
       </c>
@@ -20861,7 +20734,7 @@
         <v>138</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
@@ -20878,7 +20751,7 @@
         <v>138</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>408</v>
+        <v>386</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -20965,7 +20838,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>142</v>
       </c>
@@ -20979,10 +20852,10 @@
         <v>138</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>142</v>
       </c>
@@ -20996,10 +20869,10 @@
         <v>138</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>142</v>
       </c>
@@ -21013,10 +20886,10 @@
         <v>138</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>142</v>
       </c>
@@ -21030,10 +20903,10 @@
         <v>138</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="157.5" x14ac:dyDescent="0.25">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="126" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>142</v>
       </c>
@@ -21047,7 +20920,7 @@
         <v>138</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
@@ -21064,10 +20937,10 @@
         <v>138</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>414</v>
+        <v>387</v>
       </c>
       <c r="G70" s="14" t="s">
-        <v>415</v>
+        <v>388</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
@@ -21084,13 +20957,13 @@
         <v>138</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>414</v>
+        <v>387</v>
       </c>
       <c r="G71" s="14" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>142</v>
       </c>
@@ -21104,10 +20977,10 @@
         <v>138</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>142</v>
       </c>
@@ -21121,10 +20994,10 @@
         <v>138</v>
       </c>
       <c r="F73" s="14" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>142</v>
       </c>
@@ -21138,7 +21011,7 @@
         <v>138</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
@@ -21155,13 +21028,13 @@
         <v>138</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>419</v>
+        <v>389</v>
       </c>
       <c r="G75" s="14" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>142</v>
       </c>
@@ -21175,7 +21048,7 @@
         <v>138</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
@@ -21192,10 +21065,10 @@
         <v>138</v>
       </c>
       <c r="F77" s="14" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>142</v>
       </c>
@@ -21209,7 +21082,7 @@
         <v>138</v>
       </c>
       <c r="F78" s="14" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -21224,8 +21097,9 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="11.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.625" style="4" customWidth="1"/>
+    <col min="4" max="5" width="11.625" style="1" customWidth="1"/>
     <col min="6" max="8" width="50.625" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
@@ -21234,7 +21108,7 @@
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>145</v>
       </c>
       <c r="C1" s="3" t="s">
@@ -21275,7 +21149,7 @@
       <c r="B3" s="11">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C3" s="5"/>
+      <c r="C3" s="11"/>
       <c r="D3" s="5" t="s">
         <v>138</v>
       </c>
@@ -21287,7 +21161,7 @@
       <c r="B4" s="11">
         <v>1.2</v>
       </c>
-      <c r="C4" s="5"/>
+      <c r="C4" s="11"/>
       <c r="D4" s="5" t="s">
         <v>138</v>
       </c>
@@ -21299,7 +21173,7 @@
       <c r="B5" s="11">
         <v>1.3</v>
       </c>
-      <c r="C5" s="5"/>
+      <c r="C5" s="11"/>
       <c r="D5" s="5" t="s">
         <v>138</v>
       </c>
@@ -21311,7 +21185,7 @@
       <c r="B6" s="11">
         <v>1.4</v>
       </c>
-      <c r="C6" s="5"/>
+      <c r="C6" s="11"/>
       <c r="D6" s="5" t="s">
         <v>138</v>
       </c>
@@ -21323,7 +21197,7 @@
       <c r="B7" s="11">
         <v>1.5</v>
       </c>
-      <c r="C7" s="5"/>
+      <c r="C7" s="11"/>
       <c r="D7" s="5" t="s">
         <v>138</v>
       </c>
@@ -21335,7 +21209,7 @@
       <c r="B8" s="11">
         <v>1.6</v>
       </c>
-      <c r="C8" s="5"/>
+      <c r="C8" s="11"/>
       <c r="D8" s="5" t="s">
         <v>138</v>
       </c>
@@ -21347,7 +21221,7 @@
       <c r="B9" s="11">
         <v>2.1</v>
       </c>
-      <c r="C9" s="5"/>
+      <c r="C9" s="11"/>
       <c r="D9" s="5" t="s">
         <v>138</v>
       </c>
@@ -21359,7 +21233,7 @@
       <c r="B10" s="11">
         <v>2.1</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="11">
         <v>1057</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -21373,7 +21247,7 @@
       <c r="B11" s="11">
         <v>2.1</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="11">
         <v>1961</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -21387,7 +21261,7 @@
       <c r="B12" s="11">
         <v>2.1</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="11">
         <v>1966</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -21401,7 +21275,7 @@
       <c r="B13" s="11">
         <v>2.1</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="11">
         <v>1972</v>
       </c>
       <c r="D13" s="5" t="s">
@@ -21415,7 +21289,7 @@
       <c r="B14" s="11">
         <v>2.1</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="11">
         <v>3138</v>
       </c>
       <c r="D14" s="5" t="s">
@@ -21429,7 +21303,7 @@
       <c r="B15" s="11">
         <v>2.2000000000000002</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="11">
         <v>2455</v>
       </c>
       <c r="D15" s="5" t="s">
@@ -21443,7 +21317,7 @@
       <c r="B16" s="11">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="11">
         <v>1067</v>
       </c>
       <c r="D16" s="5" t="s">
@@ -21457,7 +21331,7 @@
       <c r="B17" s="11">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="11">
         <v>1069</v>
       </c>
       <c r="D17" s="5" t="s">
@@ -21471,7 +21345,7 @@
       <c r="B18" s="11">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="11">
         <v>1076</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -21485,7 +21359,7 @@
       <c r="B19" s="11">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="11">
         <v>1749</v>
       </c>
       <c r="D19" s="5" t="s">
@@ -21499,7 +21373,7 @@
       <c r="B20" s="11">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="11">
         <v>1911</v>
       </c>
       <c r="D20" s="5" t="s">
@@ -21513,7 +21387,7 @@
       <c r="B21" s="11">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="11">
         <v>2185</v>
       </c>
       <c r="D21" s="5" t="s">
@@ -21527,7 +21401,7 @@
       <c r="B22" s="11">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="11">
         <v>2188</v>
       </c>
       <c r="D22" s="5" t="s">
@@ -21541,7 +21415,7 @@
       <c r="B23" s="11">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="11">
         <v>2190</v>
       </c>
       <c r="D23" s="5" t="s">
@@ -21555,7 +21429,7 @@
       <c r="B24" s="11">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="11">
         <v>2417</v>
       </c>
       <c r="D24" s="5" t="s">
@@ -21569,7 +21443,7 @@
       <c r="B25" s="11">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="11">
         <v>2420</v>
       </c>
       <c r="D25" s="5" t="s">
@@ -21583,7 +21457,7 @@
       <c r="B26" s="11">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="11">
         <v>2421</v>
       </c>
       <c r="D26" s="5" t="s">
@@ -21597,7 +21471,7 @@
       <c r="B27" s="11">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="11">
         <v>2534</v>
       </c>
       <c r="D27" s="5" t="s">
@@ -21611,7 +21485,7 @@
       <c r="B28" s="11">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="11">
         <v>2548</v>
       </c>
       <c r="D28" s="5" t="s">
@@ -21625,7 +21499,7 @@
       <c r="B29" s="11">
         <v>3</v>
       </c>
-      <c r="C29" s="5"/>
+      <c r="C29" s="11"/>
       <c r="E29" s="5" t="s">
         <v>138</v>
       </c>
@@ -21637,7 +21511,7 @@
       <c r="B30" s="11">
         <v>3</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="11">
         <v>1131</v>
       </c>
       <c r="D30" s="5" t="s">
@@ -21651,7 +21525,7 @@
       <c r="B31" s="11">
         <v>3</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31" s="11">
         <v>1194</v>
       </c>
       <c r="D31" s="5" t="s">
@@ -21665,7 +21539,7 @@
       <c r="B32" s="11">
         <v>3</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="11">
         <v>1280</v>
       </c>
       <c r="D32" s="5" t="s">
@@ -21679,7 +21553,7 @@
       <c r="B33" s="11">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33" s="11">
         <v>2956</v>
       </c>
       <c r="D33" s="5" t="s">
@@ -21693,7 +21567,7 @@
       <c r="B34" s="11">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="11">
         <v>3221</v>
       </c>
       <c r="D34" s="5" t="s">
@@ -21707,7 +21581,7 @@
       <c r="B35" s="11">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35" s="11">
         <v>3222</v>
       </c>
       <c r="D35" s="5" t="s">
@@ -21721,7 +21595,7 @@
       <c r="B36" s="11">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="11">
         <v>3231</v>
       </c>
       <c r="D36" s="5" t="s">
@@ -21735,7 +21609,7 @@
       <c r="B37" s="11">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37" s="11">
         <v>3232</v>
       </c>
       <c r="D37" s="5" t="s">
@@ -21749,7 +21623,7 @@
       <c r="B38" s="11">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C38" s="11">
         <v>3233</v>
       </c>
       <c r="D38" s="5" t="s">
@@ -21763,7 +21637,7 @@
       <c r="B39" s="11">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C39" s="11">
         <v>3234</v>
       </c>
       <c r="D39" s="5" t="s">
@@ -21777,7 +21651,7 @@
       <c r="B40" s="11">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40" s="11">
         <v>3235</v>
       </c>
       <c r="D40" s="5" t="s">
@@ -21791,7 +21665,7 @@
       <c r="B41" s="11">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C41" s="5">
+      <c r="C41" s="11">
         <v>3236</v>
       </c>
       <c r="D41" s="5" t="s">
@@ -21805,7 +21679,7 @@
       <c r="B42" s="11">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C42" s="5">
+      <c r="C42" s="11">
         <v>3237</v>
       </c>
       <c r="D42" s="5" t="s">
@@ -21819,7 +21693,7 @@
       <c r="B43" s="11">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C43" s="11">
         <v>3238</v>
       </c>
       <c r="D43" s="5" t="s">
@@ -21833,7 +21707,7 @@
       <c r="B44" s="11">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C44" s="5">
+      <c r="C44" s="11">
         <v>3239</v>
       </c>
       <c r="D44" s="5" t="s">
@@ -21847,7 +21721,7 @@
       <c r="B45" s="11">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C45" s="5">
+      <c r="C45" s="11">
         <v>3240</v>
       </c>
       <c r="D45" s="5" t="s">
@@ -21861,7 +21735,7 @@
       <c r="B46" s="11">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C46" s="5">
+      <c r="C46" s="11">
         <v>3242</v>
       </c>
       <c r="D46" s="5" t="s">
@@ -21875,7 +21749,7 @@
       <c r="B47" s="11">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C47" s="5">
+      <c r="C47" s="11">
         <v>3533</v>
       </c>
       <c r="D47" s="5" t="s">
@@ -21889,7 +21763,7 @@
       <c r="B48" s="11">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C48" s="5">
+      <c r="C48" s="11">
         <v>3534</v>
       </c>
       <c r="D48" s="5" t="s">
@@ -21903,7 +21777,7 @@
       <c r="B49" s="11">
         <v>4.2</v>
       </c>
-      <c r="C49" s="5"/>
+      <c r="C49" s="11"/>
       <c r="D49" s="5" t="s">
         <v>138</v>
       </c>
@@ -21915,7 +21789,7 @@
       <c r="B50" s="11">
         <v>4.2</v>
       </c>
-      <c r="C50" s="5">
+      <c r="C50" s="11">
         <v>1361</v>
       </c>
       <c r="D50" s="5" t="s">
@@ -21929,7 +21803,7 @@
       <c r="B51" s="11">
         <v>4.2</v>
       </c>
-      <c r="C51" s="5">
+      <c r="C51" s="11">
         <v>1362</v>
       </c>
       <c r="D51" s="5" t="s">
@@ -21943,7 +21817,7 @@
       <c r="B52" s="11">
         <v>4.2</v>
       </c>
-      <c r="C52" s="5">
+      <c r="C52" s="11">
         <v>1381</v>
       </c>
       <c r="D52" s="5" t="s">
@@ -21957,7 +21831,7 @@
       <c r="B53" s="11">
         <v>4.2</v>
       </c>
-      <c r="C53" s="5">
+      <c r="C53" s="11">
         <v>2845</v>
       </c>
       <c r="D53" s="5" t="s">
@@ -21971,7 +21845,7 @@
       <c r="B54" s="11">
         <v>4.2</v>
       </c>
-      <c r="C54" s="5">
+      <c r="C54" s="11">
         <v>3088</v>
       </c>
       <c r="D54" s="5" t="s">
@@ -21985,7 +21859,7 @@
       <c r="B55" s="11">
         <v>4.2</v>
       </c>
-      <c r="C55" s="5">
+      <c r="C55" s="11">
         <v>3194</v>
       </c>
       <c r="D55" s="5" t="s">
@@ -21999,7 +21873,7 @@
       <c r="B56" s="11">
         <v>4.2</v>
       </c>
-      <c r="C56" s="5">
+      <c r="C56" s="11">
         <v>3200</v>
       </c>
       <c r="D56" s="5" t="s">
@@ -22013,7 +21887,7 @@
       <c r="B57" s="11">
         <v>4.2</v>
       </c>
-      <c r="C57" s="5">
+      <c r="C57" s="11">
         <v>3341</v>
       </c>
       <c r="D57" s="5" t="s">
@@ -22027,7 +21901,7 @@
       <c r="B58" s="11">
         <v>4.2</v>
       </c>
-      <c r="C58" s="5">
+      <c r="C58" s="11">
         <v>3342</v>
       </c>
       <c r="D58" s="5" t="s">
@@ -22041,7 +21915,7 @@
       <c r="B59" s="11">
         <v>4.2</v>
       </c>
-      <c r="C59" s="5">
+      <c r="C59" s="11">
         <v>3392</v>
       </c>
       <c r="D59" s="5" t="s">
@@ -22055,7 +21929,7 @@
       <c r="B60" s="11">
         <v>4.2</v>
       </c>
-      <c r="C60" s="5">
+      <c r="C60" s="11">
         <v>3394</v>
       </c>
       <c r="D60" s="5" t="s">
@@ -22069,7 +21943,7 @@
       <c r="B61" s="11">
         <v>4.3</v>
       </c>
-      <c r="C61" s="5">
+      <c r="C61" s="11">
         <v>1391</v>
       </c>
       <c r="D61" s="5" t="s">
@@ -22083,7 +21957,7 @@
       <c r="B62" s="11">
         <v>4.3</v>
       </c>
-      <c r="C62" s="5">
+      <c r="C62" s="11">
         <v>1408</v>
       </c>
       <c r="D62" s="5" t="s">
@@ -22097,7 +21971,7 @@
       <c r="B63" s="11">
         <v>4.3</v>
       </c>
-      <c r="C63" s="5">
+      <c r="C63" s="11">
         <v>1415</v>
       </c>
       <c r="D63" s="5" t="s">
@@ -22111,7 +21985,7 @@
       <c r="B64" s="11">
         <v>4.3</v>
       </c>
-      <c r="C64" s="5">
+      <c r="C64" s="11">
         <v>1418</v>
       </c>
       <c r="D64" s="5" t="s">
@@ -22125,7 +21999,7 @@
       <c r="B65" s="11">
         <v>4.3</v>
       </c>
-      <c r="C65" s="5">
+      <c r="C65" s="11">
         <v>1426</v>
       </c>
       <c r="D65" s="5" t="s">
@@ -22139,7 +22013,7 @@
       <c r="B66" s="11">
         <v>4.3</v>
       </c>
-      <c r="C66" s="5">
+      <c r="C66" s="11">
         <v>3129</v>
       </c>
       <c r="D66" s="5" t="s">
@@ -22153,7 +22027,7 @@
       <c r="B67" s="11">
         <v>4.3</v>
       </c>
-      <c r="C67" s="5">
+      <c r="C67" s="11">
         <v>3130</v>
       </c>
       <c r="D67" s="5" t="s">
@@ -22167,7 +22041,7 @@
       <c r="B68" s="11">
         <v>4.3</v>
       </c>
-      <c r="C68" s="5">
+      <c r="C68" s="11">
         <v>3131</v>
       </c>
       <c r="D68" s="5" t="s">
@@ -22181,7 +22055,7 @@
       <c r="B69" s="11">
         <v>4.3</v>
       </c>
-      <c r="C69" s="5">
+      <c r="C69" s="11">
         <v>3132</v>
       </c>
       <c r="D69" s="5" t="s">
@@ -22195,7 +22069,7 @@
       <c r="B70" s="11">
         <v>4.3</v>
       </c>
-      <c r="C70" s="5">
+      <c r="C70" s="11">
         <v>3133</v>
       </c>
       <c r="D70" s="5" t="s">
@@ -22209,7 +22083,7 @@
       <c r="B71" s="11">
         <v>4.3</v>
       </c>
-      <c r="C71" s="5">
+      <c r="C71" s="11">
         <v>3134</v>
       </c>
       <c r="D71" s="5" t="s">
@@ -22223,7 +22097,7 @@
       <c r="B72" s="11">
         <v>4.3</v>
       </c>
-      <c r="C72" s="5">
+      <c r="C72" s="11">
         <v>3135</v>
       </c>
       <c r="D72" s="5" t="s">
@@ -22237,7 +22111,7 @@
       <c r="B73" s="11">
         <v>4.3</v>
       </c>
-      <c r="C73" s="5">
+      <c r="C73" s="11">
         <v>3482</v>
       </c>
       <c r="D73" s="5" t="s">
@@ -22251,7 +22125,7 @@
       <c r="B74" s="11">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C74" s="5">
+      <c r="C74" s="11">
         <v>1479</v>
       </c>
       <c r="D74" s="5" t="s">
@@ -22265,7 +22139,7 @@
       <c r="B75" s="11">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C75" s="5">
+      <c r="C75" s="11">
         <v>1512</v>
       </c>
       <c r="D75" s="5" t="s">
@@ -22279,7 +22153,7 @@
       <c r="B76" s="11">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C76" s="5">
+      <c r="C76" s="11">
         <v>1748</v>
       </c>
       <c r="D76" s="5" t="s">
@@ -22293,7 +22167,7 @@
       <c r="B77" s="11">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C77" s="5">
+      <c r="C77" s="11">
         <v>1942</v>
       </c>
       <c r="D77" s="5" t="s">
@@ -22307,7 +22181,7 @@
       <c r="B78" s="11">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C78" s="5">
+      <c r="C78" s="11">
         <v>2067</v>
       </c>
       <c r="D78" s="5" t="s">
@@ -22321,7 +22195,7 @@
       <c r="B79" s="11">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C79" s="5">
+      <c r="C79" s="11">
         <v>2208</v>
       </c>
       <c r="D79" s="5" t="s">
@@ -22335,7 +22209,7 @@
       <c r="B80" s="11">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C80" s="5">
+      <c r="C80" s="11">
         <v>2426</v>
       </c>
       <c r="D80" s="5" t="s">
@@ -22349,7 +22223,7 @@
       <c r="B81" s="11">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C81" s="5">
+      <c r="C81" s="11">
         <v>2880</v>
       </c>
       <c r="D81" s="5" t="s">
@@ -22363,7 +22237,7 @@
       <c r="B82" s="11">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C82" s="5">
+      <c r="C82" s="11">
         <v>3375</v>
       </c>
       <c r="D82" s="5" t="s">
@@ -22377,7 +22251,7 @@
       <c r="B83" s="11">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C83" s="5">
+      <c r="C83" s="11">
         <v>3485</v>
       </c>
       <c r="D83" s="5" t="s">
@@ -22391,7 +22265,7 @@
       <c r="B84" s="11">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C84" s="5">
+      <c r="C84" s="11">
         <v>3486</v>
       </c>
       <c r="D84" s="5" t="s">
@@ -22405,7 +22279,7 @@
       <c r="B85" s="11">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C85" s="5">
+      <c r="C85" s="11">
         <v>3487</v>
       </c>
       <c r="D85" s="5" t="s">
@@ -22419,7 +22293,7 @@
       <c r="B86" s="11">
         <v>5.2</v>
       </c>
-      <c r="C86" s="5"/>
+      <c r="C86" s="11"/>
       <c r="D86" s="5" t="s">
         <v>138</v>
       </c>
@@ -22431,7 +22305,7 @@
       <c r="B87" s="11">
         <v>5.2</v>
       </c>
-      <c r="C87" s="5">
+      <c r="C87" s="11">
         <v>3101</v>
       </c>
       <c r="D87" s="5" t="s">
@@ -22445,7 +22319,7 @@
       <c r="B88" s="11">
         <v>5.2</v>
       </c>
-      <c r="C88" s="5">
+      <c r="C88" s="11">
         <v>3102</v>
       </c>
       <c r="D88" s="5" t="s">
@@ -22459,7 +22333,7 @@
       <c r="B89" s="11">
         <v>5.2</v>
       </c>
-      <c r="C89" s="5">
+      <c r="C89" s="11">
         <v>3103</v>
       </c>
       <c r="D89" s="5" t="s">
@@ -22473,7 +22347,7 @@
       <c r="B90" s="11">
         <v>5.2</v>
       </c>
-      <c r="C90" s="5">
+      <c r="C90" s="11">
         <v>3111</v>
       </c>
       <c r="D90" s="5" t="s">
@@ -22487,7 +22361,7 @@
       <c r="B91" s="11">
         <v>5.2</v>
       </c>
-      <c r="C91" s="5">
+      <c r="C91" s="11">
         <v>3112</v>
       </c>
       <c r="D91" s="5" t="s">
@@ -22501,7 +22375,7 @@
       <c r="B92" s="11">
         <v>5.2</v>
       </c>
-      <c r="C92" s="5">
+      <c r="C92" s="11">
         <v>3113</v>
       </c>
       <c r="D92" s="5" t="s">
@@ -22515,7 +22389,7 @@
       <c r="B93" s="11">
         <v>5.2</v>
       </c>
-      <c r="C93" s="5">
+      <c r="C93" s="11">
         <v>3114</v>
       </c>
       <c r="D93" s="5" t="s">
@@ -22529,7 +22403,7 @@
       <c r="B94" s="11">
         <v>5.2</v>
       </c>
-      <c r="C94" s="5">
+      <c r="C94" s="11">
         <v>3115</v>
       </c>
       <c r="D94" s="5" t="s">
@@ -22543,7 +22417,7 @@
       <c r="B95" s="11">
         <v>5.2</v>
       </c>
-      <c r="C95" s="5">
+      <c r="C95" s="11">
         <v>3116</v>
       </c>
       <c r="D95" s="5" t="s">
@@ -22557,7 +22431,7 @@
       <c r="B96" s="11">
         <v>5.2</v>
       </c>
-      <c r="C96" s="5">
+      <c r="C96" s="11">
         <v>3117</v>
       </c>
       <c r="D96" s="5" t="s">
@@ -22571,7 +22445,7 @@
       <c r="B97" s="11">
         <v>5.2</v>
       </c>
-      <c r="C97" s="5">
+      <c r="C97" s="11">
         <v>3118</v>
       </c>
       <c r="D97" s="5" t="s">
@@ -22585,7 +22459,7 @@
       <c r="B98" s="11">
         <v>5.2</v>
       </c>
-      <c r="C98" s="5">
+      <c r="C98" s="11">
         <v>3119</v>
       </c>
       <c r="D98" s="5" t="s">
@@ -22599,7 +22473,7 @@
       <c r="B99" s="11">
         <v>5.2</v>
       </c>
-      <c r="C99" s="5">
+      <c r="C99" s="11">
         <v>3120</v>
       </c>
       <c r="D99" s="5" t="s">
@@ -22613,7 +22487,7 @@
       <c r="B100" s="11">
         <v>6.1</v>
       </c>
-      <c r="C100" s="5">
+      <c r="C100" s="11">
         <v>1259</v>
       </c>
       <c r="D100" s="5" t="s">
@@ -22627,7 +22501,7 @@
       <c r="B101" s="11">
         <v>6.1</v>
       </c>
-      <c r="C101" s="5">
+      <c r="C101" s="11">
         <v>1649</v>
       </c>
       <c r="D101" s="5" t="s">
@@ -22641,7 +22515,7 @@
       <c r="B102" s="11">
         <v>6.1</v>
       </c>
-      <c r="C102" s="5">
+      <c r="C102" s="11">
         <v>2206</v>
       </c>
       <c r="D102" s="5" t="s">
@@ -22655,7 +22529,7 @@
       <c r="B103" s="11">
         <v>6.1</v>
       </c>
-      <c r="C103" s="5">
+      <c r="C103" s="11">
         <v>2811</v>
       </c>
       <c r="D103" s="5" t="s">
@@ -22669,7 +22543,7 @@
       <c r="B104" s="11">
         <v>6.1</v>
       </c>
-      <c r="C104" s="5">
+      <c r="C104" s="11">
         <v>3123</v>
       </c>
       <c r="D104" s="5" t="s">
@@ -22683,7 +22557,7 @@
       <c r="B105" s="11">
         <v>6.1</v>
       </c>
-      <c r="C105" s="5">
+      <c r="C105" s="11">
         <v>3124</v>
       </c>
       <c r="D105" s="5" t="s">
@@ -22697,7 +22571,7 @@
       <c r="B106" s="11">
         <v>6.1</v>
       </c>
-      <c r="C106" s="5">
+      <c r="C106" s="11">
         <v>3125</v>
       </c>
       <c r="D106" s="5" t="s">
@@ -22711,7 +22585,7 @@
       <c r="B107" s="11">
         <v>6.1</v>
       </c>
-      <c r="C107" s="5">
+      <c r="C107" s="11">
         <v>3507</v>
       </c>
       <c r="D107" s="5" t="s">
@@ -22725,7 +22599,7 @@
       <c r="B108" s="11">
         <v>6.2</v>
       </c>
-      <c r="C108" s="5"/>
+      <c r="C108" s="11"/>
       <c r="D108" s="5" t="s">
         <v>138</v>
       </c>
@@ -22737,7 +22611,7 @@
       <c r="B109" s="11">
         <v>7</v>
       </c>
-      <c r="C109" s="5"/>
+      <c r="C109" s="11"/>
       <c r="D109" s="5" t="s">
         <v>138</v>
       </c>
@@ -22749,7 +22623,7 @@
       <c r="B110" s="11">
         <v>8</v>
       </c>
-      <c r="C110" s="5">
+      <c r="C110" s="11">
         <v>2031</v>
       </c>
       <c r="D110" s="5" t="s">
@@ -22763,7 +22637,7 @@
       <c r="B111" s="11">
         <v>8</v>
       </c>
-      <c r="C111" s="5">
+      <c r="C111" s="11">
         <v>2032</v>
       </c>
       <c r="D111" s="5" t="s">
@@ -22777,7 +22651,7 @@
       <c r="B112" s="11">
         <v>8</v>
       </c>
-      <c r="C112" s="5">
+      <c r="C112" s="11">
         <v>2922</v>
       </c>
       <c r="D112" s="5" t="s">
@@ -22791,7 +22665,7 @@
       <c r="B113" s="11">
         <v>8</v>
       </c>
-      <c r="C113" s="5">
+      <c r="C113" s="11">
         <v>3094</v>
       </c>
       <c r="D113" s="5" t="s">
@@ -22805,7 +22679,7 @@
       <c r="B114" s="11">
         <v>8</v>
       </c>
-      <c r="C114" s="5">
+      <c r="C114" s="11">
         <v>3095</v>
       </c>
       <c r="D114" s="5" t="s">
@@ -22819,7 +22693,7 @@
       <c r="B115" s="11">
         <v>8</v>
       </c>
-      <c r="C115" s="5">
+      <c r="C115" s="11">
         <v>3096</v>
       </c>
       <c r="D115" s="5" t="s">
@@ -22833,7 +22707,7 @@
       <c r="B116" s="11">
         <v>9</v>
       </c>
-      <c r="C116" s="5">
+      <c r="C116" s="11">
         <v>2071</v>
       </c>
       <c r="D116" s="5" t="s">
@@ -22847,7 +22721,7 @@
       <c r="B117" s="11">
         <v>9</v>
       </c>
-      <c r="C117" s="5">
+      <c r="C117" s="11">
         <v>2211</v>
       </c>
       <c r="D117" s="5" t="s">
@@ -22861,7 +22735,7 @@
       <c r="B118" s="11">
         <v>9</v>
       </c>
-      <c r="C118" s="5">
+      <c r="C118" s="11">
         <v>2212</v>
       </c>
       <c r="D118" s="5" t="s">
@@ -22875,7 +22749,7 @@
       <c r="B119" s="11">
         <v>9</v>
       </c>
-      <c r="C119" s="5">
+      <c r="C119" s="11">
         <v>2315</v>
       </c>
       <c r="D119" s="5" t="s">
@@ -22889,7 +22763,7 @@
       <c r="B120" s="11">
         <v>9</v>
       </c>
-      <c r="C120" s="5">
+      <c r="C120" s="11">
         <v>2590</v>
       </c>
       <c r="D120" s="5" t="s">
@@ -22903,7 +22777,7 @@
       <c r="B121" s="11">
         <v>9</v>
       </c>
-      <c r="C121" s="5">
+      <c r="C121" s="11">
         <v>3090</v>
       </c>
       <c r="D121" s="5" t="s">
@@ -22917,7 +22791,7 @@
       <c r="B122" s="11">
         <v>9</v>
       </c>
-      <c r="C122" s="5">
+      <c r="C122" s="11">
         <v>3091</v>
       </c>
       <c r="D122" s="5" t="s">
@@ -22931,7 +22805,7 @@
       <c r="B123" s="11">
         <v>9</v>
       </c>
-      <c r="C123" s="5">
+      <c r="C123" s="11">
         <v>3151</v>
       </c>
       <c r="D123" s="5" t="s">
@@ -22945,7 +22819,7 @@
       <c r="B124" s="11">
         <v>9</v>
       </c>
-      <c r="C124" s="5">
+      <c r="C124" s="11">
         <v>3152</v>
       </c>
       <c r="D124" s="5" t="s">
@@ -22959,7 +22833,7 @@
       <c r="B125" s="11">
         <v>9</v>
       </c>
-      <c r="C125" s="5">
+      <c r="C125" s="11">
         <v>3432</v>
       </c>
       <c r="D125" s="5" t="s">
@@ -22973,7 +22847,7 @@
       <c r="B126" s="11">
         <v>9</v>
       </c>
-      <c r="C126" s="5">
+      <c r="C126" s="11">
         <v>3166</v>
       </c>
       <c r="D126" s="5" t="s">
@@ -22987,7 +22861,7 @@
       <c r="B127" s="11">
         <v>9</v>
       </c>
-      <c r="C127" s="5">
+      <c r="C127" s="11">
         <v>3171</v>
       </c>
       <c r="D127" s="5" t="s">
@@ -23001,7 +22875,7 @@
       <c r="B128" s="11">
         <v>9</v>
       </c>
-      <c r="C128" s="5">
+      <c r="C128" s="11">
         <v>3480</v>
       </c>
       <c r="D128" s="5" t="s">
@@ -23015,7 +22889,7 @@
       <c r="B129" s="11">
         <v>9</v>
       </c>
-      <c r="C129" s="5">
+      <c r="C129" s="11">
         <v>3481</v>
       </c>
       <c r="D129" s="5" t="s">
@@ -23029,7 +22903,7 @@
       <c r="B130" s="11">
         <v>9</v>
       </c>
-      <c r="C130" s="5">
+      <c r="C130" s="11">
         <v>3551</v>
       </c>
       <c r="D130" s="5" t="s">
@@ -23043,7 +22917,7 @@
       <c r="B131" s="11">
         <v>9</v>
       </c>
-      <c r="C131" s="5">
+      <c r="C131" s="11">
         <v>3552</v>
       </c>
       <c r="D131" s="5" t="s">
@@ -23057,7 +22931,7 @@
       <c r="B132" s="11">
         <v>9</v>
       </c>
-      <c r="C132" s="5">
+      <c r="C132" s="11">
         <v>3536</v>
       </c>
       <c r="D132" s="5" t="s">
@@ -23071,7 +22945,7 @@
       <c r="B133" s="11">
         <v>9</v>
       </c>
-      <c r="C133" s="5">
+      <c r="C133" s="11">
         <v>3556</v>
       </c>
       <c r="D133" s="5" t="s">
@@ -23085,7 +22959,7 @@
       <c r="B134" s="11">
         <v>9</v>
       </c>
-      <c r="C134" s="5">
+      <c r="C134" s="11">
         <v>3557</v>
       </c>
       <c r="D134" s="5" t="s">
@@ -23099,7 +22973,7 @@
       <c r="B135" s="11">
         <v>9</v>
       </c>
-      <c r="C135" s="5">
+      <c r="C135" s="11">
         <v>3558</v>
       </c>
       <c r="D135" s="5" t="s">
@@ -23118,8 +22992,9 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.625" customWidth="1"/>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="15" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.625" style="16" customWidth="1"/>
+    <col min="4" max="5" width="11.625" customWidth="1"/>
     <col min="6" max="8" width="50.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -23127,7 +23002,7 @@
       <c r="A1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>145</v>
       </c>
       <c r="C1" s="10" t="s">
@@ -23156,7 +23031,7 @@
       <c r="B2" s="12">
         <v>1</v>
       </c>
-      <c r="C2" s="6"/>
+      <c r="C2" s="12"/>
       <c r="D2" s="6" t="s">
         <v>138</v>
       </c>
@@ -23168,7 +23043,7 @@
       <c r="B3" s="12">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C3" s="6"/>
+      <c r="C3" s="12"/>
       <c r="D3" s="6" t="s">
         <v>138</v>
       </c>
@@ -23180,7 +23055,7 @@
       <c r="B4" s="12">
         <v>1.2</v>
       </c>
-      <c r="C4" s="6"/>
+      <c r="C4" s="12"/>
       <c r="D4" s="6" t="s">
         <v>138</v>
       </c>
@@ -23192,7 +23067,7 @@
       <c r="B5" s="12">
         <v>1.3</v>
       </c>
-      <c r="C5" s="6"/>
+      <c r="C5" s="12"/>
       <c r="D5" s="6" t="s">
         <v>138</v>
       </c>
@@ -23204,7 +23079,7 @@
       <c r="B6" s="12">
         <v>1.4</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="12"/>
       <c r="D6" s="6" t="s">
         <v>138</v>
       </c>
@@ -23216,7 +23091,7 @@
       <c r="B7" s="12">
         <v>1.5</v>
       </c>
-      <c r="C7" s="6"/>
+      <c r="C7" s="12"/>
       <c r="D7" s="6" t="s">
         <v>138</v>
       </c>
@@ -23228,7 +23103,7 @@
       <c r="B8" s="12">
         <v>1.6</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="12"/>
       <c r="D8" s="6" t="s">
         <v>138</v>
       </c>
@@ -23240,7 +23115,7 @@
       <c r="B9" s="12">
         <v>2.2000000000000002</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="12">
         <v>1963</v>
       </c>
       <c r="D9" s="6" t="s">
@@ -23254,7 +23129,7 @@
       <c r="B10" s="12">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="12"/>
       <c r="D10" s="6" t="s">
         <v>138</v>
       </c>
@@ -23266,7 +23141,7 @@
       <c r="B11" s="12">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="12">
         <v>1040</v>
       </c>
       <c r="D11" s="6" t="s">
@@ -23280,7 +23155,7 @@
       <c r="B12" s="12">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="12">
         <v>1067</v>
       </c>
       <c r="D12" s="6" t="s">
@@ -23294,7 +23169,7 @@
       <c r="B13" s="12">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="12">
         <v>1749</v>
       </c>
       <c r="D13" s="6" t="s">
@@ -23308,7 +23183,7 @@
       <c r="B14" s="12">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="12">
         <v>2188</v>
       </c>
       <c r="D14" s="6" t="s">
@@ -23322,7 +23197,7 @@
       <c r="B15" s="12">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="12">
         <v>2190</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -23336,7 +23211,7 @@
       <c r="B16" s="12">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="12">
         <v>2417</v>
       </c>
       <c r="D16" s="6" t="s">
@@ -23350,7 +23225,7 @@
       <c r="B17" s="12">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="12">
         <v>2420</v>
       </c>
       <c r="D17" s="6" t="s">
@@ -23364,7 +23239,7 @@
       <c r="B18" s="12">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="12">
         <v>2421</v>
       </c>
       <c r="D18" s="6" t="s">
@@ -23378,7 +23253,7 @@
       <c r="B19" s="12">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="12">
         <v>2548</v>
       </c>
       <c r="D19" s="6" t="s">
@@ -23392,7 +23267,7 @@
       <c r="B20" s="12">
         <v>3</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C20" s="12"/>
       <c r="E20" s="6" t="s">
         <v>138</v>
       </c>
@@ -23404,7 +23279,7 @@
       <c r="B21" s="12">
         <v>3</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="12">
         <v>1131</v>
       </c>
       <c r="D21" s="6" t="s">
@@ -23418,7 +23293,7 @@
       <c r="B22" s="12">
         <v>3</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="12">
         <v>1194</v>
       </c>
       <c r="D22" s="6" t="s">
@@ -23432,7 +23307,7 @@
       <c r="B23" s="12">
         <v>3</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="12">
         <v>3079</v>
       </c>
       <c r="D23" s="6" t="s">
@@ -23446,7 +23321,7 @@
       <c r="B24" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="12">
         <v>1334</v>
       </c>
       <c r="D24" s="6" t="s">
@@ -23460,7 +23335,7 @@
       <c r="B25" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="12">
         <v>1339</v>
       </c>
       <c r="D25" s="6" t="s">
@@ -23474,7 +23349,7 @@
       <c r="B26" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="12">
         <v>2304</v>
       </c>
       <c r="D26" s="6" t="s">
@@ -23488,7 +23363,7 @@
       <c r="B27" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="12">
         <v>2956</v>
       </c>
       <c r="D27" s="6" t="s">
@@ -23502,7 +23377,7 @@
       <c r="B28" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="12">
         <v>3221</v>
       </c>
       <c r="D28" s="6" t="s">
@@ -23516,7 +23391,7 @@
       <c r="B29" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="12">
         <v>3222</v>
       </c>
       <c r="D29" s="6" t="s">
@@ -23530,7 +23405,7 @@
       <c r="B30" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="12">
         <v>3223</v>
       </c>
       <c r="D30" s="6" t="s">
@@ -23544,7 +23419,7 @@
       <c r="B31" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="12">
         <v>3224</v>
       </c>
       <c r="D31" s="6" t="s">
@@ -23558,7 +23433,7 @@
       <c r="B32" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="12">
         <v>3225</v>
       </c>
       <c r="D32" s="6" t="s">
@@ -23572,7 +23447,7 @@
       <c r="B33" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="12">
         <v>3226</v>
       </c>
       <c r="D33" s="6" t="s">
@@ -23586,7 +23461,7 @@
       <c r="B34" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="12">
         <v>3227</v>
       </c>
       <c r="D34" s="6" t="s">
@@ -23600,7 +23475,7 @@
       <c r="B35" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="12">
         <v>3228</v>
       </c>
       <c r="D35" s="6" t="s">
@@ -23614,7 +23489,7 @@
       <c r="B36" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="12">
         <v>3229</v>
       </c>
       <c r="D36" s="6" t="s">
@@ -23628,7 +23503,7 @@
       <c r="B37" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="12">
         <v>3230</v>
       </c>
       <c r="D37" s="6" t="s">
@@ -23642,7 +23517,7 @@
       <c r="B38" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="12">
         <v>3231</v>
       </c>
       <c r="D38" s="6" t="s">
@@ -23656,7 +23531,7 @@
       <c r="B39" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="12">
         <v>3232</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -23670,7 +23545,7 @@
       <c r="B40" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="12">
         <v>3233</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -23684,7 +23559,7 @@
       <c r="B41" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="12">
         <v>3234</v>
       </c>
       <c r="D41" s="6" t="s">
@@ -23698,7 +23573,7 @@
       <c r="B42" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42" s="12">
         <v>3235</v>
       </c>
       <c r="D42" s="6" t="s">
@@ -23712,7 +23587,7 @@
       <c r="B43" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="12">
         <v>3236</v>
       </c>
       <c r="D43" s="6" t="s">
@@ -23726,7 +23601,7 @@
       <c r="B44" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44" s="12">
         <v>3237</v>
       </c>
       <c r="D44" s="6" t="s">
@@ -23740,7 +23615,7 @@
       <c r="B45" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45" s="12">
         <v>3238</v>
       </c>
       <c r="D45" s="6" t="s">
@@ -23754,7 +23629,7 @@
       <c r="B46" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46" s="12">
         <v>3239</v>
       </c>
       <c r="D46" s="6" t="s">
@@ -23768,7 +23643,7 @@
       <c r="B47" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47" s="12">
         <v>3240</v>
       </c>
       <c r="D47" s="6" t="s">
@@ -23782,7 +23657,7 @@
       <c r="B48" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48" s="12">
         <v>3241</v>
       </c>
       <c r="D48" s="6" t="s">
@@ -23796,7 +23671,7 @@
       <c r="B49" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49" s="12">
         <v>3242</v>
       </c>
       <c r="D49" s="6" t="s">
@@ -23810,7 +23685,7 @@
       <c r="B50" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C50" s="12">
         <v>3532</v>
       </c>
       <c r="D50" s="6" t="s">
@@ -23824,7 +23699,7 @@
       <c r="B51" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51" s="12">
         <v>3534</v>
       </c>
       <c r="D51" s="6" t="s">
@@ -23838,7 +23713,7 @@
       <c r="B52" s="12">
         <v>4.2</v>
       </c>
-      <c r="C52" s="6">
+      <c r="C52" s="12">
         <v>1361</v>
       </c>
       <c r="D52" s="6" t="s">
@@ -23852,7 +23727,7 @@
       <c r="B53" s="12">
         <v>4.2</v>
       </c>
-      <c r="C53" s="6">
+      <c r="C53" s="12">
         <v>1362</v>
       </c>
       <c r="D53" s="6" t="s">
@@ -23866,7 +23741,7 @@
       <c r="B54" s="12">
         <v>4.2</v>
       </c>
-      <c r="C54" s="6">
+      <c r="C54" s="12">
         <v>1372</v>
       </c>
       <c r="D54" s="6" t="s">
@@ -23880,7 +23755,7 @@
       <c r="B55" s="12">
         <v>4.2</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C55" s="12">
         <v>1374</v>
       </c>
       <c r="D55" s="6" t="s">
@@ -23894,7 +23769,7 @@
       <c r="B56" s="12">
         <v>4.2</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C56" s="12">
         <v>1381</v>
       </c>
       <c r="D56" s="6" t="s">
@@ -23908,7 +23783,7 @@
       <c r="B57" s="12">
         <v>4.2</v>
       </c>
-      <c r="C57" s="6">
+      <c r="C57" s="12">
         <v>1384</v>
       </c>
       <c r="D57" s="6" t="s">
@@ -23922,7 +23797,7 @@
       <c r="B58" s="12">
         <v>4.2</v>
       </c>
-      <c r="C58" s="6">
+      <c r="C58" s="12">
         <v>1386</v>
       </c>
       <c r="D58" s="6" t="s">
@@ -23936,7 +23811,7 @@
       <c r="B59" s="12">
         <v>4.2</v>
       </c>
-      <c r="C59" s="6">
+      <c r="C59" s="12">
         <v>2217</v>
       </c>
       <c r="D59" s="6" t="s">
@@ -23950,7 +23825,7 @@
       <c r="B60" s="12">
         <v>4.2</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C60" s="12">
         <v>3341</v>
       </c>
       <c r="D60" s="6" t="s">
@@ -23964,7 +23839,7 @@
       <c r="B61" s="12">
         <v>4.2</v>
       </c>
-      <c r="C61" s="6">
+      <c r="C61" s="12">
         <v>3342</v>
       </c>
       <c r="D61" s="6" t="s">
@@ -23978,7 +23853,7 @@
       <c r="B62" s="12">
         <v>4.3</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C62" s="12">
         <v>1340</v>
       </c>
       <c r="D62" s="6" t="s">
@@ -23992,7 +23867,7 @@
       <c r="B63" s="12">
         <v>4.3</v>
       </c>
-      <c r="C63" s="6">
+      <c r="C63" s="12">
         <v>1396</v>
       </c>
       <c r="D63" s="6" t="s">
@@ -24006,7 +23881,7 @@
       <c r="B64" s="12">
         <v>4.3</v>
       </c>
-      <c r="C64" s="6">
+      <c r="C64" s="12">
         <v>1397</v>
       </c>
       <c r="D64" s="6" t="s">
@@ -24020,7 +23895,7 @@
       <c r="B65" s="12">
         <v>4.3</v>
       </c>
-      <c r="C65" s="6">
+      <c r="C65" s="12">
         <v>1402</v>
       </c>
       <c r="D65" s="6" t="s">
@@ -24034,7 +23909,7 @@
       <c r="B66" s="12">
         <v>4.3</v>
       </c>
-      <c r="C66" s="6">
+      <c r="C66" s="12">
         <v>1415</v>
       </c>
       <c r="D66" s="6" t="s">
@@ -24048,7 +23923,7 @@
       <c r="B67" s="12">
         <v>4.3</v>
       </c>
-      <c r="C67" s="6">
+      <c r="C67" s="12">
         <v>1418</v>
       </c>
       <c r="D67" s="6" t="s">
@@ -24062,7 +23937,7 @@
       <c r="B68" s="12">
         <v>4.3</v>
       </c>
-      <c r="C68" s="6">
+      <c r="C68" s="12">
         <v>3170</v>
       </c>
       <c r="D68" s="6" t="s">
@@ -24076,7 +23951,7 @@
       <c r="B69" s="12">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C69" s="6">
+      <c r="C69" s="12">
         <v>1479</v>
       </c>
       <c r="D69" s="6" t="s">
@@ -24090,7 +23965,7 @@
       <c r="B70" s="12">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C70" s="6">
+      <c r="C70" s="12">
         <v>1748</v>
       </c>
       <c r="D70" s="6" t="s">
@@ -24104,7 +23979,7 @@
       <c r="B71" s="12">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C71" s="6">
+      <c r="C71" s="12">
         <v>1942</v>
       </c>
       <c r="D71" s="6" t="s">
@@ -24118,7 +23993,7 @@
       <c r="B72" s="12">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C72" s="6">
+      <c r="C72" s="12">
         <v>2067</v>
       </c>
       <c r="D72" s="6" t="s">
@@ -24132,7 +24007,7 @@
       <c r="B73" s="12">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C73" s="6">
+      <c r="C73" s="12">
         <v>2208</v>
       </c>
       <c r="D73" s="6" t="s">
@@ -24146,7 +24021,7 @@
       <c r="B74" s="12">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C74" s="6">
+      <c r="C74" s="12">
         <v>2426</v>
       </c>
       <c r="D74" s="6" t="s">
@@ -24160,7 +24035,7 @@
       <c r="B75" s="12">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C75" s="6">
+      <c r="C75" s="12">
         <v>2465</v>
       </c>
       <c r="D75" s="6" t="s">
@@ -24174,7 +24049,7 @@
       <c r="B76" s="12">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C76" s="6">
+      <c r="C76" s="12">
         <v>2466</v>
       </c>
       <c r="D76" s="6" t="s">
@@ -24188,7 +24063,7 @@
       <c r="B77" s="12">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C77" s="6">
+      <c r="C77" s="12">
         <v>2880</v>
       </c>
       <c r="D77" s="6" t="s">
@@ -24202,7 +24077,7 @@
       <c r="B78" s="12">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C78" s="6">
+      <c r="C78" s="12">
         <v>3375</v>
       </c>
       <c r="D78" s="6" t="s">
@@ -24216,7 +24091,7 @@
       <c r="B79" s="12">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C79" s="6">
+      <c r="C79" s="12">
         <v>3485</v>
       </c>
       <c r="D79" s="6" t="s">
@@ -24230,7 +24105,7 @@
       <c r="B80" s="12">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C80" s="6">
+      <c r="C80" s="12">
         <v>3486</v>
       </c>
       <c r="D80" s="6" t="s">
@@ -24244,7 +24119,7 @@
       <c r="B81" s="12">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C81" s="6">
+      <c r="C81" s="12">
         <v>3487</v>
       </c>
       <c r="D81" s="6" t="s">
@@ -24258,7 +24133,7 @@
       <c r="B82" s="12">
         <v>5.2</v>
       </c>
-      <c r="C82" s="6">
+      <c r="C82" s="12">
         <v>3101</v>
       </c>
       <c r="D82" s="6" t="s">
@@ -24272,7 +24147,7 @@
       <c r="B83" s="12">
         <v>5.2</v>
       </c>
-      <c r="C83" s="6">
+      <c r="C83" s="12">
         <v>3102</v>
       </c>
       <c r="D83" s="6" t="s">
@@ -24286,7 +24161,7 @@
       <c r="B84" s="12">
         <v>5.2</v>
       </c>
-      <c r="C84" s="6">
+      <c r="C84" s="12">
         <v>3103</v>
       </c>
       <c r="D84" s="6" t="s">
@@ -24300,7 +24175,7 @@
       <c r="B85" s="12">
         <v>5.2</v>
       </c>
-      <c r="C85" s="6">
+      <c r="C85" s="12">
         <v>3104</v>
       </c>
       <c r="D85" s="6" t="s">
@@ -24314,7 +24189,7 @@
       <c r="B86" s="12">
         <v>5.2</v>
       </c>
-      <c r="C86" s="6">
+      <c r="C86" s="12">
         <v>3105</v>
       </c>
       <c r="D86" s="6" t="s">
@@ -24328,7 +24203,7 @@
       <c r="B87" s="12">
         <v>5.2</v>
       </c>
-      <c r="C87" s="6">
+      <c r="C87" s="12">
         <v>3106</v>
       </c>
       <c r="D87" s="6" t="s">
@@ -24342,7 +24217,7 @@
       <c r="B88" s="12">
         <v>5.2</v>
       </c>
-      <c r="C88" s="6">
+      <c r="C88" s="12">
         <v>3107</v>
       </c>
       <c r="D88" s="6" t="s">
@@ -24356,7 +24231,7 @@
       <c r="B89" s="12">
         <v>5.2</v>
       </c>
-      <c r="C89" s="6">
+      <c r="C89" s="12">
         <v>3108</v>
       </c>
       <c r="D89" s="6" t="s">
@@ -24370,7 +24245,7 @@
       <c r="B90" s="12">
         <v>5.2</v>
       </c>
-      <c r="C90" s="6">
+      <c r="C90" s="12">
         <v>3109</v>
       </c>
       <c r="D90" s="6" t="s">
@@ -24384,7 +24259,7 @@
       <c r="B91" s="12">
         <v>5.2</v>
       </c>
-      <c r="C91" s="6">
+      <c r="C91" s="12">
         <v>3110</v>
       </c>
       <c r="D91" s="6" t="s">
@@ -24398,7 +24273,7 @@
       <c r="B92" s="12">
         <v>5.2</v>
       </c>
-      <c r="C92" s="6">
+      <c r="C92" s="12">
         <v>3111</v>
       </c>
       <c r="D92" s="6" t="s">
@@ -24412,7 +24287,7 @@
       <c r="B93" s="12">
         <v>5.2</v>
       </c>
-      <c r="C93" s="6">
+      <c r="C93" s="12">
         <v>3112</v>
       </c>
       <c r="D93" s="6" t="s">
@@ -24426,7 +24301,7 @@
       <c r="B94" s="12">
         <v>5.2</v>
       </c>
-      <c r="C94" s="6">
+      <c r="C94" s="12">
         <v>3113</v>
       </c>
       <c r="D94" s="6" t="s">
@@ -24440,7 +24315,7 @@
       <c r="B95" s="12">
         <v>5.2</v>
       </c>
-      <c r="C95" s="6">
+      <c r="C95" s="12">
         <v>3114</v>
       </c>
       <c r="D95" s="6" t="s">
@@ -24454,7 +24329,7 @@
       <c r="B96" s="12">
         <v>5.2</v>
       </c>
-      <c r="C96" s="6">
+      <c r="C96" s="12">
         <v>3115</v>
       </c>
       <c r="D96" s="6" t="s">
@@ -24468,7 +24343,7 @@
       <c r="B97" s="12">
         <v>5.2</v>
       </c>
-      <c r="C97" s="6">
+      <c r="C97" s="12">
         <v>3116</v>
       </c>
       <c r="D97" s="6" t="s">
@@ -24482,7 +24357,7 @@
       <c r="B98" s="12">
         <v>5.2</v>
       </c>
-      <c r="C98" s="6">
+      <c r="C98" s="12">
         <v>3117</v>
       </c>
       <c r="D98" s="6" t="s">
@@ -24496,7 +24371,7 @@
       <c r="B99" s="12">
         <v>5.2</v>
       </c>
-      <c r="C99" s="6">
+      <c r="C99" s="12">
         <v>3118</v>
       </c>
       <c r="D99" s="6" t="s">
@@ -24510,7 +24385,7 @@
       <c r="B100" s="12">
         <v>5.2</v>
       </c>
-      <c r="C100" s="6">
+      <c r="C100" s="12">
         <v>3119</v>
       </c>
       <c r="D100" s="6" t="s">
@@ -24524,7 +24399,7 @@
       <c r="B101" s="12">
         <v>5.2</v>
       </c>
-      <c r="C101" s="6">
+      <c r="C101" s="12">
         <v>3120</v>
       </c>
       <c r="D101" s="6" t="s">
@@ -24538,7 +24413,7 @@
       <c r="B102" s="12">
         <v>6.1</v>
       </c>
-      <c r="C102" s="6">
+      <c r="C102" s="12">
         <v>1244</v>
       </c>
       <c r="D102" s="6" t="s">
@@ -24552,7 +24427,7 @@
       <c r="B103" s="12">
         <v>6.1</v>
       </c>
-      <c r="C103" s="6">
+      <c r="C103" s="12">
         <v>1649</v>
       </c>
       <c r="D103" s="6" t="s">
@@ -24566,7 +24441,7 @@
       <c r="B104" s="12">
         <v>6.1</v>
       </c>
-      <c r="C104" s="6">
+      <c r="C104" s="12">
         <v>2016</v>
       </c>
       <c r="D104" s="6" t="s">
@@ -24580,7 +24455,7 @@
       <c r="B105" s="12">
         <v>6.1</v>
       </c>
-      <c r="C105" s="6">
+      <c r="C105" s="12">
         <v>3172</v>
       </c>
       <c r="D105" s="6" t="s">
@@ -24594,7 +24469,7 @@
       <c r="B106" s="12">
         <v>6.2</v>
       </c>
-      <c r="C106" s="6"/>
+      <c r="C106" s="12"/>
       <c r="D106" s="6" t="s">
         <v>138</v>
       </c>
@@ -24606,7 +24481,7 @@
       <c r="B107" s="12">
         <v>7</v>
       </c>
-      <c r="C107" s="6"/>
+      <c r="C107" s="12"/>
       <c r="D107" s="6" t="s">
         <v>138</v>
       </c>
@@ -24618,7 +24493,7 @@
       <c r="B108" s="12">
         <v>8</v>
       </c>
-      <c r="C108" s="6">
+      <c r="C108" s="12">
         <v>2031</v>
       </c>
       <c r="D108" s="6" t="s">
@@ -24632,7 +24507,7 @@
       <c r="B109" s="12">
         <v>8</v>
       </c>
-      <c r="C109" s="6">
+      <c r="C109" s="12">
         <v>2032</v>
       </c>
       <c r="D109" s="6" t="s">
@@ -24646,7 +24521,7 @@
       <c r="B110" s="12">
         <v>8</v>
       </c>
-      <c r="C110" s="6">
+      <c r="C110" s="12">
         <v>3145</v>
       </c>
       <c r="D110" s="6" t="s">
@@ -24660,7 +24535,7 @@
       <c r="B111" s="12">
         <v>9</v>
       </c>
-      <c r="C111" s="6">
+      <c r="C111" s="12">
         <v>2071</v>
       </c>
       <c r="D111" s="6" t="s">
@@ -24674,7 +24549,7 @@
       <c r="B112" s="12">
         <v>9</v>
       </c>
-      <c r="C112" s="6">
+      <c r="C112" s="12">
         <v>2211</v>
       </c>
       <c r="D112" s="6" t="s">
@@ -24688,7 +24563,7 @@
       <c r="B113" s="12">
         <v>9</v>
       </c>
-      <c r="C113" s="6">
+      <c r="C113" s="12">
         <v>2212</v>
       </c>
       <c r="D113" s="6" t="s">
@@ -24702,7 +24577,7 @@
       <c r="B114" s="12">
         <v>9</v>
       </c>
-      <c r="C114" s="6">
+      <c r="C114" s="12">
         <v>2216</v>
       </c>
       <c r="D114" s="6" t="s">
@@ -24716,7 +24591,7 @@
       <c r="B115" s="12">
         <v>9</v>
       </c>
-      <c r="C115" s="6">
+      <c r="C115" s="12">
         <v>2315</v>
       </c>
       <c r="D115" s="6" t="s">
@@ -24730,7 +24605,7 @@
       <c r="B116" s="12">
         <v>9</v>
       </c>
-      <c r="C116" s="6">
+      <c r="C116" s="12">
         <v>2590</v>
       </c>
       <c r="D116" s="6" t="s">
@@ -24744,7 +24619,7 @@
       <c r="B117" s="12">
         <v>9</v>
       </c>
-      <c r="C117" s="6">
+      <c r="C117" s="12">
         <v>3077</v>
       </c>
       <c r="D117" s="6" t="s">
@@ -24758,7 +24633,7 @@
       <c r="B118" s="12">
         <v>9</v>
       </c>
-      <c r="C118" s="6">
+      <c r="C118" s="12">
         <v>3082</v>
       </c>
       <c r="D118" s="6" t="s">
@@ -24772,7 +24647,7 @@
       <c r="B119" s="12">
         <v>9</v>
       </c>
-      <c r="C119" s="6">
+      <c r="C119" s="12">
         <v>3090</v>
       </c>
       <c r="D119" s="6" t="s">
@@ -24786,7 +24661,7 @@
       <c r="B120" s="12">
         <v>9</v>
       </c>
-      <c r="C120" s="6">
+      <c r="C120" s="12">
         <v>3091</v>
       </c>
       <c r="D120" s="6" t="s">
@@ -24800,7 +24675,7 @@
       <c r="B121" s="12">
         <v>9</v>
       </c>
-      <c r="C121" s="6">
+      <c r="C121" s="12">
         <v>3151</v>
       </c>
       <c r="D121" s="6" t="s">
@@ -24814,7 +24689,7 @@
       <c r="B122" s="12">
         <v>9</v>
       </c>
-      <c r="C122" s="6">
+      <c r="C122" s="12">
         <v>3152</v>
       </c>
       <c r="D122" s="6" t="s">
@@ -24828,7 +24703,7 @@
       <c r="B123" s="12">
         <v>9</v>
       </c>
-      <c r="C123" s="6">
+      <c r="C123" s="12">
         <v>3166</v>
       </c>
       <c r="D123" s="6" t="s">
@@ -24842,7 +24717,7 @@
       <c r="B124" s="12">
         <v>9</v>
       </c>
-      <c r="C124" s="6">
+      <c r="C124" s="12">
         <v>3171</v>
       </c>
       <c r="D124" s="6" t="s">
@@ -24856,7 +24731,7 @@
       <c r="B125" s="12">
         <v>9</v>
       </c>
-      <c r="C125" s="6">
+      <c r="C125" s="12">
         <v>3245</v>
       </c>
       <c r="D125" s="6" t="s">
@@ -24870,7 +24745,7 @@
       <c r="B126" s="12">
         <v>9</v>
       </c>
-      <c r="C126" s="6">
+      <c r="C126" s="12">
         <v>3257</v>
       </c>
       <c r="D126" s="6" t="s">
@@ -24884,7 +24759,7 @@
       <c r="B127" s="12">
         <v>9</v>
       </c>
-      <c r="C127" s="6">
+      <c r="C127" s="12">
         <v>3314</v>
       </c>
       <c r="D127" s="6" t="s">
@@ -24898,7 +24773,7 @@
       <c r="B128" s="12">
         <v>9</v>
       </c>
-      <c r="C128" s="6">
+      <c r="C128" s="12">
         <v>3480</v>
       </c>
       <c r="D128" s="6" t="s">
@@ -24912,7 +24787,7 @@
       <c r="B129" s="12">
         <v>9</v>
       </c>
-      <c r="C129" s="6">
+      <c r="C129" s="12">
         <v>3481</v>
       </c>
       <c r="D129" s="6" t="s">
@@ -24926,7 +24801,7 @@
       <c r="B130" s="12">
         <v>9</v>
       </c>
-      <c r="C130" s="6">
+      <c r="C130" s="12">
         <v>3536</v>
       </c>
       <c r="D130" s="6" t="s">
@@ -24940,7 +24815,7 @@
       <c r="B131" s="12">
         <v>9</v>
       </c>
-      <c r="C131" s="6">
+      <c r="C131" s="12">
         <v>3556</v>
       </c>
       <c r="D131" s="6" t="s">
@@ -24954,7 +24829,7 @@
       <c r="B132" s="12">
         <v>9</v>
       </c>
-      <c r="C132" s="6">
+      <c r="C132" s="12">
         <v>3557</v>
       </c>
       <c r="D132" s="6" t="s">
@@ -24968,7 +24843,7 @@
       <c r="B133" s="12">
         <v>9</v>
       </c>
-      <c r="C133" s="6">
+      <c r="C133" s="12">
         <v>3558</v>
       </c>
       <c r="D133" s="6" t="s">
@@ -24982,12 +24857,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c3e85fef-df06-4e67-8632-489752715f52" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6fd297-1f65-4950-8fc9-157e29c7b648">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25240,20 +25117,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c3e85fef-df06-4e67-8632-489752715f52" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6fd297-1f65-4950-8fc9-157e29c7b648">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171B3C16-7124-4B98-87E3-5FC6A9D45406}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98411DB4-5541-4967-8DBE-AF3E324DD5F5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c3e85fef-df06-4e67-8632-489752715f52"/>
+    <ds:schemaRef ds:uri="ea6fd297-1f65-4950-8fc9-157e29c7b648"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -25278,12 +25156,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98411DB4-5541-4967-8DBE-AF3E324DD5F5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171B3C16-7124-4B98-87E3-5FC6A9D45406}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c3e85fef-df06-4e67-8632-489752715f52"/>
-    <ds:schemaRef ds:uri="ea6fd297-1f65-4950-8fc9-157e29c7b648"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/dg_list.xlsx
+++ b/dg_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ialasia.sharepoint.com/sites/IALDGDESK/Shared Documents/General/Query System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1176" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43D180FF-C22E-4F12-BFD0-D6DA5514C5A2}"/>
+  <xr:revisionPtr revIDLastSave="1198" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8DDA1DE-8A97-495D-A63A-55EB651F7D28}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="27630" windowHeight="16440" activeTab="4" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3638" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3649" uniqueCount="411">
   <si>
     <t>UN Number</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1326,10 +1326,6 @@
   </si>
   <si>
     <t>Flash point BELOW -18 °C</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>For TSL Booking on TSL Vessel can be loaded in GP, but Partner's booking only be loaded in reefer.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1784,6 +1780,22 @@
  b) Prohibit if origin from China including Hong Kong.
  c) Must be declared as DG.
 2. Calcium hypochlorite, trichloroisocyanuric acid, symclosene, TCCA, and their synonyms are prohibited when declared as Class 9 under UN 3077.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(DG) For TSL Booking on TSL Vessel can be loaded in GP, but Partner's booking only be loaded in reefer.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>These batteries must be declared as DG because there are no Special Provisions (SP) for Non-DG exemption.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2796</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Only Non-DG new battery is acceptable. Prohibited if the batteries are used, damaged, defective or waste.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5432,7 +5444,7 @@
         <v>326</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>257</v>
@@ -13850,49 +13862,49 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>325</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17448,7 +17460,7 @@
         <v>138</v>
       </c>
       <c r="F226" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -19402,7 +19414,7 @@
       </c>
       <c r="E348" s="5"/>
       <c r="F348" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -19500,7 +19512,7 @@
       </c>
       <c r="E354" s="5"/>
       <c r="F354" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
@@ -19537,7 +19549,7 @@
     </row>
     <row r="357" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A357" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B357" s="11">
         <v>9</v>
@@ -19550,13 +19562,13 @@
         <v>138</v>
       </c>
       <c r="F357" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G357" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="H357" s="5" t="s">
         <v>346</v>
-      </c>
-      <c r="H357" s="5" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="358" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19574,13 +19586,13 @@
         <v>138</v>
       </c>
       <c r="F358" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G358" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="H358" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="H358" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
@@ -19598,10 +19610,10 @@
         <v>138</v>
       </c>
       <c r="F359" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H359" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
@@ -19619,13 +19631,13 @@
         <v>138</v>
       </c>
       <c r="F360" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G360" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="H360" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="H360" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
@@ -19643,13 +19655,13 @@
         <v>138</v>
       </c>
       <c r="F361" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G361" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="H361" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="H361" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.25">
@@ -19667,10 +19679,10 @@
         <v>138</v>
       </c>
       <c r="F362" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H362" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
@@ -19688,10 +19700,10 @@
         <v>138</v>
       </c>
       <c r="F363" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H363" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.25">
@@ -19709,10 +19721,10 @@
         <v>138</v>
       </c>
       <c r="F364" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H364" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -19731,7 +19743,7 @@
     <col min="3" max="3" width="11.625" style="15" customWidth="1"/>
     <col min="4" max="5" width="11.625" style="13" customWidth="1"/>
     <col min="6" max="6" width="160.125" style="13" customWidth="1"/>
-    <col min="7" max="7" width="50.625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="85.375" style="13" customWidth="1"/>
     <col min="8" max="8" width="57.75" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="57.125" style="13" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="48.625" style="13" bestFit="1" customWidth="1"/>
@@ -19800,57 +19812,57 @@
     </row>
     <row r="2" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>325</v>
       </c>
       <c r="C2" s="4"/>
       <c r="F2" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B3" s="4">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="1" t="s">
         <v>138</v>
       </c>
@@ -19860,23 +19872,27 @@
         <v>142</v>
       </c>
       <c r="B4" s="4">
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B5" s="4">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="1" t="s">
-        <v>138</v>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="94.5" x14ac:dyDescent="0.25">
@@ -19884,7 +19900,7 @@
         <v>142</v>
       </c>
       <c r="B6" s="4">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="1"/>
@@ -19892,7 +19908,7 @@
         <v>138</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="94.5" x14ac:dyDescent="0.25">
@@ -19900,7 +19916,7 @@
         <v>142</v>
       </c>
       <c r="B7" s="4">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
@@ -19908,7 +19924,7 @@
         <v>138</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="94.5" x14ac:dyDescent="0.25">
@@ -19916,7 +19932,7 @@
         <v>142</v>
       </c>
       <c r="B8" s="4">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
@@ -19924,7 +19940,7 @@
         <v>138</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="94.5" x14ac:dyDescent="0.25">
@@ -19932,10 +19948,11 @@
         <v>142</v>
       </c>
       <c r="B9" s="4">
-        <v>1.6</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+        <v>2.1</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1966</v>
+      </c>
       <c r="E9" s="1" t="s">
         <v>138</v>
       </c>
@@ -19943,7 +19960,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>142</v>
       </c>
@@ -19951,30 +19968,30 @@
         <v>2.1</v>
       </c>
       <c r="C10" s="4">
-        <v>1966</v>
+        <v>1972</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="78.75" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B11" s="4">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="C11" s="4">
-        <v>1972</v>
+        <v>1963</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="94.5" x14ac:dyDescent="0.25">
@@ -19982,49 +19999,49 @@
         <v>142</v>
       </c>
       <c r="B12" s="4">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="C12" s="4">
-        <v>1963</v>
-      </c>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C12" s="4"/>
       <c r="E12" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="94.5" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B13" s="4">
-        <v>2.2999999999999998</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C13" s="4"/>
       <c r="E13" s="1" t="s">
-        <v>138</v>
+        <v>4</v>
       </c>
       <c r="F13" s="14" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B14" s="4">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="E14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="14" t="s">
+      <c r="C14" s="4">
+        <v>3226</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F14" s="13" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>142</v>
       </c>
@@ -20032,13 +20049,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C15" s="4">
-        <v>3226</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>371</v>
+        <v>3531</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="31.5" x14ac:dyDescent="0.25">
@@ -20049,13 +20066,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C16" s="4">
-        <v>3531</v>
+        <v>3532</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -20066,13 +20083,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C17" s="4">
-        <v>3532</v>
+        <v>3533</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -20083,24 +20100,24 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C18" s="4">
-        <v>3533</v>
+        <v>3534</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B19" s="4">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C19" s="4">
-        <v>3534</v>
+        <v>1361</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>138</v>
@@ -20109,7 +20126,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>142</v>
       </c>
@@ -20117,7 +20134,7 @@
         <v>4.2</v>
       </c>
       <c r="C20" s="4">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>138</v>
@@ -20126,7 +20143,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>142</v>
       </c>
@@ -20134,16 +20151,16 @@
         <v>4.2</v>
       </c>
       <c r="C21" s="4">
-        <v>1362</v>
+        <v>1381</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>142</v>
       </c>
@@ -20151,27 +20168,27 @@
         <v>4.2</v>
       </c>
       <c r="C22" s="4">
-        <v>1381</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3341</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B23" s="4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="C23" s="4">
-        <v>3341</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>138</v>
+        <v>1415</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -20182,30 +20199,30 @@
         <v>4.3</v>
       </c>
       <c r="C24" s="4">
-        <v>1415</v>
+        <v>1418</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B25" s="4">
-        <v>4.3</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C25" s="4">
-        <v>1418</v>
+        <v>1479</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>396</v>
+        <v>372</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
@@ -20216,7 +20233,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C26" s="4">
-        <v>1479</v>
+        <v>1748</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>138</v>
@@ -20233,7 +20250,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C27" s="4">
-        <v>1748</v>
+        <v>2208</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>138</v>
@@ -20250,7 +20267,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C28" s="4">
-        <v>2208</v>
+        <v>2880</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>138</v>
@@ -20267,7 +20284,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C29" s="4">
-        <v>2880</v>
+        <v>3485</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>138</v>
@@ -20284,7 +20301,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C30" s="4">
-        <v>3485</v>
+        <v>3486</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>138</v>
@@ -20301,7 +20318,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C31" s="4">
-        <v>3486</v>
+        <v>3487</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>138</v>
@@ -20310,7 +20327,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>142</v>
       </c>
@@ -20318,16 +20335,16 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C32" s="4">
-        <v>3487</v>
+        <v>3378</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="13" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="63" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>142</v>
       </c>
@@ -20335,16 +20352,16 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C33" s="4">
-        <v>3378</v>
+        <v>2014</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="F33" s="14" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>142</v>
       </c>
@@ -20352,45 +20369,45 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C34" s="4">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F34" s="14" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F34" s="13" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B35" s="4">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="C35" s="4">
-        <v>2015</v>
-      </c>
+        <v>5.2</v>
+      </c>
+      <c r="C35" s="4"/>
       <c r="E35" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F35" s="13" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="F35" s="14" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B36" s="4">
         <v>5.2</v>
       </c>
-      <c r="C36" s="4"/>
+      <c r="C36" s="4">
+        <v>3101</v>
+      </c>
       <c r="E36" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -20401,13 +20418,13 @@
         <v>5.2</v>
       </c>
       <c r="C37" s="4">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -20418,13 +20435,13 @@
         <v>5.2</v>
       </c>
       <c r="C38" s="4">
-        <v>3102</v>
+        <v>3103</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -20435,13 +20452,13 @@
         <v>5.2</v>
       </c>
       <c r="C39" s="4">
-        <v>3103</v>
+        <v>3104</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -20452,13 +20469,13 @@
         <v>5.2</v>
       </c>
       <c r="C40" s="4">
-        <v>3104</v>
+        <v>3105</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -20469,13 +20486,13 @@
         <v>5.2</v>
       </c>
       <c r="C41" s="4">
-        <v>3105</v>
+        <v>3106</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -20486,13 +20503,13 @@
         <v>5.2</v>
       </c>
       <c r="C42" s="4">
-        <v>3106</v>
+        <v>3107</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -20503,13 +20520,13 @@
         <v>5.2</v>
       </c>
       <c r="C43" s="4">
-        <v>3107</v>
+        <v>3108</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -20520,13 +20537,13 @@
         <v>5.2</v>
       </c>
       <c r="C44" s="4">
-        <v>3108</v>
+        <v>3109</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -20537,29 +20554,29 @@
         <v>5.2</v>
       </c>
       <c r="C45" s="4">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B46" s="4">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="C46" s="4">
-        <v>3110</v>
+        <v>1649</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F46" s="14" t="s">
+      <c r="F46" s="13" t="s">
         <v>382</v>
       </c>
     </row>
@@ -20571,7 +20588,7 @@
         <v>6.1</v>
       </c>
       <c r="C47" s="4">
-        <v>1649</v>
+        <v>3483</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>138</v>
@@ -20588,54 +20605,54 @@
         <v>6.1</v>
       </c>
       <c r="C48" s="4">
-        <v>3483</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3507</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B49" s="4">
-        <v>6.1</v>
-      </c>
-      <c r="C49" s="4">
-        <v>3507</v>
-      </c>
+        <v>6.2</v>
+      </c>
+      <c r="C49" s="4"/>
       <c r="D49" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B50" s="4">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B51" s="4">
-        <v>7</v>
-      </c>
-      <c r="C51" s="4"/>
-      <c r="D51" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="C51" s="4">
+        <v>2800</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F51" s="14" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>142</v>
       </c>
@@ -20643,16 +20660,19 @@
         <v>8</v>
       </c>
       <c r="C52" s="4">
-        <v>2800</v>
+        <v>2794</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F52" s="14" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F52" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="G52" s="14" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>142</v>
       </c>
@@ -20660,33 +20680,37 @@
         <v>8</v>
       </c>
       <c r="C53" s="4">
-        <v>2794</v>
+        <v>2795</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F53" s="14" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F53" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="G53" s="14" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B54" s="4">
         <v>8</v>
       </c>
-      <c r="C54" s="4">
-        <v>2795</v>
+      <c r="C54" s="4" t="s">
+        <v>409</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F54" s="14" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F54" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="G54" s="14"/>
+    </row>
+    <row r="55" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>142</v>
       </c>
@@ -20699,11 +20723,14 @@
       <c r="E55" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F55" s="14" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="F55" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="G55" s="14" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>142</v>
       </c>
@@ -20717,10 +20744,10 @@
         <v>4</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>142</v>
       </c>
@@ -20734,10 +20761,10 @@
         <v>138</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>142</v>
       </c>
@@ -20751,10 +20778,10 @@
         <v>138</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>142</v>
       </c>
@@ -20768,7 +20795,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>142</v>
       </c>
@@ -20782,7 +20809,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>142</v>
       </c>
@@ -20796,7 +20823,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>142</v>
       </c>
@@ -20810,7 +20837,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>142</v>
       </c>
@@ -20824,7 +20851,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>142</v>
       </c>
@@ -20838,7 +20865,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="63" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>142</v>
       </c>
@@ -20851,11 +20878,14 @@
       <c r="E65" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F65" s="14" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F65" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="G65" s="14" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="63" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>142</v>
       </c>
@@ -20868,11 +20898,14 @@
       <c r="E66" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F66" s="14" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F66" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="G66" s="14" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="63" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>142</v>
       </c>
@@ -20885,11 +20918,14 @@
       <c r="E67" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F67" s="14" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F67" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="G67" s="14" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="63" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>142</v>
       </c>
@@ -20902,8 +20938,11 @@
       <c r="E68" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F68" s="14" t="s">
-        <v>401</v>
+      <c r="F68" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="G68" s="14" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="126" x14ac:dyDescent="0.25">
@@ -20920,7 +20959,7 @@
         <v>138</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
@@ -20937,10 +20976,10 @@
         <v>138</v>
       </c>
       <c r="F70" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="G70" s="14" t="s">
         <v>387</v>
-      </c>
-      <c r="G70" s="14" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
@@ -20957,10 +20996,10 @@
         <v>138</v>
       </c>
       <c r="F71" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="G71" s="14" t="s">
         <v>387</v>
-      </c>
-      <c r="G71" s="14" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
@@ -20977,10 +21016,10 @@
         <v>138</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>142</v>
       </c>
@@ -20993,11 +21032,14 @@
       <c r="E73" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F73" s="14" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F73" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="G73" s="14" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>142</v>
       </c>
@@ -21010,8 +21052,11 @@
       <c r="E74" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F74" s="14" t="s">
-        <v>405</v>
+      <c r="F74" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="G74" s="14" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
@@ -21028,10 +21073,10 @@
         <v>138</v>
       </c>
       <c r="F75" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="G75" s="14" t="s">
         <v>389</v>
-      </c>
-      <c r="G75" s="14" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
@@ -21048,7 +21093,7 @@
         <v>138</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
@@ -21065,7 +21110,7 @@
         <v>138</v>
       </c>
       <c r="F77" s="14" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
@@ -21082,7 +21127,7 @@
         <v>138</v>
       </c>
       <c r="F78" s="14" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -24857,14 +24902,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c3e85fef-df06-4e67-8632-489752715f52" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6fd297-1f65-4950-8fc9-157e29c7b648">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25117,21 +25160,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c3e85fef-df06-4e67-8632-489752715f52" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6fd297-1f65-4950-8fc9-157e29c7b648">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98411DB4-5541-4967-8DBE-AF3E324DD5F5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171B3C16-7124-4B98-87E3-5FC6A9D45406}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c3e85fef-df06-4e67-8632-489752715f52"/>
-    <ds:schemaRef ds:uri="ea6fd297-1f65-4950-8fc9-157e29c7b648"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -25156,9 +25198,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171B3C16-7124-4B98-87E3-5FC6A9D45406}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98411DB4-5541-4967-8DBE-AF3E324DD5F5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c3e85fef-df06-4e67-8632-489752715f52"/>
+    <ds:schemaRef ds:uri="ea6fd297-1f65-4950-8fc9-157e29c7b648"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/dg_list.xlsx
+++ b/dg_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ialasia.sharepoint.com/sites/IALDGDESK/Shared Documents/General/Query System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1769" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A6C8FDA-5A6F-4EEE-8049-0DAC40C7C49F}"/>
+  <xr:revisionPtr revIDLastSave="1827" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1595601-2CF2-4067-AF01-43D2E55D366E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
   </bookViews>
@@ -27,6 +27,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
     </ext>
@@ -35,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4338" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4370" uniqueCount="490">
   <si>
     <t>UN Number</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2209,6 +2220,65 @@
   <si>
     <t>4.1</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DG requires Temperature controlled by IMDG Code - Prohibited.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DG in container as Bulk or F/R , O/T cntr. - Prohibited.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heated Tank Container. - Prohibited.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The commodities are consisted of 'Wastes' - Prohibited.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DG in reefer container - All Prohibited.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DG to be prohibited handling at loading/discharging port as per local regulations.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All items which defined as SP(Special Provision) 900, 349, 350, 351, 352 and 353 in IMDG Code : Prohibited.
+- AMMONIUM HYPOCHLORITE
+- AMMONIUM NITRATE liable to self-heating sufficient to initiate decomposition
+- AMMONIUM NITRITES and mixtures of an inorganic nitrite with an ammonium salt
+- CHLORIC ACID, AQUEOUS SOLUTION with more than 10% chloric acid
+- ETHYL NITRITE pure
+- HYDROCYANIC ACID, AQUEOUS SOLUTION (HYDROGEN CYANIDE, AQUEOUS SOLUTION) with more than 20% hydrogen cyanide
+- HYDROGEN CHLORIDE, REFRIGERATED LIQUID
+- HYDROGEN CYANIDE SOLUTION, IN ALCOHOL with more than 45% hydrogen cyanide
+- MERCURY OXYCYANIDE pure
+- METHYL NITRITE
+- PERCHLORIC ACID with more than 72% acid, by mass
+- SILVER PICRATE, dry or wetted with less than 30% water by mass
+- ZINC AMMONIUM NITRITE
+- AMMONIUM BROMATE / - AMMONIUM BROMATE, SOLUTION
+- AMMONIUM CHLORATE / - AMMONIUM CHLORATE, SOLUTION
+- AMMONIUM CHLORITE / AMMONIUM CHLORITE, SOLUTION
+- AMMONIUM PERMANGANATE / - AMMONIUM PERMANGANATE, SOLUTION</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TECHNICAL NAME ( CYANAMIDE / DIVINYLBENZENE / CALCIUM HYPOCHLORITE ) : Prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALL USED &amp; WASTE BATTERY(Including Defective Battery) : Prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remark 2</t>
+  </si>
+  <si>
+    <t>Remark 3</t>
   </si>
 </sst>
 </file>
@@ -24109,7 +24179,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E642A48D-70EB-4782-A5B4-13453C27730A}">
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:AW197"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.625" style="1" bestFit="1" customWidth="1"/>
@@ -24118,11 +24188,17 @@
     <col min="4" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="83.25" style="25" customWidth="1"/>
-    <col min="7" max="7" width="105.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="7" max="9" width="105.375" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.125" style="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="67.375" style="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="131.375" style="25" customWidth="1"/>
+    <col min="13" max="22" width="9" style="25"/>
+    <col min="23" max="23" width="65" style="25" bestFit="1" customWidth="1"/>
+    <col min="24" max="49" width="9" style="25"/>
+    <col min="50" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>2</v>
       </c>
@@ -24141,119 +24217,220 @@
       <c r="F1" s="11" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="G1" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>489</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="T1" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="U1" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="V1" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="W1" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1"/>
+      <c r="AR1" s="1"/>
+      <c r="AS1" s="1"/>
+      <c r="AT1" s="1"/>
+      <c r="AU1" s="1"/>
+      <c r="AV1" s="1"/>
+      <c r="AW1" s="1"/>
+    </row>
+    <row r="2" spans="1:49" ht="299.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
         <v>463</v>
       </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="28" t="s">
+        <v>479</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>480</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>481</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>482</v>
+      </c>
+      <c r="J2" s="25" t="s">
+        <v>483</v>
+      </c>
+      <c r="K2" s="25" t="s">
+        <v>484</v>
+      </c>
+      <c r="L2" s="26" t="s">
+        <v>485</v>
+      </c>
+      <c r="M2" s="25" t="s">
+        <v>486</v>
+      </c>
+      <c r="W2" s="25" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="3" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>463</v>
       </c>
       <c r="B3" s="4">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>463</v>
       </c>
       <c r="B4" s="4">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>463</v>
       </c>
       <c r="B5" s="4">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>463</v>
       </c>
       <c r="B6" s="4">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>463</v>
       </c>
       <c r="B7" s="4">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>463</v>
       </c>
       <c r="B8" s="4">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1010</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>465</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B10" s="1">
-        <v>2.1</v>
+      <c r="B10" s="4" t="s">
+        <v>472</v>
       </c>
       <c r="C10" s="1">
-        <v>1030</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1010</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>463</v>
       </c>
@@ -24261,13 +24438,13 @@
         <v>2.1</v>
       </c>
       <c r="C11" s="1">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>463</v>
       </c>
@@ -24275,13 +24452,13 @@
         <v>2.1</v>
       </c>
       <c r="C12" s="1">
-        <v>1039</v>
+        <v>1032</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>463</v>
       </c>
@@ -24289,33 +24466,27 @@
         <v>2.1</v>
       </c>
       <c r="C13" s="1">
-        <v>1057</v>
+        <v>1039</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>472</v>
+      <c r="B14" s="1">
+        <v>2.1</v>
       </c>
       <c r="C14" s="1">
-        <v>1060</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>465</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1057</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>463</v>
       </c>
@@ -24323,7 +24494,7 @@
         <v>472</v>
       </c>
       <c r="C15" s="1">
-        <v>1081</v>
+        <v>1060</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>4</v>
@@ -24331,11 +24502,11 @@
       <c r="F15" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="25" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>463</v>
       </c>
@@ -24343,7 +24514,7 @@
         <v>472</v>
       </c>
       <c r="C16" s="1">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>4</v>
@@ -24351,7 +24522,7 @@
       <c r="F16" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24363,7 +24534,7 @@
         <v>472</v>
       </c>
       <c r="C17" s="1">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>4</v>
@@ -24371,7 +24542,7 @@
       <c r="F17" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24383,7 +24554,7 @@
         <v>472</v>
       </c>
       <c r="C18" s="1">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>4</v>
@@ -24391,7 +24562,7 @@
       <c r="F18" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24403,7 +24574,7 @@
         <v>472</v>
       </c>
       <c r="C19" s="1">
-        <v>1860</v>
+        <v>1087</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>4</v>
@@ -24411,7 +24582,7 @@
       <c r="F19" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24419,82 +24590,88 @@
       <c r="A20" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B20" s="1">
-        <v>2.1</v>
+      <c r="B20" s="4" t="s">
+        <v>472</v>
       </c>
       <c r="C20" s="1">
-        <v>1966</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>4</v>
+        <v>1860</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="G20" s="25" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>472</v>
+      <c r="B21" s="1">
+        <v>2.1</v>
       </c>
       <c r="C21" s="1">
-        <v>2200</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="25" t="s">
-        <v>465</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>473</v>
+        <v>1966</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B22" s="1">
-        <v>2.1</v>
+      <c r="B22" s="4" t="s">
+        <v>472</v>
       </c>
       <c r="C22" s="1">
-        <v>2203</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>4</v>
+        <v>2200</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="G22" s="25" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>472</v>
+      <c r="B23" s="1">
+        <v>2.1</v>
       </c>
       <c r="C23" s="1">
-        <v>2452</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F23" s="25" t="s">
-        <v>465</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>473</v>
+        <v>2203</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B24" s="1">
-        <v>2.1</v>
+      <c r="B24" s="4" t="s">
+        <v>472</v>
       </c>
       <c r="C24" s="1">
-        <v>3138</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>4</v>
+        <v>2452</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="G24" s="25" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -24505,7 +24682,7 @@
         <v>2.1</v>
       </c>
       <c r="C25" s="1">
-        <v>3252</v>
+        <v>3138</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>4</v>
@@ -24519,7 +24696,7 @@
         <v>2.1</v>
       </c>
       <c r="C26" s="1">
-        <v>3553</v>
+        <v>3252</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>4</v>
@@ -24530,10 +24707,10 @@
         <v>463</v>
       </c>
       <c r="B27" s="1">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
       <c r="C27" s="1">
-        <v>2455</v>
+        <v>3553</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>4</v>
@@ -24544,10 +24721,10 @@
         <v>463</v>
       </c>
       <c r="B28" s="1">
-        <v>2.2999999999999998</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="C28" s="1">
-        <v>1067</v>
+        <v>2455</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>4</v>
@@ -24557,20 +24734,14 @@
       <c r="A29" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>475</v>
+      <c r="B29" s="1">
+        <v>2.2999999999999998</v>
       </c>
       <c r="C29" s="1">
-        <v>1082</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" s="25" t="s">
-        <v>465</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>473</v>
+        <v>1067</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -24581,7 +24752,7 @@
         <v>475</v>
       </c>
       <c r="C30" s="1">
-        <v>1589</v>
+        <v>1082</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>4</v>
@@ -24589,7 +24760,7 @@
       <c r="F30" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24597,14 +24768,20 @@
       <c r="A31" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B31" s="1">
-        <v>2.2999999999999998</v>
+      <c r="B31" s="4" t="s">
+        <v>475</v>
       </c>
       <c r="C31" s="1">
-        <v>2186</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>4</v>
+        <v>1589</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F31" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="G31" s="25" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -24615,7 +24792,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C32" s="1">
-        <v>2188</v>
+        <v>2186</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>4</v>
@@ -24629,7 +24806,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C33" s="1">
-        <v>2534</v>
+        <v>2188</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>4</v>
@@ -24639,54 +24816,48 @@
       <c r="A34" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>476</v>
+      <c r="B34" s="1">
+        <v>2.2999999999999998</v>
       </c>
       <c r="C34" s="1">
-        <v>1093</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F34" s="25" t="s">
-        <v>465</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>473</v>
+        <v>2534</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B35" s="1">
-        <v>3</v>
+      <c r="B35" s="4" t="s">
+        <v>476</v>
       </c>
       <c r="C35" s="1">
-        <v>1131</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>4</v>
+        <v>1093</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="G35" s="25" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>476</v>
+      <c r="B36" s="1">
+        <v>3</v>
       </c>
       <c r="C36" s="1">
-        <v>1167</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F36" s="25" t="s">
-        <v>465</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>473</v>
+        <v>1131</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -24697,7 +24868,7 @@
         <v>476</v>
       </c>
       <c r="C37" s="1">
-        <v>1218</v>
+        <v>1167</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>4</v>
@@ -24705,7 +24876,7 @@
       <c r="F37" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24717,7 +24888,7 @@
         <v>476</v>
       </c>
       <c r="C38" s="1">
-        <v>1246</v>
+        <v>1218</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>4</v>
@@ -24725,7 +24896,7 @@
       <c r="F38" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24737,7 +24908,7 @@
         <v>476</v>
       </c>
       <c r="C39" s="1">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>4</v>
@@ -24745,7 +24916,7 @@
       <c r="F39" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24757,7 +24928,7 @@
         <v>476</v>
       </c>
       <c r="C40" s="1">
-        <v>1301</v>
+        <v>1247</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>4</v>
@@ -24765,7 +24936,7 @@
       <c r="F40" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24777,7 +24948,7 @@
         <v>476</v>
       </c>
       <c r="C41" s="1">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>4</v>
@@ -24785,7 +24956,7 @@
       <c r="F41" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24797,7 +24968,7 @@
         <v>476</v>
       </c>
       <c r="C42" s="1">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>4</v>
@@ -24805,7 +24976,7 @@
       <c r="F42" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24817,7 +24988,7 @@
         <v>476</v>
       </c>
       <c r="C43" s="1">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>4</v>
@@ -24825,7 +24996,7 @@
       <c r="F43" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24837,7 +25008,7 @@
         <v>476</v>
       </c>
       <c r="C44" s="1">
-        <v>1917</v>
+        <v>1304</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>4</v>
@@ -24845,7 +25016,7 @@
       <c r="F44" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24857,7 +25028,7 @@
         <v>476</v>
       </c>
       <c r="C45" s="1">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>4</v>
@@ -24865,7 +25036,7 @@
       <c r="F45" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24877,7 +25048,7 @@
         <v>476</v>
       </c>
       <c r="C46" s="1">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>4</v>
@@ -24885,7 +25056,7 @@
       <c r="F46" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24897,7 +25068,7 @@
         <v>476</v>
       </c>
       <c r="C47" s="1">
-        <v>1991</v>
+        <v>1921</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>4</v>
@@ -24905,7 +25076,7 @@
       <c r="F47" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24917,7 +25088,7 @@
         <v>476</v>
       </c>
       <c r="C48" s="1">
-        <v>2055</v>
+        <v>1991</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>4</v>
@@ -24925,7 +25096,7 @@
       <c r="F48" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24937,7 +25108,7 @@
         <v>476</v>
       </c>
       <c r="C49" s="1">
-        <v>2227</v>
+        <v>2055</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>4</v>
@@ -24945,7 +25116,7 @@
       <c r="F49" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24957,7 +25128,7 @@
         <v>476</v>
       </c>
       <c r="C50" s="1">
-        <v>2251</v>
+        <v>2227</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>4</v>
@@ -24965,7 +25136,7 @@
       <c r="F50" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G50" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24977,7 +25148,7 @@
         <v>476</v>
       </c>
       <c r="C51" s="1">
-        <v>2277</v>
+        <v>2251</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>4</v>
@@ -24985,7 +25156,7 @@
       <c r="F51" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -24997,7 +25168,7 @@
         <v>476</v>
       </c>
       <c r="C52" s="1">
-        <v>2283</v>
+        <v>2277</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>4</v>
@@ -25005,7 +25176,7 @@
       <c r="F52" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="G52" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -25017,7 +25188,7 @@
         <v>476</v>
       </c>
       <c r="C53" s="1">
-        <v>2348</v>
+        <v>2283</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>4</v>
@@ -25025,7 +25196,7 @@
       <c r="F53" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="G53" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -25037,7 +25208,7 @@
         <v>476</v>
       </c>
       <c r="C54" s="1">
-        <v>2352</v>
+        <v>2348</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>4</v>
@@ -25045,7 +25216,7 @@
       <c r="F54" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="G54" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -25057,7 +25228,7 @@
         <v>476</v>
       </c>
       <c r="C55" s="1">
-        <v>2396</v>
+        <v>2352</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>4</v>
@@ -25065,7 +25236,7 @@
       <c r="F55" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="G55" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -25077,7 +25248,7 @@
         <v>476</v>
       </c>
       <c r="C56" s="1">
-        <v>2527</v>
+        <v>2396</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>4</v>
@@ -25085,7 +25256,7 @@
       <c r="F56" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="G56" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -25097,7 +25268,7 @@
         <v>476</v>
       </c>
       <c r="C57" s="1">
-        <v>2607</v>
+        <v>2527</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>4</v>
@@ -25105,7 +25276,7 @@
       <c r="F57" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="G57" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -25117,7 +25288,7 @@
         <v>476</v>
       </c>
       <c r="C58" s="1">
-        <v>2618</v>
+        <v>2607</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>4</v>
@@ -25125,7 +25296,7 @@
       <c r="F58" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="G58" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -25137,7 +25308,7 @@
         <v>476</v>
       </c>
       <c r="C59" s="1">
-        <v>2838</v>
+        <v>2618</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>4</v>
@@ -25145,7 +25316,7 @@
       <c r="F59" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="G59" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -25157,7 +25328,7 @@
         <v>476</v>
       </c>
       <c r="C60" s="1">
-        <v>3022</v>
+        <v>2838</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>4</v>
@@ -25165,7 +25336,7 @@
       <c r="F60" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G60" s="1" t="s">
+      <c r="G60" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -25173,14 +25344,20 @@
       <c r="A61" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B61" s="1">
-        <v>3</v>
+      <c r="B61" s="4" t="s">
+        <v>476</v>
       </c>
       <c r="C61" s="1">
-        <v>3064</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>4</v>
+        <v>3022</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F61" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="G61" s="25" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -25191,7 +25368,7 @@
         <v>3</v>
       </c>
       <c r="C62" s="1">
-        <v>3269</v>
+        <v>3064</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>4</v>
@@ -25202,10 +25379,10 @@
         <v>463</v>
       </c>
       <c r="B63" s="1">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C63" s="1">
-        <v>1336</v>
+        <v>3269</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>4</v>
@@ -25219,7 +25396,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C64" s="1">
-        <v>2956</v>
+        <v>1336</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>4</v>
@@ -25233,7 +25410,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C65" s="1">
-        <v>3097</v>
+        <v>2956</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>4</v>
@@ -25247,7 +25424,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C66" s="1">
-        <v>3221</v>
+        <v>3097</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>4</v>
@@ -25261,7 +25438,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C67" s="1">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>4</v>
@@ -25275,13 +25452,10 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C68" s="1">
-        <v>3223</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F68" s="25" t="s">
-        <v>465</v>
+        <v>3222</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -25292,7 +25466,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C69" s="1">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>4</v>
@@ -25309,13 +25483,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C70" s="1">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F70" s="25" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -25326,7 +25500,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C71" s="1">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>4</v>
@@ -25343,7 +25517,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C72" s="1">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>4</v>
@@ -25360,7 +25534,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C73" s="1">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>4</v>
@@ -25377,7 +25551,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C74" s="1">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>4</v>
@@ -25394,7 +25568,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C75" s="1">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>4</v>
@@ -25411,10 +25585,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C76" s="1">
-        <v>3231</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>4</v>
+        <v>3230</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F76" s="25" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -25425,7 +25602,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C77" s="1">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>4</v>
@@ -25439,7 +25616,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C78" s="1">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>4</v>
@@ -25453,7 +25630,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C79" s="1">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>4</v>
@@ -25467,7 +25644,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C80" s="1">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>4</v>
@@ -25481,7 +25658,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C81" s="1">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>4</v>
@@ -25495,7 +25672,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C82" s="1">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>4</v>
@@ -25509,7 +25686,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C83" s="1">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>4</v>
@@ -25523,7 +25700,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C84" s="1">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>4</v>
@@ -25537,7 +25714,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C85" s="1">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>4</v>
@@ -25547,20 +25724,14 @@
       <c r="A86" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B86" s="4" t="s">
-        <v>478</v>
+      <c r="B86" s="1">
+        <v>4.0999999999999996</v>
       </c>
       <c r="C86" s="1">
-        <v>3531</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F86" s="25" t="s">
-        <v>465</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>473</v>
+        <v>3240</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -25571,7 +25742,7 @@
         <v>478</v>
       </c>
       <c r="C87" s="1">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>4</v>
@@ -25579,7 +25750,7 @@
       <c r="F87" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G87" s="1" t="s">
+      <c r="G87" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -25587,14 +25758,20 @@
       <c r="A88" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B88" s="1">
-        <v>4.0999999999999996</v>
+      <c r="B88" s="4" t="s">
+        <v>478</v>
       </c>
       <c r="C88" s="1">
-        <v>3533</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>4</v>
+        <v>3532</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F88" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="G88" s="25" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -25605,7 +25782,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C89" s="1">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>4</v>
@@ -25616,16 +25793,13 @@
         <v>463</v>
       </c>
       <c r="B90" s="1">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C90" s="1">
-        <v>1361</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F90" s="25" t="s">
-        <v>466</v>
+        <v>3534</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -25636,7 +25810,7 @@
         <v>4.2</v>
       </c>
       <c r="C91" s="1">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>4</v>
@@ -25653,10 +25827,13 @@
         <v>4.2</v>
       </c>
       <c r="C92" s="1">
-        <v>1364</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>4</v>
+        <v>1362</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F92" s="25" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -25667,7 +25844,7 @@
         <v>4.2</v>
       </c>
       <c r="C93" s="1">
-        <v>1374</v>
+        <v>1364</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>4</v>
@@ -25681,7 +25858,7 @@
         <v>4.2</v>
       </c>
       <c r="C94" s="1">
-        <v>1381</v>
+        <v>1374</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>4</v>
@@ -25695,7 +25872,7 @@
         <v>4.2</v>
       </c>
       <c r="C95" s="1">
-        <v>1387</v>
+        <v>1381</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>4</v>
@@ -25709,7 +25886,7 @@
         <v>4.2</v>
       </c>
       <c r="C96" s="1">
-        <v>1857</v>
+        <v>1387</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>4</v>
@@ -25723,7 +25900,7 @@
         <v>4.2</v>
       </c>
       <c r="C97" s="1">
-        <v>2845</v>
+        <v>1857</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>4</v>
@@ -25737,7 +25914,7 @@
         <v>4.2</v>
       </c>
       <c r="C98" s="1">
-        <v>3127</v>
+        <v>2845</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>4</v>
@@ -25751,7 +25928,7 @@
         <v>4.2</v>
       </c>
       <c r="C99" s="1">
-        <v>3194</v>
+        <v>3127</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>4</v>
@@ -25765,7 +25942,7 @@
         <v>4.2</v>
       </c>
       <c r="C100" s="1">
-        <v>3255</v>
+        <v>3194</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>4</v>
@@ -25779,7 +25956,7 @@
         <v>4.2</v>
       </c>
       <c r="C101" s="1">
-        <v>3341</v>
+        <v>3255</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>4</v>
@@ -25793,7 +25970,7 @@
         <v>4.2</v>
       </c>
       <c r="C102" s="1">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>4</v>
@@ -25807,7 +25984,7 @@
         <v>4.2</v>
       </c>
       <c r="C103" s="1">
-        <v>3392</v>
+        <v>3342</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>4</v>
@@ -25821,7 +25998,7 @@
         <v>4.2</v>
       </c>
       <c r="C104" s="1">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>4</v>
@@ -25835,7 +26012,7 @@
         <v>4.2</v>
       </c>
       <c r="C105" s="1">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>4</v>
@@ -25846,10 +26023,10 @@
         <v>463</v>
       </c>
       <c r="B106" s="1">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="C106" s="1">
-        <v>1295</v>
+        <v>3394</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>4</v>
@@ -25863,7 +26040,7 @@
         <v>4.3</v>
       </c>
       <c r="C107" s="1">
-        <v>1395</v>
+        <v>1295</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>4</v>
@@ -25877,7 +26054,7 @@
         <v>4.3</v>
       </c>
       <c r="C108" s="1">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>4</v>
@@ -25891,7 +26068,7 @@
         <v>4.3</v>
       </c>
       <c r="C109" s="1">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>4</v>
@@ -25905,7 +26082,7 @@
         <v>4.3</v>
       </c>
       <c r="C110" s="1">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>4</v>
@@ -25919,7 +26096,7 @@
         <v>4.3</v>
       </c>
       <c r="C111" s="1">
-        <v>1408</v>
+        <v>1402</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>4</v>
@@ -25933,7 +26110,7 @@
         <v>4.3</v>
       </c>
       <c r="C112" s="1">
-        <v>1415</v>
+        <v>1408</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>4</v>
@@ -25947,7 +26124,7 @@
         <v>4.3</v>
       </c>
       <c r="C113" s="1">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>4</v>
@@ -25961,7 +26138,7 @@
         <v>4.3</v>
       </c>
       <c r="C114" s="1">
-        <v>3133</v>
+        <v>1418</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>4</v>
@@ -25972,13 +26149,13 @@
         <v>463</v>
       </c>
       <c r="B115" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F115" s="25" t="s">
-        <v>467</v>
+        <v>4.3</v>
+      </c>
+      <c r="C115" s="1">
+        <v>3133</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -25988,11 +26165,11 @@
       <c r="B116" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C116" s="1">
-        <v>1442</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>4</v>
+      <c r="E116" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F116" s="25" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -26003,7 +26180,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C117" s="1">
-        <v>1479</v>
+        <v>1442</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>4</v>
@@ -26017,7 +26194,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C118" s="1">
-        <v>1502</v>
+        <v>1479</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>4</v>
@@ -26031,7 +26208,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C119" s="1">
-        <v>1512</v>
+        <v>1502</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>4</v>
@@ -26045,7 +26222,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C120" s="1">
-        <v>1748</v>
+        <v>1512</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>4</v>
@@ -26059,7 +26236,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C121" s="1">
-        <v>1942</v>
+        <v>1748</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>4</v>
@@ -26073,7 +26250,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C122" s="1">
-        <v>2067</v>
+        <v>1942</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>4</v>
@@ -26087,7 +26264,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C123" s="1">
-        <v>2208</v>
+        <v>2067</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>4</v>
@@ -26101,7 +26278,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C124" s="1">
-        <v>2426</v>
+        <v>2208</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>4</v>
@@ -26115,7 +26292,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C125" s="1">
-        <v>2880</v>
+        <v>2426</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>4</v>
@@ -26129,7 +26306,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C126" s="1">
-        <v>3100</v>
+        <v>2880</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>4</v>
@@ -26143,7 +26320,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C127" s="1">
-        <v>3121</v>
+        <v>3100</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>4</v>
@@ -26157,7 +26334,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C128" s="1">
-        <v>3137</v>
+        <v>3121</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>4</v>
@@ -26171,7 +26348,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C129" s="1">
-        <v>3212</v>
+        <v>3137</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>4</v>
@@ -26185,7 +26362,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C130" s="1">
-        <v>3375</v>
+        <v>3212</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>4</v>
@@ -26199,7 +26376,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C131" s="1">
-        <v>3377</v>
+        <v>3375</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>4</v>
@@ -26213,7 +26390,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C132" s="1">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>4</v>
@@ -26227,7 +26404,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C133" s="1">
-        <v>3485</v>
+        <v>3378</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>4</v>
@@ -26241,7 +26418,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C134" s="1">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>4</v>
@@ -26255,7 +26432,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C135" s="1">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>4</v>
@@ -26266,10 +26443,10 @@
         <v>463</v>
       </c>
       <c r="B136" s="1">
-        <v>5.2</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C136" s="1">
-        <v>3101</v>
+        <v>3487</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>4</v>
@@ -26283,7 +26460,7 @@
         <v>5.2</v>
       </c>
       <c r="C137" s="1">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>4</v>
@@ -26297,7 +26474,7 @@
         <v>5.2</v>
       </c>
       <c r="C138" s="1">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>4</v>
@@ -26311,7 +26488,7 @@
         <v>5.2</v>
       </c>
       <c r="C139" s="1">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>4</v>
@@ -26325,7 +26502,7 @@
         <v>5.2</v>
       </c>
       <c r="C140" s="1">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>4</v>
@@ -26339,7 +26516,7 @@
         <v>5.2</v>
       </c>
       <c r="C141" s="1">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>4</v>
@@ -26353,7 +26530,7 @@
         <v>5.2</v>
       </c>
       <c r="C142" s="1">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>4</v>
@@ -26367,7 +26544,7 @@
         <v>5.2</v>
       </c>
       <c r="C143" s="1">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>4</v>
@@ -26381,7 +26558,7 @@
         <v>5.2</v>
       </c>
       <c r="C144" s="1">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>4</v>
@@ -26395,7 +26572,7 @@
         <v>5.2</v>
       </c>
       <c r="C145" s="1">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>4</v>
@@ -26409,7 +26586,7 @@
         <v>5.2</v>
       </c>
       <c r="C146" s="1">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>4</v>
@@ -26423,7 +26600,7 @@
         <v>5.2</v>
       </c>
       <c r="C147" s="1">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>4</v>
@@ -26437,7 +26614,7 @@
         <v>5.2</v>
       </c>
       <c r="C148" s="1">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>4</v>
@@ -26451,7 +26628,7 @@
         <v>5.2</v>
       </c>
       <c r="C149" s="1">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>4</v>
@@ -26465,7 +26642,7 @@
         <v>5.2</v>
       </c>
       <c r="C150" s="1">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>4</v>
@@ -26479,7 +26656,7 @@
         <v>5.2</v>
       </c>
       <c r="C151" s="1">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>4</v>
@@ -26493,7 +26670,7 @@
         <v>5.2</v>
       </c>
       <c r="C152" s="1">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>4</v>
@@ -26507,7 +26684,7 @@
         <v>5.2</v>
       </c>
       <c r="C153" s="1">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>4</v>
@@ -26521,7 +26698,7 @@
         <v>5.2</v>
       </c>
       <c r="C154" s="1">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>4</v>
@@ -26535,7 +26712,7 @@
         <v>5.2</v>
       </c>
       <c r="C155" s="1">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>4</v>
@@ -26545,20 +26722,14 @@
       <c r="A156" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B156" s="4" t="s">
-        <v>474</v>
+      <c r="B156" s="1">
+        <v>5.2</v>
       </c>
       <c r="C156" s="1">
-        <v>1051</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F156" s="25" t="s">
-        <v>465</v>
-      </c>
-      <c r="G156" s="1" t="s">
-        <v>473</v>
+        <v>3120</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -26569,7 +26740,7 @@
         <v>474</v>
       </c>
       <c r="C157" s="1">
-        <v>1092</v>
+        <v>1051</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>4</v>
@@ -26577,7 +26748,7 @@
       <c r="F157" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G157" s="1" t="s">
+      <c r="G157" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -26589,7 +26760,7 @@
         <v>474</v>
       </c>
       <c r="C158" s="1">
-        <v>1143</v>
+        <v>1092</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>4</v>
@@ -26597,7 +26768,7 @@
       <c r="F158" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G158" s="1" t="s">
+      <c r="G158" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -26609,7 +26780,7 @@
         <v>474</v>
       </c>
       <c r="C159" s="1">
-        <v>1185</v>
+        <v>1143</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>4</v>
@@ -26617,7 +26788,7 @@
       <c r="F159" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G159" s="1" t="s">
+      <c r="G159" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -26625,68 +26796,68 @@
       <c r="A160" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B160" s="1">
-        <v>6.1</v>
+      <c r="B160" s="4" t="s">
+        <v>474</v>
       </c>
       <c r="C160" s="1">
-        <v>1244</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>4</v>
+        <v>1185</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F160" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="G160" s="25" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B161" s="4" t="s">
-        <v>474</v>
+      <c r="B161" s="1">
+        <v>6.1</v>
       </c>
       <c r="C161" s="1">
-        <v>1251</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F161" s="25" t="s">
-        <v>465</v>
-      </c>
-      <c r="G161" s="1" t="s">
-        <v>473</v>
+        <v>1244</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B162" s="1">
-        <v>6.1</v>
+      <c r="B162" s="4" t="s">
+        <v>474</v>
       </c>
       <c r="C162" s="1">
-        <v>1259</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>4</v>
+        <v>1251</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F162" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="G162" s="25" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B163" s="4" t="s">
-        <v>474</v>
+      <c r="B163" s="1">
+        <v>6.1</v>
       </c>
       <c r="C163" s="1">
-        <v>1545</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F163" s="25" t="s">
-        <v>465</v>
-      </c>
-      <c r="G163" s="1" t="s">
-        <v>473</v>
+        <v>1259</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -26697,7 +26868,7 @@
         <v>474</v>
       </c>
       <c r="C164" s="1">
-        <v>1614</v>
+        <v>1545</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>4</v>
@@ -26705,7 +26876,7 @@
       <c r="F164" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G164" s="1" t="s">
+      <c r="G164" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -26713,14 +26884,20 @@
       <c r="A165" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B165" s="1">
-        <v>6.1</v>
+      <c r="B165" s="4" t="s">
+        <v>474</v>
       </c>
       <c r="C165" s="1">
-        <v>1649</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>4</v>
+        <v>1614</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F165" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="G165" s="25" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -26731,7 +26908,7 @@
         <v>6.1</v>
       </c>
       <c r="C166" s="1">
-        <v>2249</v>
+        <v>1649</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>4</v>
@@ -26741,20 +26918,14 @@
       <c r="A167" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B167" s="4" t="s">
-        <v>474</v>
+      <c r="B167" s="1">
+        <v>6.1</v>
       </c>
       <c r="C167" s="1">
-        <v>2521</v>
-      </c>
-      <c r="E167" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F167" s="25" t="s">
-        <v>465</v>
-      </c>
-      <c r="G167" s="1" t="s">
-        <v>473</v>
+        <v>2249</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -26765,7 +26936,7 @@
         <v>474</v>
       </c>
       <c r="C168" s="1">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>4</v>
@@ -26773,7 +26944,7 @@
       <c r="F168" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G168" s="1" t="s">
+      <c r="G168" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -26785,7 +26956,7 @@
         <v>474</v>
       </c>
       <c r="C169" s="1">
-        <v>3073</v>
+        <v>2522</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>4</v>
@@ -26793,7 +26964,7 @@
       <c r="F169" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G169" s="1" t="s">
+      <c r="G169" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -26805,7 +26976,7 @@
         <v>474</v>
       </c>
       <c r="C170" s="1">
-        <v>3079</v>
+        <v>3073</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>4</v>
@@ -26813,7 +26984,7 @@
       <c r="F170" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G170" s="1" t="s">
+      <c r="G170" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -26825,7 +26996,7 @@
         <v>474</v>
       </c>
       <c r="C171" s="1">
-        <v>3302</v>
+        <v>3079</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>4</v>
@@ -26833,7 +27004,7 @@
       <c r="F171" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G171" s="1" t="s">
+      <c r="G171" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -26841,31 +27012,31 @@
       <c r="A172" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B172" s="1">
-        <v>6.2</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>4</v>
+      <c r="B172" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C172" s="1">
+        <v>3302</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F172" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="G172" s="25" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B173" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="C173" s="1">
-        <v>1724</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F173" s="25" t="s">
-        <v>465</v>
-      </c>
-      <c r="G173" s="1" t="s">
-        <v>473</v>
+      <c r="B173" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -26876,7 +27047,7 @@
         <v>477</v>
       </c>
       <c r="C174" s="1">
-        <v>1829</v>
+        <v>1724</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>4</v>
@@ -26884,7 +27055,7 @@
       <c r="F174" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G174" s="1" t="s">
+      <c r="G174" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -26896,7 +27067,7 @@
         <v>477</v>
       </c>
       <c r="C175" s="1">
-        <v>2218</v>
+        <v>1829</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>4</v>
@@ -26904,7 +27075,7 @@
       <c r="F175" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G175" s="1" t="s">
+      <c r="G175" s="25" t="s">
         <v>473</v>
       </c>
     </row>
@@ -26916,7 +27087,7 @@
         <v>477</v>
       </c>
       <c r="C176" s="1">
-        <v>2531</v>
+        <v>2218</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>4</v>
@@ -26924,39 +27095,45 @@
       <c r="F176" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G176" s="1" t="s">
+      <c r="G176" s="25" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B177" s="1">
-        <v>8</v>
+      <c r="B177" s="4" t="s">
+        <v>477</v>
       </c>
       <c r="C177" s="1">
-        <v>3507</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2531</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F177" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="G177" s="25" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>463</v>
       </c>
       <c r="B178" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C178" s="1">
-        <v>2071</v>
+        <v>3507</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>463</v>
       </c>
@@ -26964,13 +27141,13 @@
         <v>9</v>
       </c>
       <c r="C179" s="1">
-        <v>2211</v>
+        <v>2071</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>463</v>
       </c>
@@ -26978,13 +27155,13 @@
         <v>9</v>
       </c>
       <c r="C180" s="1">
-        <v>2216</v>
+        <v>2211</v>
       </c>
       <c r="D180" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>463</v>
       </c>
@@ -26992,13 +27169,13 @@
         <v>9</v>
       </c>
       <c r="C181" s="1">
-        <v>2315</v>
+        <v>2216</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>463</v>
       </c>
@@ -27006,13 +27183,13 @@
         <v>9</v>
       </c>
       <c r="C182" s="1">
-        <v>2590</v>
+        <v>2315</v>
       </c>
       <c r="D182" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>463</v>
       </c>
@@ -27020,16 +27197,13 @@
         <v>9</v>
       </c>
       <c r="C183" s="1">
-        <v>3090</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F183" s="25" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2590</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>463</v>
       </c>
@@ -27037,16 +27211,19 @@
         <v>9</v>
       </c>
       <c r="C184" s="1">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F184" s="25" t="s">
+        <v>487</v>
+      </c>
+      <c r="G184" s="25" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>463</v>
       </c>
@@ -27054,13 +27231,19 @@
         <v>9</v>
       </c>
       <c r="C185" s="1">
-        <v>3151</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3091</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F185" s="25" t="s">
+        <v>487</v>
+      </c>
+      <c r="G185" s="25" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>463</v>
       </c>
@@ -27068,13 +27251,13 @@
         <v>9</v>
       </c>
       <c r="C186" s="1">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>463</v>
       </c>
@@ -27082,19 +27265,13 @@
         <v>9</v>
       </c>
       <c r="C187" s="1">
-        <v>3166</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F187" s="25" t="s">
-        <v>469</v>
-      </c>
-      <c r="G187" s="1" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3152</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>463</v>
       </c>
@@ -27102,19 +27279,22 @@
         <v>9</v>
       </c>
       <c r="C188" s="1">
-        <v>3171</v>
+        <v>3166</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F188" s="25" t="s">
+        <v>487</v>
+      </c>
+      <c r="G188" s="25" t="s">
         <v>469</v>
       </c>
-      <c r="G188" s="1" t="s">
+      <c r="H188" s="25" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>463</v>
       </c>
@@ -27122,13 +27302,22 @@
         <v>9</v>
       </c>
       <c r="C189" s="1">
-        <v>3314</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3171</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F189" s="25" t="s">
+        <v>487</v>
+      </c>
+      <c r="G189" s="25" t="s">
+        <v>469</v>
+      </c>
+      <c r="H189" s="25" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>463</v>
       </c>
@@ -27136,13 +27325,13 @@
         <v>9</v>
       </c>
       <c r="C190" s="1">
-        <v>3432</v>
+        <v>3314</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>463</v>
       </c>
@@ -27150,16 +27339,13 @@
         <v>9</v>
       </c>
       <c r="C191" s="1">
-        <v>3480</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F191" s="25" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3432</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>463</v>
       </c>
@@ -27167,16 +27353,19 @@
         <v>9</v>
       </c>
       <c r="C192" s="1">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F192" s="25" t="s">
+        <v>487</v>
+      </c>
+      <c r="G192" s="25" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>463</v>
       </c>
@@ -27184,13 +27373,19 @@
         <v>9</v>
       </c>
       <c r="C193" s="1">
-        <v>3509</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3481</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F193" s="25" t="s">
+        <v>487</v>
+      </c>
+      <c r="G193" s="25" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>463</v>
       </c>
@@ -27198,13 +27393,13 @@
         <v>9</v>
       </c>
       <c r="C194" s="1">
-        <v>3536</v>
+        <v>3509</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>463</v>
       </c>
@@ -27212,19 +27407,13 @@
         <v>9</v>
       </c>
       <c r="C195" s="1">
-        <v>3556</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F195" s="25" t="s">
-        <v>469</v>
-      </c>
-      <c r="G195" s="1" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3536</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>463</v>
       </c>
@@ -27232,33 +27421,39 @@
         <v>9</v>
       </c>
       <c r="C196" s="1">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F196" s="25" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+        <v>487</v>
+      </c>
+      <c r="G196" s="25" t="s">
+        <v>469</v>
+      </c>
+      <c r="H196" s="25" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A198" s="1" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A199" s="1" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A200" s="1" t="s">
-        <v>463</v>
+      <c r="B197" s="1">
+        <v>9</v>
+      </c>
+      <c r="C197" s="1">
+        <v>3557</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F197" s="25" t="s">
+        <v>487</v>
+      </c>
+      <c r="G197" s="25" t="s">
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -29418,7 +29613,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8F21524-D944-4244-BFC9-8EC27073B31B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{655CCFA0-BDF9-4DDD-B879-49F6C9070A38}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/dg_list.xlsx
+++ b/dg_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ialasia.sharepoint.com/sites/IALDGDESK/Shared Documents/General/Query System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2323" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81F5DA43-BC1A-42F6-8A27-C2D81E1C1825}"/>
+  <xr:revisionPtr revIDLastSave="2329" documentId="13_ncr:1_{EB85D9C8-8108-4A93-AF94-36FA4FB59423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE405AA1-5195-41E0-BE10-3561D978527E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="27630" windowHeight="16440" firstSheet="1" activeTab="7" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5253" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5256" uniqueCount="658">
   <si>
     <t>UN Number</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -3037,6 +3037,10 @@
 PERCHLORIC ACID with more than 72% acid, by mass
 SILVER PICRATE, dry or wetted with less than 30% water by mass
 ZINC AMMONIUM NITRITE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prohibited except UN0503</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -28244,7 +28248,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:AG386"/>
+  <dimension ref="A1:AG387"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.625" style="7" bestFit="1" customWidth="1"/>
@@ -28371,11 +28375,11 @@
       <c r="B6" s="4">
         <v>1.4</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
+      <c r="E6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>657</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -28386,7 +28390,7 @@
         <v>1.4</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>4</v>
@@ -28400,7 +28404,7 @@
         <v>1.4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>4</v>
@@ -28414,7 +28418,7 @@
         <v>1.4</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>4</v>
@@ -28428,7 +28432,7 @@
         <v>1.4</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>4</v>
@@ -28442,7 +28446,7 @@
         <v>1.4</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>4</v>
@@ -28456,7 +28460,7 @@
         <v>1.4</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>4</v>
@@ -28470,7 +28474,7 @@
         <v>1.4</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>4</v>
@@ -28484,7 +28488,7 @@
         <v>1.4</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>4</v>
@@ -28498,7 +28502,7 @@
         <v>1.4</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>4</v>
@@ -28512,7 +28516,7 @@
         <v>1.4</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>4</v>
@@ -28526,7 +28530,7 @@
         <v>1.4</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>4</v>
@@ -28540,7 +28544,7 @@
         <v>1.4</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>4</v>
@@ -28554,7 +28558,7 @@
         <v>1.4</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>4</v>
@@ -28568,7 +28572,7 @@
         <v>1.4</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>4</v>
@@ -28582,7 +28586,7 @@
         <v>1.4</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>4</v>
@@ -28596,7 +28600,7 @@
         <v>1.4</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>4</v>
@@ -28610,7 +28614,7 @@
         <v>1.4</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>4</v>
@@ -28624,7 +28628,7 @@
         <v>1.4</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>4</v>
@@ -28638,7 +28642,7 @@
         <v>1.4</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>4</v>
@@ -28652,7 +28656,7 @@
         <v>1.4</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>4</v>
@@ -28666,7 +28670,7 @@
         <v>1.4</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>4</v>
@@ -28680,7 +28684,7 @@
         <v>1.4</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>4</v>
@@ -28694,7 +28698,7 @@
         <v>1.4</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>4</v>
@@ -28708,7 +28712,7 @@
         <v>1.4</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>4</v>
@@ -28722,7 +28726,7 @@
         <v>1.4</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>4</v>
@@ -28736,7 +28740,7 @@
         <v>1.4</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>4</v>
@@ -28750,7 +28754,7 @@
         <v>1.4</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>4</v>
@@ -28764,7 +28768,7 @@
         <v>1.4</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>4</v>
@@ -28778,7 +28782,7 @@
         <v>1.4</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>4</v>
@@ -28792,7 +28796,7 @@
         <v>1.4</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>4</v>
@@ -28806,7 +28810,7 @@
         <v>1.4</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>4</v>
@@ -28820,7 +28824,7 @@
         <v>1.4</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>4</v>
@@ -28834,7 +28838,7 @@
         <v>1.4</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>4</v>
@@ -28848,7 +28852,7 @@
         <v>1.4</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>4</v>
@@ -28862,7 +28866,7 @@
         <v>1.4</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>4</v>
@@ -28876,7 +28880,7 @@
         <v>1.4</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>4</v>
@@ -28890,7 +28894,7 @@
         <v>1.4</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>4</v>
@@ -28904,7 +28908,7 @@
         <v>1.4</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>4</v>
@@ -28918,7 +28922,7 @@
         <v>1.4</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>4</v>
@@ -28932,7 +28936,7 @@
         <v>1.4</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>4</v>
@@ -28946,7 +28950,7 @@
         <v>1.4</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>4</v>
@@ -28960,7 +28964,7 @@
         <v>1.4</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>4</v>
@@ -28974,7 +28978,7 @@
         <v>1.4</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>4</v>
@@ -28988,7 +28992,7 @@
         <v>1.4</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>4</v>
@@ -29002,7 +29006,7 @@
         <v>1.4</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>4</v>
@@ -29016,7 +29020,7 @@
         <v>1.4</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>4</v>
@@ -29030,7 +29034,7 @@
         <v>1.4</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>4</v>
@@ -29044,7 +29048,7 @@
         <v>1.4</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>4</v>
@@ -29058,7 +29062,7 @@
         <v>1.4</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>4</v>
@@ -29072,7 +29076,7 @@
         <v>1.4</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>4</v>
@@ -29086,7 +29090,7 @@
         <v>1.4</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>4</v>
@@ -29100,7 +29104,7 @@
         <v>1.4</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>4</v>
@@ -29114,7 +29118,7 @@
         <v>1.4</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>4</v>
@@ -29128,7 +29132,7 @@
         <v>1.4</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>4</v>
@@ -29142,7 +29146,7 @@
         <v>1.4</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>4</v>
@@ -29156,7 +29160,7 @@
         <v>1.4</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>4</v>
@@ -29170,7 +29174,7 @@
         <v>1.4</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>4</v>
@@ -29184,7 +29188,7 @@
         <v>1.4</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>4</v>
@@ -29198,7 +29202,7 @@
         <v>1.4</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>4</v>
@@ -29212,7 +29216,7 @@
         <v>1.4</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>4</v>
@@ -29226,7 +29230,7 @@
         <v>1.4</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>4</v>
@@ -29240,7 +29244,7 @@
         <v>1.4</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>4</v>
@@ -29254,7 +29258,7 @@
         <v>1.4</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>4</v>
@@ -29268,7 +29272,7 @@
         <v>1.4</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>4</v>
@@ -29282,7 +29286,7 @@
         <v>1.4</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>4</v>
@@ -29296,7 +29300,7 @@
         <v>1.4</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>4</v>
@@ -29310,7 +29314,7 @@
         <v>1.4</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>4</v>
@@ -29324,7 +29328,7 @@
         <v>1.4</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>4</v>
@@ -29338,7 +29342,7 @@
         <v>1.4</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>4</v>
@@ -29352,7 +29356,7 @@
         <v>1.4</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>4</v>
@@ -29366,7 +29370,7 @@
         <v>1.4</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>4</v>
@@ -29380,7 +29384,7 @@
         <v>1.4</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>4</v>
@@ -29394,7 +29398,7 @@
         <v>1.4</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>4</v>
@@ -29408,7 +29412,7 @@
         <v>1.4</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>4</v>
@@ -29422,7 +29426,7 @@
         <v>1.4</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>4</v>
@@ -29436,7 +29440,7 @@
         <v>1.4</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>4</v>
@@ -29450,7 +29454,7 @@
         <v>1.4</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>4</v>
@@ -29464,7 +29468,7 @@
         <v>1.4</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>4</v>
@@ -29478,7 +29482,7 @@
         <v>1.4</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>4</v>
@@ -29492,7 +29496,7 @@
         <v>1.4</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>4</v>
@@ -29506,7 +29510,7 @@
         <v>1.4</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>4</v>
@@ -29520,7 +29524,7 @@
         <v>1.4</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>4</v>
@@ -29534,7 +29538,7 @@
         <v>1.4</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>4</v>
@@ -29548,7 +29552,7 @@
         <v>1.4</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>4</v>
@@ -29562,7 +29566,7 @@
         <v>1.4</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>4</v>
@@ -29576,7 +29580,7 @@
         <v>1.4</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>4</v>
@@ -29590,7 +29594,7 @@
         <v>1.4</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>4</v>
@@ -29604,7 +29608,7 @@
         <v>1.4</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>4</v>
@@ -29618,7 +29622,7 @@
         <v>1.4</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>4</v>
@@ -29632,7 +29636,7 @@
         <v>1.4</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>4</v>
@@ -29646,7 +29650,7 @@
         <v>1.4</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>4</v>
@@ -29660,7 +29664,7 @@
         <v>1.4</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>4</v>
@@ -29674,7 +29678,7 @@
         <v>1.4</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>4</v>
@@ -29688,7 +29692,7 @@
         <v>1.4</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>4</v>
@@ -29702,7 +29706,7 @@
         <v>1.4</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>4</v>
@@ -29716,7 +29720,7 @@
         <v>1.4</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>4</v>
@@ -29730,7 +29734,7 @@
         <v>1.4</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>4</v>
@@ -29744,7 +29748,7 @@
         <v>1.4</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>4</v>
@@ -29758,7 +29762,7 @@
         <v>1.4</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>4</v>
@@ -29772,7 +29776,7 @@
         <v>1.4</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>4</v>
@@ -29786,7 +29790,7 @@
         <v>1.4</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>4</v>
@@ -29800,7 +29804,7 @@
         <v>1.4</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>4</v>
@@ -29814,7 +29818,7 @@
         <v>1.4</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>4</v>
@@ -29828,7 +29832,7 @@
         <v>1.4</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>4</v>
@@ -29838,8 +29842,11 @@
       <c r="A111" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="B111" s="4" t="s">
-        <v>609</v>
+      <c r="B111" s="4">
+        <v>1.4</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>608</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>4</v>
@@ -29850,7 +29857,7 @@
         <v>503</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>4</v>
@@ -29861,13 +29868,10 @@
         <v>503</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F113" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -29877,11 +29881,11 @@
       <c r="B114" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="C114" s="1">
-        <v>1032</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>4</v>
+      <c r="E114" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F114" s="13" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -29889,16 +29893,16 @@
         <v>503</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C115" s="1">
-        <v>1049</v>
+        <v>1032</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="158.25" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>503</v>
       </c>
@@ -29906,16 +29910,13 @@
         <v>472</v>
       </c>
       <c r="C116" s="1">
-        <v>1057</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F116" s="11" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1049</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="158.25" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>503</v>
       </c>
@@ -29923,10 +29924,13 @@
         <v>472</v>
       </c>
       <c r="C117" s="1">
-        <v>1961</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>4</v>
+        <v>1057</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F117" s="11" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -29937,7 +29941,7 @@
         <v>472</v>
       </c>
       <c r="C118" s="1">
-        <v>1966</v>
+        <v>1961</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>4</v>
@@ -29951,7 +29955,7 @@
         <v>472</v>
       </c>
       <c r="C119" s="1">
-        <v>1972</v>
+        <v>1966</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>4</v>
@@ -29965,7 +29969,7 @@
         <v>472</v>
       </c>
       <c r="C120" s="1">
-        <v>2203</v>
+        <v>1972</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>4</v>
@@ -29979,7 +29983,7 @@
         <v>472</v>
       </c>
       <c r="C121" s="1">
-        <v>3138</v>
+        <v>2203</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>4</v>
@@ -29993,7 +29997,7 @@
         <v>472</v>
       </c>
       <c r="C122" s="1">
-        <v>3468</v>
+        <v>3138</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>4</v>
@@ -30004,10 +30008,10 @@
         <v>503</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>613</v>
+        <v>472</v>
       </c>
       <c r="C123" s="1">
-        <v>2455</v>
+        <v>3468</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>4</v>
@@ -30018,10 +30022,13 @@
         <v>503</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>477</v>
+        <v>613</v>
+      </c>
+      <c r="C124" s="1">
+        <v>2455</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>468</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -30029,13 +30036,10 @@
         <v>503</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F125" s="13" t="s">
-        <v>614</v>
+        <v>477</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -30045,11 +30049,11 @@
       <c r="B126" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="C126" s="1">
-        <v>1131</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>4</v>
+      <c r="E126" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F126" s="13" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -30060,13 +30064,10 @@
         <v>479</v>
       </c>
       <c r="C127" s="1">
-        <v>1194</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F127" s="13" t="s">
-        <v>615</v>
+        <v>1131</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -30074,13 +30075,16 @@
         <v>503</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C128" s="1">
-        <v>1222</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>4</v>
+        <v>1194</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F128" s="13" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -30091,7 +30095,7 @@
         <v>478</v>
       </c>
       <c r="C129" s="1">
-        <v>1261</v>
+        <v>1222</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>4</v>
@@ -30105,13 +30109,10 @@
         <v>478</v>
       </c>
       <c r="C130" s="1">
-        <v>1280</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F130" s="13" t="s">
-        <v>616</v>
+        <v>1261</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -30122,13 +30123,16 @@
         <v>478</v>
       </c>
       <c r="C131" s="1">
-        <v>1865</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+        <v>1280</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F131" s="13" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>503</v>
       </c>
@@ -30136,13 +30140,10 @@
         <v>478</v>
       </c>
       <c r="C132" s="1">
-        <v>3256</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F132" s="11" t="s">
-        <v>617</v>
+        <v>1865</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
@@ -30153,7 +30154,7 @@
         <v>478</v>
       </c>
       <c r="C133" s="1">
-        <v>3343</v>
+        <v>3256</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>4</v>
@@ -30170,7 +30171,7 @@
         <v>478</v>
       </c>
       <c r="C134" s="1">
-        <v>3357</v>
+        <v>3343</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>4</v>
@@ -30187,7 +30188,7 @@
         <v>478</v>
       </c>
       <c r="C135" s="1">
-        <v>3379</v>
+        <v>3357</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>4</v>
@@ -30196,32 +30197,35 @@
         <v>617</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>503</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>482</v>
+        <v>478</v>
+      </c>
+      <c r="C136" s="1">
+        <v>3379</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F136" s="11" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>503</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="C137" s="1">
-        <v>2304</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>4</v>
+      <c r="E137" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F137" s="11" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -30232,7 +30236,7 @@
         <v>482</v>
       </c>
       <c r="C138" s="1">
-        <v>2448</v>
+        <v>2304</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>4</v>
@@ -30246,13 +30250,13 @@
         <v>482</v>
       </c>
       <c r="C139" s="1">
-        <v>2956</v>
+        <v>2448</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>503</v>
       </c>
@@ -30260,30 +30264,30 @@
         <v>482</v>
       </c>
       <c r="C140" s="1">
-        <v>3097</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F140" s="11" t="s">
-        <v>617</v>
-      </c>
-      <c r="G140" s="11" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2956</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>503</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C141" s="1">
-        <v>3176</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>4</v>
+        <v>3097</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F141" s="11" t="s">
+        <v>617</v>
+      </c>
+      <c r="G141" s="11" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -30294,7 +30298,7 @@
         <v>481</v>
       </c>
       <c r="C142" s="1">
-        <v>3221</v>
+        <v>3176</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>4</v>
@@ -30308,7 +30312,7 @@
         <v>481</v>
       </c>
       <c r="C143" s="1">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>4</v>
@@ -30322,7 +30326,7 @@
         <v>481</v>
       </c>
       <c r="C144" s="1">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>4</v>
@@ -30336,7 +30340,7 @@
         <v>481</v>
       </c>
       <c r="C145" s="1">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>4</v>
@@ -30350,7 +30354,7 @@
         <v>481</v>
       </c>
       <c r="C146" s="1">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>4</v>
@@ -30364,7 +30368,7 @@
         <v>481</v>
       </c>
       <c r="C147" s="1">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>4</v>
@@ -30378,7 +30382,7 @@
         <v>481</v>
       </c>
       <c r="C148" s="1">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>4</v>
@@ -30392,7 +30396,7 @@
         <v>481</v>
       </c>
       <c r="C149" s="1">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>4</v>
@@ -30406,7 +30410,7 @@
         <v>481</v>
       </c>
       <c r="C150" s="1">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>4</v>
@@ -30420,7 +30424,7 @@
         <v>481</v>
       </c>
       <c r="C151" s="1">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>4</v>
@@ -30434,7 +30438,7 @@
         <v>481</v>
       </c>
       <c r="C152" s="1">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>4</v>
@@ -30448,7 +30452,7 @@
         <v>481</v>
       </c>
       <c r="C153" s="1">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>4</v>
@@ -30462,7 +30466,7 @@
         <v>481</v>
       </c>
       <c r="C154" s="1">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>4</v>
@@ -30476,7 +30480,7 @@
         <v>481</v>
       </c>
       <c r="C155" s="1">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>4</v>
@@ -30490,7 +30494,7 @@
         <v>481</v>
       </c>
       <c r="C156" s="1">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>4</v>
@@ -30504,7 +30508,7 @@
         <v>481</v>
       </c>
       <c r="C157" s="1">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>4</v>
@@ -30518,7 +30522,7 @@
         <v>481</v>
       </c>
       <c r="C158" s="1">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>4</v>
@@ -30532,7 +30536,7 @@
         <v>481</v>
       </c>
       <c r="C159" s="1">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>4</v>
@@ -30546,7 +30550,7 @@
         <v>481</v>
       </c>
       <c r="C160" s="1">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>4</v>
@@ -30560,30 +30564,27 @@
         <v>481</v>
       </c>
       <c r="C161" s="1">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>503</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C162" s="1">
-        <v>3319</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F162" s="11" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3240</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>503</v>
       </c>
@@ -30591,10 +30592,13 @@
         <v>482</v>
       </c>
       <c r="C163" s="1">
-        <v>3380</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>4</v>
+        <v>3319</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F163" s="11" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -30602,33 +30606,27 @@
         <v>503</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>621</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F164" s="13" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" ht="362.25" x14ac:dyDescent="0.25">
+        <v>482</v>
+      </c>
+      <c r="C164" s="1">
+        <v>3380</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>503</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>621</v>
       </c>
-      <c r="C165" s="1">
-        <v>1361</v>
-      </c>
       <c r="E165" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F165" s="11" t="s">
-        <v>623</v>
-      </c>
-      <c r="G165" s="11" t="s">
-        <v>624</v>
+      <c r="F165" s="13" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="362.25" x14ac:dyDescent="0.25">
@@ -30639,7 +30637,7 @@
         <v>621</v>
       </c>
       <c r="C166" s="1">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>4</v>
@@ -30651,7 +30649,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="362.25" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>503</v>
       </c>
@@ -30659,10 +30657,16 @@
         <v>621</v>
       </c>
       <c r="C167" s="1">
-        <v>1364</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>4</v>
+        <v>1362</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F167" s="11" t="s">
+        <v>623</v>
+      </c>
+      <c r="G167" s="11" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -30670,16 +30674,16 @@
         <v>503</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C168" s="1">
-        <v>1374</v>
+        <v>1364</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>503</v>
       </c>
@@ -30687,16 +30691,13 @@
         <v>620</v>
       </c>
       <c r="C169" s="1">
-        <v>1376</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F169" s="11" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1374</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>503</v>
       </c>
@@ -30704,10 +30705,13 @@
         <v>620</v>
       </c>
       <c r="C170" s="1">
-        <v>1381</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>4</v>
+        <v>1376</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F170" s="11" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -30718,7 +30722,7 @@
         <v>620</v>
       </c>
       <c r="C171" s="1">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>4</v>
@@ -30732,7 +30736,7 @@
         <v>620</v>
       </c>
       <c r="C172" s="1">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>4</v>
@@ -30746,7 +30750,7 @@
         <v>620</v>
       </c>
       <c r="C173" s="1">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>4</v>
@@ -30760,7 +30764,7 @@
         <v>620</v>
       </c>
       <c r="C174" s="1">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>4</v>
@@ -30774,7 +30778,7 @@
         <v>620</v>
       </c>
       <c r="C175" s="1">
-        <v>1857</v>
+        <v>1387</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>4</v>
@@ -30788,7 +30792,7 @@
         <v>620</v>
       </c>
       <c r="C176" s="1">
-        <v>2217</v>
+        <v>1857</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>4</v>
@@ -30802,7 +30806,7 @@
         <v>620</v>
       </c>
       <c r="C177" s="1">
-        <v>2447</v>
+        <v>2217</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>4</v>
@@ -30816,7 +30820,7 @@
         <v>620</v>
       </c>
       <c r="C178" s="1">
-        <v>2845</v>
+        <v>2447</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>4</v>
@@ -30830,7 +30834,7 @@
         <v>620</v>
       </c>
       <c r="C179" s="1">
-        <v>2846</v>
+        <v>2845</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>4</v>
@@ -30844,7 +30848,7 @@
         <v>620</v>
       </c>
       <c r="C180" s="1">
-        <v>2870</v>
+        <v>2846</v>
       </c>
       <c r="D180" s="1" t="s">
         <v>4</v>
@@ -30858,13 +30862,13 @@
         <v>620</v>
       </c>
       <c r="C181" s="1">
-        <v>2881</v>
+        <v>2870</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>503</v>
       </c>
@@ -30872,19 +30876,13 @@
         <v>620</v>
       </c>
       <c r="C182" s="1">
-        <v>3127</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F182" s="11" t="s">
-        <v>617</v>
-      </c>
-      <c r="G182" s="11" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2881</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>503</v>
       </c>
@@ -30892,10 +30890,16 @@
         <v>620</v>
       </c>
       <c r="C183" s="1">
-        <v>3194</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>4</v>
+        <v>3127</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F183" s="11" t="s">
+        <v>617</v>
+      </c>
+      <c r="G183" s="11" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -30906,13 +30910,13 @@
         <v>620</v>
       </c>
       <c r="C184" s="1">
-        <v>3200</v>
+        <v>3194</v>
       </c>
       <c r="D184" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>503</v>
       </c>
@@ -30920,19 +30924,13 @@
         <v>620</v>
       </c>
       <c r="C185" s="1">
-        <v>3255</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F185" s="11" t="s">
-        <v>617</v>
-      </c>
-      <c r="G185" s="11" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3200</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>503</v>
       </c>
@@ -30940,10 +30938,16 @@
         <v>620</v>
       </c>
       <c r="C186" s="1">
-        <v>3341</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>4</v>
+        <v>3255</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F186" s="11" t="s">
+        <v>617</v>
+      </c>
+      <c r="G186" s="11" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -30954,7 +30958,7 @@
         <v>620</v>
       </c>
       <c r="C187" s="1">
-        <v>3391</v>
+        <v>3341</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>4</v>
@@ -30968,7 +30972,7 @@
         <v>620</v>
       </c>
       <c r="C188" s="1">
-        <v>3392</v>
+        <v>3391</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>4</v>
@@ -30982,7 +30986,7 @@
         <v>620</v>
       </c>
       <c r="C189" s="1">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="D189" s="1" t="s">
         <v>4</v>
@@ -30996,7 +31000,7 @@
         <v>620</v>
       </c>
       <c r="C190" s="1">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>4</v>
@@ -31007,10 +31011,10 @@
         <v>503</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="C191" s="1">
-        <v>1395</v>
+        <v>3394</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>4</v>
@@ -31024,27 +31028,24 @@
         <v>628</v>
       </c>
       <c r="C192" s="1">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>503</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C193" s="1">
-        <v>1405</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F193" s="11" t="s">
-        <v>629</v>
+        <v>1398</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
@@ -31055,7 +31056,7 @@
         <v>627</v>
       </c>
       <c r="C194" s="1">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>4</v>
@@ -31064,7 +31065,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>503</v>
       </c>
@@ -31072,10 +31073,13 @@
         <v>627</v>
       </c>
       <c r="C195" s="1">
-        <v>1409</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>4</v>
+        <v>1408</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F195" s="11" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -31086,7 +31090,7 @@
         <v>627</v>
       </c>
       <c r="C196" s="1">
-        <v>1415</v>
+        <v>1409</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>4</v>
@@ -31100,7 +31104,7 @@
         <v>627</v>
       </c>
       <c r="C197" s="1">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>4</v>
@@ -31114,13 +31118,13 @@
         <v>627</v>
       </c>
       <c r="C198" s="1">
-        <v>1928</v>
+        <v>1418</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>503</v>
       </c>
@@ -31128,33 +31132,30 @@
         <v>627</v>
       </c>
       <c r="C199" s="1">
-        <v>3133</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F199" s="11" t="s">
-        <v>617</v>
-      </c>
-      <c r="G199" s="11" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1928</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>503</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C200" s="1">
-        <v>1479</v>
+        <v>3133</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F200" s="13" t="s">
-        <v>632</v>
+      <c r="F200" s="11" t="s">
+        <v>617</v>
+      </c>
+      <c r="G200" s="11" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -31165,10 +31166,13 @@
         <v>631</v>
       </c>
       <c r="C201" s="1">
-        <v>1512</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>4</v>
+        <v>1479</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F201" s="13" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -31176,16 +31180,16 @@
         <v>503</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C202" s="1">
-        <v>1748</v>
+        <v>1512</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>503</v>
       </c>
@@ -31193,16 +31197,13 @@
         <v>630</v>
       </c>
       <c r="C203" s="1">
-        <v>1942</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F203" s="11" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1748</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>503</v>
       </c>
@@ -31210,13 +31211,13 @@
         <v>630</v>
       </c>
       <c r="C204" s="1">
-        <v>2014</v>
+        <v>1942</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F204" s="13" t="s">
-        <v>634</v>
+      <c r="F204" s="11" t="s">
+        <v>633</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -31227,19 +31228,16 @@
         <v>630</v>
       </c>
       <c r="C205" s="1">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F205" s="13" t="s">
-        <v>635</v>
-      </c>
-      <c r="G205" s="13" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>503</v>
       </c>
@@ -31247,16 +31245,19 @@
         <v>630</v>
       </c>
       <c r="C206" s="1">
-        <v>2067</v>
+        <v>2015</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F206" s="11" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F206" s="13" t="s">
+        <v>635</v>
+      </c>
+      <c r="G206" s="13" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>503</v>
       </c>
@@ -31264,10 +31265,13 @@
         <v>630</v>
       </c>
       <c r="C207" s="1">
-        <v>2208</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>4</v>
+        <v>2067</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F207" s="11" t="s">
+        <v>633</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -31278,7 +31282,7 @@
         <v>630</v>
       </c>
       <c r="C208" s="1">
-        <v>2426</v>
+        <v>2208</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>4</v>
@@ -31292,13 +31296,10 @@
         <v>630</v>
       </c>
       <c r="C209" s="1">
-        <v>2468</v>
-      </c>
-      <c r="E209" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F209" s="13" t="s">
-        <v>636</v>
+        <v>2426</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -31309,15 +31310,16 @@
         <v>630</v>
       </c>
       <c r="C210" s="1">
-        <v>2880</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E210" s="7"/>
-      <c r="F210" s="7"/>
-    </row>
-    <row r="211" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+        <v>2468</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F210" s="13" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>503</v>
       </c>
@@ -31325,17 +31327,13 @@
         <v>630</v>
       </c>
       <c r="C211" s="1">
-        <v>3100</v>
-      </c>
-      <c r="E211" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F211" s="11" t="s">
-        <v>617</v>
-      </c>
-      <c r="G211" s="11" t="s">
-        <v>618</v>
-      </c>
+        <v>2880</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E211" s="7"/>
+      <c r="F211" s="7"/>
     </row>
     <row r="212" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
@@ -31345,7 +31343,7 @@
         <v>630</v>
       </c>
       <c r="C212" s="1">
-        <v>3121</v>
+        <v>3100</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>4</v>
@@ -31365,7 +31363,7 @@
         <v>630</v>
       </c>
       <c r="C213" s="1">
-        <v>3137</v>
+        <v>3121</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>4</v>
@@ -31377,7 +31375,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>503</v>
       </c>
@@ -31385,13 +31383,16 @@
         <v>630</v>
       </c>
       <c r="C214" s="1">
-        <v>3149</v>
+        <v>3137</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F214" s="11" t="s">
-        <v>637</v>
+        <v>617</v>
+      </c>
+      <c r="G214" s="11" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -31402,10 +31403,13 @@
         <v>630</v>
       </c>
       <c r="C215" s="1">
-        <v>3212</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>4</v>
+        <v>3149</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F215" s="11" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -31416,13 +31420,10 @@
         <v>630</v>
       </c>
       <c r="C216" s="1">
-        <v>3375</v>
-      </c>
-      <c r="E216" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F216" s="11" t="s">
-        <v>638</v>
+        <v>3212</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -31433,10 +31434,13 @@
         <v>630</v>
       </c>
       <c r="C217" s="1">
-        <v>3485</v>
-      </c>
-      <c r="D217" s="1" t="s">
-        <v>4</v>
+        <v>3375</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F217" s="11" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -31447,7 +31451,7 @@
         <v>630</v>
       </c>
       <c r="C218" s="1">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="D218" s="1" t="s">
         <v>4</v>
@@ -31461,38 +31465,38 @@
         <v>630</v>
       </c>
       <c r="C219" s="1">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>503</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>640</v>
-      </c>
-      <c r="E220" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F220" s="11" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+        <v>630</v>
+      </c>
+      <c r="C220" s="1">
+        <v>3487</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>503</v>
       </c>
       <c r="B221" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="C221" s="1">
-        <v>3101</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>4</v>
+      <c r="E221" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F221" s="11" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -31503,7 +31507,7 @@
         <v>640</v>
       </c>
       <c r="C222" s="1">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="D222" s="1" t="s">
         <v>4</v>
@@ -31514,10 +31518,10 @@
         <v>503</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C223" s="1">
-        <v>3111</v>
+        <v>3102</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>4</v>
@@ -31531,7 +31535,7 @@
         <v>639</v>
       </c>
       <c r="C224" s="1">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>4</v>
@@ -31545,7 +31549,7 @@
         <v>639</v>
       </c>
       <c r="C225" s="1">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>4</v>
@@ -31559,7 +31563,7 @@
         <v>639</v>
       </c>
       <c r="C226" s="1">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>4</v>
@@ -31573,7 +31577,7 @@
         <v>639</v>
       </c>
       <c r="C227" s="1">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="D227" s="1" t="s">
         <v>4</v>
@@ -31587,7 +31591,7 @@
         <v>639</v>
       </c>
       <c r="C228" s="1">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>4</v>
@@ -31601,7 +31605,7 @@
         <v>639</v>
       </c>
       <c r="C229" s="1">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="D229" s="1" t="s">
         <v>4</v>
@@ -31615,7 +31619,7 @@
         <v>639</v>
       </c>
       <c r="C230" s="1">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>4</v>
@@ -31629,7 +31633,7 @@
         <v>639</v>
       </c>
       <c r="C231" s="1">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>4</v>
@@ -31643,7 +31647,7 @@
         <v>639</v>
       </c>
       <c r="C232" s="1">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>4</v>
@@ -31654,16 +31658,16 @@
         <v>503</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>476</v>
+        <v>639</v>
       </c>
       <c r="C233" s="1">
-        <v>1135</v>
+        <v>3120</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>503</v>
       </c>
@@ -31671,30 +31675,30 @@
         <v>476</v>
       </c>
       <c r="C234" s="1">
-        <v>1510</v>
-      </c>
-      <c r="E234" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F234" s="11" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1135</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="63" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>503</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C235" s="1">
-        <v>1600</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+        <v>1510</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F235" s="11" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>503</v>
       </c>
@@ -31702,16 +31706,13 @@
         <v>475</v>
       </c>
       <c r="C236" s="1">
-        <v>1614</v>
-      </c>
-      <c r="E236" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F236" s="11" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1600</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>503</v>
       </c>
@@ -31719,13 +31720,16 @@
         <v>475</v>
       </c>
       <c r="C237" s="1">
-        <v>1649</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+        <v>1614</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F237" s="11" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>503</v>
       </c>
@@ -31733,16 +31737,13 @@
         <v>475</v>
       </c>
       <c r="C238" s="1">
-        <v>2023</v>
-      </c>
-      <c r="E238" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F238" s="11" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+        <v>1649</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" ht="63" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>503</v>
       </c>
@@ -31750,19 +31751,16 @@
         <v>475</v>
       </c>
       <c r="C239" s="1">
-        <v>2249</v>
+        <v>2023</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F239" s="11" t="s">
-        <v>617</v>
-      </c>
-      <c r="G239" s="11" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>503</v>
       </c>
@@ -31770,13 +31768,19 @@
         <v>475</v>
       </c>
       <c r="C240" s="1">
-        <v>2312</v>
-      </c>
-      <c r="D240" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6" ht="63" x14ac:dyDescent="0.25">
+        <v>2249</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F240" s="11" t="s">
+        <v>617</v>
+      </c>
+      <c r="G240" s="11" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>503</v>
       </c>
@@ -31784,13 +31788,10 @@
         <v>475</v>
       </c>
       <c r="C241" s="1">
-        <v>2480</v>
-      </c>
-      <c r="E241" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F241" s="11" t="s">
-        <v>642</v>
+        <v>2312</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="242" spans="1:6" ht="63" x14ac:dyDescent="0.25">
@@ -31801,13 +31802,13 @@
         <v>475</v>
       </c>
       <c r="C242" s="1">
-        <v>3123</v>
+        <v>2480</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F242" s="11" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="243" spans="1:6" ht="63" x14ac:dyDescent="0.25">
@@ -31818,7 +31819,7 @@
         <v>475</v>
       </c>
       <c r="C243" s="1">
-        <v>3125</v>
+        <v>3123</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>4</v>
@@ -31827,7 +31828,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" ht="63" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>503</v>
       </c>
@@ -31835,13 +31836,16 @@
         <v>475</v>
       </c>
       <c r="C244" s="1">
-        <v>3250</v>
-      </c>
-      <c r="D244" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
+        <v>3125</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F244" s="11" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>503</v>
       </c>
@@ -31849,13 +31853,13 @@
         <v>475</v>
       </c>
       <c r="C245" s="1">
-        <v>3315</v>
-      </c>
-      <c r="F245" s="11" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3250</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>503</v>
       </c>
@@ -31863,10 +31867,10 @@
         <v>475</v>
       </c>
       <c r="C246" s="1">
-        <v>3483</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>4</v>
+        <v>3315</v>
+      </c>
+      <c r="F246" s="11" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -31877,7 +31881,7 @@
         <v>475</v>
       </c>
       <c r="C247" s="1">
-        <v>3507</v>
+        <v>3483</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>4</v>
@@ -31888,7 +31892,10 @@
         <v>503</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>644</v>
+        <v>475</v>
+      </c>
+      <c r="C248" s="1">
+        <v>3507</v>
       </c>
       <c r="D248" s="1" t="s">
         <v>4</v>
@@ -31899,47 +31906,41 @@
         <v>503</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="250" spans="1:6" ht="63" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>503</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="C250" s="1">
-        <v>1744</v>
-      </c>
-      <c r="E250" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F250" s="11" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
+        <v>645</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" ht="63" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>503</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>647</v>
+        <v>480</v>
       </c>
       <c r="C251" s="1">
-        <v>2211</v>
+        <v>1744</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F251" s="11" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>503</v>
       </c>
@@ -31947,10 +31948,13 @@
         <v>647</v>
       </c>
       <c r="C252" s="1">
-        <v>2212</v>
-      </c>
-      <c r="D252" s="1" t="s">
-        <v>4</v>
+        <v>2211</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F252" s="11" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -31958,10 +31962,10 @@
         <v>503</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C253" s="1">
-        <v>2315</v>
+        <v>2212</v>
       </c>
       <c r="D253" s="1" t="s">
         <v>4</v>
@@ -31975,7 +31979,7 @@
         <v>646</v>
       </c>
       <c r="C254" s="1">
-        <v>2590</v>
+        <v>2315</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>4</v>
@@ -31989,13 +31993,10 @@
         <v>646</v>
       </c>
       <c r="C255" s="1">
-        <v>3090</v>
-      </c>
-      <c r="E255" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F255" s="13" t="s">
-        <v>622</v>
+        <v>2590</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -32006,7 +32007,7 @@
         <v>646</v>
       </c>
       <c r="C256" s="1">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>4</v>
@@ -32023,10 +32024,13 @@
         <v>646</v>
       </c>
       <c r="C257" s="1">
-        <v>3151</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>4</v>
+        <v>3091</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F257" s="13" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -32037,7 +32041,7 @@
         <v>646</v>
       </c>
       <c r="C258" s="1">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>4</v>
@@ -32051,13 +32055,13 @@
         <v>646</v>
       </c>
       <c r="C259" s="1">
-        <v>3245</v>
+        <v>3152</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="260" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>503</v>
       </c>
@@ -32065,13 +32069,10 @@
         <v>646</v>
       </c>
       <c r="C260" s="1">
-        <v>3257</v>
-      </c>
-      <c r="E260" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F260" s="11" t="s">
-        <v>617</v>
+        <v>3245</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="261" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
@@ -32082,7 +32083,7 @@
         <v>646</v>
       </c>
       <c r="C261" s="1">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>4</v>
@@ -32091,7 +32092,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="262" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>503</v>
       </c>
@@ -32099,16 +32100,16 @@
         <v>646</v>
       </c>
       <c r="C262" s="1">
-        <v>3314</v>
+        <v>3258</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F262" s="11" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>503</v>
       </c>
@@ -32116,10 +32117,13 @@
         <v>646</v>
       </c>
       <c r="C263" s="1">
-        <v>3432</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>4</v>
+        <v>3314</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F263" s="11" t="s">
+        <v>649</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -32130,13 +32134,10 @@
         <v>646</v>
       </c>
       <c r="C264" s="1">
-        <v>3480</v>
-      </c>
-      <c r="E264" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F264" s="13" t="s">
-        <v>622</v>
+        <v>3432</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -32147,7 +32148,7 @@
         <v>646</v>
       </c>
       <c r="C265" s="1">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>4</v>
@@ -32157,7 +32158,21 @@
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A266" s="1"/>
+      <c r="A266" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C266" s="1">
+        <v>3481</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F266" s="13" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
@@ -32518,6 +32533,9 @@
     </row>
     <row r="386" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A387" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -34396,6 +34414,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="c3e85fef-df06-4e67-8632-489752715f52" xsi:nil="true"/>
@@ -34404,15 +34431,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -34665,6 +34683,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171B3C16-7124-4B98-87E3-5FC6A9D45406}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98411DB4-5541-4967-8DBE-AF3E324DD5F5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -34675,14 +34701,21 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171B3C16-7124-4B98-87E3-5FC6A9D45406}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABBE40C2-C8D8-4683-9F69-1C4C3AB93DFD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ea6fd297-1f65-4950-8fc9-157e29c7b648"/>
+    <ds:schemaRef ds:uri="c3e85fef-df06-4e67-8632-489752715f52"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76CF2354-7F11-4501-903D-C4D6E66547E3}"/>
 </file>
--- a/dg_list.xlsx
+++ b/dg_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ialasia.sharepoint.com/sites/IALDGDESK/Shared Documents/General/Query System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="249" documentId="8_{283FAEA1-D05F-4837-8EED-DE95F23FE8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCCD82DE-3E59-41E0-853F-664E7F17499E}"/>
+  <xr:revisionPtr revIDLastSave="382" documentId="8_{283FAEA1-D05F-4837-8EED-DE95F23FE8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{154E6126-6D85-4BFD-A850-83235367E7A8}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="7" activeTab="8" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="8" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
   </bookViews>
   <sheets>
     <sheet name="IAL_20250923" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="NSS_20260528" sheetId="9" r:id="rId7"/>
     <sheet name="YML_20230425" sheetId="10" r:id="rId8"/>
     <sheet name="OOCL_20260101" sheetId="11" r:id="rId9"/>
-    <sheet name="ESL" sheetId="7" r:id="rId10"/>
+    <sheet name="ESL_20260501" sheetId="7" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6404" uniqueCount="1057">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6454" uniqueCount="1082">
   <si>
     <t>UN Number</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -4517,10 +4517,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> Only accept OOCL B/L on OOCL vessel`</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1818</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4882,12 +4878,239 @@
 2)Pakistan and China </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>Submission of the following documents is mandatory:
+o Container Packing Certificate
+o (MSDS)Material Safety Data Sheet
+o Vanning Survey Report from a recognized authority
+o To be stowed ON DECK only.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Only allowed in Shipper-Owned Tanks or Shipper-Owned Containers.
+Requires prior approval from the ESL DG Desk and Claims Team. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flammable Liquids with Flashpoint -18 Degree Celsius and Less</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fibres Vegetable are acceptable
+Fibres Animal are strictly prohibited.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accepted DG in reefers for quality purpose only:
+•Acceptable in SOC for quality purpose
+•If in OOCL reefers, subject to in-house restrictions</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fishmeal shipments must be accompanied by a certificate from a recognized authority stating the following:
+o Moisture content
+o Fat content
+o Details of antioxidant treatment for meals older than 6 months
+o Antioxidant concentration at the time of shipment
+o Packing details, including number of bags and total mass of consignment
+o Temperature of fishmeal at time of dispatch from factory
+o Date of production
+o Confirmation that fishmeal has been weathered for at least 28 days before shipment
+o Confirmation that containers are packed to minimize free air space
+Fishmeal declared Non-Hazardous Strictly Prohibited.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Packaging in bags is prohibited
+A Container Packing Certificate is mandatory
+Port approval must be obtained before cargo acceptance</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>To be stowed ON DECK only.
+Warning Mark “CAUTION – MAY CONTAIN FLAMMABLE VAPOUR” to be attached on container.
+Shipper declaration mandatory for compliance as per IMDG special provision 965.
+Closed Container unit only acceptable for IBC (Intermediate Bulk Container) Packaging</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All types of waste cargo either dg or non-dg is strictly prohibited.
+The chemical substance Divinylbenzene is strictly prohibited.
+For all chemical substances shipped under UNNO 3077 and UNNO 3082, confirmation must be
+obtained from the shipper that the chemical substances are not classified as "dg waste".</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lithium Batteries
+1. Lithium Batteries Declared as Hazardous Goods (DG)
+Strictly Prohibited:
+UN3480 – Lithium-ion Batteries
+UN3090 – Lithium Metal Batteries
+Other types of Lithium Battery Shipments (DG):
+Acceptance may be considered subject to the following conditions:
+Only brand-new lithium batteries are acceptable.
+Lithium batteries declared as hazardous must not be co-loaded with any other DG cargo
+in the same container.
+Stowage category "ON DECK FOR LITHIUM BATTERIES" must be informed to respective port terminal and correctly updated in the CBF documents.
+2. Lithium Batteries Declared as Non-Hazardous Goods (Non-DG)
+All Lithium Batteries declared non-hazardous are Strictly Prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fuel tank must be no more than 1/4 full, and total flammable liquid must not exceed 250 liters.
+Batteries must be:
+o Protected from damage, short circuits, and accidental activation
+o Battery connections must be properly insulated
+Vehicles must be:
+o Loaded in an upright position
+o Properly secured and lashed within the container</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accepted only in ISO tanks
+Tank inspection certificate and MSDS (Material Safety Data Sheet) must be submitted</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Declarations under UNNO 3171 are no longer accepted, in line with the latest IMDG classification.
+Battery-Powered Vehicles must be declared under
+UNNO 3556 – VEHICLE, LITHIUM ION BATTERY POWERED
+UNNO 3557 – VEHICLE, LITHIUM METAL BATTERY POWERED
+UNNO 3558 – VEHICLE, SODIUM ION BATTERY POWERED
+Shipper confirmation of brand-new vehicles is acceptable as a basis for acceptance.
+Shipper confirmation is mandatory for Battery Charge percentage acceptable in the range of 30 to 40 percent only.
+Stowage category "ON DECK FOR LITHIUM BATTERIES" must be informed to respective port terminal and correctly updated in the CBF documents.
+Under Special Provision 961 of the IMDG Code, vehicles can be shipped as nonhazardous if the below conditions are met.
+o There are no signs of leakage from the battery, engine, fuel cell, compressed gas cylinder or accumulator, or fuel tank when applicable.
+o The fuel tank(s) of the vehicle or equipment powered by a flammable liquid fuel is empty and installed batteries are protected from short circuits.
+o The fuel tank must be emptied of flammable gas, pressure must not exceed 2 bars, the shut-off valve must be closed and secured, and batteries must be protected from short circuits or
+o The vehicle or equipment is solely powered by a wet or dry electronic storage battery or a sodium battery, and the battery is protected from short circuits.
+All Vehicles declared non-dg loading from Sohar (Oman) port not acceptable.
+*Shipper declaration for non-hazardous vehicles must be submitted to ESL local operation team.
+*Vehicle shipments declared non-DG will be liable for random inspection by port authorities.
+*Shipper will be responsible for all costs including inspections by port authority and penalty of misdeclaration if the vehicle declared non-DG does contain fuel and batteries connected to the vehicle.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ESL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All Cargo as Per Special Provision 900 Of the IMDG Code are prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heated Tanks are prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Military Cargo either DG or Non-DG on ESL owned vessels are prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Non-Hazardous Chemical Commodities are restricted
+For consortium partner bookings loaded on ESL-operated vessels, including chemical commodities declared as non-DG, it is assumed that the partner booking desk has obtained the necessary verification and written approval from their respective DG Desk.
+Shippers are fully responsible for the accurate and complete declaration of their cargo. In the event of any misdeclaration or non-declaration, a fee of USD 30,000 per container will be charged, in addition to any losses or damages arising from the improper declaration.
+The hazardous goods included in imdg special provision 900 of IMDG Code are Strictly Prohibited.
+a. Ammonium Bromate
+b. Ammonium Bromate Solution
+c. Ammonium Chlorate
+d. Ammonium Chlorate Solution
+e. Ammonium Chlorite
+f. Ammonium Nitrate liable to self-heating sufficient to initiate a decomposition
+g. Ammonium Nitrites and Mixtures of an Inorganic Nitrite with an Ammonium Salt
+h. Ammonium Permanganate
+i. Ammonium Permanganate Solution
+j. Chloric Acid Aqueous Solution with a concentration exceeding 10%
+k. Ethyl Nitrite Pure
+l. Hydrocyanic Acid with more than 20% acid by mass
+m. Hydrogen Cyanide, solution with more than 45%
+n. Hydrogen Cyanide
+o. Mercury Oxycyanide Pure
+p. Methyl Nitrite
+q. Perchloric Acid with more than 72% acid, by mass
+r. Silver Picrate, Dry or Wet with Less Than 30% Water by mass
+s. Zinc Ammonium Nitrite</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Waste Cargo either DG or Non-DG on ESL owned vessels are prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DG cargo in all operational/working reefer containers are prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Temperature controlled commodities, including chemical substances classified as DG or Non-DG, in dry containers are strictly prohibited for loading on ESL and Partner vessels.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Strictly prohibited if the technical name includes Calcium Hypochlorite or Ammonium Nitrate.
+Calcium Hypochlorite could be declared under various synonyms (some of which are listed below) all of which are prohibited:
+Whitening Agent
+Bleaching Powder
+Calcium Oxychloride
+Chloride Of Lime / Chlorinated Lime
+Hypochlorous Acid
+Calcium Salt / Lime Chloride
+Prechloroisocyanoric Acid (UN 2465)
+Sodium Di-Isocyanorate (UN 2466) </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SELF-HEATING SUBSTANCES
+Carbon and Charcoal in any form either declared Hazardous or Non-Hazardous is Strictly Prohibited loading on ESL vessels.
+All types of dg or non-dg Soybean Meal, Cottonseed Meal, Rapeseed Meal, Sunflower Meal is Strictly Prohibited loading on ESL vessels.
+All types of dg or non-dg Seed Cakes, Animal Feed Cakes is Strictly Prohibited loading on ESL vessels. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DG Cargo in Liquid Form – Packed in Single Plastic Outer Packaging
+For Dangerous Goods in liquid form packed in single plastic outer packaging (UN Packaging Codes: 1H1 / 1H2 Plastic Drums or 3H1 / 3H2 Plastic Jerricans), the following conditions must be met: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <family val="1"/>
+        <charset val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Each tier of drums or jerricans must be separated with timber sheet partitions. 
+The door side must be secured with solid materials to prevent any cargo movement during
+transit.
+Shippers must submit stuffing photos for each container prior to loading any DG units.
+The permitted use of 1H1 / 1H2 plastics drums and 3H1 / 3H2 jerricans as single packagings shall be two years from their date of manufacture.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Only residue tanks with flashpoints of –18°C or lower are acceptable. Rest All Strictly Prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All DG shipments declared under IMO Class 5.1 are strictly prohibited on the ASL-owned vessels.
+For all IMO Class 5.1 shipments loaded on other ESL-owned vessels, a Vanning Survey Report is mandatory prior to loading.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4929,6 +5152,13 @@
       <name val="Segoe UI Symbol"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Wingdings"/>
+      <family val="1"/>
+      <charset val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -4967,7 +5197,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5012,6 +5242,12 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8536,17 +8772,31 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEC4A6B7-48C3-4A88-9C22-C440F152E82D}">
-  <dimension ref="A1:H133"/>
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:Q134"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.625" customWidth="1"/>
     <col min="2" max="2" width="15" style="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.625" style="14" customWidth="1"/>
     <col min="4" max="5" width="11.625" customWidth="1"/>
-    <col min="6" max="8" width="50.625" customWidth="1"/>
+    <col min="6" max="6" width="160.625" customWidth="1"/>
+    <col min="7" max="7" width="50.625" customWidth="1"/>
+    <col min="8" max="8" width="63.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="133.375" customWidth="1"/>
+    <col min="10" max="10" width="62.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="57" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="79.25" customWidth="1"/>
+    <col min="13" max="13" width="35.125" customWidth="1"/>
+    <col min="14" max="14" width="23.625" customWidth="1"/>
+    <col min="15" max="15" width="33.875" customWidth="1"/>
+    <col min="16" max="16" width="90.875" customWidth="1"/>
+    <col min="17" max="17" width="50.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -8566,137 +8816,233 @@
         <v>134</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>135</v>
+        <v>492</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="B2" s="9">
-        <v>1</v>
-      </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>493</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="F2" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>1073</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>1076</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>1077</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>1064</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>1078</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>1079</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B3" s="9">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B4" s="9">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B5" s="9">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B6" s="9">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B7" s="9">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B8" s="9">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B9" s="9">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="C9" s="9">
-        <v>1963</v>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="C9" s="9"/>
       <c r="D9" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B10" s="9">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="C10" s="9"/>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C10" s="9">
+        <v>1963</v>
+      </c>
       <c r="D10" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:17" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B11" s="9">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C11" s="9">
-        <v>1040</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C11" s="9"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>143</v>
       </c>
@@ -8704,13 +9050,17 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C12" s="9">
-        <v>1067</v>
+        <v>1040</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>143</v>
       </c>
@@ -8718,13 +9068,17 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C13" s="9">
-        <v>1749</v>
+        <v>1067</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>143</v>
       </c>
@@ -8732,13 +9086,17 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C14" s="9">
-        <v>2188</v>
+        <v>1749</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>143</v>
       </c>
@@ -8746,13 +9104,17 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C15" s="9">
-        <v>2190</v>
+        <v>2188</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>143</v>
       </c>
@@ -8760,13 +9122,17 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C16" s="9">
-        <v>2417</v>
+        <v>2190</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>143</v>
       </c>
@@ -8774,13 +9140,17 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C17" s="9">
-        <v>2420</v>
+        <v>2417</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>143</v>
       </c>
@@ -8788,13 +9158,17 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C18" s="9">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>143</v>
       </c>
@@ -8802,39 +9176,55 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C19" s="9">
-        <v>2548</v>
+        <v>2421</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B20" s="9">
-        <v>3</v>
-      </c>
-      <c r="C20" s="9"/>
-      <c r="E20" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C20" s="9">
+        <v>2548</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B21" s="9">
         <v>3</v>
       </c>
-      <c r="C21" s="9">
-        <v>1131</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C21" s="9"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H21" s="7"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>143</v>
       </c>
@@ -8842,13 +9232,17 @@
         <v>3</v>
       </c>
       <c r="C22" s="9">
-        <v>1194</v>
+        <v>1131</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>143</v>
       </c>
@@ -8856,27 +9250,35 @@
         <v>3</v>
       </c>
       <c r="C23" s="9">
-        <v>3079</v>
+        <v>1194</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B24" s="9">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="C24" s="9">
-        <v>1334</v>
+        <v>3079</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>143</v>
       </c>
@@ -8884,13 +9286,18 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C25" s="9">
-        <v>1339</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1334</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>143</v>
       </c>
@@ -8898,13 +9305,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C26" s="9">
-        <v>2304</v>
+        <v>1339</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+    </row>
+    <row r="27" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>143</v>
       </c>
@@ -8912,13 +9323,18 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C27" s="9">
-        <v>2956</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2304</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>143</v>
       </c>
@@ -8926,13 +9342,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C28" s="9">
-        <v>3221</v>
+        <v>2956</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>143</v>
       </c>
@@ -8940,13 +9360,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C29" s="9">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>143</v>
       </c>
@@ -8954,13 +9378,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C30" s="9">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>143</v>
       </c>
@@ -8968,13 +9396,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C31" s="9">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>143</v>
       </c>
@@ -8982,13 +9414,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C32" s="9">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>143</v>
       </c>
@@ -8996,13 +9432,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C33" s="9">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>143</v>
       </c>
@@ -9010,13 +9450,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C34" s="9">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>143</v>
       </c>
@@ -9024,13 +9468,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C35" s="9">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>143</v>
       </c>
@@ -9038,13 +9486,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C36" s="9">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>143</v>
       </c>
@@ -9052,13 +9504,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C37" s="9">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>143</v>
       </c>
@@ -9066,13 +9522,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C38" s="9">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>143</v>
       </c>
@@ -9080,13 +9540,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C39" s="9">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>143</v>
       </c>
@@ -9094,13 +9558,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C40" s="9">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>143</v>
       </c>
@@ -9108,13 +9576,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C41" s="9">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>143</v>
       </c>
@@ -9122,13 +9594,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C42" s="9">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>143</v>
       </c>
@@ -9136,13 +9612,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C43" s="9">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>143</v>
       </c>
@@ -9150,13 +9630,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C44" s="9">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>143</v>
       </c>
@@ -9164,13 +9648,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C45" s="9">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>143</v>
       </c>
@@ -9178,13 +9666,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C46" s="9">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>143</v>
       </c>
@@ -9192,13 +9684,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C47" s="9">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>143</v>
       </c>
@@ -9206,13 +9702,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C48" s="9">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="D48" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
         <v>143</v>
       </c>
@@ -9220,13 +9720,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C49" s="9">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
         <v>143</v>
       </c>
@@ -9234,13 +9738,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C50" s="9">
-        <v>3532</v>
+        <v>3242</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
         <v>143</v>
       </c>
@@ -9248,27 +9756,35 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C51" s="9">
-        <v>3534</v>
+        <v>3532</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B52" s="9">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C52" s="9">
-        <v>1361</v>
+        <v>3534</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
+    </row>
+    <row r="53" spans="1:8" ht="63" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
         <v>143</v>
       </c>
@@ -9276,13 +9792,19 @@
         <v>4.2</v>
       </c>
       <c r="C53" s="9">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E53" s="7"/>
+      <c r="F53" s="11" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G53" s="7"/>
+      <c r="H53" s="7"/>
+    </row>
+    <row r="54" spans="1:8" ht="63" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>143</v>
       </c>
@@ -9290,13 +9812,19 @@
         <v>4.2</v>
       </c>
       <c r="C54" s="9">
-        <v>1372</v>
+        <v>1362</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E54" s="7"/>
+      <c r="F54" s="11" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+    </row>
+    <row r="55" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
         <v>143</v>
       </c>
@@ -9304,13 +9832,19 @@
         <v>4.2</v>
       </c>
       <c r="C55" s="9">
-        <v>1374</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1372</v>
+      </c>
+      <c r="D55" s="8"/>
+      <c r="E55" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="F55" s="15" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+    </row>
+    <row r="56" spans="1:8" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>143</v>
       </c>
@@ -9318,13 +9852,18 @@
         <v>4.2</v>
       </c>
       <c r="C56" s="9">
-        <v>1381</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1374</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F56" s="15" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
         <v>143</v>
       </c>
@@ -9332,13 +9871,17 @@
         <v>4.2</v>
       </c>
       <c r="C57" s="9">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
         <v>143</v>
       </c>
@@ -9346,13 +9889,17 @@
         <v>4.2</v>
       </c>
       <c r="C58" s="9">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+    </row>
+    <row r="59" spans="1:8" ht="63" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
         <v>143</v>
       </c>
@@ -9360,13 +9907,19 @@
         <v>4.2</v>
       </c>
       <c r="C59" s="9">
-        <v>2217</v>
+        <v>1386</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E59" s="7"/>
+      <c r="F59" s="11" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
+    </row>
+    <row r="60" spans="1:8" ht="63" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
         <v>143</v>
       </c>
@@ -9374,13 +9927,19 @@
         <v>4.2</v>
       </c>
       <c r="C60" s="9">
-        <v>3341</v>
+        <v>2217</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E60" s="7"/>
+      <c r="F60" s="11" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
         <v>143</v>
       </c>
@@ -9388,27 +9947,35 @@
         <v>4.2</v>
       </c>
       <c r="C61" s="9">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7"/>
+      <c r="H61" s="7"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B62" s="9">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="C62" s="9">
-        <v>1340</v>
+        <v>3342</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
         <v>143</v>
       </c>
@@ -9416,13 +9983,17 @@
         <v>4.3</v>
       </c>
       <c r="C63" s="9">
-        <v>1396</v>
+        <v>1340</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
         <v>143</v>
       </c>
@@ -9430,13 +10001,17 @@
         <v>4.3</v>
       </c>
       <c r="C64" s="9">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>143</v>
       </c>
@@ -9444,13 +10019,17 @@
         <v>4.3</v>
       </c>
       <c r="C65" s="9">
-        <v>1402</v>
+        <v>1397</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
+      <c r="H65" s="7"/>
+    </row>
+    <row r="66" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
         <v>143</v>
       </c>
@@ -9458,13 +10037,19 @@
         <v>4.3</v>
       </c>
       <c r="C66" s="9">
-        <v>1415</v>
+        <v>1402</v>
       </c>
       <c r="D66" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E66" s="7"/>
+      <c r="F66" s="15" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G66" s="7"/>
+      <c r="H66" s="7"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
         <v>143</v>
       </c>
@@ -9472,13 +10057,17 @@
         <v>4.3</v>
       </c>
       <c r="C67" s="9">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="7"/>
+      <c r="H67" s="7"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
         <v>143</v>
       </c>
@@ -9486,27 +10075,35 @@
         <v>4.3</v>
       </c>
       <c r="C68" s="9">
-        <v>3170</v>
+        <v>1418</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="7"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B69" s="9">
-        <v>5.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="C69" s="9">
-        <v>1479</v>
+        <v>3170</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
         <v>143</v>
       </c>
@@ -9514,13 +10111,17 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C70" s="9">
-        <v>1748</v>
+        <v>1479</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
         <v>143</v>
       </c>
@@ -9528,13 +10129,17 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C71" s="9">
-        <v>1942</v>
+        <v>1748</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
+      <c r="G71" s="7"/>
+      <c r="H71" s="7"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
         <v>143</v>
       </c>
@@ -9542,13 +10147,17 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C72" s="9">
-        <v>2067</v>
+        <v>1942</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
+      <c r="G72" s="7"/>
+      <c r="H72" s="7"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
         <v>143</v>
       </c>
@@ -9556,13 +10165,17 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C73" s="9">
-        <v>2208</v>
+        <v>2067</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="7"/>
+      <c r="H73" s="7"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
         <v>143</v>
       </c>
@@ -9570,13 +10183,17 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C74" s="9">
-        <v>2426</v>
+        <v>2208</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
         <v>143</v>
       </c>
@@ -9584,13 +10201,17 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C75" s="9">
-        <v>2465</v>
+        <v>2426</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="7"/>
+      <c r="H75" s="7"/>
+    </row>
+    <row r="76" spans="1:8" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
         <v>143</v>
       </c>
@@ -9598,13 +10219,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C76" s="9">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E76" s="7"/>
+      <c r="F76" s="11" t="s">
+        <v>1077</v>
+      </c>
+      <c r="G76" s="7"/>
+      <c r="H76" s="7"/>
+    </row>
+    <row r="77" spans="1:8" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
         <v>143</v>
       </c>
@@ -9612,13 +10239,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C77" s="9">
-        <v>2880</v>
+        <v>2466</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E77" s="7"/>
+      <c r="F77" s="11" t="s">
+        <v>1077</v>
+      </c>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="8" t="s">
         <v>143</v>
       </c>
@@ -9626,13 +10259,17 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C78" s="9">
-        <v>3375</v>
+        <v>2880</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E78" s="7"/>
+      <c r="F78" s="7"/>
+      <c r="G78" s="7"/>
+      <c r="H78" s="7"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
         <v>143</v>
       </c>
@@ -9640,13 +10277,17 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C79" s="9">
-        <v>3485</v>
+        <v>3375</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
+      <c r="G79" s="7"/>
+      <c r="H79" s="7"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="8" t="s">
         <v>143</v>
       </c>
@@ -9654,13 +10295,17 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C80" s="9">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E80" s="7"/>
+      <c r="F80" s="7"/>
+      <c r="G80" s="7"/>
+      <c r="H80" s="7"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
         <v>143</v>
       </c>
@@ -9668,27 +10313,35 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C81" s="9">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B82" s="9">
-        <v>5.2</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C82" s="9">
-        <v>3101</v>
+        <v>3487</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E82" s="7"/>
+      <c r="F82" s="7"/>
+      <c r="G82" s="7"/>
+      <c r="H82" s="7"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
         <v>143</v>
       </c>
@@ -9696,13 +10349,17 @@
         <v>5.2</v>
       </c>
       <c r="C83" s="9">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E83" s="7"/>
+      <c r="F83" s="7"/>
+      <c r="G83" s="7"/>
+      <c r="H83" s="7"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="8" t="s">
         <v>143</v>
       </c>
@@ -9710,13 +10367,17 @@
         <v>5.2</v>
       </c>
       <c r="C84" s="9">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E84" s="7"/>
+      <c r="F84" s="7"/>
+      <c r="G84" s="7"/>
+      <c r="H84" s="7"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
         <v>143</v>
       </c>
@@ -9724,13 +10385,17 @@
         <v>5.2</v>
       </c>
       <c r="C85" s="9">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E85" s="7"/>
+      <c r="F85" s="7"/>
+      <c r="G85" s="7"/>
+      <c r="H85" s="7"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="8" t="s">
         <v>143</v>
       </c>
@@ -9738,13 +10403,17 @@
         <v>5.2</v>
       </c>
       <c r="C86" s="9">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E86" s="7"/>
+      <c r="F86" s="7"/>
+      <c r="G86" s="7"/>
+      <c r="H86" s="7"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
         <v>143</v>
       </c>
@@ -9752,13 +10421,17 @@
         <v>5.2</v>
       </c>
       <c r="C87" s="9">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E87" s="7"/>
+      <c r="F87" s="7"/>
+      <c r="G87" s="7"/>
+      <c r="H87" s="7"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="8" t="s">
         <v>143</v>
       </c>
@@ -9766,13 +10439,17 @@
         <v>5.2</v>
       </c>
       <c r="C88" s="9">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E88" s="7"/>
+      <c r="F88" s="7"/>
+      <c r="G88" s="7"/>
+      <c r="H88" s="7"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
         <v>143</v>
       </c>
@@ -9780,13 +10457,17 @@
         <v>5.2</v>
       </c>
       <c r="C89" s="9">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E89" s="7"/>
+      <c r="F89" s="7"/>
+      <c r="G89" s="7"/>
+      <c r="H89" s="7"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="8" t="s">
         <v>143</v>
       </c>
@@ -9794,13 +10475,17 @@
         <v>5.2</v>
       </c>
       <c r="C90" s="9">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E90" s="7"/>
+      <c r="F90" s="7"/>
+      <c r="G90" s="7"/>
+      <c r="H90" s="7"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
         <v>143</v>
       </c>
@@ -9808,13 +10493,17 @@
         <v>5.2</v>
       </c>
       <c r="C91" s="9">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E91" s="7"/>
+      <c r="F91" s="7"/>
+      <c r="G91" s="7"/>
+      <c r="H91" s="7"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
         <v>143</v>
       </c>
@@ -9822,13 +10511,17 @@
         <v>5.2</v>
       </c>
       <c r="C92" s="9">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="D92" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E92" s="7"/>
+      <c r="F92" s="7"/>
+      <c r="G92" s="7"/>
+      <c r="H92" s="7"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
         <v>143</v>
       </c>
@@ -9836,13 +10529,17 @@
         <v>5.2</v>
       </c>
       <c r="C93" s="9">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="D93" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="7"/>
+      <c r="H93" s="7"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="8" t="s">
         <v>143</v>
       </c>
@@ -9850,13 +10547,17 @@
         <v>5.2</v>
       </c>
       <c r="C94" s="9">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E94" s="7"/>
+      <c r="F94" s="7"/>
+      <c r="G94" s="7"/>
+      <c r="H94" s="7"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
         <v>143</v>
       </c>
@@ -9864,13 +10565,17 @@
         <v>5.2</v>
       </c>
       <c r="C95" s="9">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E95" s="7"/>
+      <c r="F95" s="7"/>
+      <c r="G95" s="7"/>
+      <c r="H95" s="7"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="8" t="s">
         <v>143</v>
       </c>
@@ -9878,13 +10583,17 @@
         <v>5.2</v>
       </c>
       <c r="C96" s="9">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E96" s="7"/>
+      <c r="F96" s="7"/>
+      <c r="G96" s="7"/>
+      <c r="H96" s="7"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
         <v>143</v>
       </c>
@@ -9892,13 +10601,17 @@
         <v>5.2</v>
       </c>
       <c r="C97" s="9">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
+      <c r="G97" s="7"/>
+      <c r="H97" s="7"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="8" t="s">
         <v>143</v>
       </c>
@@ -9906,13 +10619,17 @@
         <v>5.2</v>
       </c>
       <c r="C98" s="9">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E98" s="7"/>
+      <c r="F98" s="7"/>
+      <c r="G98" s="7"/>
+      <c r="H98" s="7"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
         <v>143</v>
       </c>
@@ -9920,13 +10637,17 @@
         <v>5.2</v>
       </c>
       <c r="C99" s="9">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E99" s="7"/>
+      <c r="F99" s="7"/>
+      <c r="G99" s="7"/>
+      <c r="H99" s="7"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="8" t="s">
         <v>143</v>
       </c>
@@ -9934,13 +10655,17 @@
         <v>5.2</v>
       </c>
       <c r="C100" s="9">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E100" s="7"/>
+      <c r="F100" s="7"/>
+      <c r="G100" s="7"/>
+      <c r="H100" s="7"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
         <v>143</v>
       </c>
@@ -9948,27 +10673,35 @@
         <v>5.2</v>
       </c>
       <c r="C101" s="9">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="7"/>
+      <c r="H101" s="7"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B102" s="9">
-        <v>6.1</v>
+        <v>5.2</v>
       </c>
       <c r="C102" s="9">
-        <v>1244</v>
+        <v>3120</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E102" s="7"/>
+      <c r="F102" s="7"/>
+      <c r="G102" s="7"/>
+      <c r="H102" s="7"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
         <v>143</v>
       </c>
@@ -9976,13 +10709,17 @@
         <v>6.1</v>
       </c>
       <c r="C103" s="9">
-        <v>1649</v>
+        <v>1244</v>
       </c>
       <c r="D103" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E103" s="7"/>
+      <c r="F103" s="7"/>
+      <c r="G103" s="7"/>
+      <c r="H103" s="7"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="8" t="s">
         <v>143</v>
       </c>
@@ -9990,13 +10727,17 @@
         <v>6.1</v>
       </c>
       <c r="C104" s="9">
-        <v>2016</v>
+        <v>1649</v>
       </c>
       <c r="D104" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E104" s="7"/>
+      <c r="F104" s="7"/>
+      <c r="G104" s="7"/>
+      <c r="H104" s="7"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
         <v>143</v>
       </c>
@@ -10004,51 +10745,67 @@
         <v>6.1</v>
       </c>
       <c r="C105" s="9">
-        <v>3172</v>
+        <v>2016</v>
       </c>
       <c r="D105" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E105" s="7"/>
+      <c r="F105" s="7"/>
+      <c r="G105" s="7"/>
+      <c r="H105" s="7"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B106" s="9">
-        <v>6.2</v>
-      </c>
-      <c r="C106" s="9"/>
+        <v>6.1</v>
+      </c>
+      <c r="C106" s="9">
+        <v>3172</v>
+      </c>
       <c r="D106" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E106" s="7"/>
+      <c r="F106" s="7"/>
+      <c r="G106" s="7"/>
+      <c r="H106" s="7"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B107" s="9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E107" s="7"/>
+      <c r="F107" s="7"/>
+      <c r="G107" s="7"/>
+      <c r="H107" s="7"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B108" s="9">
-        <v>8</v>
-      </c>
-      <c r="C108" s="9">
-        <v>2031</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C108" s="9"/>
       <c r="D108" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E108" s="7"/>
+      <c r="F108" s="7"/>
+      <c r="G108" s="7"/>
+      <c r="H108" s="7"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
         <v>143</v>
       </c>
@@ -10056,13 +10813,17 @@
         <v>8</v>
       </c>
       <c r="C109" s="9">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="D109" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E109" s="7"/>
+      <c r="F109" s="7"/>
+      <c r="G109" s="7"/>
+      <c r="H109" s="7"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="8" t="s">
         <v>143</v>
       </c>
@@ -10070,27 +10831,35 @@
         <v>8</v>
       </c>
       <c r="C110" s="9">
-        <v>3145</v>
+        <v>2032</v>
       </c>
       <c r="D110" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E110" s="7"/>
+      <c r="F110" s="7"/>
+      <c r="G110" s="7"/>
+      <c r="H110" s="7"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B111" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C111" s="9">
-        <v>2071</v>
+        <v>3145</v>
       </c>
       <c r="D111" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E111" s="7"/>
+      <c r="F111" s="7"/>
+      <c r="G111" s="7"/>
+      <c r="H111" s="7"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="8" t="s">
         <v>143</v>
       </c>
@@ -10098,13 +10867,17 @@
         <v>9</v>
       </c>
       <c r="C112" s="9">
-        <v>2211</v>
+        <v>2071</v>
       </c>
       <c r="D112" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E112" s="7"/>
+      <c r="F112" s="7"/>
+      <c r="G112" s="7"/>
+      <c r="H112" s="7"/>
+    </row>
+    <row r="113" spans="1:8" ht="63" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
         <v>143</v>
       </c>
@@ -10112,13 +10885,18 @@
         <v>9</v>
       </c>
       <c r="C113" s="9">
-        <v>2212</v>
-      </c>
-      <c r="D113" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2211</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F113" s="15" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G113" s="7"/>
+      <c r="H113" s="7"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
         <v>143</v>
       </c>
@@ -10126,13 +10904,17 @@
         <v>9</v>
       </c>
       <c r="C114" s="9">
-        <v>2216</v>
+        <v>2212</v>
       </c>
       <c r="D114" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E114" s="7"/>
+      <c r="F114" s="7"/>
+      <c r="G114" s="7"/>
+      <c r="H114" s="7"/>
+    </row>
+    <row r="115" spans="1:8" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
         <v>143</v>
       </c>
@@ -10140,13 +10922,19 @@
         <v>9</v>
       </c>
       <c r="C115" s="9">
-        <v>2315</v>
-      </c>
-      <c r="D115" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2216</v>
+      </c>
+      <c r="D115" s="8"/>
+      <c r="E115" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F115" s="15" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G115" s="7"/>
+      <c r="H115" s="7"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="8" t="s">
         <v>143</v>
       </c>
@@ -10154,13 +10942,17 @@
         <v>9</v>
       </c>
       <c r="C116" s="9">
-        <v>2590</v>
+        <v>2315</v>
       </c>
       <c r="D116" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E116" s="7"/>
+      <c r="F116" s="7"/>
+      <c r="G116" s="7"/>
+      <c r="H116" s="7"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
         <v>143</v>
       </c>
@@ -10168,13 +10960,17 @@
         <v>9</v>
       </c>
       <c r="C117" s="9">
-        <v>3077</v>
+        <v>2590</v>
       </c>
       <c r="D117" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E117" s="7"/>
+      <c r="F117" s="7"/>
+      <c r="G117" s="7"/>
+      <c r="H117" s="7"/>
+    </row>
+    <row r="118" spans="1:8" ht="63" x14ac:dyDescent="0.25">
       <c r="A118" s="8" t="s">
         <v>143</v>
       </c>
@@ -10182,13 +10978,18 @@
         <v>9</v>
       </c>
       <c r="C118" s="9">
-        <v>3082</v>
-      </c>
-      <c r="D118" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3077</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F118" s="15" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G118" s="7"/>
+      <c r="H118" s="7"/>
+    </row>
+    <row r="119" spans="1:8" ht="63" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
         <v>143</v>
       </c>
@@ -10196,13 +10997,18 @@
         <v>9</v>
       </c>
       <c r="C119" s="9">
-        <v>3090</v>
-      </c>
-      <c r="D119" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3082</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F119" s="15" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G119" s="7"/>
+      <c r="H119" s="7"/>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="8" t="s">
         <v>143</v>
       </c>
@@ -10210,13 +11016,17 @@
         <v>9</v>
       </c>
       <c r="C120" s="9">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="D120" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E120" s="7"/>
+      <c r="F120" s="7"/>
+      <c r="G120" s="7"/>
+      <c r="H120" s="7"/>
+    </row>
+    <row r="121" spans="1:8" ht="204.75" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
         <v>143</v>
       </c>
@@ -10224,13 +11034,18 @@
         <v>9</v>
       </c>
       <c r="C121" s="9">
-        <v>3151</v>
-      </c>
-      <c r="D121" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3091</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F121" s="15" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G121" s="7"/>
+      <c r="H121" s="7"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="8" t="s">
         <v>143</v>
       </c>
@@ -10238,13 +11053,17 @@
         <v>9</v>
       </c>
       <c r="C122" s="9">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="D122" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E122" s="7"/>
+      <c r="F122" s="7"/>
+      <c r="G122" s="7"/>
+      <c r="H122" s="7"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
         <v>143</v>
       </c>
@@ -10252,13 +11071,17 @@
         <v>9</v>
       </c>
       <c r="C123" s="9">
-        <v>3166</v>
+        <v>3152</v>
       </c>
       <c r="D123" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E123" s="7"/>
+      <c r="F123" s="7"/>
+      <c r="G123" s="7"/>
+      <c r="H123" s="7"/>
+    </row>
+    <row r="124" spans="1:8" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A124" s="8" t="s">
         <v>143</v>
       </c>
@@ -10266,13 +11089,18 @@
         <v>9</v>
       </c>
       <c r="C124" s="9">
-        <v>3171</v>
-      </c>
-      <c r="D124" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3166</v>
+      </c>
+      <c r="E124" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F124" s="15" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G124" s="7"/>
+      <c r="H124" s="7"/>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
         <v>143</v>
       </c>
@@ -10280,13 +11108,17 @@
         <v>9</v>
       </c>
       <c r="C125" s="9">
-        <v>3245</v>
+        <v>3171</v>
       </c>
       <c r="D125" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E125" s="7"/>
+      <c r="F125" s="7"/>
+      <c r="G125" s="7"/>
+      <c r="H125" s="7"/>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="8" t="s">
         <v>143</v>
       </c>
@@ -10294,13 +11126,17 @@
         <v>9</v>
       </c>
       <c r="C126" s="9">
-        <v>3257</v>
+        <v>3245</v>
       </c>
       <c r="D126" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E126" s="7"/>
+      <c r="F126" s="7"/>
+      <c r="G126" s="7"/>
+      <c r="H126" s="7"/>
+    </row>
+    <row r="127" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
         <v>143</v>
       </c>
@@ -10308,13 +11144,18 @@
         <v>9</v>
       </c>
       <c r="C127" s="9">
-        <v>3314</v>
-      </c>
-      <c r="D127" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3257</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F127" s="15" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G127" s="7"/>
+      <c r="H127" s="7"/>
+    </row>
+    <row r="128" spans="1:8" ht="63" x14ac:dyDescent="0.25">
       <c r="A128" s="8" t="s">
         <v>143</v>
       </c>
@@ -10322,13 +11163,18 @@
         <v>9</v>
       </c>
       <c r="C128" s="9">
-        <v>3480</v>
-      </c>
-      <c r="D128" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3314</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F128" s="15" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G128" s="7"/>
+      <c r="H128" s="7"/>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
         <v>143</v>
       </c>
@@ -10336,13 +11182,17 @@
         <v>9</v>
       </c>
       <c r="C129" s="9">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="D129" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E129" s="7"/>
+      <c r="F129" s="7"/>
+      <c r="G129" s="7"/>
+      <c r="H129" s="7"/>
+    </row>
+    <row r="130" spans="1:8" ht="204.75" x14ac:dyDescent="0.25">
       <c r="A130" s="8" t="s">
         <v>143</v>
       </c>
@@ -10350,13 +11200,18 @@
         <v>9</v>
       </c>
       <c r="C130" s="9">
-        <v>3536</v>
-      </c>
-      <c r="D130" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3481</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F130" s="15" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G130" s="7"/>
+      <c r="H130" s="7"/>
+    </row>
+    <row r="131" spans="1:8" ht="204.75" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
         <v>143</v>
       </c>
@@ -10364,13 +11219,18 @@
         <v>9</v>
       </c>
       <c r="C131" s="9">
-        <v>3556</v>
-      </c>
-      <c r="D131" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3536</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F131" s="15" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G131" s="7"/>
+      <c r="H131" s="7"/>
+    </row>
+    <row r="132" spans="1:8" ht="267.75" x14ac:dyDescent="0.25">
       <c r="A132" s="8" t="s">
         <v>143</v>
       </c>
@@ -10378,13 +11238,18 @@
         <v>9</v>
       </c>
       <c r="C132" s="9">
-        <v>3557</v>
-      </c>
-      <c r="D132" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3556</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F132" s="15" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G132" s="7"/>
+      <c r="H132" s="7"/>
+    </row>
+    <row r="133" spans="1:8" ht="267.75" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
         <v>143</v>
       </c>
@@ -10392,11 +11257,35 @@
         <v>9</v>
       </c>
       <c r="C133" s="9">
+        <v>3557</v>
+      </c>
+      <c r="E133" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F133" s="15" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G133" s="7"/>
+      <c r="H133" s="7"/>
+    </row>
+    <row r="134" spans="1:8" ht="267.75" x14ac:dyDescent="0.25">
+      <c r="A134" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B134" s="9">
+        <v>9</v>
+      </c>
+      <c r="C134" s="9">
         <v>3558</v>
       </c>
-      <c r="D133" s="8" t="s">
-        <v>138</v>
-      </c>
+      <c r="E134" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F134" s="15" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G134" s="7"/>
+      <c r="H134" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -36318,7 +37207,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1B92D88-400F-47B4-B24C-8836CEA21312}">
   <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
+    <tabColor theme="5" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:AA357"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -36418,43 +37307,43 @@
         <v>663</v>
       </c>
       <c r="F2" s="13" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G2" s="13" t="s">
         <v>1030</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>1031</v>
       </c>
-      <c r="H2" s="13" t="s">
-        <v>1032</v>
-      </c>
       <c r="I2" s="11" t="s">
+        <v>1046</v>
+      </c>
+      <c r="J2" s="11" t="s">
         <v>1047</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="K2" s="11" t="s">
         <v>1048</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="L2" s="11" t="s">
         <v>1049</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="M2" s="11" t="s">
         <v>1050</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="N2" s="13" t="s">
         <v>1051</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="O2" s="11" t="s">
         <v>1052</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="P2" s="11" t="s">
         <v>1053</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="Q2" s="11" t="s">
         <v>1054</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="R2" s="11" t="s">
         <v>1055</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -37372,7 +38261,7 @@
         <v>667</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -37487,7 +38376,7 @@
         <v>667</v>
       </c>
       <c r="F76" s="13" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -37529,7 +38418,7 @@
         <v>667</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -37652,13 +38541,13 @@
         <v>3</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F88" s="13" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -37669,13 +38558,13 @@
         <v>3</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F89" s="13" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -37731,13 +38620,13 @@
         <v>3</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F93" s="13" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -37846,13 +38735,13 @@
         <v>3</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F101" s="13" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -38135,7 +39024,7 @@
         <v>776</v>
       </c>
       <c r="G121" s="11" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -39077,7 +39966,7 @@
         <v>667</v>
       </c>
       <c r="F187" s="11" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -40109,7 +40998,7 @@
         <v>667</v>
       </c>
       <c r="F260" s="11" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -40460,7 +41349,7 @@
         <v>947</v>
       </c>
       <c r="G284" s="11" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="285" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
@@ -40488,7 +41377,7 @@
         <v>667</v>
       </c>
       <c r="F286" s="11" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
@@ -41006,7 +41895,7 @@
         <v>667</v>
       </c>
       <c r="F323" s="13" t="s">
-        <v>985</v>
+        <v>842</v>
       </c>
     </row>
     <row r="324" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
@@ -41020,7 +41909,7 @@
         <v>667</v>
       </c>
       <c r="F324" s="11" t="s">
-        <v>1044</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="325" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
@@ -41031,13 +41920,13 @@
         <v>8</v>
       </c>
       <c r="C325" s="4" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F325" s="11" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -41048,7 +41937,7 @@
         <v>8</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="D326" s="1" t="s">
         <v>667</v>
@@ -41062,7 +41951,7 @@
         <v>8</v>
       </c>
       <c r="C327" s="4" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D327" s="1" t="s">
         <v>667</v>
@@ -41076,7 +41965,7 @@
         <v>8</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D328" s="1" t="s">
         <v>667</v>
@@ -41090,7 +41979,7 @@
         <v>8</v>
       </c>
       <c r="C329" s="4" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="D329" s="1" t="s">
         <v>667</v>
@@ -41104,7 +41993,7 @@
         <v>8</v>
       </c>
       <c r="C330" s="4" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="D330" s="1" t="s">
         <v>667</v>
@@ -41118,7 +42007,7 @@
         <v>8</v>
       </c>
       <c r="C331" s="4" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D331" s="1" t="s">
         <v>667</v>
@@ -41135,7 +42024,7 @@
         <v>667</v>
       </c>
       <c r="F332" s="11" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="333" spans="1:6" ht="63" x14ac:dyDescent="0.25">
@@ -41146,13 +42035,13 @@
         <v>9</v>
       </c>
       <c r="C333" s="4" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F333" s="11" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -41163,7 +42052,7 @@
         <v>9</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="D334" s="1" t="s">
         <v>667</v>
@@ -41177,7 +42066,7 @@
         <v>9</v>
       </c>
       <c r="C335" s="4" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D335" s="1" t="s">
         <v>667</v>
@@ -41191,7 +42080,7 @@
         <v>9</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>667</v>
@@ -41208,7 +42097,7 @@
         <v>9</v>
       </c>
       <c r="C337" s="4" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D337" s="1" t="s">
         <v>667</v>
@@ -41222,13 +42111,13 @@
         <v>9</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F338" s="11" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="339" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
@@ -41239,13 +42128,13 @@
         <v>9</v>
       </c>
       <c r="C339" s="4" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F339" s="11" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="340" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
@@ -41256,13 +42145,13 @@
         <v>9</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F340" s="11" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="341" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
@@ -41273,13 +42162,13 @@
         <v>9</v>
       </c>
       <c r="C341" s="4" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F341" s="11" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -41290,7 +42179,7 @@
         <v>9</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D342" s="1" t="s">
         <v>667</v>
@@ -41304,7 +42193,7 @@
         <v>9</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D343" s="1" t="s">
         <v>667</v>
@@ -41318,13 +42207,13 @@
         <v>9</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F344" s="11" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -41335,13 +42224,13 @@
         <v>9</v>
       </c>
       <c r="C345" s="4" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F345" s="13" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="346" spans="1:6" ht="63" x14ac:dyDescent="0.25">
@@ -41352,13 +42241,13 @@
         <v>9</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F346" s="11" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="347" spans="1:6" ht="63" x14ac:dyDescent="0.25">
@@ -41369,13 +42258,13 @@
         <v>9</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F347" s="11" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -41386,7 +42275,7 @@
         <v>9</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="D348" s="1" t="s">
         <v>667</v>
@@ -41400,13 +42289,13 @@
         <v>9</v>
       </c>
       <c r="C349" s="4" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F349" s="11" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="350" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
@@ -41417,13 +42306,13 @@
         <v>9</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F350" s="11" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -41434,13 +42323,13 @@
         <v>9</v>
       </c>
       <c r="C351" s="4" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F351" s="13" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -41451,7 +42340,7 @@
         <v>9</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="D352" s="1" t="s">
         <v>667</v>
@@ -41465,13 +42354,13 @@
         <v>9</v>
       </c>
       <c r="C353" s="4" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F353" s="11" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="354" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
@@ -41482,13 +42371,13 @@
         <v>9</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F354" s="11" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="355" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
@@ -41499,13 +42388,13 @@
         <v>9</v>
       </c>
       <c r="C355" s="4" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F355" s="11" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="356" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
@@ -41516,13 +42405,13 @@
         <v>9</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F356" s="11" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -41533,13 +42422,13 @@
         <v>9</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>667</v>
       </c>
       <c r="F357" s="13" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
   </sheetData>
@@ -41837,5 +42726,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F42932-D23F-4ACA-89F9-CC0704771B44}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B02E8AA-A911-4DC7-BB9C-889657F93CEA}"/>
 </file>
--- a/dg_list.xlsx
+++ b/dg_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ialasia.sharepoint.com/sites/IALDGDESK/Shared Documents/General/Query System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="423" documentId="8_{283FAEA1-D05F-4837-8EED-DE95F23FE8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F5EECC6-0009-4AA2-97FA-D08F53EC9A63}"/>
+  <xr:revisionPtr revIDLastSave="483" documentId="8_{283FAEA1-D05F-4837-8EED-DE95F23FE8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{397F4BB5-D169-4D6D-B6FC-D287B74612F4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="27630" windowHeight="16440" firstSheet="3" activeTab="8" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="27630" windowHeight="16440" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
   </bookViews>
   <sheets>
     <sheet name="IAL_20250923" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6459" uniqueCount="1081">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6513" uniqueCount="1090">
   <si>
     <t>UN Number</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5038,6 +5038,52 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Only residue tanks with flashpoints of –18°C or lower are acceptable. Rest All Strictly Prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All DG shipments declared under IMO Class 5.1 are strictly prohibited on the ASL-owned vessels.
+For all IMO Class 5.1 shipments loaded on other ESL-owned vessels, a Vanning Survey Report is mandatory prior to loading.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All types of waste cargo either dg or non-dg is strictly prohibited.
+The chemical substance Divinylbenzene is strictly prohibited.
+For all chemical substances shipped under UNNO 3077 and UNNO 3082, confirmation must be obtained from the shipper that the chemical substances are not classified as "dg waste".</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lithium Batteries
+1. Lithium Batteries Declared as Hazardous Goods (DG)
+Strictly Prohibited:
+UN3480 – Lithium-ion Batteries
+UN3090 – Lithium Metal Batteries
+Other types of Lithium Battery Shipments (DG):
+Acceptance may be considered subject to the following conditions:
+Only brand-new lithium batteries are acceptable.
+Lithium batteries declared as hazardous must not be co-loaded with any other DG cargo in the same container.
+Stowage category "ON DECK FOR LITHIUM BATTERIES" must be informed to respective port terminal and correctly updated in the CBF documents.
+2. Lithium Batteries Declared as Non-Hazardous Goods (Non-DG)
+All Lithium Batteries declared non-hazardous are Strictly Prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batteries are prohibited,if batteries (DG/non-DG) are used, defective, damaged and waste. Only brand new batteries are accepted.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All waste/used/damaged/defective batteries are prohibited whether they are DG or Non-DG.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DG and Non-DG lithium batteries, as well as Non-DG sodium ion batteries, must be stowed on deck, away from heat and protected from sunlight.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All vehicles powered by lithium ion, lithium metal, or sodium ion batteries are prohibited.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">DG Cargo in Liquid Form – Packed in Single Plastic Outer Packaging
 For Dangerous Goods in liquid form packed in single plastic outer packaging (UN Packaging Codes: 1H1 / 1H2 Plastic Drums or 3H1 / 3H2 Plastic Jerricans), the following conditions must be met: </t>
@@ -5061,41 +5107,30 @@
         <family val="1"/>
       </rPr>
       <t>Each tier of drums or jerricans must be separated with timber sheet partitions. 
-The door side must be secured with solid materials to prevent any cargo movement during
-transit.
+The door side must be secured with solid materials to prevent any cargo movement during transit.
 Shippers must submit stuffing photos for each container prior to loading any DG units.
 The permitted use of 1H1 / 1H2 plastics drums and 3H1 / 3H2 jerricans as single packagings shall be two years from their date of manufacture.</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Only residue tanks with flashpoints of –18°C or lower are acceptable. Rest All Strictly Prohibited</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>All DG shipments declared under IMO Class 5.1 are strictly prohibited on the ASL-owned vessels.
-For all IMO Class 5.1 shipments loaded on other ESL-owned vessels, a Vanning Survey Report is mandatory prior to loading.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>All types of waste cargo either dg or non-dg is strictly prohibited.
-The chemical substance Divinylbenzene is strictly prohibited.
-For all chemical substances shipped under UNNO 3077 and UNNO 3082, confirmation must be obtained from the shipper that the chemical substances are not classified as "dg waste".</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lithium Batteries
-1. Lithium Batteries Declared as Hazardous Goods (DG)
-Strictly Prohibited:
-UN3480 – Lithium-ion Batteries
-UN3090 – Lithium Metal Batteries
-Other types of Lithium Battery Shipments (DG):
-Acceptance may be considered subject to the following conditions:
-Only brand-new lithium batteries are acceptable.
-Lithium batteries declared as hazardous must not be co-loaded with any other DG cargo in the same container.
-Stowage category "ON DECK FOR LITHIUM BATTERIES" must be informed to respective port terminal and correctly updated in the CBF documents.
-2. Lithium Batteries Declared as Non-Hazardous Goods (Non-DG)
-All Lithium Batteries declared non-hazardous are Strictly Prohibited</t>
+    <t>2794</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2795</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3028</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3171</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3496</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5580,7 +5615,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:R216"/>
+  <dimension ref="A1:R221"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.625" style="1" customWidth="1"/>
@@ -5668,13 +5703,13 @@
         <v>324</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>100</v>
+        <v>1081</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>118</v>
+        <v>1083</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>114</v>
+        <v>1082</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>255</v>
@@ -8399,16 +8434,13 @@
         <v>8</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>98</v>
+        <v>1085</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>4</v>
+        <v>666</v>
       </c>
       <c r="F195" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G195" s="13" t="s">
-        <v>99</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
@@ -8419,10 +8451,13 @@
         <v>8</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>4</v>
+        <v>1086</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="F196" s="13" t="s">
+        <v>1081</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
@@ -8433,10 +8468,16 @@
         <v>8</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>4</v>
+        <v>98</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F197" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="G197" s="13" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
@@ -8447,10 +8488,13 @@
         <v>8</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>4</v>
+        <v>1087</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="F198" s="13" t="s">
+        <v>1081</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
@@ -8461,13 +8505,10 @@
         <v>8</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F199" s="13" t="s">
-        <v>106</v>
+        <v>101</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
@@ -8475,10 +8516,10 @@
         <v>3</v>
       </c>
       <c r="B200" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>4</v>
@@ -8489,10 +8530,10 @@
         <v>3</v>
       </c>
       <c r="B201" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>4</v>
@@ -8503,13 +8544,16 @@
         <v>3</v>
       </c>
       <c r="B202" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>4</v>
+        <v>104</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F202" s="13" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
@@ -8520,19 +8564,10 @@
         <v>9</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F203" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G203" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="H203" s="13" t="s">
-        <v>112</v>
+        <v>107</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
@@ -8543,19 +8578,10 @@
         <v>9</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F204" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G204" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="H204" s="13" t="s">
-        <v>113</v>
+        <v>108</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
@@ -8566,7 +8592,7 @@
         <v>9</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>4</v>
@@ -8580,10 +8606,19 @@
         <v>9</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>4</v>
+        <v>110</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F206" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="G206" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H206" s="13" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
@@ -8594,7 +8629,7 @@
         <v>9</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>4</v>
@@ -8603,7 +8638,10 @@
         <v>100</v>
       </c>
       <c r="G207" s="13" t="s">
-        <v>119</v>
+        <v>114</v>
+      </c>
+      <c r="H207" s="13" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
@@ -8614,7 +8652,7 @@
         <v>9</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>4</v>
@@ -8628,13 +8666,10 @@
         <v>9</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F209" s="13" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
@@ -8645,7 +8680,7 @@
         <v>9</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>4</v>
@@ -8654,13 +8689,7 @@
         <v>100</v>
       </c>
       <c r="G210" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="H210" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="I210" s="13" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
@@ -8671,10 +8700,13 @@
         <v>9</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>4</v>
+        <v>1088</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F211" s="13" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
@@ -8685,13 +8717,10 @@
         <v>9</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F212" s="13" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
@@ -8702,22 +8731,13 @@
         <v>9</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E213" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D213" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F213" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G213" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="H213" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="I213" s="13" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
@@ -8728,13 +8748,22 @@
         <v>9</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D214" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E214" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F214" s="13" t="s">
-        <v>118</v>
+        <v>100</v>
+      </c>
+      <c r="G214" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H214" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="I214" s="13" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
@@ -8745,13 +8774,13 @@
         <v>9</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D215" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E215" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F215" s="13" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
@@ -8762,12 +8791,103 @@
         <v>9</v>
       </c>
       <c r="C216" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B217" s="4">
+        <v>9</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F217" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B218" s="4">
+        <v>9</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F218" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="G218" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H218" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I218" s="13" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B219" s="4">
+        <v>9</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F219" s="13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B220" s="4">
+        <v>9</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F220" s="13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B221" s="4">
+        <v>9</v>
+      </c>
+      <c r="C221" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D216" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F216" s="13" t="s">
+      <c r="D221" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F221" s="13" t="s">
         <v>118</v>
       </c>
     </row>
@@ -8783,7 +8903,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:Q134"/>
+  <dimension ref="A1:P135"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.625" customWidth="1"/>
@@ -8801,10 +8921,9 @@
     <col min="14" max="14" width="107" customWidth="1"/>
     <col min="15" max="15" width="33.875" customWidth="1"/>
     <col min="16" max="16" width="90.875" customWidth="1"/>
-    <col min="17" max="17" width="50.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -8853,11 +8972,8 @@
       <c r="P1" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="Q1" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="393.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:16" s="1" customFormat="1" ht="393.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1066</v>
       </c>
@@ -8890,19 +9006,16 @@
         <v>1074</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="O2" s="11" t="s">
         <v>1075</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>1076</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>143</v>
       </c>
@@ -8918,7 +9031,7 @@
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>143</v>
       </c>
@@ -8934,7 +9047,7 @@
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>143</v>
       </c>
@@ -8950,7 +9063,7 @@
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>143</v>
       </c>
@@ -8966,7 +9079,7 @@
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>143</v>
       </c>
@@ -8982,7 +9095,7 @@
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>143</v>
       </c>
@@ -8998,7 +9111,7 @@
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>143</v>
       </c>
@@ -9014,7 +9127,7 @@
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>143</v>
       </c>
@@ -9032,7 +9145,7 @@
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:17" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>143</v>
       </c>
@@ -9050,7 +9163,7 @@
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>143</v>
       </c>
@@ -9068,7 +9181,7 @@
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>143</v>
       </c>
@@ -9086,7 +9199,7 @@
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>143</v>
       </c>
@@ -9104,7 +9217,7 @@
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>143</v>
       </c>
@@ -9122,7 +9235,7 @@
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>143</v>
       </c>
@@ -9228,7 +9341,7 @@
         <v>1057</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H21" s="7"/>
     </row>
@@ -10111,21 +10224,21 @@
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B70" s="9">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C70" s="9">
-        <v>1479</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F70" s="11" t="s">
+        <v>1077</v>
+      </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
     </row>
@@ -10137,7 +10250,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C71" s="9">
-        <v>1748</v>
+        <v>1479</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>138</v>
@@ -10155,7 +10268,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C72" s="9">
-        <v>1942</v>
+        <v>1748</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>138</v>
@@ -10173,7 +10286,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C73" s="9">
-        <v>2067</v>
+        <v>1942</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>138</v>
@@ -10191,10 +10304,10 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C74" s="9">
-        <v>2208</v>
+        <v>2067</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>138</v>
+        <v>666</v>
       </c>
       <c r="E74" s="7"/>
       <c r="F74" s="7"/>
@@ -10209,7 +10322,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C75" s="9">
-        <v>2426</v>
+        <v>2208</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>138</v>
@@ -10219,7 +10332,7 @@
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
     </row>
-    <row r="76" spans="1:8" ht="157.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
         <v>143</v>
       </c>
@@ -10227,15 +10340,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C76" s="9">
-        <v>2465</v>
+        <v>2426</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>138</v>
       </c>
       <c r="E76" s="7"/>
-      <c r="F76" s="11" t="s">
-        <v>1074</v>
-      </c>
+      <c r="F76" s="7"/>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
     </row>
@@ -10247,7 +10358,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C77" s="9">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>138</v>
@@ -10259,7 +10370,7 @@
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A78" s="8" t="s">
         <v>143</v>
       </c>
@@ -10267,13 +10378,15 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C78" s="9">
-        <v>2880</v>
+        <v>2466</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>138</v>
       </c>
       <c r="E78" s="7"/>
-      <c r="F78" s="7"/>
+      <c r="F78" s="11" t="s">
+        <v>1074</v>
+      </c>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
     </row>
@@ -10285,7 +10398,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C79" s="9">
-        <v>3375</v>
+        <v>2880</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>138</v>
@@ -10303,7 +10416,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C80" s="9">
-        <v>3485</v>
+        <v>3375</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>138</v>
@@ -10321,7 +10434,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C81" s="9">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>138</v>
@@ -10339,7 +10452,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C82" s="9">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>138</v>
@@ -10354,10 +10467,10 @@
         <v>143</v>
       </c>
       <c r="B83" s="9">
-        <v>5.2</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="C83" s="9">
-        <v>3101</v>
+        <v>3487</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>138</v>
@@ -10375,7 +10488,7 @@
         <v>5.2</v>
       </c>
       <c r="C84" s="9">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>138</v>
@@ -10393,7 +10506,7 @@
         <v>5.2</v>
       </c>
       <c r="C85" s="9">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>138</v>
@@ -10411,7 +10524,7 @@
         <v>5.2</v>
       </c>
       <c r="C86" s="9">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>138</v>
@@ -10429,7 +10542,7 @@
         <v>5.2</v>
       </c>
       <c r="C87" s="9">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>138</v>
@@ -10447,7 +10560,7 @@
         <v>5.2</v>
       </c>
       <c r="C88" s="9">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>138</v>
@@ -10465,7 +10578,7 @@
         <v>5.2</v>
       </c>
       <c r="C89" s="9">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>138</v>
@@ -10483,7 +10596,7 @@
         <v>5.2</v>
       </c>
       <c r="C90" s="9">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>138</v>
@@ -10501,7 +10614,7 @@
         <v>5.2</v>
       </c>
       <c r="C91" s="9">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>138</v>
@@ -10519,7 +10632,7 @@
         <v>5.2</v>
       </c>
       <c r="C92" s="9">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="D92" s="8" t="s">
         <v>138</v>
@@ -10537,7 +10650,7 @@
         <v>5.2</v>
       </c>
       <c r="C93" s="9">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="D93" s="8" t="s">
         <v>138</v>
@@ -10555,7 +10668,7 @@
         <v>5.2</v>
       </c>
       <c r="C94" s="9">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>138</v>
@@ -10573,7 +10686,7 @@
         <v>5.2</v>
       </c>
       <c r="C95" s="9">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>138</v>
@@ -10591,7 +10704,7 @@
         <v>5.2</v>
       </c>
       <c r="C96" s="9">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>138</v>
@@ -10609,7 +10722,7 @@
         <v>5.2</v>
       </c>
       <c r="C97" s="9">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>138</v>
@@ -10627,7 +10740,7 @@
         <v>5.2</v>
       </c>
       <c r="C98" s="9">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>138</v>
@@ -10645,7 +10758,7 @@
         <v>5.2</v>
       </c>
       <c r="C99" s="9">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>138</v>
@@ -10663,7 +10776,7 @@
         <v>5.2</v>
       </c>
       <c r="C100" s="9">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>138</v>
@@ -10681,7 +10794,7 @@
         <v>5.2</v>
       </c>
       <c r="C101" s="9">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>138</v>
@@ -10699,7 +10812,7 @@
         <v>5.2</v>
       </c>
       <c r="C102" s="9">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>138</v>
@@ -10714,10 +10827,10 @@
         <v>143</v>
       </c>
       <c r="B103" s="9">
-        <v>6.1</v>
+        <v>5.2</v>
       </c>
       <c r="C103" s="9">
-        <v>1244</v>
+        <v>3120</v>
       </c>
       <c r="D103" s="8" t="s">
         <v>138</v>
@@ -10735,7 +10848,7 @@
         <v>6.1</v>
       </c>
       <c r="C104" s="9">
-        <v>1649</v>
+        <v>1244</v>
       </c>
       <c r="D104" s="8" t="s">
         <v>138</v>
@@ -10753,7 +10866,7 @@
         <v>6.1</v>
       </c>
       <c r="C105" s="9">
-        <v>2016</v>
+        <v>1649</v>
       </c>
       <c r="D105" s="8" t="s">
         <v>138</v>
@@ -10771,7 +10884,7 @@
         <v>6.1</v>
       </c>
       <c r="C106" s="9">
-        <v>3172</v>
+        <v>2016</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>138</v>
@@ -10786,9 +10899,11 @@
         <v>143</v>
       </c>
       <c r="B107" s="9">
-        <v>6.2</v>
-      </c>
-      <c r="C107" s="9"/>
+        <v>6.1</v>
+      </c>
+      <c r="C107" s="9">
+        <v>3172</v>
+      </c>
       <c r="D107" s="8" t="s">
         <v>138</v>
       </c>
@@ -10802,7 +10917,7 @@
         <v>143</v>
       </c>
       <c r="B108" s="9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="C108" s="9"/>
       <c r="D108" s="8" t="s">
@@ -10818,11 +10933,9 @@
         <v>143</v>
       </c>
       <c r="B109" s="9">
-        <v>8</v>
-      </c>
-      <c r="C109" s="9">
-        <v>2031</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C109" s="9"/>
       <c r="D109" s="8" t="s">
         <v>138</v>
       </c>
@@ -10839,7 +10952,7 @@
         <v>8</v>
       </c>
       <c r="C110" s="9">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="D110" s="8" t="s">
         <v>138</v>
@@ -10857,7 +10970,7 @@
         <v>8</v>
       </c>
       <c r="C111" s="9">
-        <v>3145</v>
+        <v>2032</v>
       </c>
       <c r="D111" s="8" t="s">
         <v>138</v>
@@ -10872,10 +10985,10 @@
         <v>143</v>
       </c>
       <c r="B112" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C112" s="9">
-        <v>2071</v>
+        <v>3145</v>
       </c>
       <c r="D112" s="8" t="s">
         <v>138</v>
@@ -10885,7 +10998,7 @@
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
     </row>
-    <row r="113" spans="1:8" ht="63" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
         <v>143</v>
       </c>
@@ -10893,18 +11006,17 @@
         <v>9</v>
       </c>
       <c r="C113" s="9">
-        <v>2211</v>
-      </c>
-      <c r="E113" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="F113" s="15" t="s">
-        <v>1062</v>
-      </c>
+        <v>2071</v>
+      </c>
+      <c r="D113" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E113" s="7"/>
+      <c r="F113" s="7"/>
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" ht="63" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
         <v>143</v>
       </c>
@@ -10912,17 +11024,18 @@
         <v>9</v>
       </c>
       <c r="C114" s="9">
-        <v>2212</v>
-      </c>
-      <c r="D114" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="E114" s="7"/>
-      <c r="F114" s="7"/>
+        <v>2211</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F114" s="15" t="s">
+        <v>1062</v>
+      </c>
       <c r="G114" s="7"/>
       <c r="H114" s="7"/>
     </row>
-    <row r="115" spans="1:8" ht="173.25" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
         <v>143</v>
       </c>
@@ -10930,19 +11043,17 @@
         <v>9</v>
       </c>
       <c r="C115" s="9">
-        <v>2216</v>
-      </c>
-      <c r="D115" s="8"/>
-      <c r="E115" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="F115" s="15" t="s">
-        <v>1060</v>
-      </c>
+        <v>2212</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E115" s="7"/>
+      <c r="F115" s="7"/>
       <c r="G115" s="7"/>
       <c r="H115" s="7"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A116" s="8" t="s">
         <v>143</v>
       </c>
@@ -10950,13 +11061,15 @@
         <v>9</v>
       </c>
       <c r="C116" s="9">
-        <v>2315</v>
-      </c>
-      <c r="D116" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="E116" s="7"/>
-      <c r="F116" s="7"/>
+        <v>2216</v>
+      </c>
+      <c r="D116" s="8"/>
+      <c r="E116" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F116" s="15" t="s">
+        <v>1060</v>
+      </c>
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
     </row>
@@ -10968,7 +11081,7 @@
         <v>9</v>
       </c>
       <c r="C117" s="9">
-        <v>2590</v>
+        <v>2315</v>
       </c>
       <c r="D117" s="8" t="s">
         <v>138</v>
@@ -10978,7 +11091,7 @@
       <c r="G117" s="7"/>
       <c r="H117" s="7"/>
     </row>
-    <row r="118" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="8" t="s">
         <v>143</v>
       </c>
@@ -10986,14 +11099,13 @@
         <v>9</v>
       </c>
       <c r="C118" s="9">
-        <v>3077</v>
-      </c>
-      <c r="E118" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="F118" s="15" t="s">
-        <v>1079</v>
-      </c>
+        <v>2590</v>
+      </c>
+      <c r="D118" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E118" s="7"/>
+      <c r="F118" s="7"/>
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
     </row>
@@ -11005,18 +11117,18 @@
         <v>9</v>
       </c>
       <c r="C119" s="9">
-        <v>3082</v>
+        <v>3077</v>
       </c>
       <c r="E119" s="8" t="s">
         <v>138</v>
       </c>
       <c r="F119" s="15" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="G119" s="7"/>
       <c r="H119" s="7"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A120" s="8" t="s">
         <v>143</v>
       </c>
@@ -11024,17 +11136,18 @@
         <v>9</v>
       </c>
       <c r="C120" s="9">
-        <v>3090</v>
-      </c>
-      <c r="D120" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="E120" s="7"/>
-      <c r="F120" s="7"/>
+        <v>3082</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F120" s="15" t="s">
+        <v>1078</v>
+      </c>
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
     </row>
-    <row r="121" spans="1:8" ht="189" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
         <v>143</v>
       </c>
@@ -11042,18 +11155,17 @@
         <v>9</v>
       </c>
       <c r="C121" s="9">
-        <v>3091</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="F121" s="15" t="s">
-        <v>1080</v>
-      </c>
+        <v>3090</v>
+      </c>
+      <c r="D121" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E121" s="7"/>
+      <c r="F121" s="7"/>
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" ht="189" x14ac:dyDescent="0.25">
       <c r="A122" s="8" t="s">
         <v>143</v>
       </c>
@@ -11061,13 +11173,14 @@
         <v>9</v>
       </c>
       <c r="C122" s="9">
-        <v>3151</v>
-      </c>
-      <c r="D122" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="E122" s="7"/>
-      <c r="F122" s="7"/>
+        <v>3091</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F122" s="15" t="s">
+        <v>1079</v>
+      </c>
       <c r="G122" s="7"/>
       <c r="H122" s="7"/>
     </row>
@@ -11079,7 +11192,7 @@
         <v>9</v>
       </c>
       <c r="C123" s="9">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="D123" s="8" t="s">
         <v>138</v>
@@ -11089,7 +11202,7 @@
       <c r="G123" s="7"/>
       <c r="H123" s="7"/>
     </row>
-    <row r="124" spans="1:8" ht="110.25" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="8" t="s">
         <v>143</v>
       </c>
@@ -11097,18 +11210,17 @@
         <v>9</v>
       </c>
       <c r="C124" s="9">
-        <v>3166</v>
-      </c>
-      <c r="E124" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="F124" s="15" t="s">
-        <v>1063</v>
-      </c>
+        <v>3152</v>
+      </c>
+      <c r="D124" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E124" s="7"/>
+      <c r="F124" s="7"/>
       <c r="G124" s="7"/>
       <c r="H124" s="7"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
         <v>143</v>
       </c>
@@ -11116,13 +11228,14 @@
         <v>9</v>
       </c>
       <c r="C125" s="9">
-        <v>3171</v>
-      </c>
-      <c r="D125" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="E125" s="7"/>
-      <c r="F125" s="7"/>
+        <v>3166</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F125" s="15" t="s">
+        <v>1063</v>
+      </c>
       <c r="G125" s="7"/>
       <c r="H125" s="7"/>
     </row>
@@ -11134,7 +11247,7 @@
         <v>9</v>
       </c>
       <c r="C126" s="9">
-        <v>3245</v>
+        <v>3171</v>
       </c>
       <c r="D126" s="8" t="s">
         <v>138</v>
@@ -11144,7 +11257,7 @@
       <c r="G126" s="7"/>
       <c r="H126" s="7"/>
     </row>
-    <row r="127" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
         <v>143</v>
       </c>
@@ -11152,18 +11265,17 @@
         <v>9</v>
       </c>
       <c r="C127" s="9">
-        <v>3257</v>
-      </c>
-      <c r="E127" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="F127" s="15" t="s">
-        <v>1064</v>
-      </c>
+        <v>3245</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E127" s="7"/>
+      <c r="F127" s="7"/>
       <c r="G127" s="7"/>
       <c r="H127" s="7"/>
     </row>
-    <row r="128" spans="1:8" ht="63" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A128" s="8" t="s">
         <v>143</v>
       </c>
@@ -11171,18 +11283,18 @@
         <v>9</v>
       </c>
       <c r="C128" s="9">
-        <v>3314</v>
+        <v>3257</v>
       </c>
       <c r="E128" s="8" t="s">
         <v>138</v>
       </c>
       <c r="F128" s="15" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="G128" s="7"/>
       <c r="H128" s="7"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" ht="63" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
         <v>143</v>
       </c>
@@ -11190,17 +11302,18 @@
         <v>9</v>
       </c>
       <c r="C129" s="9">
-        <v>3480</v>
-      </c>
-      <c r="D129" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="E129" s="7"/>
-      <c r="F129" s="7"/>
+        <v>3314</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F129" s="15" t="s">
+        <v>1062</v>
+      </c>
       <c r="G129" s="7"/>
       <c r="H129" s="7"/>
     </row>
-    <row r="130" spans="1:8" ht="189" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="8" t="s">
         <v>143</v>
       </c>
@@ -11208,14 +11321,13 @@
         <v>9</v>
       </c>
       <c r="C130" s="9">
-        <v>3481</v>
-      </c>
-      <c r="E130" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="F130" s="15" t="s">
-        <v>1080</v>
-      </c>
+        <v>3480</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E130" s="7"/>
+      <c r="F130" s="7"/>
       <c r="G130" s="7"/>
       <c r="H130" s="7"/>
     </row>
@@ -11227,18 +11339,18 @@
         <v>9</v>
       </c>
       <c r="C131" s="9">
-        <v>3536</v>
+        <v>3481</v>
       </c>
       <c r="E131" s="8" t="s">
         <v>138</v>
       </c>
       <c r="F131" s="15" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="G131" s="7"/>
       <c r="H131" s="7"/>
     </row>
-    <row r="132" spans="1:8" ht="267.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" ht="189" x14ac:dyDescent="0.25">
       <c r="A132" s="8" t="s">
         <v>143</v>
       </c>
@@ -11246,13 +11358,13 @@
         <v>9</v>
       </c>
       <c r="C132" s="9">
-        <v>3556</v>
+        <v>3536</v>
       </c>
       <c r="E132" s="8" t="s">
         <v>138</v>
       </c>
       <c r="F132" s="15" t="s">
-        <v>1065</v>
+        <v>1079</v>
       </c>
       <c r="G132" s="7"/>
       <c r="H132" s="7"/>
@@ -11265,7 +11377,7 @@
         <v>9</v>
       </c>
       <c r="C133" s="9">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="E133" s="8" t="s">
         <v>138</v>
@@ -11284,7 +11396,7 @@
         <v>9</v>
       </c>
       <c r="C134" s="9">
-        <v>3558</v>
+        <v>3557</v>
       </c>
       <c r="E134" s="8" t="s">
         <v>138</v>
@@ -11294,6 +11406,25 @@
       </c>
       <c r="G134" s="7"/>
       <c r="H134" s="7"/>
+    </row>
+    <row r="135" spans="1:8" ht="267.75" x14ac:dyDescent="0.25">
+      <c r="A135" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B135" s="9">
+        <v>9</v>
+      </c>
+      <c r="C135" s="9">
+        <v>3558</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F135" s="15" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G135" s="7"/>
+      <c r="H135" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -11306,7 +11437,7 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:J302"/>
+  <dimension ref="A1:K309"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.625" style="1" customWidth="1"/>
@@ -11355,7 +11486,7 @@
         <v>351</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>247</v>
+        <v>1080</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>256</v>
@@ -15159,7 +15290,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>144</v>
       </c>
@@ -15173,7 +15304,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>144</v>
       </c>
@@ -15187,7 +15318,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>144</v>
       </c>
@@ -15201,7 +15332,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>144</v>
       </c>
@@ -15215,7 +15346,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>144</v>
       </c>
@@ -15229,7 +15360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>144</v>
       </c>
@@ -15243,7 +15374,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>144</v>
       </c>
@@ -15257,7 +15388,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>144</v>
       </c>
@@ -15268,7 +15399,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>144</v>
       </c>
@@ -15279,7 +15410,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>144</v>
       </c>
@@ -15293,7 +15424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>144</v>
       </c>
@@ -15307,7 +15438,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>144</v>
       </c>
@@ -15321,7 +15452,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>144</v>
       </c>
@@ -15335,7 +15466,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>144</v>
       </c>
@@ -15349,7 +15480,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>144</v>
       </c>
@@ -15357,13 +15488,16 @@
         <v>8</v>
       </c>
       <c r="C287" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D287" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1085</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F287" s="13" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>144</v>
       </c>
@@ -15371,10 +15505,13 @@
         <v>8</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D288" s="1" t="s">
-        <v>4</v>
+        <v>1086</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F288" s="13" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
@@ -15385,10 +15522,13 @@
         <v>8</v>
       </c>
       <c r="C289" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D289" s="1" t="s">
-        <v>4</v>
+        <v>98</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F289" s="13" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -15396,30 +15536,30 @@
         <v>144</v>
       </c>
       <c r="B290" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D290" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+        <v>1087</v>
+      </c>
+      <c r="E290" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F290" s="13" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B291" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C291" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="E291" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F291" s="11" t="s">
-        <v>259</v>
+        <v>101</v>
+      </c>
+      <c r="D291" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
@@ -15427,19 +15567,13 @@
         <v>144</v>
       </c>
       <c r="B292" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E292" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F292" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="G292" s="13" t="s">
-        <v>248</v>
+        <v>102</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
@@ -15447,10 +15581,10 @@
         <v>144</v>
       </c>
       <c r="B293" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C293" s="4" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D293" s="1" t="s">
         <v>4</v>
@@ -15464,13 +15598,13 @@
         <v>9</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>144</v>
       </c>
@@ -15478,16 +15612,16 @@
         <v>9</v>
       </c>
       <c r="C295" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D295" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E295" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F295" s="11" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>144</v>
       </c>
@@ -15495,7 +15629,7 @@
         <v>9</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>4</v>
@@ -15503,25 +15637,28 @@
       <c r="F296" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="G296" s="11" t="s">
-        <v>260</v>
+      <c r="G296" s="13" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B297" s="4">
-        <v>9</v>
+      <c r="B297" s="4" t="s">
+        <v>646</v>
       </c>
       <c r="C297" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D297" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="E297" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F297" s="13" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>144</v>
       </c>
@@ -15529,16 +15666,13 @@
         <v>9</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D298" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F298" s="11" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>144</v>
       </c>
@@ -15546,39 +15680,30 @@
         <v>9</v>
       </c>
       <c r="C299" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E299" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F299" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="G299" s="11" t="s">
-        <v>260</v>
+        <v>116</v>
+      </c>
+      <c r="D299" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B300" s="4">
-        <v>9</v>
+      <c r="B300" s="4" t="s">
+        <v>646</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>130</v>
+        <v>1004</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F300" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="G300" s="13" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>144</v>
       </c>
@@ -15586,19 +15711,16 @@
         <v>9</v>
       </c>
       <c r="C301" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E301" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F301" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="G301" s="13" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F301" s="11" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>144</v>
       </c>
@@ -15606,17 +15728,158 @@
         <v>9</v>
       </c>
       <c r="C302" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E302" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F302" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="G302" s="11" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A303" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B303" s="4">
+        <v>9</v>
+      </c>
+      <c r="C303" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E303" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F303" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="G303" s="11"/>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A304" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B304" s="4">
+        <v>9</v>
+      </c>
+      <c r="C304" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="305" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A305" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B305" s="4">
+        <v>9</v>
+      </c>
+      <c r="C305" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F305" s="11" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="306" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A306" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B306" s="4">
+        <v>9</v>
+      </c>
+      <c r="C306" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E306" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F306" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="G306" s="11" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A307" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B307" s="4">
+        <v>9</v>
+      </c>
+      <c r="C307" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E307" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F307" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="G307" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="H307" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="K307" s="13"/>
+    </row>
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A308" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B308" s="4">
+        <v>9</v>
+      </c>
+      <c r="C308" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E308" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F308" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="G308" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="H308" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="K308" s="13"/>
+    </row>
+    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A309" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B309" s="4">
+        <v>9</v>
+      </c>
+      <c r="C309" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E302" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F302" s="13" t="s">
+      <c r="E309" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F309" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="G309" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="G302" s="13" t="s">
+      <c r="H309" s="13" t="s">
         <v>249</v>
       </c>
+      <c r="K309" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -42727,7 +42990,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15C0222B-442F-4A58-BCA1-53A14B33859D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53B60D16-DC4C-4137-9ADF-E43B6645E7E6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/dg_list.xlsx
+++ b/dg_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ialasia.sharepoint.com/sites/IALDGDESK/Shared Documents/General/Query System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1814" documentId="8_{283FAEA1-D05F-4837-8EED-DE95F23FE8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DB678F4-5DBB-4C45-B407-8A7D3CD79D9D}"/>
+  <xr:revisionPtr revIDLastSave="2890" documentId="8_{283FAEA1-D05F-4837-8EED-DE95F23FE8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03C903D3-CF28-4E1A-96A9-28ACE27C8132}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="810" firstSheet="3" activeTab="12" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="810" firstSheet="11" activeTab="14" xr2:uid="{2B4A3045-7B50-47EE-8DB7-F3DBBFC6F21D}"/>
   </bookViews>
   <sheets>
     <sheet name="IAL_20250923" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,8 @@
     <sheet name="COSCO_20250126" sheetId="13" r:id="rId11"/>
     <sheet name="KMTC_20250901" sheetId="14" r:id="rId12"/>
     <sheet name="PIL_20241206" sheetId="15" r:id="rId13"/>
+    <sheet name="UNIFEEDER_20250612" sheetId="16" r:id="rId14"/>
+    <sheet name="ZIM_202507" sheetId="17" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -52,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8074" uniqueCount="1207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9528" uniqueCount="1306">
   <si>
     <t>UN Number</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -5893,6 +5895,499 @@
   </si>
   <si>
     <t>All Commodities which are Prohibited Alongside at Singapore berth (Transit / Transhipment / Discharge) due to national regulations (variants of PSA Group 1, Weight Restrictions and etc.) . PIL will accept to other ports subject no restrictions to that port, space availability and not under the PIL Prohibited List.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All Types of Electric Vehicle (including E-bikes) will only be accepted as DG under IMO 9 (UN 3171/3166) - ON DECK STOWAGE ONLY Accepting PIL Bookings and for loading on PIL Owned Vessels</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battery Energy Storage Systems (BESS) classified under UN 3536 and Lithium Ion Battery (UN3480) are considered restricted commodities. The maximum quantity allowed for transport is included within the overall limit for Electric Vehicle (EV) shipments.
+The maximum count per VVD is subject to the latest PIL circular regarding the carriage of electric vessels with lithium-ion cells or batteries.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNIFEEDER</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-26 degCel and below</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(FISHMEALUNSTABILIZED) - Accepted as non-Dg if complies Special Provision 928</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All kinds of industrialhazardous waste cargo(including all waste cargo covered by Basel Convention)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Military equipment, weapon, ammunition, cartridges, hunting rifles,sporting guns- Prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DGrequiring temperature control. - Prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DGinLiveReefer,OT,FRandFB - Prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dangerous goods tobecarried in containers as bulk. - Prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllUsedBatteriesifthey are waste - Prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lithium batteries/SodiumIonBatteries (including power bank) are notacceptable for fullcontainer load</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dangerous goods carried in flexi bag. – Prohibited (For detailed info, refer Flexi PL)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Including (non-activated / carbon black) Charcoal / Bamboo Charcoal / Barbecue Charcoal / Bio wood / Carbon Briquettes/Carbon ofVegetable Origin or Packages / Coconut Shell /Hardwood / Magnesia Carbon Brick / Coal Vegetable package - Prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;Prohibited to, ONLY when the Chemical/Technical name is Calcium Hypochlorite, SDID (Sodium Dichloroisocyanurate Dihydrate), Troclosene sodium, Dihydrate, dichloro-s-triazinetrione sodium salt and 1,3-Dichloro-s-triazine-2,4,6-trione sodium salt and its synonyms.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prohibited if booking as non-DG(Battery powered Vehicle / Battery Powered Equipment)
+&lt;The Following regulations apply only to VEHICLES with Lithium-ion Batteries&gt;
+- Vehicle with used lithium-ion batteries are prohibited
+- Lithium cell or battery test summary in accordance with sub-section 38.3 of Manual test is mandatory
+- MSDS for Lithium cell or battery is mandatory</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sodium-ion battery-powered vehicles- Accepted as NON-HAZ under SP 961 / Accepted as DG under SP 962.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Allsubstances withsubsidiary explosive risks andwhich igniteonexposuretoair- Prohibited</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All commodities covered under SpecialProvision 113, 349, 350, 351, 352 353, 900, 976 ofthe IMDG code (41-22)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accepted if complies with SpecialProvision 962 For DG / Special Provision 961 For NON-DG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accepted as non-DG if complies with Special Provision 979 (Latestself-heating testreport mandatory)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Acceptedas DG if provided with 38.3 TestReport &amp; Confirmation that the batteries are New &amp; Undamaged</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(COPRA)- Accepted as DG if complies with Special Provision 926 (Moisture contentshould be lessthan 5%)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(FERROSILICON) - Accepted as non-DG if complies with SpecialProvision 39 &amp; SpecialProvision 223</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(SULPHUR)- Accepted as non-Dg if complies Special Provision 242</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(ALCOHOLIC BEVERAGES PGIII)- Accepted as non-DGif complies with SpecialProvision 144 &amp; Special Provision 145</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>For allNONHAZ Shipments with SpecialProvision - SDS, LOI &amp; Non Haz Declaration Certificate Required.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>For portAEJEA- Transshipment ofIMDG Class 5.1 - Prohibited.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>POL/POD AJMAN - Prohibited.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wet blue leather products</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>For ShanghaiWGQterminal – “Highly toxic chemicals “and “other dangerous chemicals “that are prohibited for discharge by the state for inland transportation.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZIM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Not accepted in regular Reefer containers, only when the reefers are with  “explosion-proof electrical fittings” as per IMDG Code  7.3.7.6 and a visible audible alarm and copy of the relevant certificate confirming that is provided.
+Sub-risk of 2.1 is also considered as Class 2.1 for this purpose.
+MSDS is required in order to verify the exact cargo characteristics.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prohibited as per SP90</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Not accepted in DV, If loaded in IsoTank , to be accepted only in T50 type ISOTANK subject to</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>not accepted unless the reefer's Control/Set Temperature is at least 10°C below the Flash Point, i.e. the lowest Flash Point accepted in regular reefers is -13°C.  
+Substances with Flash Point below -13°C may be accepted only in Reefers with  “explosion-proof electrical fittings” as per IMDG Code 7.7.3.2.3 or 7.7.3.2.5 5 &amp; copy of the relevant certificate confirming that is provided.
+Sub-risk of 3 is also considered as Class 3 for this purpose.
+MSDS required in order to verify the Flash Point.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZIM prohibits all self-reactive substances with subsidiary explosive risks (see SP 181 in the IMDG code)</t>
+  </si>
+  <si>
+    <t>ZIM prohibits all self-reactive substances with subsidiary explosive risks (see SP 181 in the IMDG code)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(Accept only in SOC ISOTANK, Prohibit in RF)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(Prohibited as per SP900)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Substance is prohibited except with special authorization granted by the competent authorities. 
+Require MSDS in order to have it ready in case of leakage.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prohibited for Used Batteries</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>From India in DV not accept withot  a full vanning &amp; lashing survey.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Any substance indicated in this list even if it is in "LIMITED QUANTITIES" or "EXCEPTED QUANITITIES".</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Any substance which appears in the PROHIBITED LIST of the PARTNER is not accepted.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Any ARMS &amp; WEAPONS are not accepted, other MILITARY GOODS for military purposes may be considered on a case-by-case basis by the ZIM's Global Special Cargo Division.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>All DG substances are prohibited in non – operated Reefer unit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Any substance which is PROHIBITED FOR TRANSPORT BY THE IMDG CODE is not accepted, therefore the transport of the following substances is prohibited (as per IMDG Code Special Provision 900):
+AMMONIUM HYPOCHLORITE
+AMMONIUM NITRATE liable to self-heating sufficient to initiate a decomposition
+AMMONIUM NITRITES and mixtures of an inorganic nitrite with an ammonium salt
+CHLORIC ACID, AQUEOUS SOLUTION with more than 10% chloric acid
+ETHYL NITRITE pure
+HYDROCYANIC ACID, AQUEOUS SOLUTION (HYDROGEN CYANIDE, AQUEOUS SOLUTION) with more than 20% hydrogen cyanide
+HYDROGEN CHLORIDE, REFRIGERATED LIQUID
+HYDROGEN CYANIDE SOLUTION IN ALCOHOL with more than 45% hydrogen cyanide
+MERCURY OXYCYANIDE pure
+METHYL NITRITE
+PERCHLORIC ACID with more than 72% acid, by mass
+SILVER PICRATE, dry or wetted with less than 30% water by mass
+ZINC AMMONIUM NITRITE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Applicable also to any substance indicated in this list in "Limited Quantities" unless specified otherwise.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dangerous cargo in REEFERS: 
+Permitted only for commercial/quality purpose.
+Class 2.1 is not accepted in Reefer containers, unless the reefers are with  “explosion-proof electrical fittings” as per IMDG Code 7.7.3.2.3 or 7.7.3.2.5,  and copy of the relevant certificate confirming that is provided.
+Sub-risk of 2.1 is also considered as Class 2.1 for this purpose. MSDS required. 
+Class 3 is not accepted unless the Control/Set Temperature is at least 10°C below the flash point, i.e. the lowest Flash Point accepted in regular reefers is -13°C. Substances with Flash Point below -13°C may be accepted only in Reefers with  “explosion-proof electrical fittings” as per IMDG Code 7.7.3.2.3 or 7.7.3.2.5 5, and copy of the relevant certificate confirming that is provided.
+Sub-risk of 3 is also considered as Class 3 for this purpose. MSDS required. 
+In case of failure of the refrigerating system causing the temp of the cargo to increase to the  Flash Point Temp, the reefer shall be disconnected from the power supply.
+ZIM accept other classes of DG in Reefer provided they are with no subsidiary explosive risk. 
+Dangerous cargo is not permitted in Non Operation Reefer  = N.O.R</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Solid dry Bulk Dangerous Goods in dry Bulk container:
+Accepted only in Certified Closed Bulk Containers (BK2), and provided the commodity is permitted by IMDG Code to be shipped in this package.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Generic and "Not Otherwise Specified" (N.O.S) Proper Shipping Names that are assigned to special provision 274 or 318 in column 6 of the Dangerous Goods List, shall be supplemented with the technical or chemical group names See also paragraph 3.1.2.8.1 of the IMDG Code.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>If a partner requires additional forms/certificates/surveys/LOI, etc, or has any restriction or additional requirement, for any partner's cargo on his vessel: Same to be also required and restricted, for this Partner, when he requests to ship his cargo on Zim's operated vessels.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vanning Survey
+To be done by marine surveyor in order to certify the followings:
+1. The container is clean, dry and apparently fit to receive the goods.
+2. No incompatible goods have been packed into the container.
+3. All packages have been externally inspected for damage, and only sound packages have been packed.
+4. The container and packages therein were properly marked, labeled and placard.
+5. All packages are intact and have been properly packed, securely blocked and braced to prevent the    
+    Packages from changing position, falling on the floor, or sliding.
+6. Survey report should be available for presentation.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Any Charcoal or coal/Carbon shipment: either DG or not DG, shell be declared as such during booking (same as done for DG) and require ZIM prior approval. MSDS, Self-Heating-Test Certificate/report, photos of the package and of the commodity &amp; Packaging details to be provided.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP386:
+For all "stabilized" DG Substances with SAPT (Self-Accelerating Polymerization Temperature ) of 45C or below, in Isotanks (or 50C for regular DV unit), there is a need to use a Temperature-Controlled-Isotank (or a Reefer), with a set temp of at least 10°C below the SAP (which need to be above +60°C).
+The following UNNO's are indicated as "stabilized" by the IMDG code:1010, 1060, 1081, 1082, 1085, 1086, 1087, 1092, 1093, 1143, 1167, 1185, 1218, 1246, 1247, 1251, 1301, 1302, 1303, 1304, 1545, 1589, 1614, 1724, 1829, 1860, 1917, 1919, 1921, 1991, 2055, 2200, 2218, 2227, 2251, 2277, 2283, 2348, 2352, 2383, 2396, 2452, 2521, 2522,2527, 2531, 2607, 2618, 2838, 3022, 3073, 3079, 3302,2522, 3302,3531, 3532, 3533, 3534. 
+MSDS is required in order to verify the SAPT (Self-Accelerating Polymerization Temperature) of the cargo, and in order to ensure that when the substance is stabilized by Temperature Controlled, the Set-Temp of the temp-control-Isotank/Reefer is at least 10°C below the SAPT.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class 2 : For all class 2 in refrigerated state (RF or RF ISOTANK )" substance holding time " must be given by the Shipper ."Holding Time" must be valid till end of marine voyage + 30 days</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Required:
+a. A Vanning Survey report and Certificate are required prior loading. 
+b. For lighters makers outside of (other than) USA, Canada, Europe, Japan &amp; Australia: final approval is subject to packaging certificate and a Vanning Survey &amp; report by an independent surveyor including photos of container been loaded with cargo.
+c. For lighters or Lighters Refills to the US, also required a US DOT (Department Of Transport) permit that complies with 49 CFR 173.21(I) and approved by US DOT, with the Test Report ID Number. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class 3 in operational Reefer containers: 
+Accepted only subject to the above paragraph (b).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSDS required in order to verify the Flash point. If below 50C operational Reefer may be required, especially during the Northern hemisphere Summertime (May-Oct).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSDS required in order to verify the Flash point. If below 50C operational Reefer may be required, especially during the Northern hemisphere Summer time (May-Oct).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. MSDS indicating the SADT is required.
+2. Permitted only if SADT is more than 55ºC.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1. If declared as Non-DG, MSDS and Laboratory Certificate required, stating the cargo density as per SP299.
+2. Will be stowed on deck, 1st tier. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSDS to be provided, and also Laboratory Certificate stating the cargo moisture is required. Maximum humidity allowed 6%.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSDS to be provided. Laboratory Certificate stating the cargo moisture is required.
+Maximum humidity allowed 6%. Weight limitation per package: Maximum 100 kg.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSDS required in order to verify the exact nature of the substance, as well as moisture and fat content.
+Notwithstanding SP928, Fish meal is to be regarded as hazardous cargo at all times, no exemptions.
+To be stowed on deck only, preferably 1st (or otherwise 2nd) tier, and “Away from heat sources”.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSDS required.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>See also the SP 932 regarding the Weathering Certificate required from the Partner, stating that the shipment was stored under cover, but in the open air, in the size in which it was packaged, for not less than 3 days prior to shipment.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>As per SP 932 Requires a certificate from the maker or shipper, stating that the shipment was stored under cover, but in the open air, in the size in which it was packaged, for not less than 3 days prior to shipment.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>acceptable provided shipper to supply at least 2 fire extinguishers (minimum 12kg each) of dry lithium chloride powder, dry sodium chloride or graphite powder.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">acceptable provided shipper to supply at least 2 fire extinguishers (minimum 12kg each) of dry lithium chloride powder, dry sodium chloride or graphite powder. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">MSDS is required in order to verify that it does not contains Calcium Hypochlorite which is not accepted, or any of the SP900 prohibited substances. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSDS required in order to determine that it is not a pure substance (which is prohibited as per IMDG SP900)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSDS required in order to determine that it is not a prohibited substance as per IMDG SP900.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Acceptable only in ISO TK’s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSDS required in order to verify the percentage of the Chloric  Acid (Max. 10%) as per IMDG code SP 900.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Risk of decomposition when exposed to continuous heat (exothermic decomposition &gt;= 60øC). Shipments preformed via the Red Sea or Arabian Sea during the summertime (June-Sept) will be limited to be stowed in RF containers only. 
+MSDS required in order to verify that it does not contains Calcium Hypochlorite which is not accepted &amp; in order to determine that it is not prohibited as per IMDG SP900 &amp; 349.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Risk of decomposition when exposed to continuous heat (exothermic decomposition &gt;= 60øC). Shipments preformed via the Red Sea, Arabian Sea &amp; Bengal sea, during the summertime (June-Sept) will be limited to be stowed in RF containers only. 
+MSDS required in order to verify the decomposition Temp (SADT = Self Accelerating Decomposition Temperature).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Risk of decomposition when exposed to continuous heat (exothermic decomposition &gt;= 60øC).
+limited to be stowed in operational Reefer containers only.   
+MSDS required to verify the exothermic decomposition temp.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">All Liquid Toxic substances of packing group I 
+Require MSDS in order to have it ready in case of leakage.  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>verify it is not a pure substance, which is prohibited as per IMDG SP 900.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>verify the percentage of the Hydrogen Cyanide (Max. 45%) as per IMDG code SP 900.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>verify the percentage of the Hydrogen Cyanide (Max. 20%) as per IMDG code SP 900.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSDS required. Prohibited if containing Calcium Hypochlorite.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>On Deck Only</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSDS &amp; Vanning Survey required
+Not acceptable in plastic Jericans.
+(This requirement is not applicable if in limited /excepted quantities). 
+If made in India: Prohibited (as packages quality cannot be verified)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSDS &amp; Vanning Survey required
+Not acceptable in plastic Jericans.
+(This requirement is not applicable if in limited /excepted quantities). 
+If made in India: Prohibited (as packages quality cannot be verified).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prohibited in all Japanese ports if substance is CYANAMIDE.
+For shipments to Japan MSDS is required in order to verify that substance is not CYANAMIDE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSDS required in order to verify the exact nature of the substance, as well as moisture and fat content.
+Notwithstanding SP928, Fish meal is to be regarded as hazardous cargo at all times, no exemptions.
+To be stowed on deck only, preferably 1st (or otherwise 2nd) tier, and “Away from heat sources</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>If loaded in DV container as per SP965 Section 2.1 and 2 Shipper to declare  the substance is packed in hermetically sealed packagings or IBCs, which conform to packing group II performance level for liquid dangerous goods according to the provisions of 6.1 or 6.5, respectively
+As per SP965 Section  4 : The Shipper to mark the container doors with a warning sticker "CAUTION - MAY CONTAIN FLAMMABLE VAPOUR" with lettering not less than 25 mm high.
+.On-Deck stowage only</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) Technical name to be checked in order to verify the exact substance and if it belongs also to another class or UN Number.
+2) Prohibited if Calcium Hypochlorite involved.
+3) In case of Paradichelorobenzene or 1, 4-Dichelorobenzene: accepted only in sealed drums.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) Technical name to be checked in order to verify the exact substance and if it belongs to another class or UN Number.
+flammable gases/fumes are not acceptable in reefers.
+3) Prohibited if Calcium Hypochlorite involved.
+4) Prohibited  In case of Divinylbenzene</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Notwithstanding SP188, Batteries are to be considered as IMO cargo. 
+Not permitted with other Dangerous cargo in the same CTU (except with another DG batteries)
+Used Batteries are prohibited 
+On-Deck stowage only. 
+Away from heat source,</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Not permitted with other Dangerous cargo in the same CTU (except with another DG batteries)
+Used Batteries are prohibited.
+On-Deck stowage only</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Not permitted with other Dangerous cargo in the same CTU (except with another DG batteries)
+Partner to guaranty batteries state of charge (SOC) up to 40%
+Used Batteries are prohibited 
+On-Deck stowage only. 
+Away from heat source</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>For any hybrid vehicle the following is required:
+Not permitted with other Dangerous cargo in the same CTU (except with another DG batteries)
+Partner to guaranty batteries state of charge (SOC) up to 40%
+Used Batteries are prohibited 
+On-Deck stowage only. 
+Away from heat source</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Not permitted with other Dangerous cargo in the same CTU (except with another DG batteries)
+Notwithstanding SP188, Batteries are to be considered as IMO cargo. 
+Used Batteries are prohibited 
+On-Deck stowage only. 
+Away from heat source,</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Notwithstanding SP188, Batteries are to be considered as IMO cargo.
+A certificate is required proving that the battery has successfully passed the test specified in section 38.3 of the “UN Manual of Tests and Criteria”.
+Away from heat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Partner to guaranty batteries state of charge (SOC) up to 40%
+Used Batteries are prohibited 
+On-Deck stowage only. 
+Away from heat source</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -19707,15 +20202,16 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:R106"/>
+  <dimension ref="A1:R110"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.75" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="67.625" style="1" customWidth="1"/>
-    <col min="6" max="7" width="106.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="175.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="106.25" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="72.375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="67.875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="71.875" style="1" customWidth="1"/>
@@ -19786,7 +20282,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="157.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="126" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1193</v>
       </c>
@@ -21133,7 +21629,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>1193</v>
       </c>
@@ -21147,7 +21643,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>1193</v>
       </c>
@@ -21158,7 +21654,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>1193</v>
       </c>
@@ -21169,7 +21665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>1193</v>
       </c>
@@ -21180,7 +21676,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>1193</v>
       </c>
@@ -21191,7 +21687,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>1193</v>
       </c>
@@ -21202,7 +21698,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>1193</v>
       </c>
@@ -21213,7 +21709,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>1193</v>
       </c>
@@ -21227,7 +21723,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>1193</v>
       </c>
@@ -21241,7 +21737,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>1193</v>
       </c>
@@ -21253,6 +21749,8815 @@
       </c>
       <c r="D106" s="1" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B107" s="1">
+        <v>9</v>
+      </c>
+      <c r="C107" s="1">
+        <v>3166</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B108" s="1">
+        <v>9</v>
+      </c>
+      <c r="C108" s="1">
+        <v>3171</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B109" s="1">
+        <v>9</v>
+      </c>
+      <c r="C109" s="1">
+        <v>3480</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F109" s="11" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B110" s="1">
+        <v>9</v>
+      </c>
+      <c r="C110" s="1">
+        <v>3536</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F110" s="11" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54206634-8959-41FD-878B-7ED3DB1E562B}">
+  <sheetPr>
+    <tabColor theme="3" tint="0.89999084444715716"/>
+  </sheetPr>
+  <dimension ref="A1:S290"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="91.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="95.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="54" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="38.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="70.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="55.875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="54" style="1" customWidth="1"/>
+    <col min="15" max="15" width="73.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="98.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="92" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="83.375" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="63" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>1220</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>1221</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B7" s="4">
+        <v>1.4</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B8" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B9" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1057</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1961</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1966</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1972</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B14" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2203</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2455</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B17" s="1">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B18" s="1">
+        <v>3</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1089</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B19" s="1">
+        <v>3</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1100</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B20" s="1">
+        <v>3</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1108</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B21" s="1">
+        <v>3</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1113</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B22" s="1">
+        <v>3</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1131</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B23" s="1">
+        <v>3</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1144</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B24" s="1">
+        <v>3</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1155</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B25" s="1">
+        <v>3</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1159</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B26" s="1">
+        <v>3</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1167</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B27" s="1">
+        <v>3</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1194</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B28" s="1">
+        <v>3</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1203</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B29" s="1">
+        <v>3</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1204</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B30" s="1">
+        <v>3</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1208</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B31" s="1">
+        <v>3</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1218</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B32" s="1">
+        <v>3</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1221</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B33" s="1">
+        <v>3</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1243</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B34" s="1">
+        <v>3</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1280</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B35" s="1">
+        <v>3</v>
+      </c>
+      <c r="C35" s="1">
+        <v>1302</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B36" s="1">
+        <v>3</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1303</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B37" s="1">
+        <v>3</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1991</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B38" s="1">
+        <v>3</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1999</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B39" s="1">
+        <v>3</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2059</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B40" s="1">
+        <v>3</v>
+      </c>
+      <c r="C40" s="1">
+        <v>2186</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B41" s="1">
+        <v>3</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2356</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B42" s="1">
+        <v>3</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2363</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B43" s="1">
+        <v>3</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2371</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B44" s="1">
+        <v>3</v>
+      </c>
+      <c r="C44" s="1">
+        <v>2389</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B45" s="1">
+        <v>3</v>
+      </c>
+      <c r="C45" s="1">
+        <v>2456</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B46" s="1">
+        <v>3</v>
+      </c>
+      <c r="C46" s="1">
+        <v>2459</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B47" s="1">
+        <v>3</v>
+      </c>
+      <c r="C47" s="1">
+        <v>2460</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B48" s="1">
+        <v>3</v>
+      </c>
+      <c r="C48" s="1">
+        <v>2461</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B49" s="1">
+        <v>3</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2561</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B50" s="1">
+        <v>3</v>
+      </c>
+      <c r="C50" s="1">
+        <v>2749</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B51" s="1">
+        <v>3</v>
+      </c>
+      <c r="C51" s="1">
+        <v>2983</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B52" s="1">
+        <v>3</v>
+      </c>
+      <c r="C52" s="1">
+        <v>3064</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B53" s="1">
+        <v>3</v>
+      </c>
+      <c r="C53" s="1">
+        <v>3065</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B54" s="1">
+        <v>3</v>
+      </c>
+      <c r="C54" s="1">
+        <v>3343</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B55" s="1">
+        <v>3</v>
+      </c>
+      <c r="C55" s="1">
+        <v>3357</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B56" s="1">
+        <v>3</v>
+      </c>
+      <c r="C56" s="1">
+        <v>3379</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B57" s="1">
+        <v>3</v>
+      </c>
+      <c r="C57" s="1">
+        <v>3475</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B58" s="1">
+        <v>3</v>
+      </c>
+      <c r="C58" s="1">
+        <v>3555</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B59" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C59" s="1">
+        <v>1310</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B60" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C60" s="1">
+        <v>1320</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B61" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C61" s="1">
+        <v>1321</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B62" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1322</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B63" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C63" s="1">
+        <v>1324</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B64" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C64" s="1">
+        <v>1336</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B65" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C65" s="1">
+        <v>1337</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B66" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C66" s="1">
+        <v>1338</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B67" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C67" s="1">
+        <v>1339</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B68" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C68" s="1">
+        <v>1344</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B69" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C69" s="1">
+        <v>1347</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B70" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C70" s="1">
+        <v>1349</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B71" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C71" s="1">
+        <v>1350</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B72" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C72" s="1">
+        <v>1353</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B73" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C73" s="1">
+        <v>1354</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B74" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C74" s="1">
+        <v>1356</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B75" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C75" s="1">
+        <v>1571</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B76" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C76" s="1">
+        <v>2000</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B77" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C77" s="1">
+        <v>2304</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B78" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C78" s="1">
+        <v>2555</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B79" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C79" s="1">
+        <v>2556</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B80" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C80" s="1">
+        <v>2557</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B81" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C81" s="1">
+        <v>2852</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B82" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C82" s="1">
+        <v>2956</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B83" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C83" s="1">
+        <v>3097</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B84" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C84" s="1">
+        <v>3221</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B85" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C85" s="1">
+        <v>3222</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B86" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C86" s="1">
+        <v>3223</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B87" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C87" s="1">
+        <v>3224</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B88" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C88" s="1">
+        <v>3225</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B89" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C89" s="1">
+        <v>3226</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B90" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C90" s="1">
+        <v>3227</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B91" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C91" s="1">
+        <v>3228</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B92" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C92" s="1">
+        <v>3229</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B93" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C93" s="1">
+        <v>3230</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B94" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C94" s="1">
+        <v>3231</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B95" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C95" s="1">
+        <v>3232</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B96" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C96" s="1">
+        <v>3233</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B97" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C97" s="1">
+        <v>3234</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B98" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C98" s="1">
+        <v>3235</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B99" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C99" s="1">
+        <v>3236</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B100" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C100" s="1">
+        <v>3237</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B101" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C101" s="1">
+        <v>3238</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B102" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C102" s="1">
+        <v>3239</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B103" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C103" s="1">
+        <v>3240</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B104" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C104" s="1">
+        <v>3241</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B105" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C105" s="1">
+        <v>3241</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B106" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C106" s="1">
+        <v>3317</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B107" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C107" s="1">
+        <v>3319</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B108" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C108" s="1">
+        <v>3344</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B109" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C109" s="1">
+        <v>3380</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B110" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C110" s="1">
+        <v>1361</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B111" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C111" s="1">
+        <v>1362</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B112" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C112" s="1">
+        <v>1363</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B113" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C113" s="1">
+        <v>1364</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B114" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C114" s="1">
+        <v>1374</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B115" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C115" s="1">
+        <v>1380</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B116" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C116" s="1">
+        <v>1381</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B117" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C117" s="1">
+        <v>1383</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B118" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C118" s="1">
+        <v>1384</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B119" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C119" s="1">
+        <v>1387</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B120" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C120" s="1">
+        <v>1857</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B121" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C121" s="1">
+        <v>2002</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B122" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C122" s="1">
+        <v>2006</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B123" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C123" s="1">
+        <v>2447</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B124" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C124" s="1">
+        <v>2845</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B125" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C125" s="1">
+        <v>2846</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B126" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C126" s="1">
+        <v>2870</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B127" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C127" s="1">
+        <v>2881</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B128" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C128" s="1">
+        <v>3088</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B129" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C129" s="1">
+        <v>3126</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B130" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C130" s="1">
+        <v>3127</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B131" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C131" s="1">
+        <v>3128</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B132" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C132" s="1">
+        <v>3194</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B133" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C133" s="1">
+        <v>3200</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B134" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C134" s="1">
+        <v>3255</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B135" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C135" s="1">
+        <v>3341</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B136" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C136" s="1">
+        <v>3342</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B137" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C137" s="1">
+        <v>3391</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B138" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C138" s="1">
+        <v>3392</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B139" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C139" s="1">
+        <v>3393</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B140" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C140" s="1">
+        <v>3394</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B141" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C141" s="1">
+        <v>1402</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B142" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C142" s="1">
+        <v>1408</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B143" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C143" s="1">
+        <v>1415</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B144" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C144" s="1">
+        <v>1418</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B145" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C145" s="1">
+        <v>1928</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B146" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C146" s="1">
+        <v>3129</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B147" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C147" s="1">
+        <v>3130</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B148" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C148" s="1">
+        <v>3131</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B149" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C149" s="1">
+        <v>3132</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B150" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C150" s="1">
+        <v>3133</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B151" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C151" s="1">
+        <v>3135</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B152" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C152" s="1">
+        <v>3292</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B153" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B154" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C154" s="1">
+        <v>1438</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B155" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C155" s="1">
+        <v>1442</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B156" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C156" s="1">
+        <v>1445</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B157" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C157" s="1">
+        <v>1446</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B158" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C158" s="1">
+        <v>1447</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B159" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C159" s="1">
+        <v>1450</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B160" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C160" s="1">
+        <v>1451</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B161" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C161" s="1">
+        <v>1452</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B162" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C162" s="1">
+        <v>1454</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B163" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C163" s="1">
+        <v>1455</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B164" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C164" s="1">
+        <v>1457</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B165" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C165" s="1">
+        <v>1458</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B166" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C166" s="1">
+        <v>1459</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B167" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C167" s="1">
+        <v>1461</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B168" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C168" s="1">
+        <v>1462</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B169" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C169" s="1">
+        <v>1467</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B170" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C170" s="1">
+        <v>1469</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B171" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C171" s="1">
+        <v>3375</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B172" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C172" s="1">
+        <v>3485</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B173" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C173" s="1">
+        <v>1470</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B174" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C174" s="1">
+        <v>1474</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B175" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C175" s="1">
+        <v>1475</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B176" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C176" s="1">
+        <v>1477</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B177" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C177" s="1">
+        <v>1479</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B178" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C178" s="1">
+        <v>1481</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B179" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C179" s="1">
+        <v>1482</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B180" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C180" s="1">
+        <v>1485</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B181" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C181" s="1">
+        <v>1486</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B182" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C182" s="1">
+        <v>1487</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B183" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C183" s="1">
+        <v>1489</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B184" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C184" s="1">
+        <v>1493</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B185" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C185" s="1">
+        <v>1495</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B186" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C186" s="1">
+        <v>1496</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B187" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C187" s="1">
+        <v>1498</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B188" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C188" s="1">
+        <v>1499</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B189" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C189" s="1">
+        <v>1502</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B190" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C190" s="1">
+        <v>3378</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B191" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C191" s="1">
+        <v>3218</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B192" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C192" s="1">
+        <v>1508</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B193" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C193" s="1">
+        <v>1510</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B194" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C194" s="1">
+        <v>1512</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B195" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C195" s="1">
+        <v>1513</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B196" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C196" s="1">
+        <v>1514</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B197" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C197" s="1">
+        <v>1746</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B198" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C198" s="1">
+        <v>1748</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B199" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C199" s="1">
+        <v>1873</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B200" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C200" s="1">
+        <v>1942</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B201" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C201" s="1">
+        <v>2067</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B202" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C202" s="1">
+        <v>2072</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B203" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C203" s="1">
+        <v>2208</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B204" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C204" s="1">
+        <v>2426</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B205" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C205" s="1">
+        <v>2427</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B206" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C206" s="1">
+        <v>2428</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B207" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C207" s="1">
+        <v>2429</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B208" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C208" s="1">
+        <v>2573</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B209" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C209" s="1">
+        <v>3486</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B210" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C210" s="1">
+        <v>3487</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B211" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C211" s="1">
+        <v>2626</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B212" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C212" s="1">
+        <v>2627</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B213" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C213" s="1">
+        <v>2720</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B214" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C214" s="1">
+        <v>2721</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B215" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C215" s="1">
+        <v>2723</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B216" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C216" s="1">
+        <v>2724</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B217" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C217" s="1">
+        <v>2725</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B218" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C218" s="1">
+        <v>2880</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B219" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C219" s="1">
+        <v>3100</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B220" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C220" s="1">
+        <v>3121</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B221" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C221" s="1">
+        <v>3137</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B222" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C222" s="1">
+        <v>3210</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B223" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C223" s="1">
+        <v>3211</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B224" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C224" s="1">
+        <v>3212</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B225" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C225" s="1">
+        <v>3213</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B226" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C226" s="1">
+        <v>3214</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B227" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C227" s="1">
+        <v>3219</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B228" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B229" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C229" s="1">
+        <v>1259</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B230" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C230" s="1">
+        <v>1506</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B231" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C231" s="1">
+        <v>1599</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B232" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C232" s="1">
+        <v>1613</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B233" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C233" s="1">
+        <v>1625</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B234" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C234" s="1">
+        <v>1627</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B235" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C235" s="1">
+        <v>1642</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B236" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C236" s="1">
+        <v>1649</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B237" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C237" s="1">
+        <v>1687</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B238" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C238" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B239" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C239" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B240" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C240" s="1">
+        <v>2249</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B241" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C241" s="1">
+        <v>2312</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B242" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C242" s="1">
+        <v>2480</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B243" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C243" s="1">
+        <v>2481</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B244" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C244" s="1">
+        <v>3123</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B245" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C245" s="1">
+        <v>3125</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B246" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C246" s="1">
+        <v>3250</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B247" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C247" s="1">
+        <v>3283</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B248" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C248" s="1">
+        <v>3294</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B249" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C249" s="1">
+        <v>3383</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B250" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C250" s="1">
+        <v>3483</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A251" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B251" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C251" s="1">
+        <v>3489</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B252" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C252" s="1">
+        <v>3490</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A253" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B253" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C253" s="1">
+        <v>3491</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B254" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C254" s="1">
+        <v>3507</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A255" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B255" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A256" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B256" s="1">
+        <v>7</v>
+      </c>
+      <c r="D256" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A257" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B257" s="1">
+        <v>8</v>
+      </c>
+      <c r="C257" s="1">
+        <v>1791</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B258" s="1">
+        <v>8</v>
+      </c>
+      <c r="C258" s="1">
+        <v>1908</v>
+      </c>
+      <c r="D258" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B259" s="1">
+        <v>8</v>
+      </c>
+      <c r="C259" s="1">
+        <v>2028</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B260" s="1">
+        <v>8</v>
+      </c>
+      <c r="C260" s="1">
+        <v>2031</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B261" s="1">
+        <v>8</v>
+      </c>
+      <c r="C261" s="1">
+        <v>2032</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A262" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B262" s="1">
+        <v>8</v>
+      </c>
+      <c r="C262" s="1">
+        <v>2794</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F262" s="1" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B263" s="1">
+        <v>8</v>
+      </c>
+      <c r="C263" s="1">
+        <v>2795</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F263" s="1" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A264" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B264" s="1">
+        <v>8</v>
+      </c>
+      <c r="C264" s="1">
+        <v>2800</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F264" s="1" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A265" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B265" s="1">
+        <v>8</v>
+      </c>
+      <c r="C265" s="1">
+        <v>3028</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F265" s="1" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B266" s="1">
+        <v>9</v>
+      </c>
+      <c r="C266" s="1">
+        <v>2071</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A267" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B267" s="1">
+        <v>9</v>
+      </c>
+      <c r="C267" s="1">
+        <v>2211</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A268" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B268" s="1">
+        <v>9</v>
+      </c>
+      <c r="C268" s="1">
+        <v>2212</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A269" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B269" s="1">
+        <v>9</v>
+      </c>
+      <c r="C269" s="1">
+        <v>2315</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A270" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B270" s="1">
+        <v>9</v>
+      </c>
+      <c r="C270" s="1">
+        <v>2590</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A271" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B271" s="1">
+        <v>9</v>
+      </c>
+      <c r="C271" s="1">
+        <v>3077</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A272" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B272" s="1">
+        <v>9</v>
+      </c>
+      <c r="C272" s="1">
+        <v>3090</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F272" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G272" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="H272" s="1" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A273" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B273" s="1">
+        <v>9</v>
+      </c>
+      <c r="C273" s="1">
+        <v>3091</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F273" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G273" s="1" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A274" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B274" s="1">
+        <v>9</v>
+      </c>
+      <c r="C274" s="1">
+        <v>3151</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A275" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B275" s="1">
+        <v>9</v>
+      </c>
+      <c r="C275" s="1">
+        <v>3152</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A276" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B276" s="1">
+        <v>9</v>
+      </c>
+      <c r="C276" s="1">
+        <v>3166</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F276" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G276" s="1" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A277" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B277" s="1">
+        <v>9</v>
+      </c>
+      <c r="C277" s="1">
+        <v>3171</v>
+      </c>
+      <c r="E277" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F277" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G277" s="11" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A278" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B278" s="1">
+        <v>9</v>
+      </c>
+      <c r="C278" s="1">
+        <v>3245</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A279" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B279" s="1">
+        <v>9</v>
+      </c>
+      <c r="C279" s="1">
+        <v>3257</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A280" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B280" s="1">
+        <v>9</v>
+      </c>
+      <c r="C280" s="1">
+        <v>3314</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A281" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B281" s="1">
+        <v>9</v>
+      </c>
+      <c r="C281" s="1">
+        <v>3432</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A282" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B282" s="1">
+        <v>9</v>
+      </c>
+      <c r="C282" s="1">
+        <v>3480</v>
+      </c>
+      <c r="E282" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F282" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G282" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="H282" s="1" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A283" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B283" s="1">
+        <v>9</v>
+      </c>
+      <c r="C283" s="1">
+        <v>3481</v>
+      </c>
+      <c r="E283" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F283" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G283" s="1" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A284" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B284" s="1">
+        <v>9</v>
+      </c>
+      <c r="C284" s="1">
+        <v>3496</v>
+      </c>
+      <c r="E284" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F284" s="1" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A285" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B285" s="1">
+        <v>9</v>
+      </c>
+      <c r="C285" s="1">
+        <v>3536</v>
+      </c>
+      <c r="E285" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F285" s="1" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A286" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B286" s="1">
+        <v>9</v>
+      </c>
+      <c r="C286" s="1">
+        <v>3551</v>
+      </c>
+      <c r="E286" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F286" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G286" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="H286" s="1" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A287" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B287" s="1">
+        <v>9</v>
+      </c>
+      <c r="C287" s="1">
+        <v>3552</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F287" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G287" s="1" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A288" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B288" s="1">
+        <v>9</v>
+      </c>
+      <c r="C288" s="1">
+        <v>3556</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F288" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G288" s="11" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A289" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B289" s="1">
+        <v>9</v>
+      </c>
+      <c r="C289" s="1">
+        <v>3557</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F289" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G289" s="11" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A290" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B290" s="1">
+        <v>9</v>
+      </c>
+      <c r="C290" s="1">
+        <v>3558</v>
+      </c>
+      <c r="E290" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F290" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G290" s="1" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE9CC31-97C1-4EEE-8C72-712B4DCC06AB}">
+  <dimension ref="A1:S472"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="193.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="158.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="77.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="155.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="53.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="111.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="85.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="88.75" style="1" customWidth="1"/>
+    <col min="14" max="14" width="55.5" style="1" customWidth="1"/>
+    <col min="15" max="15" width="235.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="225.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="240.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="40" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>1254</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>1256</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>1257</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>1260</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B7" s="4">
+        <v>1.4</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B8" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B9" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="63" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1057</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2455</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B14" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1017</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2186</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B17" s="1">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>1242</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B18" s="1">
+        <v>3</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1194</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B19" s="1">
+        <v>3</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1204</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B20" s="1">
+        <v>3</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1222</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B21" s="1">
+        <v>3</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2029</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B22" s="1">
+        <v>3</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2059</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B23" s="1">
+        <v>3</v>
+      </c>
+      <c r="C23" s="1">
+        <v>3064</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B24" s="1">
+        <v>3</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3343</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B25" s="1">
+        <v>3</v>
+      </c>
+      <c r="C25" s="1">
+        <v>3357</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B26" s="1">
+        <v>3</v>
+      </c>
+      <c r="C26" s="1">
+        <v>3379</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B27" s="1">
+        <v>3</v>
+      </c>
+      <c r="C27" s="1">
+        <v>3484</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B28" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C28" s="1">
+        <v>3221</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B29" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C29" s="1">
+        <v>3222</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B30" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C30" s="1">
+        <v>3223</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B31" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C31" s="1">
+        <v>3224</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B32" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C32" s="1">
+        <v>3225</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B33" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C33" s="1">
+        <v>3226</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B34" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C34" s="1">
+        <v>3227</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B35" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C35" s="1">
+        <v>3228</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B36" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C36" s="1">
+        <v>3229</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B37" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C37" s="1">
+        <v>3230</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B38" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C38" s="1">
+        <v>3231</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B39" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C39" s="1">
+        <v>3232</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B40" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C40" s="1">
+        <v>3233</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B41" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C41" s="1">
+        <v>3234</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B42" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C42" s="1">
+        <v>3235</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B43" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C43" s="1">
+        <v>3236</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B44" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C44" s="1">
+        <v>3237</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B45" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C45" s="1">
+        <v>3238</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B46" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C46" s="1">
+        <v>3239</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B47" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C47" s="1">
+        <v>3240</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B48" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C48" s="1">
+        <v>3360</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B49" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C49" s="1">
+        <v>3532</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B50" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C50" s="1">
+        <v>3533</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B51" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C51" s="1">
+        <v>3534</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B52" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C52" s="1">
+        <v>1320</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B53" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C53" s="1">
+        <v>1322</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B54" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C54" s="1">
+        <v>1336</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B55" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C55" s="1">
+        <v>1337</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B56" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C56" s="1">
+        <v>1344</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B57" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C57" s="1">
+        <v>1347</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B58" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C58" s="1">
+        <v>1348</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B59" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C59" s="1">
+        <v>1349</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B60" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C60" s="1">
+        <v>1354</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B61" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C61" s="1">
+        <v>1355</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B62" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1356</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B63" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C63" s="1">
+        <v>1357</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B64" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C64" s="1">
+        <v>1517</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B65" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C65" s="1">
+        <v>1571</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B66" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C66" s="1">
+        <v>2555</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B67" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C67" s="1">
+        <v>2556</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B68" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C68" s="1">
+        <v>2557</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B69" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C69" s="1">
+        <v>2852</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B70" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C70" s="1">
+        <v>3317</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B71" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C71" s="1">
+        <v>3319</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B72" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C72" s="1">
+        <v>3344</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B73" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C73" s="1">
+        <v>3364</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B74" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C74" s="1">
+        <v>3365</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B75" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C75" s="1">
+        <v>3366</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B76" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C76" s="1">
+        <v>3367</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B77" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C77" s="1">
+        <v>3368</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B78" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C78" s="1">
+        <v>3369</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B79" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C79" s="1">
+        <v>3370</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B80" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C80" s="1">
+        <v>3376</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B81" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C81" s="1">
+        <v>3380</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B82" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C82" s="1">
+        <v>3474</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B83" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C83" s="1">
+        <v>1361</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B84" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C84" s="1">
+        <v>1362</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B85" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C85" s="1">
+        <v>1365</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B86" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C86" s="1">
+        <v>1372</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B87" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C87" s="1">
+        <v>1374</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B88" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C88" s="1">
+        <v>1380</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B89" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C89" s="1">
+        <v>1381</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B90" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C90" s="1">
+        <v>1383</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B91" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C91" s="1">
+        <v>2845</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B92" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C92" s="1">
+        <v>2846</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B93" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C93" s="1">
+        <v>2870</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B94" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C94" s="1">
+        <v>3088</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B95" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C95" s="1">
+        <v>3126</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B96" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C96" s="1">
+        <v>3127</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B97" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C97" s="1">
+        <v>3128</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B98" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C98" s="1">
+        <v>3194</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B99" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C99" s="1">
+        <v>3200</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B100" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C100" s="1">
+        <v>3341</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B101" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C101" s="1">
+        <v>3342</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B102" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C102" s="1">
+        <v>3391</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B103" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C103" s="1">
+        <v>3392</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B104" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C104" s="1">
+        <v>3393</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B105" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C105" s="1">
+        <v>3394</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B106" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="C106" s="1">
+        <v>3400</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B107" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C107" s="1">
+        <v>1183</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B108" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C108" s="1">
+        <v>1242</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B109" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C109" s="1">
+        <v>1295</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B110" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C110" s="1">
+        <v>1395</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B111" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C111" s="1">
+        <v>1398</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B112" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C112" s="1">
+        <v>1405</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B113" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C113" s="1">
+        <v>1408</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B114" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C114" s="1">
+        <v>1415</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B115" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C115" s="1">
+        <v>1418</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B116" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C116" s="1">
+        <v>1423</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B117" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C117" s="1">
+        <v>2988</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B118" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C118" s="1">
+        <v>2813</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B119" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C119" s="1">
+        <v>3129</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B120" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C120" s="1">
+        <v>3130</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B121" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C121" s="1">
+        <v>3131</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B122" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C122" s="1">
+        <v>3132</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B123" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C123" s="1">
+        <v>3133</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B124" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C124" s="1">
+        <v>3134</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B125" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C125" s="1">
+        <v>3135</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B126" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C126" s="1">
+        <v>3148</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B127" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C127" s="1">
+        <v>3209</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B128" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C128" s="1">
+        <v>3395</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B129" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C129" s="1">
+        <v>3396</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B130" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C130" s="1">
+        <v>3397</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B131" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C131" s="1">
+        <v>3398</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B132" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="C132" s="1">
+        <v>3399</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B133" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C133" s="1">
+        <v>1479</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B134" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C134" s="1">
+        <v>1873</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B135" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C135" s="1">
+        <v>1512</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B136" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C136" s="1">
+        <v>1748</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B137" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C137" s="1">
+        <v>1942</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B138" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C138" s="1">
+        <v>2014</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B139" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C139" s="1">
+        <v>2015</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B140" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C140" s="1">
+        <v>2067</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B141" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C141" s="1">
+        <v>2626</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B142" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C142" s="1">
+        <v>2208</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B143" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C143" s="1">
+        <v>2880</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B144" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C144" s="1">
+        <v>3100</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B145" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C145" s="1">
+        <v>3121</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B146" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C146" s="1">
+        <v>3212</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B147" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C147" s="1">
+        <v>3375</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B148" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C148" s="1">
+        <v>3378</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B149" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C149" s="1">
+        <v>3377</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B150" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C150" s="1">
+        <v>3485</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B151" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C151" s="1">
+        <v>3486</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B152" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C152" s="1">
+        <v>3487</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B153" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B154" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B155" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C155" s="1">
+        <v>1642</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B156" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C156" s="1">
+        <v>3294</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B157" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C157" s="1">
+        <v>1613</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B158" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C158" s="1">
+        <v>1051</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B159" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C159" s="1">
+        <v>2249</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F159" s="11" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B160" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C160" s="1">
+        <v>3488</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B161" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C161" s="1">
+        <v>3489</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B162" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C162" s="1">
+        <v>3490</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B163" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C163" s="1">
+        <v>3491</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B164" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B165" s="1">
+        <v>7</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B166" s="1">
+        <v>8</v>
+      </c>
+      <c r="C166" s="1">
+        <v>1791</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B167" s="1">
+        <v>8</v>
+      </c>
+      <c r="C167" s="1">
+        <v>1830</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B168" s="1">
+        <v>8</v>
+      </c>
+      <c r="C168" s="1">
+        <v>2031</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B169" s="1">
+        <v>8</v>
+      </c>
+      <c r="C169" s="1">
+        <v>2032</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B170" s="1">
+        <v>8</v>
+      </c>
+      <c r="C170" s="1">
+        <v>2922</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B171" s="1">
+        <v>8</v>
+      </c>
+      <c r="C171" s="1">
+        <v>1744</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B172" s="1">
+        <v>8</v>
+      </c>
+      <c r="C172" s="1">
+        <v>2794</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B173" s="1">
+        <v>8</v>
+      </c>
+      <c r="C173" s="1">
+        <v>2795</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B174" s="1">
+        <v>8</v>
+      </c>
+      <c r="C174" s="1">
+        <v>2796</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B175" s="1">
+        <v>8</v>
+      </c>
+      <c r="C175" s="1">
+        <v>3028</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B176" s="1">
+        <v>9</v>
+      </c>
+      <c r="C176" s="1">
+        <v>2216</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B177" s="1">
+        <v>9</v>
+      </c>
+      <c r="C177" s="1">
+        <v>2211</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B178" s="1">
+        <v>9</v>
+      </c>
+      <c r="C178" s="1">
+        <v>3077</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F178" s="11" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B179" s="1">
+        <v>9</v>
+      </c>
+      <c r="C179" s="1">
+        <v>3082</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F179" s="11" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B180" s="1">
+        <v>9</v>
+      </c>
+      <c r="C180" s="1">
+        <v>3090</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F180" s="8" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B181" s="1">
+        <v>9</v>
+      </c>
+      <c r="C181" s="1">
+        <v>3091</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F181" s="8" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B182" s="1">
+        <v>9</v>
+      </c>
+      <c r="C182" s="1">
+        <v>3166</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F182" s="8" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B183" s="1">
+        <v>9</v>
+      </c>
+      <c r="C183" s="1">
+        <v>3171</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F183" s="8" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B184" s="1">
+        <v>9</v>
+      </c>
+      <c r="C184" s="1">
+        <v>3480</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F184" s="8" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B185" s="1">
+        <v>9</v>
+      </c>
+      <c r="C185" s="1">
+        <v>3481</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B186" s="1">
+        <v>9</v>
+      </c>
+      <c r="C186" s="1">
+        <v>3551</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F186" s="8" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B187" s="1">
+        <v>9</v>
+      </c>
+      <c r="C187" s="1">
+        <v>3552</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F187" s="8" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B188" s="1">
+        <v>9</v>
+      </c>
+      <c r="C188" s="1">
+        <v>3556</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F188" s="8" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B189" s="1">
+        <v>9</v>
+      </c>
+      <c r="C189" s="1">
+        <v>3557</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F189" s="8" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B190" s="1">
+        <v>9</v>
+      </c>
+      <c r="C190" s="1">
+        <v>3558</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F190" s="8" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B191" s="1">
+        <v>9</v>
+      </c>
+      <c r="C191" s="1">
+        <v>3496</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B192" s="1">
+        <v>9</v>
+      </c>
+      <c r="C192" s="1">
+        <v>2315</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B193" s="1">
+        <v>9</v>
+      </c>
+      <c r="C193" s="1">
+        <v>3151</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B194" s="1">
+        <v>9</v>
+      </c>
+      <c r="C194" s="1">
+        <v>3152</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B195" s="1">
+        <v>9</v>
+      </c>
+      <c r="C195" s="1">
+        <v>3432</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B196" s="1">
+        <v>9</v>
+      </c>
+      <c r="C196" s="1">
+        <v>3536</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A251" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A253" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A256" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A257" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A262" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A264" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A265" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A267" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A268" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A269" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A270" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A271" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A272" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A273" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A274" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A275" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A276" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A277" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A278" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A279" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A280" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A281" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A282" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A283" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A284" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A285" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A286" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A287" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A288" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A289" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A290" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A291" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A292" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A293" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A294" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A295" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A296" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A297" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A298" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A299" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A300" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A302" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A303" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A304" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A305" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A306" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A307" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A308" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A309" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A310" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A311" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A312" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A313" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A314" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A315" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A316" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A317" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A318" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A319" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A320" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A321" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A322" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A323" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A324" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A325" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A326" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A327" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A328" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A329" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A330" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A331" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A332" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A333" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A334" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A335" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A336" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A337" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A338" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A339" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A340" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A341" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A342" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A343" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A344" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A345" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A346" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A347" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A348" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A349" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A350" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A351" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A352" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A353" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A354" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A355" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A356" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A357" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A358" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A359" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A360" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A361" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A362" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A363" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A364" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A365" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A366" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A367" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A368" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A369" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A370" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A371" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A372" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A373" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A374" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A375" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A376" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A377" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A378" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A379" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A380" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A381" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A382" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A383" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A384" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A385" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A386" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A387" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A388" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A389" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A390" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A391" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A392" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A393" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A394" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A395" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A396" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A397" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A398" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A399" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A400" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A401" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A402" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A403" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A404" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A405" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A406" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A407" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A408" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A409" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A410" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A411" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A412" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A413" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A414" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A415" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A416" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A417" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A418" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A419" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A420" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A421" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A422" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A423" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A424" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A425" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A426" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A427" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A428" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A429" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A430" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A431" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A432" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A433" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A434" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A435" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A436" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A437" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A438" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A439" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A440" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A441" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A442" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A443" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A444" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A445" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A446" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A447" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A448" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A449" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A450" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A451" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A452" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A453" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A454" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A455" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A456" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A457" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A458" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A459" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A460" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A461" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A462" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A463" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A464" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A465" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A466" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A467" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A468" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A469" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A470" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A471" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A472" s="1" t="s">
+        <v>1238</v>
       </c>
     </row>
   </sheetData>
@@ -53544,5 +62849,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1DF4873-5537-4746-AC77-18F538814C44}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CBECBE0-9C0E-450A-976E-864B941119E7}"/>
 </file>